--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED3B1FDE-650E-4B0F-B89D-B3529559ABC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6828894-98C7-4054-BC07-24E1F5E42488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4680" windowWidth="61350" windowHeight="27570" xr2:uid="{D7C1C753-0486-404B-8498-9D23BF02A5A7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" xr2:uid="{D7C1C753-0486-404B-8498-9D23BF02A5A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -207,9 +207,6 @@
   </si>
   <si>
     <t>Two 1-Year</t>
-  </si>
-  <si>
-    <t>Skin Savvy</t>
   </si>
   <si>
     <t>Jenny Madden_A</t>
@@ -455,9 +452,6 @@
     <t>114 Central_203_Rentokil</t>
   </si>
   <si>
-    <t>114 Central_204_Skin Savvy</t>
-  </si>
-  <si>
     <t>114 Central_205_Jenny Madden_A</t>
   </si>
   <si>
@@ -471,6 +465,12 @@
   </si>
   <si>
     <t>114 Central_208_SRD Captial</t>
+  </si>
+  <si>
+    <t>VACANT_204</t>
+  </si>
+  <si>
+    <t>114 Central_204_VACANT_204</t>
   </si>
 </sst>
 </file>
@@ -1839,7 +1839,7 @@
         <v>204</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>49</v>
@@ -1872,10 +1872,10 @@
         <v>5.0498068713153078E-2</v>
       </c>
       <c r="N18" s="14">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="O18" s="14">
-        <v>12180</v>
+        <v>0</v>
       </c>
       <c r="P18" s="14">
         <v>130000</v>
@@ -1887,36 +1887,30 @@
         <v>0</v>
       </c>
       <c r="S18" s="15">
-        <v>12180</v>
+        <v>0</v>
       </c>
       <c r="T18" s="15">
-        <v>5615.2510672900999</v>
+        <v>-6564.7489327099001</v>
       </c>
       <c r="U18" s="16">
-        <v>19.613526570048307</v>
+        <v>0</v>
       </c>
       <c r="V18" s="16">
-        <v>9.0422722500645722</v>
+        <v>-10.571254319983737</v>
       </c>
       <c r="W18" s="17">
-        <v>38777</v>
+        <v>46140</v>
       </c>
       <c r="X18" s="18">
-        <v>45658</v>
+        <v>46140</v>
       </c>
       <c r="Y18" s="17">
-        <v>46022</v>
+        <v>46140</v>
       </c>
       <c r="Z18" s="19"/>
-      <c r="AA18" s="17">
-        <v>46022</v>
-      </c>
-      <c r="AB18" s="20">
-        <v>0.67457072771872439</v>
-      </c>
-      <c r="AC18" s="20">
-        <v>274.03333333333336</v>
-      </c>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
       <c r="AD18" s="17"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -1927,7 +1921,7 @@
         <v>205</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>49</v>
@@ -2013,7 +2007,7 @@
         <v>209</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>49</v>
@@ -2099,7 +2093,7 @@
         <v>206</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>49</v>
@@ -2176,7 +2170,7 @@
       </c>
       <c r="AC21" s="20"/>
       <c r="AD21" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -2187,7 +2181,7 @@
         <v>207</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>49</v>
@@ -2273,7 +2267,7 @@
         <v>208</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>49</v>
@@ -2358,7 +2352,7 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -2389,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>41</v>
@@ -2398,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G25" s="5">
         <v>4000</v>
@@ -2458,10 +2452,10 @@
         <v>49064</v>
       </c>
       <c r="Z25" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA25" s="23" t="s">
         <v>66</v>
-      </c>
-      <c r="AA25" s="23" t="s">
-        <v>67</v>
       </c>
       <c r="AB25" s="20"/>
       <c r="AC25" s="20"/>
@@ -2475,16 +2469,16 @@
         <v>2</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="E26" s="5">
         <v>1</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G26" s="5">
         <v>1</v>
@@ -2544,10 +2538,10 @@
         <v>47603</v>
       </c>
       <c r="Z26" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA26" s="23" t="s">
         <v>66</v>
-      </c>
-      <c r="AA26" s="23" t="s">
-        <v>67</v>
       </c>
       <c r="AB26" s="20"/>
       <c r="AC26" s="20"/>
@@ -2561,16 +2555,16 @@
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" s="5">
         <v>1</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G27" s="5">
         <v>1</v>
@@ -2642,7 +2636,7 @@
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -2677,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>41</v>
@@ -2686,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="5">
         <v>4064</v>
@@ -2749,7 +2743,7 @@
         <v>0.03</v>
       </c>
       <c r="AA29" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AB29" s="20">
         <v>0</v>
@@ -2767,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>49</v>
@@ -2776,7 +2770,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G30" s="5">
         <v>4199</v>
@@ -2839,7 +2833,7 @@
         <v>0.05</v>
       </c>
       <c r="AA30" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AB30" s="20">
         <v>1.9988242210464433</v>
@@ -2855,16 +2849,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="E31" s="5">
         <v>3</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G31" s="5">
         <v>1</v>
@@ -2927,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB31" s="20"/>
       <c r="AC31" s="20"/>
@@ -2941,16 +2935,16 @@
         <v>4</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E32" s="5">
         <v>3</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G32" s="5">
         <v>1</v>
@@ -3018,7 +3012,7 @@
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B33"/>
       <c r="F33" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J33" s="11"/>
       <c r="K33" s="8"/>
@@ -3037,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>41</v>
@@ -3046,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G34" s="5">
         <v>721</v>
@@ -3106,7 +3100,7 @@
         <v>46538</v>
       </c>
       <c r="Z34" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA34" s="23" t="s">
         <v>53</v>
@@ -3125,7 +3119,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>41</v>
@@ -3134,7 +3128,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G35" s="5">
         <v>996</v>
@@ -3194,7 +3188,7 @@
         <v>46706</v>
       </c>
       <c r="Z35" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA35" s="23" t="s">
         <v>53</v>
@@ -3213,7 +3207,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>41</v>
@@ -3222,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G36" s="5">
         <v>1533</v>
@@ -3282,7 +3276,7 @@
         <v>47299</v>
       </c>
       <c r="Z36" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA36" s="23" t="s">
         <v>53</v>
@@ -3301,7 +3295,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>41</v>
@@ -3310,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G37" s="5">
         <v>2508</v>
@@ -3370,10 +3364,10 @@
         <v>47573</v>
       </c>
       <c r="Z37" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA37" s="23" t="s">
         <v>88</v>
-      </c>
-      <c r="AA37" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="AB37" s="20">
         <v>3</v>
@@ -3389,16 +3383,16 @@
         <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="E38" s="5">
         <v>2</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G38" s="5">
         <v>1189</v>
@@ -3458,10 +3452,10 @@
         <v>46265</v>
       </c>
       <c r="Z38" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA38" s="23" t="s">
         <v>93</v>
-      </c>
-      <c r="AA38" s="23" t="s">
-        <v>94</v>
       </c>
       <c r="AB38" s="20">
         <v>4</v>
@@ -3477,16 +3471,16 @@
         <v>6</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="E39" s="5">
         <v>2</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G39" s="5">
         <v>1286</v>
@@ -3567,16 +3561,16 @@
         <v>7</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E40" s="5">
         <v>2</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G40" s="5">
         <v>775</v>
@@ -3651,46 +3645,46 @@
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="J45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="M45" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N45" s="28" t="s">
         <v>108</v>
-      </c>
-      <c r="N45" s="28" t="s">
-        <v>109</v>
       </c>
       <c r="O45" s="28" t="s">
         <v>14</v>
@@ -3699,10 +3693,10 @@
         <v>27</v>
       </c>
       <c r="Q45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R45" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>32</v>
@@ -3719,7 +3713,7 @@
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
@@ -3728,10 +3722,10 @@
         <v>1</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
@@ -3787,7 +3781,7 @@
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>8</v>
@@ -3796,10 +3790,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F47" s="5">
         <v>1</v>
@@ -3855,7 +3849,7 @@
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>8</v>
@@ -3864,10 +3858,10 @@
         <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F48" s="5">
         <v>2</v>
@@ -3923,7 +3917,7 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>8</v>
@@ -3932,10 +3926,10 @@
         <v>1</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F49" s="5">
         <v>3</v>
@@ -3991,7 +3985,7 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>8</v>
@@ -4000,10 +3994,10 @@
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F50" s="5">
         <v>4</v>
@@ -4059,7 +4053,7 @@
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>8</v>
@@ -4068,10 +4062,10 @@
         <v>1</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F51" s="5">
         <v>5</v>
@@ -4127,7 +4121,7 @@
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>8</v>
@@ -4136,10 +4130,10 @@
         <v>1</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F52" s="5">
         <v>6</v>
@@ -4195,7 +4189,7 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>8</v>
@@ -4204,10 +4198,10 @@
         <v>1</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F53" s="5">
         <v>7</v>
@@ -4263,7 +4257,7 @@
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>8</v>
@@ -4272,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F54" s="5">
         <v>8</v>
@@ -4331,7 +4325,7 @@
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>8</v>
@@ -4340,10 +4334,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F55" s="5">
         <v>9</v>
@@ -4399,7 +4393,7 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>8</v>
@@ -4408,10 +4402,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F56" s="5">
         <v>10</v>
@@ -4467,7 +4461,7 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>8</v>
@@ -4476,10 +4470,10 @@
         <v>1</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E57" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F57" s="30">
         <v>11</v>
@@ -4535,7 +4529,7 @@
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B58" s="30" t="s">
         <v>8</v>
@@ -4544,10 +4538,10 @@
         <v>1</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F58" s="30">
         <v>12</v>
@@ -4603,7 +4597,7 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B59" s="30" t="s">
         <v>8</v>
@@ -4612,10 +4606,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E59" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F59" s="30">
         <v>13</v>
@@ -4671,7 +4665,7 @@
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B60" s="30" t="s">
         <v>8</v>
@@ -4680,10 +4674,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E60" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F60" s="30">
         <v>14</v>
@@ -4739,7 +4733,7 @@
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B61" s="30" t="s">
         <v>8</v>
@@ -4748,10 +4742,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F61" s="30">
         <v>15</v>
@@ -4807,7 +4801,7 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B62" s="35" t="s">
         <v>8</v>
@@ -4816,10 +4810,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F62" s="35">
         <v>16</v>
@@ -4875,7 +4869,7 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B63" s="35" t="s">
         <v>8</v>
@@ -4884,10 +4878,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E63" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F63" s="35">
         <v>17</v>
@@ -4943,7 +4937,7 @@
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B64" s="35" t="s">
         <v>8</v>
@@ -4952,10 +4946,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F64" s="35">
         <v>18</v>
@@ -5011,7 +5005,7 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B65" s="35" t="s">
         <v>8</v>
@@ -5020,10 +5014,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E65" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F65" s="35">
         <v>19</v>
@@ -5079,7 +5073,7 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B66" s="35" t="s">
         <v>8</v>
@@ -5088,10 +5082,10 @@
         <v>1</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E66" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F66" s="35">
         <v>20</v>
@@ -5147,75 +5141,75 @@
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V67" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>8</v>
@@ -5224,10 +5218,10 @@
         <v>2</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F68" s="5">
         <v>1</v>
@@ -5283,7 +5277,7 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>8</v>
@@ -5292,10 +5286,10 @@
         <v>2</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F69" s="5">
         <v>2</v>
@@ -5351,7 +5345,7 @@
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>8</v>
@@ -5360,10 +5354,10 @@
         <v>2</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F70" s="5">
         <v>3</v>
@@ -5419,7 +5413,7 @@
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>8</v>
@@ -5428,10 +5422,10 @@
         <v>2</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F71" s="5">
         <v>4</v>
@@ -5487,75 +5481,75 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V72" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>8</v>
@@ -5564,10 +5558,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F73" s="5">
         <v>1</v>
@@ -5623,7 +5617,7 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>8</v>
@@ -5632,10 +5626,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F74" s="5">
         <v>2</v>
@@ -5691,7 +5685,7 @@
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>8</v>
@@ -5700,10 +5694,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F75" s="5">
         <v>3</v>
@@ -5759,7 +5753,7 @@
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>8</v>
@@ -5768,10 +5762,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F76" s="5">
         <v>4</v>
@@ -5827,7 +5821,7 @@
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>8</v>
@@ -5836,10 +5830,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F77" s="5">
         <v>5</v>
@@ -5895,7 +5889,7 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>8</v>
@@ -5904,10 +5898,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F78" s="5">
         <v>6</v>
@@ -5963,7 +5957,7 @@
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>8</v>
@@ -5972,10 +5966,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F79" s="5">
         <v>7</v>
@@ -6031,7 +6025,7 @@
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>8</v>
@@ -6040,10 +6034,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F80" s="5">
         <v>8</v>
@@ -6099,7 +6093,7 @@
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>8</v>
@@ -6108,10 +6102,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F81" s="5">
         <v>9</v>
@@ -6167,7 +6161,7 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>8</v>
@@ -6176,10 +6170,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F82" s="5">
         <v>10</v>
@@ -6235,7 +6229,7 @@
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>8</v>
@@ -6244,10 +6238,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F83" s="5">
         <v>11</v>
@@ -6303,7 +6297,7 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>8</v>
@@ -6312,10 +6306,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F84" s="5">
         <v>12</v>
@@ -6371,7 +6365,7 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>8</v>
@@ -6380,10 +6374,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F85" s="5">
         <v>13</v>
@@ -6439,7 +6433,7 @@
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>8</v>
@@ -6448,10 +6442,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F86" s="5">
         <v>14</v>
@@ -6507,75 +6501,75 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V87" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>8</v>
@@ -6584,10 +6578,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F88" s="5">
         <v>1</v>
@@ -6643,7 +6637,7 @@
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>8</v>
@@ -6652,10 +6646,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F89" s="5">
         <v>2</v>
@@ -6711,7 +6705,7 @@
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>8</v>
@@ -6720,10 +6714,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F90" s="5">
         <v>3</v>
@@ -6779,7 +6773,7 @@
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>8</v>
@@ -6788,10 +6782,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F91" s="5">
         <v>4</v>
@@ -6847,7 +6841,7 @@
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>8</v>
@@ -6856,10 +6850,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F92" s="5">
         <v>5</v>
@@ -6915,7 +6909,7 @@
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>8</v>
@@ -6924,10 +6918,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F93" s="5">
         <v>6</v>
@@ -6983,7 +6977,7 @@
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>8</v>
@@ -6992,10 +6986,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F94" s="5">
         <v>7</v>
@@ -7051,7 +7045,7 @@
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>8</v>
@@ -7060,10 +7054,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F95" s="5">
         <v>8</v>
@@ -7119,7 +7113,7 @@
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>8</v>
@@ -7128,10 +7122,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F96" s="5">
         <v>9</v>
@@ -7187,7 +7181,7 @@
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>8</v>
@@ -7196,10 +7190,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F97" s="5">
         <v>10</v>
@@ -7255,7 +7249,7 @@
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>8</v>
@@ -7264,10 +7258,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F98" s="5">
         <v>11</v>
@@ -7323,75 +7317,75 @@
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V99" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
@@ -7400,10 +7394,10 @@
         <v>1</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F100" s="5">
         <v>1</v>
@@ -7459,7 +7453,7 @@
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
@@ -7468,10 +7462,10 @@
         <v>1</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F101" s="5">
         <v>2</v>
@@ -7527,7 +7521,7 @@
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
@@ -7536,10 +7530,10 @@
         <v>1</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F102" s="5">
         <v>3</v>
@@ -7595,7 +7589,7 @@
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
@@ -7604,10 +7598,10 @@
         <v>1</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F103" s="5">
         <v>4</v>
@@ -7663,7 +7657,7 @@
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>7</v>
@@ -7672,10 +7666,10 @@
         <v>1</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F104" s="5">
         <v>5</v>
@@ -7731,7 +7725,7 @@
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>7</v>
@@ -7740,10 +7734,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F105" s="5">
         <v>6</v>
@@ -7799,7 +7793,7 @@
     </row>
     <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>7</v>
@@ -7808,10 +7802,10 @@
         <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F106" s="5">
         <v>7</v>
@@ -7867,7 +7861,7 @@
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>7</v>
@@ -7876,10 +7870,10 @@
         <v>1</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F107" s="5">
         <v>8</v>
@@ -7935,7 +7929,7 @@
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>7</v>
@@ -7944,10 +7938,10 @@
         <v>1</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F108" s="5">
         <v>9</v>
@@ -8003,7 +7997,7 @@
     </row>
     <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>7</v>
@@ -8012,10 +8006,10 @@
         <v>1</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F109" s="5">
         <v>10</v>
@@ -8071,7 +8065,7 @@
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B110" s="30" t="s">
         <v>7</v>
@@ -8080,10 +8074,10 @@
         <v>1</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E110" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F110" s="30">
         <v>11</v>
@@ -8139,7 +8133,7 @@
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B111" s="30" t="s">
         <v>7</v>
@@ -8148,10 +8142,10 @@
         <v>1</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E111" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F111" s="30">
         <v>12</v>
@@ -8207,7 +8201,7 @@
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B112" s="30" t="s">
         <v>7</v>
@@ -8216,10 +8210,10 @@
         <v>1</v>
       </c>
       <c r="D112" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E112" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F112" s="30">
         <v>13</v>
@@ -8275,7 +8269,7 @@
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B113" s="30" t="s">
         <v>7</v>
@@ -8284,10 +8278,10 @@
         <v>1</v>
       </c>
       <c r="D113" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E113" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F113" s="30">
         <v>14</v>
@@ -8343,7 +8337,7 @@
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B114" s="30" t="s">
         <v>7</v>
@@ -8352,10 +8346,10 @@
         <v>1</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E114" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F114" s="30">
         <v>15</v>
@@ -8411,75 +8405,75 @@
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V115" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>7</v>
@@ -8488,10 +8482,10 @@
         <v>2</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F116" s="5">
         <v>1</v>
@@ -8547,7 +8541,7 @@
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>7</v>
@@ -8556,10 +8550,10 @@
         <v>2</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F117" s="5">
         <v>2</v>
@@ -8615,7 +8609,7 @@
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>7</v>
@@ -8624,10 +8618,10 @@
         <v>2</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F118" s="5">
         <v>3</v>
@@ -8683,7 +8677,7 @@
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>7</v>
@@ -8692,10 +8686,10 @@
         <v>2</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F119" s="5">
         <v>4</v>
@@ -8751,7 +8745,7 @@
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>7</v>
@@ -8760,10 +8754,10 @@
         <v>2</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F120" s="5">
         <v>5</v>
@@ -8819,7 +8813,7 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" s="30" t="s">
         <v>7</v>
@@ -8828,10 +8822,10 @@
         <v>2</v>
       </c>
       <c r="D121" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E121" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F121" s="30">
         <v>6</v>
@@ -8887,7 +8881,7 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B122" s="30" t="s">
         <v>7</v>
@@ -8896,10 +8890,10 @@
         <v>2</v>
       </c>
       <c r="D122" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E122" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F122" s="30">
         <v>7</v>
@@ -8955,7 +8949,7 @@
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B123" s="30" t="s">
         <v>7</v>
@@ -8964,10 +8958,10 @@
         <v>2</v>
       </c>
       <c r="D123" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E123" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F123" s="30">
         <v>8</v>
@@ -9023,7 +9017,7 @@
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B124" s="30" t="s">
         <v>7</v>
@@ -9032,10 +9026,10 @@
         <v>2</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E124" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F124" s="30">
         <v>9</v>
@@ -9091,7 +9085,7 @@
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B125" s="30" t="s">
         <v>7</v>
@@ -9100,10 +9094,10 @@
         <v>2</v>
       </c>
       <c r="D125" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E125" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F125" s="30">
         <v>10</v>
@@ -9159,75 +9153,75 @@
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V126" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>7</v>
@@ -9236,10 +9230,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F127" s="5">
         <v>1</v>
@@ -9295,7 +9289,7 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>7</v>
@@ -9304,10 +9298,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F128" s="5">
         <v>2</v>
@@ -9363,7 +9357,7 @@
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>7</v>
@@ -9372,10 +9366,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F129" s="5">
         <v>3</v>
@@ -9431,7 +9425,7 @@
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>7</v>
@@ -9440,10 +9434,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F130" s="5">
         <v>4</v>
@@ -9499,7 +9493,7 @@
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>7</v>
@@ -9508,10 +9502,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F131" s="5">
         <v>5</v>
@@ -9567,7 +9561,7 @@
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>7</v>
@@ -9576,10 +9570,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F132" s="5">
         <v>6</v>
@@ -9635,7 +9629,7 @@
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>7</v>
@@ -9644,10 +9638,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F133" s="5">
         <v>7</v>
@@ -9703,7 +9697,7 @@
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>7</v>
@@ -9712,10 +9706,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F134" s="5">
         <v>8</v>
@@ -9771,7 +9765,7 @@
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>7</v>
@@ -9780,10 +9774,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F135" s="5">
         <v>9</v>
@@ -9839,7 +9833,7 @@
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>7</v>
@@ -9848,10 +9842,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F136" s="5">
         <v>10</v>
@@ -9907,7 +9901,7 @@
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>7</v>
@@ -9916,10 +9910,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F137" s="5">
         <v>11</v>
@@ -9975,75 +9969,75 @@
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V138" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>9</v>
@@ -10052,10 +10046,10 @@
         <v>1</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F139" s="5">
         <v>1</v>
@@ -10111,7 +10105,7 @@
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>9</v>
@@ -10120,10 +10114,10 @@
         <v>1</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F140" s="5">
         <v>2</v>
@@ -10179,7 +10173,7 @@
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>9</v>
@@ -10188,10 +10182,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F141" s="5">
         <v>3</v>
@@ -10247,7 +10241,7 @@
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>9</v>
@@ -10256,10 +10250,10 @@
         <v>1</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F142" s="5">
         <v>4</v>
@@ -10315,7 +10309,7 @@
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>9</v>
@@ -10324,10 +10318,10 @@
         <v>1</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F143" s="5">
         <v>5</v>
@@ -10383,75 +10377,75 @@
     </row>
     <row r="144" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V144" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>9</v>
@@ -10460,10 +10454,10 @@
         <v>2</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F145" s="5">
         <v>1</v>
@@ -10519,7 +10513,7 @@
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>9</v>
@@ -10528,10 +10522,10 @@
         <v>2</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F146" s="5">
         <v>2</v>
@@ -10587,7 +10581,7 @@
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>9</v>
@@ -10596,10 +10590,10 @@
         <v>2</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F147" s="5">
         <v>3</v>
@@ -10655,7 +10649,7 @@
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>9</v>
@@ -10664,10 +10658,10 @@
         <v>2</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F148" s="5">
         <v>4</v>
@@ -10723,7 +10717,7 @@
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>9</v>
@@ -10732,10 +10726,10 @@
         <v>2</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F149" s="5">
         <v>5</v>
@@ -10789,75 +10783,75 @@
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V150" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>9</v>
@@ -10866,10 +10860,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F151" s="5">
         <v>1</v>
@@ -10925,7 +10919,7 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>9</v>
@@ -10934,10 +10928,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F152" s="5">
         <v>2</v>
@@ -10993,7 +10987,7 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>9</v>
@@ -11002,10 +10996,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F153" s="5">
         <v>3</v>
@@ -11061,7 +11055,7 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>9</v>
@@ -11070,10 +11064,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F154" s="5">
         <v>4</v>
@@ -11129,7 +11123,7 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>9</v>
@@ -11138,10 +11132,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F155" s="5">
         <v>5</v>
@@ -11197,75 +11191,75 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V156" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>9</v>
@@ -11274,10 +11268,10 @@
         <v>4</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F157" s="5">
         <v>1</v>
@@ -11333,7 +11327,7 @@
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>9</v>
@@ -11342,10 +11336,10 @@
         <v>4</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F158" s="5">
         <v>2</v>
@@ -11401,7 +11395,7 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>9</v>
@@ -11410,10 +11404,10 @@
         <v>4</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F159" s="5">
         <v>3</v>
@@ -11469,7 +11463,7 @@
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>9</v>
@@ -11478,10 +11472,10 @@
         <v>4</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F160" s="5">
         <v>4</v>
@@ -11537,7 +11531,7 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>9</v>
@@ -11546,10 +11540,10 @@
         <v>4</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F161" s="5">
         <v>5</v>
@@ -11605,7 +11599,7 @@
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>9</v>
@@ -11614,10 +11608,10 @@
         <v>4</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F162" s="5">
         <v>6</v>
@@ -11673,7 +11667,7 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>9</v>
@@ -11682,10 +11676,10 @@
         <v>4</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F163" s="5">
         <v>7</v>
@@ -11741,7 +11735,7 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>9</v>
@@ -11750,10 +11744,10 @@
         <v>4</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F164" s="5">
         <v>8</v>
@@ -11809,7 +11803,7 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>9</v>
@@ -11818,10 +11812,10 @@
         <v>4</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F165" s="5">
         <v>9</v>
@@ -11877,7 +11871,7 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>9</v>
@@ -11886,10 +11880,10 @@
         <v>4</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F166" s="5">
         <v>10</v>
@@ -11945,7 +11939,7 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B167" s="30" t="s">
         <v>9</v>
@@ -11954,10 +11948,10 @@
         <v>4</v>
       </c>
       <c r="D167" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F167" s="30">
         <v>11</v>
@@ -12013,7 +12007,7 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B168" s="30" t="s">
         <v>9</v>
@@ -12022,10 +12016,10 @@
         <v>4</v>
       </c>
       <c r="D168" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F168" s="30">
         <v>12</v>
@@ -12081,7 +12075,7 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B169" s="30" t="s">
         <v>9</v>
@@ -12090,10 +12084,10 @@
         <v>4</v>
       </c>
       <c r="D169" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F169" s="30">
         <v>13</v>
@@ -12149,7 +12143,7 @@
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A170" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B170" s="30" t="s">
         <v>9</v>
@@ -12158,10 +12152,10 @@
         <v>4</v>
       </c>
       <c r="D170" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F170" s="30">
         <v>14</v>
@@ -12217,7 +12211,7 @@
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A171" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B171" s="30" t="s">
         <v>9</v>
@@ -12226,10 +12220,10 @@
         <v>4</v>
       </c>
       <c r="D171" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F171" s="30">
         <v>15</v>
@@ -12285,7 +12279,7 @@
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A172" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B172" s="35" t="s">
         <v>9</v>
@@ -12294,10 +12288,10 @@
         <v>4</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E172" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F172" s="35">
         <v>16</v>
@@ -12353,7 +12347,7 @@
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A173" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B173" s="35" t="s">
         <v>9</v>
@@ -12362,10 +12356,10 @@
         <v>4</v>
       </c>
       <c r="D173" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E173" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F173" s="35">
         <v>17</v>
@@ -12421,7 +12415,7 @@
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A174" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B174" s="35" t="s">
         <v>9</v>
@@ -12430,10 +12424,10 @@
         <v>4</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E174" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F174" s="35">
         <v>18</v>
@@ -12489,7 +12483,7 @@
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A175" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B175" s="35" t="s">
         <v>9</v>
@@ -12498,10 +12492,10 @@
         <v>4</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E175" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F175" s="35">
         <v>19</v>
@@ -12557,7 +12551,7 @@
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A176" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B176" s="35" t="s">
         <v>9</v>
@@ -12566,10 +12560,10 @@
         <v>4</v>
       </c>
       <c r="D176" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E176" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F176" s="35">
         <v>20</v>
@@ -12625,7 +12619,7 @@
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A177" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B177" s="44" t="s">
         <v>9</v>
@@ -12634,10 +12628,10 @@
         <v>4</v>
       </c>
       <c r="D177" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E177" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F177" s="44">
         <v>21</v>
@@ -12693,7 +12687,7 @@
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A178" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B178" s="44" t="s">
         <v>9</v>
@@ -12702,10 +12696,10 @@
         <v>4</v>
       </c>
       <c r="D178" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E178" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F178" s="44">
         <v>22</v>
@@ -12761,7 +12755,7 @@
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A179" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B179" s="44" t="s">
         <v>9</v>
@@ -12770,10 +12764,10 @@
         <v>4</v>
       </c>
       <c r="D179" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E179" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F179" s="44">
         <v>23</v>
@@ -12829,7 +12823,7 @@
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A180" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B180" s="44" t="s">
         <v>9</v>
@@ -12838,10 +12832,10 @@
         <v>4</v>
       </c>
       <c r="D180" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E180" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F180" s="44">
         <v>24</v>
@@ -12897,7 +12891,7 @@
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A181" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B181" s="44" t="s">
         <v>9</v>
@@ -12906,10 +12900,10 @@
         <v>4</v>
       </c>
       <c r="D181" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E181" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F181" s="44">
         <v>25</v>
@@ -12965,75 +12959,75 @@
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V182" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>9</v>
@@ -13042,10 +13036,10 @@
         <v>5</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F183" s="5">
         <v>1</v>
@@ -13101,7 +13095,7 @@
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>9</v>
@@ -13110,10 +13104,10 @@
         <v>5</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F184" s="5">
         <v>2</v>
@@ -13169,7 +13163,7 @@
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>9</v>
@@ -13178,10 +13172,10 @@
         <v>5</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F185" s="5">
         <v>3</v>
@@ -13237,7 +13231,7 @@
     </row>
     <row r="186" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>9</v>
@@ -13246,10 +13240,10 @@
         <v>5</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F186" s="5">
         <v>4</v>
@@ -13305,7 +13299,7 @@
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A187" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B187" s="30" t="s">
         <v>9</v>
@@ -13314,10 +13308,10 @@
         <v>5</v>
       </c>
       <c r="D187" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F187" s="30">
         <v>5</v>
@@ -13373,7 +13367,7 @@
     </row>
     <row r="188" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A188" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B188" s="30" t="s">
         <v>9</v>
@@ -13382,10 +13376,10 @@
         <v>5</v>
       </c>
       <c r="D188" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F188" s="30">
         <v>6</v>
@@ -13441,7 +13435,7 @@
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A189" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B189" s="35" t="s">
         <v>9</v>
@@ -13450,10 +13444,10 @@
         <v>5</v>
       </c>
       <c r="D189" s="35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E189" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F189" s="35">
         <v>7</v>
@@ -13509,7 +13503,7 @@
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A190" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B190" s="35" t="s">
         <v>9</v>
@@ -13518,10 +13512,10 @@
         <v>5</v>
       </c>
       <c r="D190" s="35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E190" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F190" s="35">
         <v>8</v>
@@ -13577,75 +13571,75 @@
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V191" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>9</v>
@@ -13654,10 +13648,10 @@
         <v>6</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F192" s="5">
         <v>1</v>
@@ -13713,75 +13707,75 @@
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V193" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="194" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>9</v>
@@ -13790,10 +13784,10 @@
         <v>7</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F194" s="5">
         <v>1</v>
@@ -13849,75 +13843,75 @@
     </row>
     <row r="195" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V195" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>6</v>
@@ -13929,7 +13923,7 @@
         <v>40</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F196" s="5">
         <v>1</v>
@@ -13985,75 +13979,75 @@
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V197" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>6</v>
@@ -14065,7 +14059,7 @@
         <v>44</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F198" s="5">
         <v>1</v>
@@ -14121,7 +14115,7 @@
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>6</v>
@@ -14133,7 +14127,7 @@
         <v>44</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F199" s="5">
         <v>1</v>
@@ -14189,75 +14183,75 @@
     </row>
     <row r="200" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V200" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="201" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>6</v>
@@ -14269,7 +14263,7 @@
         <v>45</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F201" s="5">
         <v>1</v>
@@ -14325,7 +14319,7 @@
     </row>
     <row r="202" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>6</v>
@@ -14337,7 +14331,7 @@
         <v>45</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F202" s="5">
         <v>2</v>
@@ -14393,7 +14387,7 @@
     </row>
     <row r="203" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>6</v>
@@ -14405,7 +14399,7 @@
         <v>45</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F203" s="5">
         <v>3</v>
@@ -14461,7 +14455,7 @@
     </row>
     <row r="204" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>6</v>
@@ -14473,7 +14467,7 @@
         <v>45</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F204" s="5">
         <v>4</v>
@@ -14529,7 +14523,7 @@
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>6</v>
@@ -14541,7 +14535,7 @@
         <v>45</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F205" s="5">
         <v>5</v>
@@ -14597,7 +14591,7 @@
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>6</v>
@@ -14609,7 +14603,7 @@
         <v>45</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F206" s="5">
         <v>6</v>
@@ -14665,7 +14659,7 @@
     </row>
     <row r="207" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A207" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B207" s="30" t="s">
         <v>6</v>
@@ -14677,7 +14671,7 @@
         <v>45</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F207" s="30">
         <v>7</v>
@@ -14733,7 +14727,7 @@
     </row>
     <row r="208" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A208" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B208" s="30" t="s">
         <v>6</v>
@@ -14745,7 +14739,7 @@
         <v>45</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F208" s="30">
         <v>8</v>
@@ -14801,7 +14795,7 @@
     </row>
     <row r="209" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A209" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B209" s="30" t="s">
         <v>6</v>
@@ -14813,7 +14807,7 @@
         <v>45</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F209" s="30">
         <v>9</v>
@@ -14869,7 +14863,7 @@
     </row>
     <row r="210" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A210" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B210" s="30" t="s">
         <v>6</v>
@@ -14881,7 +14875,7 @@
         <v>45</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F210" s="30">
         <v>10</v>
@@ -14937,7 +14931,7 @@
     </row>
     <row r="211" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A211" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B211" s="30" t="s">
         <v>6</v>
@@ -14949,7 +14943,7 @@
         <v>45</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F211" s="30">
         <v>11</v>
@@ -15005,7 +14999,7 @@
     </row>
     <row r="212" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A212" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B212" s="35" t="s">
         <v>6</v>
@@ -15017,7 +15011,7 @@
         <v>45</v>
       </c>
       <c r="E212" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F212" s="35">
         <v>12</v>
@@ -15073,7 +15067,7 @@
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A213" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B213" s="35" t="s">
         <v>6</v>
@@ -15085,7 +15079,7 @@
         <v>45</v>
       </c>
       <c r="E213" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F213" s="35">
         <v>13</v>
@@ -15141,7 +15135,7 @@
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A214" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B214" s="35" t="s">
         <v>6</v>
@@ -15153,7 +15147,7 @@
         <v>45</v>
       </c>
       <c r="E214" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F214" s="35">
         <v>14</v>
@@ -15209,7 +15203,7 @@
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A215" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B215" s="35" t="s">
         <v>6</v>
@@ -15221,7 +15215,7 @@
         <v>45</v>
       </c>
       <c r="E215" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F215" s="35">
         <v>15</v>
@@ -15277,7 +15271,7 @@
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A216" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B216" s="35" t="s">
         <v>6</v>
@@ -15289,7 +15283,7 @@
         <v>45</v>
       </c>
       <c r="E216" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F216" s="35">
         <v>16</v>
@@ -15345,75 +15339,75 @@
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V217" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>6</v>
@@ -15425,7 +15419,7 @@
         <v>47</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F218" s="5">
         <v>1</v>
@@ -15481,7 +15475,7 @@
     </row>
     <row r="219" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>6</v>
@@ -15493,7 +15487,7 @@
         <v>47</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F219" s="5">
         <v>2</v>
@@ -15549,7 +15543,7 @@
     </row>
     <row r="220" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>6</v>
@@ -15561,7 +15555,7 @@
         <v>47</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F220" s="5">
         <v>3</v>
@@ -15617,7 +15611,7 @@
     </row>
     <row r="221" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>6</v>
@@ -15629,7 +15623,7 @@
         <v>47</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F221" s="5">
         <v>4</v>
@@ -15685,7 +15679,7 @@
     </row>
     <row r="222" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>6</v>
@@ -15697,7 +15691,7 @@
         <v>47</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F222" s="5">
         <v>5</v>
@@ -15753,7 +15747,7 @@
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>6</v>
@@ -15765,7 +15759,7 @@
         <v>47</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F223" s="5">
         <v>6</v>
@@ -15821,75 +15815,75 @@
     </row>
     <row r="224" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V224" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="225" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>6</v>
@@ -15901,7 +15895,7 @@
         <v>48</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F225" s="5">
         <v>1</v>
@@ -15957,75 +15951,75 @@
     </row>
     <row r="226" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V226" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="227" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>6</v>
@@ -16037,7 +16031,7 @@
         <v>52</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F227" s="5">
         <v>1</v>
@@ -16093,75 +16087,75 @@
     </row>
     <row r="228" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V228" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>6</v>
@@ -16173,7 +16167,7 @@
         <v>54</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F229" s="5">
         <v>1</v>
@@ -16229,7 +16223,7 @@
     </row>
     <row r="230" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>6</v>
@@ -16241,7 +16235,7 @@
         <v>54</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F230" s="5">
         <v>2</v>
@@ -16297,7 +16291,7 @@
     </row>
     <row r="231" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A231" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B231" s="30" t="s">
         <v>6</v>
@@ -16309,7 +16303,7 @@
         <v>54</v>
       </c>
       <c r="E231" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F231" s="30">
         <v>3</v>
@@ -16365,7 +16359,7 @@
     </row>
     <row r="232" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A232" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B232" s="35" t="s">
         <v>6</v>
@@ -16377,7 +16371,7 @@
         <v>54</v>
       </c>
       <c r="E232" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F232" s="35">
         <v>4</v>
@@ -16433,75 +16427,75 @@
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V233" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="234" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>6</v>
@@ -16510,28 +16504,28 @@
         <v>204</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F234" s="5">
         <v>1</v>
       </c>
       <c r="G234" s="29">
-        <v>45658</v>
+        <v>46140</v>
       </c>
       <c r="H234" s="29">
-        <v>46022</v>
+        <v>46140</v>
       </c>
       <c r="I234" s="11">
         <v>0</v>
       </c>
       <c r="J234" s="14">
-        <v>1223</v>
+        <v>0</v>
       </c>
       <c r="K234" s="41">
-        <v>14676</v>
+        <v>0</v>
       </c>
       <c r="L234" s="5" t="s">
         <v>38</v>
@@ -16549,95 +16543,95 @@
         <v>5.0498068713153078E-2</v>
       </c>
       <c r="Q234" s="14">
-        <v>23.632850241545892</v>
+        <v>0</v>
       </c>
       <c r="R234" s="14">
-        <v>824.99999999999989</v>
+        <v>0</v>
       </c>
       <c r="S234" s="29">
-        <v>38777</v>
+        <v>46140</v>
       </c>
       <c r="T234" s="29">
-        <v>45658</v>
+        <v>46140</v>
       </c>
       <c r="U234" s="29">
-        <v>46022</v>
+        <v>46140</v>
       </c>
       <c r="V234" s="14">
-        <v>274.03333333333336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V235" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>6</v>
@@ -16646,10 +16640,10 @@
         <v>205</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F236" s="5">
         <v>1</v>
@@ -16705,7 +16699,7 @@
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>6</v>
@@ -16714,10 +16708,10 @@
         <v>205</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F237" s="5">
         <v>2</v>
@@ -16773,7 +16767,7 @@
     </row>
     <row r="238" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>6</v>
@@ -16782,10 +16776,10 @@
         <v>205</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F238" s="5">
         <v>3</v>
@@ -16841,75 +16835,75 @@
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V239" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="240" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>6</v>
@@ -16918,10 +16912,10 @@
         <v>209</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F240" s="5">
         <v>1</v>
@@ -16977,7 +16971,7 @@
     </row>
     <row r="241" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>6</v>
@@ -16986,10 +16980,10 @@
         <v>209</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F241" s="5">
         <v>2</v>
@@ -17045,7 +17039,7 @@
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>6</v>
@@ -17054,10 +17048,10 @@
         <v>209</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F242" s="5">
         <v>3</v>
@@ -17113,75 +17107,75 @@
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V243" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>6</v>
@@ -17190,10 +17184,10 @@
         <v>206</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F244" s="5">
         <v>1</v>
@@ -17249,7 +17243,7 @@
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>6</v>
@@ -17258,10 +17252,10 @@
         <v>206</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F245" s="5">
         <v>1</v>
@@ -17317,7 +17311,7 @@
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>6</v>
@@ -17326,10 +17320,10 @@
         <v>206</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F246" s="5">
         <v>1</v>
@@ -17385,7 +17379,7 @@
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>6</v>
@@ -17394,10 +17388,10 @@
         <v>206</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F247" s="5">
         <v>1</v>
@@ -17453,7 +17447,7 @@
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>6</v>
@@ -17462,10 +17456,10 @@
         <v>206</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F248" s="5">
         <v>1</v>
@@ -17521,7 +17515,7 @@
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>6</v>
@@ -17530,10 +17524,10 @@
         <v>206</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F249" s="5">
         <v>1</v>
@@ -17589,75 +17583,75 @@
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V250" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>6</v>
@@ -17666,10 +17660,10 @@
         <v>207</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F251" s="5">
         <v>1</v>
@@ -17725,7 +17719,7 @@
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>6</v>
@@ -17734,10 +17728,10 @@
         <v>207</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F252" s="5">
         <v>2</v>
@@ -17793,7 +17787,7 @@
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>6</v>
@@ -17802,10 +17796,10 @@
         <v>207</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F253" s="5">
         <v>3</v>
@@ -17861,7 +17855,7 @@
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>6</v>
@@ -17870,10 +17864,10 @@
         <v>207</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F254" s="5">
         <v>4</v>
@@ -17929,7 +17923,7 @@
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A255" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B255" s="30" t="s">
         <v>6</v>
@@ -17938,10 +17932,10 @@
         <v>207</v>
       </c>
       <c r="D255" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E255" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F255" s="30">
         <v>5</v>
@@ -17997,7 +17991,7 @@
     </row>
     <row r="256" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A256" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B256" s="30" t="s">
         <v>6</v>
@@ -18006,10 +18000,10 @@
         <v>207</v>
       </c>
       <c r="D256" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E256" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F256" s="30">
         <v>6</v>
@@ -18065,75 +18059,75 @@
     </row>
     <row r="257" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="S257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V257" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="258" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>6</v>
@@ -18142,10 +18136,10 @@
         <v>208</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F258" s="5">
         <v>1</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CAA7158-3300-436D-A5B9-5DB5B1790BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CD99F63-21D9-441A-9548-BC1A36FEBB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-52875" yWindow="2205" windowWidth="50145" windowHeight="27570" xr2:uid="{D7C1C753-0486-404B-8498-9D23BF02A5A7}"/>
+    <workbookView xWindow="0" yWindow="4830" windowWidth="57810" windowHeight="27570" xr2:uid="{D7C1C753-0486-404B-8498-9D23BF02A5A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3474,7 +3474,7 @@
         <v>45108</v>
       </c>
       <c r="Y38" s="17">
-        <v>46265</v>
+        <v>46996</v>
       </c>
       <c r="Z38" s="24" t="s">
         <v>90</v>
@@ -3483,7 +3483,7 @@
         <v>91</v>
       </c>
       <c r="AB38" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC38" s="20"/>
       <c r="AD38" s="23"/>
@@ -13243,7 +13243,7 @@
         <v>12.615643397813288</v>
       </c>
       <c r="R183" s="14">
-        <v>5000</v>
+        <v>3750</v>
       </c>
       <c r="S183" s="29">
         <v>45066</v>
@@ -13252,7 +13252,7 @@
         <v>45108</v>
       </c>
       <c r="U183" s="29">
-        <v>46265</v>
+        <v>46996</v>
       </c>
       <c r="V183" s="14">
         <v>0</v>
@@ -13312,7 +13312,7 @@
         <v>25.231286795626577</v>
       </c>
       <c r="R184" s="14">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="S184" s="17">
         <v>45066</v>
@@ -13321,7 +13321,7 @@
         <v>45108</v>
       </c>
       <c r="U184" s="29">
-        <v>46265</v>
+        <v>46996</v>
       </c>
       <c r="V184" s="14">
         <v>0</v>
@@ -13381,7 +13381,7 @@
         <v>26.24053826745164</v>
       </c>
       <c r="R185" s="14">
-        <v>10400</v>
+        <v>7800</v>
       </c>
       <c r="S185" s="17">
         <v>45066</v>
@@ -13390,7 +13390,7 @@
         <v>45108</v>
       </c>
       <c r="U185" s="29">
-        <v>46265</v>
+        <v>46996</v>
       </c>
       <c r="V185" s="14">
         <v>0</v>
@@ -13450,7 +13450,7 @@
         <v>27.249789739276704</v>
       </c>
       <c r="R186" s="14">
-        <v>10800</v>
+        <v>8100</v>
       </c>
       <c r="S186" s="17">
         <v>45066</v>
@@ -13459,7 +13459,7 @@
         <v>45108</v>
       </c>
       <c r="U186" s="29">
-        <v>46265</v>
+        <v>46996</v>
       </c>
       <c r="V186" s="14">
         <v>0</v>
@@ -13467,142 +13467,142 @@
       <c r="W186" s="14"/>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A187" s="30" t="s">
+      <c r="A187" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B187" s="30" t="s">
+      <c r="B187" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C187" s="30">
+      <c r="C187" s="5">
         <v>5</v>
       </c>
-      <c r="D187" s="30" t="s">
+      <c r="D187" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E187" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="F187" s="30">
+      <c r="E187" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F187" s="5">
         <v>5</v>
       </c>
-      <c r="G187" s="31">
+      <c r="G187" s="17">
         <v>46266</v>
       </c>
-      <c r="H187" s="31">
+      <c r="H187" s="17">
         <v>46630</v>
       </c>
-      <c r="I187" s="32">
+      <c r="I187" s="11">
         <v>0.11111111111111116</v>
       </c>
-      <c r="J187" s="33">
+      <c r="J187" s="14">
         <v>3000</v>
       </c>
-      <c r="K187" s="42">
+      <c r="K187" s="41">
         <v>36000</v>
       </c>
-      <c r="L187" s="30" t="s">
+      <c r="L187" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M187" s="34">
+      <c r="M187" s="7">
         <v>1189</v>
       </c>
-      <c r="N187" s="32">
+      <c r="N187" s="11">
         <v>0.39</v>
       </c>
-      <c r="O187" s="32">
+      <c r="O187" s="11">
         <v>0.39</v>
       </c>
-      <c r="P187" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q187" s="33">
+      <c r="P187" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q187" s="14">
         <v>30.277544154751894</v>
       </c>
-      <c r="R187" s="33">
-        <v>12000</v>
-      </c>
-      <c r="S187" s="31">
+      <c r="R187" s="14">
+        <v>9000</v>
+      </c>
+      <c r="S187" s="17">
         <v>45066</v>
       </c>
-      <c r="T187" s="31">
+      <c r="T187" s="17">
         <v>45108</v>
       </c>
       <c r="U187" s="29">
-        <v>46265</v>
-      </c>
-      <c r="V187" s="33">
-        <v>0</v>
-      </c>
-      <c r="W187" s="33"/>
+        <v>46996</v>
+      </c>
+      <c r="V187" s="14">
+        <v>0</v>
+      </c>
+      <c r="W187" s="14"/>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A188" s="30" t="s">
+      <c r="A188" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B188" s="30" t="s">
+      <c r="B188" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C188" s="30">
+      <c r="C188" s="5">
         <v>5</v>
       </c>
-      <c r="D188" s="30" t="s">
+      <c r="D188" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E188" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="F188" s="30">
+      <c r="E188" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F188" s="5">
         <v>6</v>
       </c>
-      <c r="G188" s="31">
+      <c r="G188" s="17">
         <v>46631</v>
       </c>
-      <c r="H188" s="31">
+      <c r="H188" s="17">
         <v>46996</v>
       </c>
-      <c r="I188" s="32">
+      <c r="I188" s="11">
         <v>3.3333333333333437E-2</v>
       </c>
-      <c r="J188" s="33">
+      <c r="J188" s="14">
         <v>3100</v>
       </c>
-      <c r="K188" s="42">
+      <c r="K188" s="41">
         <v>37200</v>
       </c>
-      <c r="L188" s="30" t="s">
+      <c r="L188" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M188" s="34">
+      <c r="M188" s="7">
         <v>1189</v>
       </c>
-      <c r="N188" s="32">
+      <c r="N188" s="11">
         <v>0.39</v>
       </c>
-      <c r="O188" s="32">
+      <c r="O188" s="11">
         <v>0.39</v>
       </c>
-      <c r="P188" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q188" s="33">
+      <c r="P188" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q188" s="14">
         <v>31.286795626576957</v>
       </c>
-      <c r="R188" s="33">
-        <v>12400</v>
-      </c>
-      <c r="S188" s="31">
+      <c r="R188" s="14">
+        <v>9300</v>
+      </c>
+      <c r="S188" s="17">
         <v>45066</v>
       </c>
-      <c r="T188" s="31">
+      <c r="T188" s="17">
         <v>45108</v>
       </c>
       <c r="U188" s="29">
-        <v>46265</v>
-      </c>
-      <c r="V188" s="33">
-        <v>0</v>
-      </c>
-      <c r="W188" s="33"/>
+        <v>46996</v>
+      </c>
+      <c r="V188" s="14">
+        <v>0</v>
+      </c>
+      <c r="W188" s="14"/>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="35" t="s">
@@ -13657,7 +13657,7 @@
         <v>33.30529857022708</v>
       </c>
       <c r="R189" s="38">
-        <v>13200</v>
+        <v>9900</v>
       </c>
       <c r="S189" s="36">
         <v>45066</v>
@@ -13666,7 +13666,7 @@
         <v>45108</v>
       </c>
       <c r="U189" s="29">
-        <v>46265</v>
+        <v>46996</v>
       </c>
       <c r="V189" s="38">
         <v>0</v>
@@ -13726,7 +13726,7 @@
         <v>34.314550042052147</v>
       </c>
       <c r="R190" s="38">
-        <v>13600</v>
+        <v>10200</v>
       </c>
       <c r="S190" s="36">
         <v>45066</v>
@@ -13735,7 +13735,7 @@
         <v>45108</v>
       </c>
       <c r="U190" s="29">
-        <v>46265</v>
+        <v>46996</v>
       </c>
       <c r="V190" s="38">
         <v>0</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CD99F63-21D9-441A-9548-BC1A36FEBB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F3578BC-0C73-4DD0-BC9D-FEEE74D61272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4830" windowWidth="57810" windowHeight="27570" xr2:uid="{D7C1C753-0486-404B-8498-9D23BF02A5A7}"/>
+    <workbookView xWindow="495" yWindow="2100" windowWidth="57810" windowHeight="27570" xr2:uid="{D7C1C753-0486-404B-8498-9D23BF02A5A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3897,7 +3897,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="17">
-        <v>45383</v>
+        <v>45748</v>
       </c>
       <c r="H48" s="17">
         <v>46112</v>
@@ -3966,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="G49" s="17">
-        <v>45383</v>
+        <v>46113</v>
       </c>
       <c r="H49" s="17">
         <v>46477</v>
@@ -4035,7 +4035,7 @@
         <v>4</v>
       </c>
       <c r="G50" s="17">
-        <v>45383</v>
+        <v>46478</v>
       </c>
       <c r="H50" s="17">
         <v>46843</v>
@@ -4104,7 +4104,7 @@
         <v>5</v>
       </c>
       <c r="G51" s="17">
-        <v>45383</v>
+        <v>46844</v>
       </c>
       <c r="H51" s="17">
         <v>47208</v>
@@ -4173,7 +4173,7 @@
         <v>6</v>
       </c>
       <c r="G52" s="17">
-        <v>45383</v>
+        <v>47209</v>
       </c>
       <c r="H52" s="17">
         <v>47573</v>
@@ -4242,7 +4242,7 @@
         <v>7</v>
       </c>
       <c r="G53" s="17">
-        <v>45383</v>
+        <v>47574</v>
       </c>
       <c r="H53" s="17">
         <v>47938</v>
@@ -4311,7 +4311,7 @@
         <v>8</v>
       </c>
       <c r="G54" s="17">
-        <v>45383</v>
+        <v>47939</v>
       </c>
       <c r="H54" s="17">
         <v>48304</v>
@@ -4380,7 +4380,7 @@
         <v>9</v>
       </c>
       <c r="G55" s="17">
-        <v>45383</v>
+        <v>48305</v>
       </c>
       <c r="H55" s="17">
         <v>48669</v>
@@ -4449,7 +4449,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="17">
-        <v>45383</v>
+        <v>48670</v>
       </c>
       <c r="H56" s="17">
         <v>49034</v>
@@ -4518,7 +4518,7 @@
         <v>11</v>
       </c>
       <c r="G57" s="31">
-        <v>45383</v>
+        <v>49035</v>
       </c>
       <c r="H57" s="31">
         <v>49399</v>
@@ -4587,7 +4587,7 @@
         <v>12</v>
       </c>
       <c r="G58" s="31">
-        <v>45383</v>
+        <v>49400</v>
       </c>
       <c r="H58" s="31">
         <v>49765</v>
@@ -4656,7 +4656,7 @@
         <v>13</v>
       </c>
       <c r="G59" s="31">
-        <v>45383</v>
+        <v>49766</v>
       </c>
       <c r="H59" s="31">
         <v>50130</v>
@@ -4725,7 +4725,7 @@
         <v>14</v>
       </c>
       <c r="G60" s="31">
-        <v>45383</v>
+        <v>50131</v>
       </c>
       <c r="H60" s="31">
         <v>50495</v>
@@ -4794,7 +4794,7 @@
         <v>15</v>
       </c>
       <c r="G61" s="31">
-        <v>45383</v>
+        <v>50496</v>
       </c>
       <c r="H61" s="31">
         <v>50860</v>
@@ -4863,7 +4863,7 @@
         <v>16</v>
       </c>
       <c r="G62" s="36">
-        <v>45383</v>
+        <v>50861</v>
       </c>
       <c r="H62" s="36">
         <v>51226</v>
@@ -4932,7 +4932,7 @@
         <v>17</v>
       </c>
       <c r="G63" s="36">
-        <v>45383</v>
+        <v>51227</v>
       </c>
       <c r="H63" s="36">
         <v>51591</v>
@@ -5001,7 +5001,7 @@
         <v>18</v>
       </c>
       <c r="G64" s="36">
-        <v>45383</v>
+        <v>51592</v>
       </c>
       <c r="H64" s="36">
         <v>51956</v>
@@ -5070,7 +5070,7 @@
         <v>19</v>
       </c>
       <c r="G65" s="36">
-        <v>45383</v>
+        <v>51957</v>
       </c>
       <c r="H65" s="36">
         <v>52321</v>
@@ -5139,7 +5139,7 @@
         <v>20</v>
       </c>
       <c r="G66" s="36">
-        <v>45383</v>
+        <v>52322</v>
       </c>
       <c r="H66" s="36">
         <v>52687</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F3578BC-0C73-4DD0-BC9D-FEEE74D61272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1C6774F-EECC-4CE7-B1DE-F5A099FBC9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="2100" windowWidth="57810" windowHeight="27570" xr2:uid="{D7C1C753-0486-404B-8498-9D23BF02A5A7}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="51615" windowHeight="27570" xr2:uid="{E3CDC22C-56CE-4F9B-82DA-520B345C859B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
     <t>Cancel</t>
   </si>
   <si>
-    <t>Nabig Sakr and Maria</t>
+    <t>Nabig Sakr</t>
   </si>
   <si>
     <t>Retail</t>
@@ -173,19 +173,19 @@
     <t>NNN</t>
   </si>
   <si>
-    <t>EJS Toybox</t>
+    <t>EJS Westfield Toybox, LLC d/b/a Learning Express</t>
   </si>
   <si>
-    <t>Reves Smoothie</t>
+    <t>Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
   </si>
   <si>
     <t>3% Annually</t>
   </si>
   <si>
-    <t>GP Mobile</t>
+    <t>Luna Wireless</t>
   </si>
   <si>
-    <t>Ashford Schael</t>
+    <t>Ashford - Schael, LLC</t>
   </si>
   <si>
     <t>Office</t>
@@ -197,34 +197,52 @@
     <t>Each Year</t>
   </si>
   <si>
-    <t>None</t>
+    <t>American Retail Shippers</t>
   </si>
   <si>
-    <t>Rentokil</t>
+    <t>Annual Variable</t>
+  </si>
+  <si>
+    <t>One 1-Year</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Rentokil North America dba Terminix</t>
   </si>
   <si>
     <t>Two 1-Year</t>
   </si>
   <si>
-    <t>Jenny Madden_A</t>
+    <t>VACANT_204</t>
   </si>
   <si>
-    <t>Jenny Madden_B</t>
+    <t>Jenny Madden Design, LLC A</t>
   </si>
   <si>
-    <t>Dave Rossi</t>
+    <t>Jenny Madden Design, LLC B</t>
   </si>
   <si>
-    <t>Westfield Education</t>
+    <t>Dave Rossi Photography, LLC</t>
   </si>
   <si>
-    <t>SRD Captial</t>
+    <t>Yes; 2 years 90 day notice to Anniversayr</t>
+  </si>
+  <si>
+    <t>Westfield Education Association</t>
+  </si>
+  <si>
+    <t>One-Two Year</t>
+  </si>
+  <si>
+    <t>SRD Capital Management, LLC</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Summit Health</t>
+    <t>CITY PROPERTY USA NJ, LLC</t>
   </si>
   <si>
     <t>15 South1</t>
@@ -245,7 +263,7 @@
     <t>Easement</t>
   </si>
   <si>
-    <t>Wonder</t>
+    <t>HDR HOLDINGS LLC D/B/A WONDER</t>
   </si>
   <si>
     <t>36 South1</t>
@@ -254,7 +272,7 @@
     <t>Two 5-Year 3% Annual Inc</t>
   </si>
   <si>
-    <t>Longo Architects</t>
+    <t>Longo Architects &amp; Associates, LLC</t>
   </si>
   <si>
     <t>36 South2</t>
@@ -275,7 +293,7 @@
     <t>Two 5-Year 7.5% Jump then Flat</t>
   </si>
   <si>
-    <t>Georges Appliance</t>
+    <t>George's Appliance, LLC</t>
   </si>
   <si>
     <t>1280 Springfield1</t>
@@ -284,16 +302,19 @@
     <t>3.0% Annual</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>Juice House</t>
   </si>
   <si>
     <t>3.5% Annual</t>
   </si>
   <si>
-    <t>Ksquared Air</t>
+    <t>Uppleside Down Wellness, LLC D/B/A Air</t>
   </si>
   <si>
-    <t>Your Kids Urgent Care</t>
+    <t>SLK Enterprises, LLC D/B/A AFC Urgent Care</t>
   </si>
   <si>
     <t>2.0% Annual</t>
@@ -302,7 +323,7 @@
     <t>Three 5-Yr w 2% Ann Inc</t>
   </si>
   <si>
-    <t>Sana Yoga</t>
+    <t>Sana Yoga Studio, LLC</t>
   </si>
   <si>
     <t>Commercial</t>
@@ -315,6 +336,9 @@
   </si>
   <si>
     <t>Two 2-Year</t>
+  </si>
+  <si>
+    <t>VACANT_6</t>
   </si>
   <si>
     <t>Apartment</t>
@@ -365,7 +389,10 @@
     <t>Sec Dep</t>
   </si>
   <si>
-    <t>36 South_1_Wonder</t>
+    <t>Cancel Date</t>
+  </si>
+  <si>
+    <t>36 South_1_HDR HOLDINGS LLC D/B/A WONDER</t>
   </si>
   <si>
     <t>Original</t>
@@ -380,7 +407,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>36 South_2_Longo Architects</t>
+    <t>36 South_2_Longo Architects &amp; Associates, LLC</t>
   </si>
   <si>
     <t>36 South_3_Verizon</t>
@@ -389,7 +416,7 @@
     <t>36 South_3_Easement</t>
   </si>
   <si>
-    <t>15 South_1_Summit Health</t>
+    <t>15 South_1_CITY PROPERTY USA NJ, LLC</t>
   </si>
   <si>
     <t>15 South_2_Wells Fargo</t>
@@ -398,94 +425,67 @@
     <t>15 South_3_Easement</t>
   </si>
   <si>
-    <t>1280 Springfield_1_Georges Appliance</t>
+    <t>1280 Springfield_1_George's Appliance, LLC</t>
   </si>
   <si>
     <t>1280 Springfield_2_Juice House</t>
   </si>
   <si>
-    <t>1280 Springfield_3_Ksquared Air</t>
+    <t>1280 Springfield_3_Uppleside Down Wellness, LLC D/B/A Air</t>
   </si>
   <si>
-    <t>1280 Springfield_4_Your Kids Urgent Care</t>
+    <t>1280 Springfield_4_SLK Enterprises, LLC D/B/A AFC Urgent Care</t>
   </si>
   <si>
     <t>Option_3</t>
   </si>
   <si>
-    <t>1280 Springfield_5_Sana Yoga</t>
+    <t>1280 Springfield_5_Sana Yoga Studio, LLC</t>
+  </si>
+  <si>
+    <t>1280 Springfield_6_VACANT_6</t>
   </si>
   <si>
     <t>1280 Springfield_7_Alan DiEsso</t>
   </si>
   <si>
-    <t>114 Central_1_Nabig Sakr and Maria</t>
+    <t>114 Central_1_Nabig Sakr</t>
   </si>
   <si>
-    <t>114 Central_2_EJS Toybox</t>
+    <t>114 Central_2_EJS Westfield Toybox, LLC d/b/a Learning Express</t>
   </si>
   <si>
-    <t>114 Central_3_Reves Smoothie</t>
+    <t>114 Central_3_Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
   </si>
   <si>
-    <t>114 Central_4_GP Mobile</t>
+    <t>114 Central_4_Luna Wireless</t>
   </si>
   <si>
-    <t>114 Central_201_Ashford Schael</t>
+    <t>114 Central_201_Ashford - Schael, LLC</t>
   </si>
   <si>
-    <t>114 Central_203_Rentokil</t>
+    <t>114 Central_202_American Retail Shippers</t>
   </si>
   <si>
-    <t>114 Central_205_Jenny Madden_A</t>
-  </si>
-  <si>
-    <t>114 Central_209_Jenny Madden_B</t>
-  </si>
-  <si>
-    <t>114 Central_206_Dave Rossi</t>
-  </si>
-  <si>
-    <t>114 Central_207_Westfield Education</t>
-  </si>
-  <si>
-    <t>114 Central_208_SRD Captial</t>
-  </si>
-  <si>
-    <t>VACANT_204</t>
+    <t>114 Central_203_Rentokil North America dba Terminix</t>
   </si>
   <si>
     <t>114 Central_204_VACANT_204</t>
   </si>
   <si>
-    <t>Tang Pacific LLC</t>
+    <t>114 Central_205_Jenny Madden Design, LLC A</t>
   </si>
   <si>
-    <t>Annual Variable</t>
+    <t>114 Central_209_Jenny Madden Design, LLC B</t>
   </si>
   <si>
-    <t>One 1-Year</t>
+    <t>114 Central_206_Dave Rossi Photography, LLC</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>114 Central_207_Westfield Education Association</t>
   </si>
   <si>
-    <t>Yes; 2 years 90 day notice to Anniversayr</t>
-  </si>
-  <si>
-    <t>One-Two Year</t>
-  </si>
-  <si>
-    <t>VACANT_6</t>
-  </si>
-  <si>
-    <t>Cancel Date</t>
-  </si>
-  <si>
-    <t>1280 Springfield_6_VACANT_6</t>
-  </si>
-  <si>
-    <t>114 Central_202_Tang Pacific LLC</t>
+    <t>114 Central_208_SRD Capital Management, LLC</t>
   </si>
 </sst>
 </file>
@@ -658,6 +658,7 @@
     <xf numFmtId="44" fontId="0" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -668,7 +669,6 @@
     <xf numFmtId="44" fontId="2" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -1007,7 +1007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8947F0F2-180F-4DE0-A581-ACC631E7E8F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15774CFB-F4DC-488E-AFD7-E6B72E2613CD}">
   <dimension ref="A1:AD260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1686,7 +1686,7 @@
         <v>202</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>49</v>
@@ -1755,17 +1755,17 @@
         <v>46538</v>
       </c>
       <c r="Z16" s="19" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="AA16" s="17" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="AB16" s="20">
         <v>1</v>
       </c>
       <c r="AC16" s="20"/>
       <c r="AD16" s="17" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -1776,7 +1776,7 @@
         <v>203</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>49</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z17" s="19"/>
       <c r="AA17" s="23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AB17" s="20">
         <v>2</v>
@@ -1862,7 +1862,7 @@
         <v>204</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>49</v>
@@ -1922,13 +1922,13 @@
         <v>-10.571254319983737</v>
       </c>
       <c r="W18" s="17">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="X18" s="17">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="Y18" s="17">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="Z18" s="19"/>
       <c r="AA18" s="17"/>
@@ -1944,7 +1944,7 @@
         <v>205</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>49</v>
@@ -2030,7 +2030,7 @@
         <v>209</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>49</v>
@@ -2116,7 +2116,7 @@
         <v>206</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>49</v>
@@ -2185,7 +2185,7 @@
         <v>47968</v>
       </c>
       <c r="Z21" s="19" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="AA21" s="17">
         <v>46142</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="AC21" s="20"/>
       <c r="AD21" s="17" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -2206,7 +2206,7 @@
         <v>207</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>49</v>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z22" s="19"/>
       <c r="AA22" s="17" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="AB22" s="20">
         <v>1</v>
@@ -2292,7 +2292,7 @@
         <v>208</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>49</v>
@@ -2377,7 +2377,7 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>41</v>
@@ -2417,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G25" s="5">
         <v>4000</v>
@@ -2477,10 +2477,10 @@
         <v>49064</v>
       </c>
       <c r="Z25" s="24" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AA25" s="23" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AB25" s="20"/>
       <c r="AC25" s="20"/>
@@ -2494,16 +2494,16 @@
         <v>2</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E26" s="5">
         <v>1</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G26" s="5">
         <v>1</v>
@@ -2563,10 +2563,10 @@
         <v>47603</v>
       </c>
       <c r="Z26" s="24" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AA26" s="23" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AB26" s="20"/>
       <c r="AC26" s="20"/>
@@ -2580,16 +2580,16 @@
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E27" s="5">
         <v>1</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G27" s="5">
         <v>1</v>
@@ -2661,7 +2661,7 @@
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>41</v>
@@ -2705,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G29" s="5">
         <v>4064</v>
@@ -2768,7 +2768,7 @@
         <v>0.03</v>
       </c>
       <c r="AA29" s="23" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AB29" s="20">
         <v>0</v>
@@ -2786,7 +2786,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>49</v>
@@ -2795,7 +2795,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G30" s="5">
         <v>4199</v>
@@ -2858,7 +2858,7 @@
         <v>0.05</v>
       </c>
       <c r="AA30" s="23" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AB30" s="20">
         <v>1.9988242210464433</v>
@@ -2874,16 +2874,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E31" s="5">
         <v>3</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G31" s="5">
         <v>1</v>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="23" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AB31" s="20"/>
       <c r="AC31" s="20"/>
@@ -2960,16 +2960,16 @@
         <v>4</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E32" s="5">
         <v>3</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G32" s="5">
         <v>1</v>
@@ -3037,7 +3037,7 @@
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B33"/>
       <c r="F33" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J33" s="11"/>
       <c r="K33" s="8"/>
@@ -3056,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>41</v>
@@ -3065,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G34" s="5">
         <v>721</v>
@@ -3125,10 +3125,10 @@
         <v>46538</v>
       </c>
       <c r="Z34" s="24" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AA34" s="23" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="AB34" s="20">
         <v>3</v>
@@ -3144,7 +3144,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>41</v>
@@ -3153,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G35" s="5">
         <v>996</v>
@@ -3213,10 +3213,10 @@
         <v>46706</v>
       </c>
       <c r="Z35" s="24" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AA35" s="23" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="AB35" s="20">
         <v>2</v>
@@ -3232,7 +3232,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>41</v>
@@ -3241,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G36" s="5">
         <v>1533</v>
@@ -3301,10 +3301,10 @@
         <v>47299</v>
       </c>
       <c r="Z36" s="24" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AA36" s="23" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="AB36" s="20">
         <v>2</v>
@@ -3320,7 +3320,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>41</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G37" s="5">
         <v>2508</v>
@@ -3389,10 +3389,10 @@
         <v>47573</v>
       </c>
       <c r="Z37" s="24" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="23" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="AB37" s="20">
         <v>3</v>
@@ -3408,16 +3408,16 @@
         <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E38" s="5">
         <v>2</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G38" s="5">
         <v>1189</v>
@@ -3477,10 +3477,10 @@
         <v>46996</v>
       </c>
       <c r="Z38" s="24" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="AA38" s="23" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AB38" s="20">
         <v>3</v>
@@ -3496,16 +3496,16 @@
         <v>6</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E39" s="5">
         <v>2</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G39" s="5">
         <v>1286</v>
@@ -3565,10 +3565,10 @@
         <v>45626</v>
       </c>
       <c r="Z39" s="24" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="AA39" s="23" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="AB39" s="20">
         <v>0</v>
@@ -3586,16 +3586,16 @@
         <v>7</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E40" s="5">
         <v>2</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G40" s="5">
         <v>775</v>
@@ -3655,10 +3655,10 @@
         <v>45626</v>
       </c>
       <c r="Z40" s="24" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="AA40" s="23" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="AB40" s="20">
         <v>1.5</v>
@@ -3670,46 +3670,46 @@
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="N45" s="28" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="O45" s="28" t="s">
         <v>14</v>
@@ -3718,10 +3718,10 @@
         <v>27</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>32</v>
@@ -3736,12 +3736,12 @@
         <v>38</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
@@ -3750,10 +3750,10 @@
         <v>1</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>8</v>
@@ -3819,10 +3819,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F47" s="5">
         <v>1</v>
@@ -3879,7 +3879,7 @@
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>8</v>
@@ -3888,10 +3888,10 @@
         <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F48" s="5">
         <v>2</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>8</v>
@@ -3957,10 +3957,10 @@
         <v>1</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F49" s="5">
         <v>3</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>8</v>
@@ -4026,10 +4026,10 @@
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F50" s="5">
         <v>4</v>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>8</v>
@@ -4095,10 +4095,10 @@
         <v>1</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F51" s="5">
         <v>5</v>
@@ -4155,7 +4155,7 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>8</v>
@@ -4164,10 +4164,10 @@
         <v>1</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F52" s="5">
         <v>6</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>8</v>
@@ -4233,10 +4233,10 @@
         <v>1</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F53" s="5">
         <v>7</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>8</v>
@@ -4302,10 +4302,10 @@
         <v>1</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F54" s="5">
         <v>8</v>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>8</v>
@@ -4371,10 +4371,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F55" s="5">
         <v>9</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>8</v>
@@ -4440,10 +4440,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F56" s="5">
         <v>10</v>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>8</v>
@@ -4509,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E57" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F57" s="30">
         <v>11</v>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B58" s="30" t="s">
         <v>8</v>
@@ -4578,10 +4578,10 @@
         <v>1</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F58" s="30">
         <v>12</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B59" s="30" t="s">
         <v>8</v>
@@ -4647,10 +4647,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E59" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F59" s="30">
         <v>13</v>
@@ -4707,7 +4707,7 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B60" s="30" t="s">
         <v>8</v>
@@ -4716,10 +4716,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E60" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F60" s="30">
         <v>14</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B61" s="30" t="s">
         <v>8</v>
@@ -4785,10 +4785,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F61" s="30">
         <v>15</v>
@@ -4845,7 +4845,7 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="35" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B62" s="35" t="s">
         <v>8</v>
@@ -4854,10 +4854,10 @@
         <v>1</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F62" s="35">
         <v>16</v>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="35" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B63" s="35" t="s">
         <v>8</v>
@@ -4923,10 +4923,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E63" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F63" s="35">
         <v>17</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="35" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B64" s="35" t="s">
         <v>8</v>
@@ -4992,10 +4992,10 @@
         <v>1</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E64" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F64" s="35">
         <v>18</v>
@@ -5052,7 +5052,7 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="35" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B65" s="35" t="s">
         <v>8</v>
@@ -5061,10 +5061,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E65" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F65" s="35">
         <v>19</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="35" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B66" s="35" t="s">
         <v>8</v>
@@ -5130,10 +5130,10 @@
         <v>1</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E66" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F66" s="35">
         <v>20</v>
@@ -5190,76 +5190,76 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V67" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W67" s="40"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>8</v>
@@ -5268,10 +5268,10 @@
         <v>2</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F68" s="5">
         <v>1</v>
@@ -5309,7 +5309,7 @@
       <c r="Q68" s="14">
         <v>25.077399380804952</v>
       </c>
-      <c r="R68" s="51">
+      <c r="R68" s="41">
         <v>17000</v>
       </c>
       <c r="S68" s="29">
@@ -5328,7 +5328,7 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>8</v>
@@ -5337,10 +5337,10 @@
         <v>2</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F69" s="5">
         <v>2</v>
@@ -5378,7 +5378,7 @@
       <c r="Q69" s="14">
         <v>26.43486544415337</v>
       </c>
-      <c r="R69" s="51">
+      <c r="R69" s="41">
         <v>17000</v>
       </c>
       <c r="S69" s="17">
@@ -5397,7 +5397,7 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>8</v>
@@ -5406,10 +5406,10 @@
         <v>2</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F70" s="5">
         <v>3</v>
@@ -5447,7 +5447,7 @@
       <c r="Q70" s="14">
         <v>27.75660871636104</v>
       </c>
-      <c r="R70" s="51">
+      <c r="R70" s="41">
         <v>17000</v>
       </c>
       <c r="S70" s="17">
@@ -5466,7 +5466,7 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>8</v>
@@ -5475,10 +5475,10 @@
         <v>2</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F71" s="5">
         <v>4</v>
@@ -5516,7 +5516,7 @@
       <c r="Q71" s="14">
         <v>29.144439152179089</v>
       </c>
-      <c r="R71" s="51">
+      <c r="R71" s="41">
         <v>17000</v>
       </c>
       <c r="S71" s="17">
@@ -5535,76 +5535,76 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V72" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W72" s="40"/>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>8</v>
@@ -5613,10 +5613,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F73" s="5">
         <v>1</v>
@@ -5633,7 +5633,7 @@
       <c r="J73" s="14">
         <v>808.9375</v>
       </c>
-      <c r="K73" s="41">
+      <c r="K73" s="42">
         <v>9707.25</v>
       </c>
       <c r="L73" s="5" t="s">
@@ -5673,7 +5673,7 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>8</v>
@@ -5682,10 +5682,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F74" s="5">
         <v>2</v>
@@ -5742,7 +5742,7 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>8</v>
@@ -5751,10 +5751,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F75" s="5">
         <v>3</v>
@@ -5811,7 +5811,7 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>8</v>
@@ -5820,10 +5820,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F76" s="5">
         <v>4</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>8</v>
@@ -5889,10 +5889,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F77" s="5">
         <v>5</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>8</v>
@@ -5958,10 +5958,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F78" s="5">
         <v>6</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>8</v>
@@ -6027,10 +6027,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F79" s="5">
         <v>7</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>8</v>
@@ -6096,10 +6096,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F80" s="5">
         <v>8</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>8</v>
@@ -6165,10 +6165,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F81" s="5">
         <v>9</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>8</v>
@@ -6234,10 +6234,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F82" s="5">
         <v>10</v>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>8</v>
@@ -6303,10 +6303,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F83" s="5">
         <v>11</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>8</v>
@@ -6372,10 +6372,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F84" s="5">
         <v>12</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>8</v>
@@ -6441,10 +6441,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F85" s="5">
         <v>13</v>
@@ -6501,7 +6501,7 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>8</v>
@@ -6510,10 +6510,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F86" s="5">
         <v>14</v>
@@ -6570,76 +6570,76 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V87" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W87" s="40"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>8</v>
@@ -6648,10 +6648,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F88" s="5">
         <v>1</v>
@@ -6668,7 +6668,7 @@
       <c r="J88" s="14">
         <v>0</v>
       </c>
-      <c r="K88" s="41">
+      <c r="K88" s="42">
         <v>0</v>
       </c>
       <c r="L88" s="5" t="s">
@@ -6708,7 +6708,7 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>8</v>
@@ -6717,10 +6717,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F89" s="5">
         <v>2</v>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>8</v>
@@ -6786,10 +6786,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F90" s="5">
         <v>3</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>8</v>
@@ -6855,10 +6855,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F91" s="5">
         <v>4</v>
@@ -6915,7 +6915,7 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>8</v>
@@ -6924,10 +6924,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F92" s="5">
         <v>5</v>
@@ -6984,7 +6984,7 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>8</v>
@@ -6993,10 +6993,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F93" s="5">
         <v>6</v>
@@ -7053,7 +7053,7 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>8</v>
@@ -7062,10 +7062,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F94" s="5">
         <v>7</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>8</v>
@@ -7131,10 +7131,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F95" s="5">
         <v>8</v>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>8</v>
@@ -7200,10 +7200,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F96" s="5">
         <v>9</v>
@@ -7260,7 +7260,7 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>8</v>
@@ -7269,10 +7269,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F97" s="5">
         <v>10</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>8</v>
@@ -7338,10 +7338,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F98" s="5">
         <v>11</v>
@@ -7398,76 +7398,76 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V99" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W99" s="40"/>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
@@ -7476,10 +7476,10 @@
         <v>1</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F100" s="5">
         <v>1</v>
@@ -7496,7 +7496,7 @@
       <c r="J100" s="14">
         <v>15833.339999999998</v>
       </c>
-      <c r="K100" s="41">
+      <c r="K100" s="42">
         <v>190000.08</v>
       </c>
       <c r="L100" s="5" t="s">
@@ -7536,7 +7536,7 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
@@ -7545,10 +7545,10 @@
         <v>1</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F101" s="5">
         <v>2</v>
@@ -7605,7 +7605,7 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
@@ -7614,10 +7614,10 @@
         <v>1</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F102" s="5">
         <v>3</v>
@@ -7674,7 +7674,7 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
@@ -7683,10 +7683,10 @@
         <v>1</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F103" s="5">
         <v>4</v>
@@ -7743,7 +7743,7 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>7</v>
@@ -7752,10 +7752,10 @@
         <v>1</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F104" s="5">
         <v>5</v>
@@ -7812,7 +7812,7 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>7</v>
@@ -7821,10 +7821,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F105" s="5">
         <v>6</v>
@@ -7881,7 +7881,7 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>7</v>
@@ -7890,10 +7890,10 @@
         <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F106" s="5">
         <v>7</v>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>7</v>
@@ -7959,10 +7959,10 @@
         <v>1</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F107" s="5">
         <v>8</v>
@@ -8019,7 +8019,7 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>7</v>
@@ -8028,10 +8028,10 @@
         <v>1</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F108" s="5">
         <v>9</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>1</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F109" s="5">
         <v>10</v>
@@ -8157,7 +8157,7 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="30" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B110" s="30" t="s">
         <v>7</v>
@@ -8166,10 +8166,10 @@
         <v>1</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E110" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F110" s="30">
         <v>11</v>
@@ -8226,7 +8226,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="30" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B111" s="30" t="s">
         <v>7</v>
@@ -8235,10 +8235,10 @@
         <v>1</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E111" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F111" s="30">
         <v>12</v>
@@ -8295,7 +8295,7 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="30" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B112" s="30" t="s">
         <v>7</v>
@@ -8304,10 +8304,10 @@
         <v>1</v>
       </c>
       <c r="D112" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E112" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F112" s="30">
         <v>13</v>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="30" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B113" s="30" t="s">
         <v>7</v>
@@ -8373,10 +8373,10 @@
         <v>1</v>
       </c>
       <c r="D113" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E113" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F113" s="30">
         <v>14</v>
@@ -8433,7 +8433,7 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="30" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B114" s="30" t="s">
         <v>7</v>
@@ -8442,10 +8442,10 @@
         <v>1</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E114" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F114" s="30">
         <v>15</v>
@@ -8502,76 +8502,76 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V115" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W115" s="40"/>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>7</v>
@@ -8580,10 +8580,10 @@
         <v>2</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F116" s="5">
         <v>1</v>
@@ -8600,7 +8600,7 @@
       <c r="J116" s="14">
         <v>2600</v>
       </c>
-      <c r="K116" s="41">
+      <c r="K116" s="42">
         <v>31200</v>
       </c>
       <c r="L116" s="5" t="s">
@@ -8640,7 +8640,7 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>7</v>
@@ -8649,10 +8649,10 @@
         <v>2</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F117" s="5">
         <v>2</v>
@@ -8709,7 +8709,7 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>7</v>
@@ -8718,10 +8718,10 @@
         <v>2</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F118" s="5">
         <v>3</v>
@@ -8778,7 +8778,7 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>7</v>
@@ -8787,10 +8787,10 @@
         <v>2</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F119" s="5">
         <v>4</v>
@@ -8847,7 +8847,7 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>7</v>
@@ -8856,10 +8856,10 @@
         <v>2</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F120" s="5">
         <v>5</v>
@@ -8916,7 +8916,7 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="30" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B121" s="30" t="s">
         <v>7</v>
@@ -8925,10 +8925,10 @@
         <v>2</v>
       </c>
       <c r="D121" s="30" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E121" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F121" s="30">
         <v>6</v>
@@ -8985,7 +8985,7 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="30" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B122" s="30" t="s">
         <v>7</v>
@@ -8994,10 +8994,10 @@
         <v>2</v>
       </c>
       <c r="D122" s="30" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E122" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F122" s="30">
         <v>7</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="30" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B123" s="30" t="s">
         <v>7</v>
@@ -9063,10 +9063,10 @@
         <v>2</v>
       </c>
       <c r="D123" s="30" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E123" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F123" s="30">
         <v>8</v>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="30" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B124" s="30" t="s">
         <v>7</v>
@@ -9132,10 +9132,10 @@
         <v>2</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E124" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F124" s="30">
         <v>9</v>
@@ -9192,7 +9192,7 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="30" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B125" s="30" t="s">
         <v>7</v>
@@ -9201,10 +9201,10 @@
         <v>2</v>
       </c>
       <c r="D125" s="30" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E125" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F125" s="30">
         <v>10</v>
@@ -9261,76 +9261,76 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V126" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W126" s="40"/>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>7</v>
@@ -9339,10 +9339,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F127" s="5">
         <v>1</v>
@@ -9359,7 +9359,7 @@
       <c r="J127" s="14">
         <v>0</v>
       </c>
-      <c r="K127" s="41">
+      <c r="K127" s="42">
         <v>0</v>
       </c>
       <c r="L127" s="5" t="s">
@@ -9399,7 +9399,7 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>7</v>
@@ -9408,10 +9408,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F128" s="5">
         <v>2</v>
@@ -9468,7 +9468,7 @@
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>7</v>
@@ -9477,10 +9477,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F129" s="5">
         <v>3</v>
@@ -9537,7 +9537,7 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>7</v>
@@ -9546,10 +9546,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F130" s="5">
         <v>4</v>
@@ -9606,7 +9606,7 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>7</v>
@@ -9615,10 +9615,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F131" s="5">
         <v>5</v>
@@ -9675,7 +9675,7 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>7</v>
@@ -9684,10 +9684,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F132" s="5">
         <v>6</v>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>7</v>
@@ -9753,10 +9753,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F133" s="5">
         <v>7</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>7</v>
@@ -9822,10 +9822,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F134" s="5">
         <v>8</v>
@@ -9882,7 +9882,7 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>7</v>
@@ -9891,10 +9891,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F135" s="5">
         <v>9</v>
@@ -9951,7 +9951,7 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>7</v>
@@ -9960,10 +9960,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F136" s="5">
         <v>10</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>7</v>
@@ -10029,10 +10029,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F137" s="5">
         <v>11</v>
@@ -10089,76 +10089,76 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V138" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W138" s="40"/>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>9</v>
@@ -10167,10 +10167,10 @@
         <v>1</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F139" s="5">
         <v>1</v>
@@ -10187,7 +10187,7 @@
       <c r="J139" s="14">
         <v>2485.19</v>
       </c>
-      <c r="K139" s="41">
+      <c r="K139" s="42">
         <v>29822.28</v>
       </c>
       <c r="L139" s="5" t="s">
@@ -10227,7 +10227,7 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>9</v>
@@ -10236,10 +10236,10 @@
         <v>1</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F140" s="5">
         <v>2</v>
@@ -10256,7 +10256,7 @@
       <c r="J140" s="14">
         <v>2559.75</v>
       </c>
-      <c r="K140" s="41">
+      <c r="K140" s="42">
         <v>30717</v>
       </c>
       <c r="L140" s="5" t="s">
@@ -10296,7 +10296,7 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>9</v>
@@ -10305,10 +10305,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F141" s="5">
         <v>3</v>
@@ -10325,7 +10325,7 @@
       <c r="J141" s="14">
         <v>2636.54</v>
       </c>
-      <c r="K141" s="41">
+      <c r="K141" s="42">
         <v>31638.48</v>
       </c>
       <c r="L141" s="5" t="s">
@@ -10365,7 +10365,7 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>9</v>
@@ -10374,10 +10374,10 @@
         <v>1</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F142" s="5">
         <v>4</v>
@@ -10394,7 +10394,7 @@
       <c r="J142" s="14">
         <v>2715.64</v>
       </c>
-      <c r="K142" s="41">
+      <c r="K142" s="42">
         <v>32587.68</v>
       </c>
       <c r="L142" s="5" t="s">
@@ -10434,7 +10434,7 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>9</v>
@@ -10443,10 +10443,10 @@
         <v>1</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F143" s="5">
         <v>5</v>
@@ -10463,7 +10463,7 @@
       <c r="J143" s="14">
         <v>2797.11</v>
       </c>
-      <c r="K143" s="41">
+      <c r="K143" s="42">
         <v>33565.32</v>
       </c>
       <c r="L143" s="5" t="s">
@@ -10503,76 +10503,76 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V144" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W144" s="40"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>9</v>
@@ -10581,10 +10581,10 @@
         <v>2</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F145" s="5">
         <v>1</v>
@@ -10601,7 +10601,7 @@
       <c r="J145" s="14">
         <v>3812.47</v>
       </c>
-      <c r="K145" s="41">
+      <c r="K145" s="42">
         <v>45749.64</v>
       </c>
       <c r="L145" s="5" t="s">
@@ -10641,7 +10641,7 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>9</v>
@@ -10650,10 +10650,10 @@
         <v>2</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F146" s="5">
         <v>2</v>
@@ -10670,7 +10670,7 @@
       <c r="J146" s="14">
         <v>3945.91</v>
       </c>
-      <c r="K146" s="41">
+      <c r="K146" s="42">
         <v>47350.92</v>
       </c>
       <c r="L146" s="5" t="s">
@@ -10710,7 +10710,7 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>9</v>
@@ -10719,10 +10719,10 @@
         <v>2</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F147" s="5">
         <v>3</v>
@@ -10739,7 +10739,7 @@
       <c r="J147" s="14">
         <v>4084.02</v>
       </c>
-      <c r="K147" s="41">
+      <c r="K147" s="42">
         <v>49008.24</v>
       </c>
       <c r="L147" s="5" t="s">
@@ -10779,7 +10779,7 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>9</v>
@@ -10788,10 +10788,10 @@
         <v>2</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F148" s="5">
         <v>4</v>
@@ -10808,7 +10808,7 @@
       <c r="J148" s="14">
         <v>4226.96</v>
       </c>
-      <c r="K148" s="41">
+      <c r="K148" s="42">
         <v>50723.519999999997</v>
       </c>
       <c r="L148" s="5" t="s">
@@ -10848,7 +10848,7 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>9</v>
@@ -10857,10 +10857,10 @@
         <v>2</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F149" s="5">
         <v>5</v>
@@ -10877,7 +10877,7 @@
       <c r="J149" s="14">
         <v>1841.77</v>
       </c>
-      <c r="K149" s="41"/>
+      <c r="K149" s="42"/>
       <c r="L149" s="5" t="s">
         <v>43</v>
       </c>
@@ -10915,76 +10915,76 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V150" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W150" s="40"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>9</v>
@@ -10993,10 +10993,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F151" s="5">
         <v>1</v>
@@ -11013,7 +11013,7 @@
       <c r="J151" s="14">
         <v>4000</v>
       </c>
-      <c r="K151" s="41">
+      <c r="K151" s="42">
         <v>48000</v>
       </c>
       <c r="L151" s="5" t="s">
@@ -11053,7 +11053,7 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>9</v>
@@ -11062,10 +11062,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F152" s="5">
         <v>2</v>
@@ -11082,7 +11082,7 @@
       <c r="J152" s="14">
         <v>4120</v>
       </c>
-      <c r="K152" s="41">
+      <c r="K152" s="42">
         <v>49440</v>
       </c>
       <c r="L152" s="5" t="s">
@@ -11122,7 +11122,7 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>9</v>
@@ -11131,10 +11131,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F153" s="5">
         <v>3</v>
@@ -11151,7 +11151,7 @@
       <c r="J153" s="14">
         <v>4243.5999999999995</v>
       </c>
-      <c r="K153" s="41">
+      <c r="K153" s="42">
         <v>50923.199999999997</v>
       </c>
       <c r="L153" s="5" t="s">
@@ -11191,7 +11191,7 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>9</v>
@@ -11200,10 +11200,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F154" s="5">
         <v>4</v>
@@ -11220,7 +11220,7 @@
       <c r="J154" s="14">
         <v>4370.9083333333338</v>
       </c>
-      <c r="K154" s="41">
+      <c r="K154" s="42">
         <v>52450.9</v>
       </c>
       <c r="L154" s="5" t="s">
@@ -11260,7 +11260,7 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>9</v>
@@ -11269,10 +11269,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F155" s="5">
         <v>5</v>
@@ -11289,7 +11289,7 @@
       <c r="J155" s="14">
         <v>4502.0349999999999</v>
       </c>
-      <c r="K155" s="41">
+      <c r="K155" s="42">
         <v>54024.42</v>
       </c>
       <c r="L155" s="5" t="s">
@@ -11329,76 +11329,76 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V156" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W156" s="40"/>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>9</v>
@@ -11407,10 +11407,10 @@
         <v>4</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F157" s="5">
         <v>1</v>
@@ -11427,7 +11427,7 @@
       <c r="J157" s="14">
         <v>7942</v>
       </c>
-      <c r="K157" s="41">
+      <c r="K157" s="42">
         <v>95304</v>
       </c>
       <c r="L157" s="5" t="s">
@@ -11467,7 +11467,7 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>9</v>
@@ -11476,10 +11476,10 @@
         <v>4</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F158" s="5">
         <v>2</v>
@@ -11496,7 +11496,7 @@
       <c r="J158" s="14">
         <v>8100.84</v>
       </c>
-      <c r="K158" s="41">
+      <c r="K158" s="42">
         <v>97210.08</v>
       </c>
       <c r="L158" s="5" t="s">
@@ -11536,7 +11536,7 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>9</v>
@@ -11545,10 +11545,10 @@
         <v>4</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F159" s="5">
         <v>3</v>
@@ -11565,7 +11565,7 @@
       <c r="J159" s="14">
         <v>8262.8566666666666</v>
       </c>
-      <c r="K159" s="41">
+      <c r="K159" s="42">
         <v>99154.28</v>
       </c>
       <c r="L159" s="5" t="s">
@@ -11605,7 +11605,7 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>9</v>
@@ -11614,10 +11614,10 @@
         <v>4</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F160" s="5">
         <v>4</v>
@@ -11634,7 +11634,7 @@
       <c r="J160" s="14">
         <v>8428.1141666666663</v>
       </c>
-      <c r="K160" s="41">
+      <c r="K160" s="42">
         <v>101137.37</v>
       </c>
       <c r="L160" s="5" t="s">
@@ -11674,7 +11674,7 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>9</v>
@@ -11683,10 +11683,10 @@
         <v>4</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F161" s="5">
         <v>5</v>
@@ -11703,7 +11703,7 @@
       <c r="J161" s="14">
         <v>8596.6766666666663</v>
       </c>
-      <c r="K161" s="41">
+      <c r="K161" s="42">
         <v>103160.12</v>
       </c>
       <c r="L161" s="5" t="s">
@@ -11743,7 +11743,7 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>9</v>
@@ -11752,10 +11752,10 @@
         <v>4</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F162" s="5">
         <v>6</v>
@@ -11772,7 +11772,7 @@
       <c r="J162" s="14">
         <v>8768.61</v>
       </c>
-      <c r="K162" s="41">
+      <c r="K162" s="42">
         <v>105223.32</v>
       </c>
       <c r="L162" s="5" t="s">
@@ -11812,7 +11812,7 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>9</v>
@@ -11821,10 +11821,10 @@
         <v>4</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F163" s="5">
         <v>7</v>
@@ -11841,7 +11841,7 @@
       <c r="J163" s="14">
         <v>8943.9825000000001</v>
       </c>
-      <c r="K163" s="41">
+      <c r="K163" s="42">
         <v>107327.79</v>
       </c>
       <c r="L163" s="5" t="s">
@@ -11881,7 +11881,7 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>9</v>
@@ -11890,10 +11890,10 @@
         <v>4</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F164" s="5">
         <v>8</v>
@@ -11910,7 +11910,7 @@
       <c r="J164" s="14">
         <v>9122.8625000000011</v>
       </c>
-      <c r="K164" s="41">
+      <c r="K164" s="42">
         <v>109474.35</v>
       </c>
       <c r="L164" s="5" t="s">
@@ -11950,7 +11950,7 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>9</v>
@@ -11959,10 +11959,10 @@
         <v>4</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F165" s="5">
         <v>9</v>
@@ -11979,7 +11979,7 @@
       <c r="J165" s="14">
         <v>9305.3191666666662</v>
       </c>
-      <c r="K165" s="41">
+      <c r="K165" s="42">
         <v>111663.83</v>
       </c>
       <c r="L165" s="5" t="s">
@@ -12019,7 +12019,7 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>9</v>
@@ -12028,10 +12028,10 @@
         <v>4</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F166" s="5">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       <c r="J166" s="14">
         <v>9491.4258333333328</v>
       </c>
-      <c r="K166" s="41">
+      <c r="K166" s="42">
         <v>113897.11</v>
       </c>
       <c r="L166" s="5" t="s">
@@ -12088,7 +12088,7 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="30" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B167" s="30" t="s">
         <v>9</v>
@@ -12097,10 +12097,10 @@
         <v>4</v>
       </c>
       <c r="D167" s="30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F167" s="30">
         <v>11</v>
@@ -12117,7 +12117,7 @@
       <c r="J167" s="33">
         <v>9681.25</v>
       </c>
-      <c r="K167" s="42">
+      <c r="K167" s="43">
         <v>116175</v>
       </c>
       <c r="L167" s="30" t="s">
@@ -12157,7 +12157,7 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" s="30" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B168" s="30" t="s">
         <v>9</v>
@@ -12166,10 +12166,10 @@
         <v>4</v>
       </c>
       <c r="D168" s="30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F168" s="30">
         <v>12</v>
@@ -12186,7 +12186,7 @@
       <c r="J168" s="33">
         <v>9874.8700000000008</v>
       </c>
-      <c r="K168" s="42">
+      <c r="K168" s="43">
         <v>118498.44</v>
       </c>
       <c r="L168" s="30" t="s">
@@ -12226,7 +12226,7 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="30" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B169" s="30" t="s">
         <v>9</v>
@@ -12235,10 +12235,10 @@
         <v>4</v>
       </c>
       <c r="D169" s="30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F169" s="30">
         <v>13</v>
@@ -12255,7 +12255,7 @@
       <c r="J169" s="33">
         <v>10072.370000000001</v>
       </c>
-      <c r="K169" s="42">
+      <c r="K169" s="43">
         <v>120868.44</v>
       </c>
       <c r="L169" s="30" t="s">
@@ -12295,7 +12295,7 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" s="30" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B170" s="30" t="s">
         <v>9</v>
@@ -12304,10 +12304,10 @@
         <v>4</v>
       </c>
       <c r="D170" s="30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F170" s="30">
         <v>14</v>
@@ -12324,7 +12324,7 @@
       <c r="J170" s="33">
         <v>10273.82</v>
       </c>
-      <c r="K170" s="42">
+      <c r="K170" s="43">
         <v>123285.84</v>
       </c>
       <c r="L170" s="30" t="s">
@@ -12364,7 +12364,7 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" s="30" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B171" s="30" t="s">
         <v>9</v>
@@ -12373,10 +12373,10 @@
         <v>4</v>
       </c>
       <c r="D171" s="30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F171" s="30">
         <v>15</v>
@@ -12393,7 +12393,7 @@
       <c r="J171" s="33">
         <v>10479.289999999999</v>
       </c>
-      <c r="K171" s="42">
+      <c r="K171" s="43">
         <v>125751.48</v>
       </c>
       <c r="L171" s="30" t="s">
@@ -12433,7 +12433,7 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="35" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B172" s="35" t="s">
         <v>9</v>
@@ -12442,10 +12442,10 @@
         <v>4</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E172" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F172" s="35">
         <v>16</v>
@@ -12462,7 +12462,7 @@
       <c r="J172" s="38">
         <v>10688.88</v>
       </c>
-      <c r="K172" s="43">
+      <c r="K172" s="44">
         <v>128266.56</v>
       </c>
       <c r="L172" s="35" t="s">
@@ -12502,7 +12502,7 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" s="35" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B173" s="35" t="s">
         <v>9</v>
@@ -12511,10 +12511,10 @@
         <v>4</v>
       </c>
       <c r="D173" s="35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E173" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F173" s="35">
         <v>17</v>
@@ -12531,7 +12531,7 @@
       <c r="J173" s="38">
         <v>10902.66</v>
       </c>
-      <c r="K173" s="43">
+      <c r="K173" s="44">
         <v>130831.92</v>
       </c>
       <c r="L173" s="35" t="s">
@@ -12571,7 +12571,7 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" s="35" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B174" s="35" t="s">
         <v>9</v>
@@ -12580,10 +12580,10 @@
         <v>4</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E174" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F174" s="35">
         <v>18</v>
@@ -12600,7 +12600,7 @@
       <c r="J174" s="38">
         <v>11120.71</v>
       </c>
-      <c r="K174" s="43">
+      <c r="K174" s="44">
         <v>133448.51999999999</v>
       </c>
       <c r="L174" s="35" t="s">
@@ -12640,7 +12640,7 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" s="35" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B175" s="35" t="s">
         <v>9</v>
@@ -12649,10 +12649,10 @@
         <v>4</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E175" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F175" s="35">
         <v>19</v>
@@ -12669,7 +12669,7 @@
       <c r="J175" s="38">
         <v>11343.13</v>
       </c>
-      <c r="K175" s="43">
+      <c r="K175" s="44">
         <v>136117.56</v>
       </c>
       <c r="L175" s="35" t="s">
@@ -12709,7 +12709,7 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="35" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B176" s="35" t="s">
         <v>9</v>
@@ -12718,10 +12718,10 @@
         <v>4</v>
       </c>
       <c r="D176" s="35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E176" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F176" s="35">
         <v>20</v>
@@ -12738,7 +12738,7 @@
       <c r="J176" s="38">
         <v>11569.99</v>
       </c>
-      <c r="K176" s="43">
+      <c r="K176" s="44">
         <v>138839.88</v>
       </c>
       <c r="L176" s="35" t="s">
@@ -12777,422 +12777,422 @@
       <c r="W176" s="38"/>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A177" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="B177" s="44" t="s">
+      <c r="A177" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B177" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C177" s="44">
+      <c r="C177" s="45">
         <v>4</v>
       </c>
-      <c r="D177" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E177" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="F177" s="44">
+      <c r="D177" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E177" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F177" s="45">
         <v>21</v>
       </c>
-      <c r="G177" s="45">
+      <c r="G177" s="46">
         <v>51227</v>
       </c>
-      <c r="H177" s="45">
+      <c r="H177" s="46">
         <v>51591</v>
       </c>
-      <c r="I177" s="46">
+      <c r="I177" s="47">
         <v>2.0000017286099459E-2</v>
       </c>
-      <c r="J177" s="47">
+      <c r="J177" s="48">
         <v>11801.39</v>
       </c>
-      <c r="K177" s="48">
+      <c r="K177" s="49">
         <v>141616.68</v>
       </c>
-      <c r="L177" s="44" t="s">
+      <c r="L177" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="M177" s="49">
+      <c r="M177" s="50">
         <v>2508</v>
       </c>
-      <c r="N177" s="46">
+      <c r="N177" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O177" s="46">
+      <c r="O177" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P177" s="46">
+      <c r="P177" s="47">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q177" s="47">
+      <c r="Q177" s="48">
         <v>56.465980861244013</v>
       </c>
-      <c r="R177" s="47">
+      <c r="R177" s="48">
         <v>35404.17</v>
       </c>
-      <c r="S177" s="45">
+      <c r="S177" s="46">
         <v>43866</v>
       </c>
-      <c r="T177" s="45">
+      <c r="T177" s="46">
         <v>44044</v>
       </c>
       <c r="U177" s="29">
         <v>47573</v>
       </c>
-      <c r="V177" s="47">
-        <v>0</v>
-      </c>
-      <c r="W177" s="47"/>
+      <c r="V177" s="48">
+        <v>0</v>
+      </c>
+      <c r="W177" s="48"/>
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A178" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="B178" s="44" t="s">
+      <c r="A178" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B178" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C178" s="44">
+      <c r="C178" s="45">
         <v>4</v>
       </c>
-      <c r="D178" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E178" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="F178" s="44">
+      <c r="D178" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E178" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F178" s="45">
         <v>22</v>
       </c>
-      <c r="G178" s="45">
+      <c r="G178" s="46">
         <v>51592</v>
       </c>
-      <c r="H178" s="45">
+      <c r="H178" s="46">
         <v>51956</v>
       </c>
-      <c r="I178" s="46">
+      <c r="I178" s="47">
         <v>2.000018641871848E-2</v>
       </c>
-      <c r="J178" s="47">
+      <c r="J178" s="48">
         <v>12037.42</v>
       </c>
-      <c r="K178" s="48">
+      <c r="K178" s="49">
         <v>144449.04</v>
       </c>
-      <c r="L178" s="44" t="s">
+      <c r="L178" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="M178" s="49">
+      <c r="M178" s="50">
         <v>2508</v>
       </c>
-      <c r="N178" s="46">
+      <c r="N178" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O178" s="46">
+      <c r="O178" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P178" s="46">
+      <c r="P178" s="47">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q178" s="47">
+      <c r="Q178" s="48">
         <v>57.595311004784691</v>
       </c>
-      <c r="R178" s="47">
+      <c r="R178" s="48">
         <v>36112.26</v>
       </c>
-      <c r="S178" s="45">
+      <c r="S178" s="46">
         <v>43866</v>
       </c>
-      <c r="T178" s="45">
+      <c r="T178" s="46">
         <v>44044</v>
       </c>
       <c r="U178" s="29">
         <v>47573</v>
       </c>
-      <c r="V178" s="47">
-        <v>0</v>
-      </c>
-      <c r="W178" s="47"/>
+      <c r="V178" s="48">
+        <v>0</v>
+      </c>
+      <c r="W178" s="48"/>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A179" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="B179" s="44" t="s">
+      <c r="A179" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B179" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C179" s="44">
+      <c r="C179" s="45">
         <v>4</v>
       </c>
-      <c r="D179" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E179" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="F179" s="44">
+      <c r="D179" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E179" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F179" s="45">
         <v>23</v>
       </c>
-      <c r="G179" s="45">
+      <c r="G179" s="46">
         <v>51957</v>
       </c>
-      <c r="H179" s="45">
+      <c r="H179" s="46">
         <v>52321</v>
       </c>
-      <c r="I179" s="46">
+      <c r="I179" s="47">
         <v>1.9999302176047618E-2</v>
       </c>
-      <c r="J179" s="47">
+      <c r="J179" s="48">
         <v>12278.160000000002</v>
       </c>
-      <c r="K179" s="48">
+      <c r="K179" s="49">
         <v>147337.92000000001</v>
       </c>
-      <c r="L179" s="44" t="s">
+      <c r="L179" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="M179" s="49">
+      <c r="M179" s="50">
         <v>2508</v>
       </c>
-      <c r="N179" s="46">
+      <c r="N179" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O179" s="46">
+      <c r="O179" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P179" s="46">
+      <c r="P179" s="47">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q179" s="47">
+      <c r="Q179" s="48">
         <v>58.747177033492825</v>
       </c>
-      <c r="R179" s="47">
+      <c r="R179" s="48">
         <v>36834.480000000003</v>
       </c>
-      <c r="S179" s="45">
+      <c r="S179" s="46">
         <v>43866</v>
       </c>
-      <c r="T179" s="45">
+      <c r="T179" s="46">
         <v>44044</v>
       </c>
       <c r="U179" s="29">
         <v>47573</v>
       </c>
-      <c r="V179" s="47">
-        <v>0</v>
-      </c>
-      <c r="W179" s="47"/>
+      <c r="V179" s="48">
+        <v>0</v>
+      </c>
+      <c r="W179" s="48"/>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A180" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="B180" s="44" t="s">
+      <c r="A180" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B180" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C180" s="44">
+      <c r="C180" s="45">
         <v>4</v>
       </c>
-      <c r="D180" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E180" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="F180" s="44">
+      <c r="D180" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E180" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F180" s="45">
         <v>24</v>
       </c>
-      <c r="G180" s="45">
+      <c r="G180" s="46">
         <v>52322</v>
       </c>
-      <c r="H180" s="45">
+      <c r="H180" s="46">
         <v>52687</v>
       </c>
-      <c r="I180" s="46">
+      <c r="I180" s="47">
         <v>1.9999739374629399E-2</v>
       </c>
-      <c r="J180" s="47">
+      <c r="J180" s="48">
         <v>12523.720000000001</v>
       </c>
-      <c r="K180" s="48">
+      <c r="K180" s="49">
         <v>150284.64000000001</v>
       </c>
-      <c r="L180" s="44" t="s">
+      <c r="L180" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="M180" s="49">
+      <c r="M180" s="50">
         <v>2508</v>
       </c>
-      <c r="N180" s="46">
+      <c r="N180" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O180" s="46">
+      <c r="O180" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P180" s="46">
+      <c r="P180" s="47">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q180" s="47">
+      <c r="Q180" s="48">
         <v>59.922105263157903</v>
       </c>
-      <c r="R180" s="47">
+      <c r="R180" s="48">
         <v>37571.160000000003</v>
       </c>
-      <c r="S180" s="45">
+      <c r="S180" s="46">
         <v>43866</v>
       </c>
-      <c r="T180" s="45">
+      <c r="T180" s="46">
         <v>44044</v>
       </c>
       <c r="U180" s="29">
         <v>47573</v>
       </c>
-      <c r="V180" s="47">
-        <v>0</v>
-      </c>
-      <c r="W180" s="47"/>
+      <c r="V180" s="48">
+        <v>0</v>
+      </c>
+      <c r="W180" s="48"/>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A181" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="B181" s="44" t="s">
+      <c r="A181" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B181" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C181" s="44">
+      <c r="C181" s="45">
         <v>4</v>
       </c>
-      <c r="D181" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E181" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="F181" s="44">
+      <c r="D181" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E181" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F181" s="45">
         <v>25</v>
       </c>
-      <c r="G181" s="45">
+      <c r="G181" s="46">
         <v>52688</v>
       </c>
-      <c r="H181" s="45">
+      <c r="H181" s="46">
         <v>53052</v>
       </c>
-      <c r="I181" s="46">
+      <c r="I181" s="47">
         <v>2.000044715148519E-2</v>
       </c>
-      <c r="J181" s="47">
+      <c r="J181" s="48">
         <v>12774.199999999999</v>
       </c>
-      <c r="K181" s="48">
+      <c r="K181" s="49">
         <v>153290.4</v>
       </c>
-      <c r="L181" s="44" t="s">
+      <c r="L181" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="M181" s="49">
+      <c r="M181" s="50">
         <v>2508</v>
       </c>
-      <c r="N181" s="46">
+      <c r="N181" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O181" s="46">
+      <c r="O181" s="47">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P181" s="46">
+      <c r="P181" s="47">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q181" s="47">
+      <c r="Q181" s="48">
         <v>61.120574162679425</v>
       </c>
-      <c r="R181" s="47">
+      <c r="R181" s="48">
         <v>38322.6</v>
       </c>
-      <c r="S181" s="45">
+      <c r="S181" s="46">
         <v>43866</v>
       </c>
-      <c r="T181" s="45">
+      <c r="T181" s="46">
         <v>44044</v>
       </c>
       <c r="U181" s="29">
         <v>47573</v>
       </c>
-      <c r="V181" s="47">
-        <v>0</v>
-      </c>
-      <c r="W181" s="47"/>
+      <c r="V181" s="48">
+        <v>0</v>
+      </c>
+      <c r="W181" s="48"/>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V182" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W182" s="40"/>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>9</v>
@@ -13201,10 +13201,10 @@
         <v>5</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F183" s="5">
         <v>1</v>
@@ -13221,7 +13221,7 @@
       <c r="J183" s="14">
         <v>1250</v>
       </c>
-      <c r="K183" s="41">
+      <c r="K183" s="42">
         <v>15000</v>
       </c>
       <c r="L183" s="5" t="s">
@@ -13261,7 +13261,7 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>9</v>
@@ -13270,10 +13270,10 @@
         <v>5</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F184" s="5">
         <v>2</v>
@@ -13290,7 +13290,7 @@
       <c r="J184" s="14">
         <v>2500</v>
       </c>
-      <c r="K184" s="41">
+      <c r="K184" s="42">
         <v>30000</v>
       </c>
       <c r="L184" s="5" t="s">
@@ -13330,7 +13330,7 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>9</v>
@@ -13339,10 +13339,10 @@
         <v>5</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F185" s="5">
         <v>3</v>
@@ -13359,7 +13359,7 @@
       <c r="J185" s="14">
         <v>2600</v>
       </c>
-      <c r="K185" s="41">
+      <c r="K185" s="42">
         <v>31200</v>
       </c>
       <c r="L185" s="5" t="s">
@@ -13399,7 +13399,7 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>9</v>
@@ -13408,10 +13408,10 @@
         <v>5</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F186" s="5">
         <v>4</v>
@@ -13428,7 +13428,7 @@
       <c r="J186" s="14">
         <v>2700</v>
       </c>
-      <c r="K186" s="41">
+      <c r="K186" s="42">
         <v>32400</v>
       </c>
       <c r="L186" s="5" t="s">
@@ -13468,7 +13468,7 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>9</v>
@@ -13477,10 +13477,10 @@
         <v>5</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F187" s="5">
         <v>5</v>
@@ -13497,7 +13497,7 @@
       <c r="J187" s="14">
         <v>3000</v>
       </c>
-      <c r="K187" s="41">
+      <c r="K187" s="42">
         <v>36000</v>
       </c>
       <c r="L187" s="5" t="s">
@@ -13537,7 +13537,7 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>9</v>
@@ -13546,10 +13546,10 @@
         <v>5</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F188" s="5">
         <v>6</v>
@@ -13566,7 +13566,7 @@
       <c r="J188" s="14">
         <v>3100</v>
       </c>
-      <c r="K188" s="41">
+      <c r="K188" s="42">
         <v>37200</v>
       </c>
       <c r="L188" s="5" t="s">
@@ -13606,7 +13606,7 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="35" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B189" s="35" t="s">
         <v>9</v>
@@ -13615,10 +13615,10 @@
         <v>5</v>
       </c>
       <c r="D189" s="35" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E189" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F189" s="35">
         <v>7</v>
@@ -13635,7 +13635,7 @@
       <c r="J189" s="38">
         <v>3300</v>
       </c>
-      <c r="K189" s="43">
+      <c r="K189" s="44">
         <v>39600</v>
       </c>
       <c r="L189" s="35" t="s">
@@ -13675,7 +13675,7 @@
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" s="35" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B190" s="35" t="s">
         <v>9</v>
@@ -13684,10 +13684,10 @@
         <v>5</v>
       </c>
       <c r="D190" s="35" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E190" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F190" s="35">
         <v>8</v>
@@ -13704,7 +13704,7 @@
       <c r="J190" s="38">
         <v>3400</v>
       </c>
-      <c r="K190" s="43">
+      <c r="K190" s="44">
         <v>40800</v>
       </c>
       <c r="L190" s="35" t="s">
@@ -13744,76 +13744,76 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V191" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W191" s="40"/>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>9</v>
@@ -13822,10 +13822,10 @@
         <v>6</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F192" s="5">
         <v>1</v>
@@ -13842,7 +13842,7 @@
       <c r="J192" s="14">
         <v>1</v>
       </c>
-      <c r="K192" s="41">
+      <c r="K192" s="42">
         <v>12</v>
       </c>
       <c r="L192" s="5" t="s">
@@ -13882,76 +13882,76 @@
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V193" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W193" s="40"/>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>9</v>
@@ -13960,10 +13960,10 @@
         <v>7</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F194" s="5">
         <v>1</v>
@@ -13980,7 +13980,7 @@
       <c r="J194" s="14">
         <v>1800</v>
       </c>
-      <c r="K194" s="41">
+      <c r="K194" s="42">
         <v>21600</v>
       </c>
       <c r="L194" s="5" t="s">
@@ -14020,76 +14020,76 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V195" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W195" s="40"/>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>6</v>
@@ -14101,7 +14101,7 @@
         <v>40</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F196" s="5">
         <v>1</v>
@@ -14118,7 +14118,7 @@
       <c r="J196" s="14">
         <v>3200</v>
       </c>
-      <c r="K196" s="41">
+      <c r="K196" s="42">
         <v>38400</v>
       </c>
       <c r="L196" s="5" t="s">
@@ -14139,7 +14139,7 @@
       <c r="Q196" s="14">
         <v>36.124176857949202</v>
       </c>
-      <c r="R196" s="51">
+      <c r="R196" s="41">
         <v>5600</v>
       </c>
       <c r="S196" s="29">
@@ -14158,76 +14158,76 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V197" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W197" s="40"/>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>6</v>
@@ -14239,7 +14239,7 @@
         <v>44</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F198" s="5">
         <v>1</v>
@@ -14256,7 +14256,7 @@
       <c r="J198" s="14">
         <v>3608.35</v>
       </c>
-      <c r="K198" s="41">
+      <c r="K198" s="42">
         <v>43300.2</v>
       </c>
       <c r="L198" s="5" t="s">
@@ -14277,7 +14277,7 @@
       <c r="Q198" s="14">
         <v>31.838382352941174</v>
       </c>
-      <c r="R198" s="51">
+      <c r="R198" s="41">
         <v>3228</v>
       </c>
       <c r="S198" s="29">
@@ -14296,7 +14296,7 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>6</v>
@@ -14308,7 +14308,7 @@
         <v>44</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F199" s="5">
         <v>1</v>
@@ -14325,7 +14325,7 @@
       <c r="J199" s="14">
         <v>3608.35</v>
       </c>
-      <c r="K199" s="41">
+      <c r="K199" s="42">
         <v>43300.2</v>
       </c>
       <c r="L199" s="5" t="s">
@@ -14346,7 +14346,7 @@
       <c r="Q199" s="14">
         <v>31.838382352941174</v>
       </c>
-      <c r="R199" s="51">
+      <c r="R199" s="41">
         <v>3228</v>
       </c>
       <c r="S199" s="29">
@@ -14365,76 +14365,76 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V200" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W200" s="40"/>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>6</v>
@@ -14446,7 +14446,7 @@
         <v>45</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F201" s="5">
         <v>1</v>
@@ -14463,7 +14463,7 @@
       <c r="J201" s="14">
         <v>3916</v>
       </c>
-      <c r="K201" s="41">
+      <c r="K201" s="42">
         <v>46992</v>
       </c>
       <c r="L201" s="5" t="s">
@@ -14503,7 +14503,7 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>6</v>
@@ -14515,7 +14515,7 @@
         <v>45</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F202" s="5">
         <v>2</v>
@@ -14532,7 +14532,7 @@
       <c r="J202" s="14">
         <v>4033.48</v>
       </c>
-      <c r="K202" s="41">
+      <c r="K202" s="42">
         <v>48401.760000000002</v>
       </c>
       <c r="L202" s="5" t="s">
@@ -14553,7 +14553,7 @@
       <c r="Q202" s="14">
         <v>46.764985507246379</v>
       </c>
-      <c r="R202" s="51">
+      <c r="R202" s="41">
         <v>7832</v>
       </c>
       <c r="S202" s="17">
@@ -14572,7 +14572,7 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>6</v>
@@ -14584,7 +14584,7 @@
         <v>45</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F203" s="5">
         <v>3</v>
@@ -14601,7 +14601,7 @@
       <c r="J203" s="14">
         <v>4154.2233333333334</v>
       </c>
-      <c r="K203" s="41">
+      <c r="K203" s="42">
         <v>49850.68</v>
       </c>
       <c r="L203" s="5" t="s">
@@ -14622,7 +14622,7 @@
       <c r="Q203" s="14">
         <v>48.164908212560384</v>
       </c>
-      <c r="R203" s="51">
+      <c r="R203" s="41">
         <v>7832</v>
       </c>
       <c r="S203" s="17">
@@ -14641,7 +14641,7 @@
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>6</v>
@@ -14653,7 +14653,7 @@
         <v>45</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F204" s="5">
         <v>4</v>
@@ -14670,7 +14670,7 @@
       <c r="J204" s="14">
         <v>4279.0458333333336</v>
       </c>
-      <c r="K204" s="41">
+      <c r="K204" s="42">
         <v>51348.55</v>
       </c>
       <c r="L204" s="5" t="s">
@@ -14691,7 +14691,7 @@
       <c r="Q204" s="14">
         <v>49.61212560386474</v>
       </c>
-      <c r="R204" s="51">
+      <c r="R204" s="41">
         <v>7832</v>
       </c>
       <c r="S204" s="17">
@@ -14710,7 +14710,7 @@
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>6</v>
@@ -14722,7 +14722,7 @@
         <v>45</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F205" s="5">
         <v>5</v>
@@ -14739,7 +14739,7 @@
       <c r="J205" s="14">
         <v>4407.13</v>
       </c>
-      <c r="K205" s="41">
+      <c r="K205" s="42">
         <v>52885.56</v>
       </c>
       <c r="L205" s="5" t="s">
@@ -14760,7 +14760,7 @@
       <c r="Q205" s="14">
         <v>51.097159420289856</v>
       </c>
-      <c r="R205" s="51">
+      <c r="R205" s="41">
         <v>7832</v>
       </c>
       <c r="S205" s="17">
@@ -14779,7 +14779,7 @@
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>6</v>
@@ -14791,7 +14791,7 @@
         <v>45</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F206" s="5">
         <v>6</v>
@@ -14808,7 +14808,7 @@
       <c r="J206" s="14">
         <v>4407.13</v>
       </c>
-      <c r="K206" s="41">
+      <c r="K206" s="42">
         <v>52885.56</v>
       </c>
       <c r="L206" s="5" t="s">
@@ -14829,7 +14829,7 @@
       <c r="Q206" s="14">
         <v>51.097159420289856</v>
       </c>
-      <c r="R206" s="51">
+      <c r="R206" s="41">
         <v>7832</v>
       </c>
       <c r="S206" s="17">
@@ -14848,7 +14848,7 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" s="30" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B207" s="30" t="s">
         <v>6</v>
@@ -14860,7 +14860,7 @@
         <v>45</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F207" s="30">
         <v>7</v>
@@ -14877,7 +14877,7 @@
       <c r="J207" s="33">
         <v>4540.1125000000002</v>
       </c>
-      <c r="K207" s="42">
+      <c r="K207" s="43">
         <v>54481.35</v>
       </c>
       <c r="L207" s="30" t="s">
@@ -14898,7 +14898,7 @@
       <c r="Q207" s="33">
         <v>52.638985507246375</v>
       </c>
-      <c r="R207" s="51">
+      <c r="R207" s="41">
         <v>7832</v>
       </c>
       <c r="S207" s="31">
@@ -14917,7 +14917,7 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" s="30" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B208" s="30" t="s">
         <v>6</v>
@@ -14929,7 +14929,7 @@
         <v>45</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F208" s="30">
         <v>8</v>
@@ -14946,7 +14946,7 @@
       <c r="J208" s="33">
         <v>4675.5408333333335</v>
       </c>
-      <c r="K208" s="42">
+      <c r="K208" s="43">
         <v>56106.49</v>
       </c>
       <c r="L208" s="30" t="s">
@@ -14967,7 +14967,7 @@
       <c r="Q208" s="33">
         <v>54.209169082125605</v>
       </c>
-      <c r="R208" s="51">
+      <c r="R208" s="41">
         <v>7832</v>
       </c>
       <c r="S208" s="31">
@@ -14986,7 +14986,7 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" s="30" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B209" s="30" t="s">
         <v>6</v>
@@ -14998,7 +14998,7 @@
         <v>45</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F209" s="30">
         <v>9</v>
@@ -15015,7 +15015,7 @@
       <c r="J209" s="33">
         <v>4815.8641666666672</v>
       </c>
-      <c r="K209" s="42">
+      <c r="K209" s="43">
         <v>57790.37</v>
       </c>
       <c r="L209" s="30" t="s">
@@ -15036,7 +15036,7 @@
       <c r="Q209" s="33">
         <v>55.836106280193242</v>
       </c>
-      <c r="R209" s="51">
+      <c r="R209" s="41">
         <v>7832</v>
       </c>
       <c r="S209" s="31">
@@ -15055,7 +15055,7 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" s="30" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B210" s="30" t="s">
         <v>6</v>
@@ -15067,7 +15067,7 @@
         <v>45</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F210" s="30">
         <v>10</v>
@@ -15084,7 +15084,7 @@
       <c r="J210" s="33">
         <v>4960.2666666666664</v>
       </c>
-      <c r="K210" s="42">
+      <c r="K210" s="43">
         <v>59523.199999999997</v>
       </c>
       <c r="L210" s="30" t="s">
@@ -15105,7 +15105,7 @@
       <c r="Q210" s="33">
         <v>57.510338164251202</v>
       </c>
-      <c r="R210" s="51">
+      <c r="R210" s="41">
         <v>7832</v>
       </c>
       <c r="S210" s="31">
@@ -15124,7 +15124,7 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" s="30" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B211" s="30" t="s">
         <v>6</v>
@@ -15136,7 +15136,7 @@
         <v>45</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F211" s="30">
         <v>11</v>
@@ -15153,7 +15153,7 @@
       <c r="J211" s="33">
         <v>5109.5641666666661</v>
       </c>
-      <c r="K211" s="42">
+      <c r="K211" s="43">
         <v>61314.77</v>
       </c>
       <c r="L211" s="30" t="s">
@@ -15174,7 +15174,7 @@
       <c r="Q211" s="33">
         <v>59.241323671497582</v>
       </c>
-      <c r="R211" s="51">
+      <c r="R211" s="41">
         <v>7832</v>
       </c>
       <c r="S211" s="31">
@@ -15193,7 +15193,7 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" s="35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B212" s="35" t="s">
         <v>6</v>
@@ -15205,7 +15205,7 @@
         <v>45</v>
       </c>
       <c r="E212" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F212" s="35">
         <v>12</v>
@@ -15222,7 +15222,7 @@
       <c r="J212" s="38">
         <v>5211.7554499999997</v>
       </c>
-      <c r="K212" s="43">
+      <c r="K212" s="44">
         <v>62541.065399999999</v>
       </c>
       <c r="L212" s="35" t="s">
@@ -15243,7 +15243,7 @@
       <c r="Q212" s="38">
         <v>60.426150144927533</v>
       </c>
-      <c r="R212" s="51">
+      <c r="R212" s="41">
         <v>7832</v>
       </c>
       <c r="S212" s="36">
@@ -15262,7 +15262,7 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" s="35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B213" s="35" t="s">
         <v>6</v>
@@ -15274,7 +15274,7 @@
         <v>45</v>
       </c>
       <c r="E213" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F213" s="35">
         <v>13</v>
@@ -15291,7 +15291,7 @@
       <c r="J213" s="38">
         <v>5315.9905589999998</v>
       </c>
-      <c r="K213" s="43">
+      <c r="K213" s="44">
         <v>63791.886707999998</v>
       </c>
       <c r="L213" s="35" t="s">
@@ -15312,7 +15312,7 @@
       <c r="Q213" s="38">
         <v>61.634673147826085</v>
       </c>
-      <c r="R213" s="51">
+      <c r="R213" s="41">
         <v>7832</v>
       </c>
       <c r="S213" s="36">
@@ -15331,7 +15331,7 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" s="35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B214" s="35" t="s">
         <v>6</v>
@@ -15343,7 +15343,7 @@
         <v>45</v>
       </c>
       <c r="E214" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F214" s="35">
         <v>14</v>
@@ -15360,7 +15360,7 @@
       <c r="J214" s="38">
         <v>5422.3103701800001</v>
       </c>
-      <c r="K214" s="43">
+      <c r="K214" s="44">
         <v>65067.724442159997</v>
       </c>
       <c r="L214" s="35" t="s">
@@ -15381,7 +15381,7 @@
       <c r="Q214" s="38">
         <v>62.867366610782604</v>
       </c>
-      <c r="R214" s="51">
+      <c r="R214" s="41">
         <v>7832</v>
       </c>
       <c r="S214" s="36">
@@ -15400,7 +15400,7 @@
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" s="35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B215" s="35" t="s">
         <v>6</v>
@@ -15412,7 +15412,7 @@
         <v>45</v>
       </c>
       <c r="E215" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F215" s="35">
         <v>15</v>
@@ -15429,7 +15429,7 @@
       <c r="J215" s="38">
         <v>5530.7565775836001</v>
       </c>
-      <c r="K215" s="43">
+      <c r="K215" s="44">
         <v>66369.078931003198</v>
       </c>
       <c r="L215" s="35" t="s">
@@ -15450,7 +15450,7 @@
       <c r="Q215" s="38">
         <v>64.124713942998255</v>
       </c>
-      <c r="R215" s="51">
+      <c r="R215" s="41">
         <v>7832</v>
       </c>
       <c r="S215" s="36">
@@ -15469,7 +15469,7 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" s="35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B216" s="35" t="s">
         <v>6</v>
@@ -15481,7 +15481,7 @@
         <v>45</v>
       </c>
       <c r="E216" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F216" s="35">
         <v>16</v>
@@ -15498,7 +15498,7 @@
       <c r="J216" s="38">
         <v>5641.3717091352728</v>
       </c>
-      <c r="K216" s="43">
+      <c r="K216" s="44">
         <v>67696.46050962327</v>
       </c>
       <c r="L216" s="35" t="s">
@@ -15519,7 +15519,7 @@
       <c r="Q216" s="38">
         <v>65.407208221858227</v>
       </c>
-      <c r="R216" s="51">
+      <c r="R216" s="41">
         <v>7832</v>
       </c>
       <c r="S216" s="36">
@@ -15538,76 +15538,76 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V217" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W217" s="40"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>6</v>
@@ -15619,7 +15619,7 @@
         <v>47</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F218" s="5">
         <v>1</v>
@@ -15636,7 +15636,7 @@
       <c r="J218" s="14">
         <v>4410</v>
       </c>
-      <c r="K218" s="41">
+      <c r="K218" s="42">
         <v>52920</v>
       </c>
       <c r="L218" s="5" t="s">
@@ -15651,13 +15651,13 @@
       <c r="O218" s="11">
         <v>0.29342051491622395</v>
       </c>
-      <c r="P218" s="50">
+      <c r="P218" s="51">
         <v>0.1741</v>
       </c>
       <c r="Q218" s="14">
         <v>36.852367688022284</v>
       </c>
-      <c r="R218" s="51">
+      <c r="R218" s="41">
         <v>3000</v>
       </c>
       <c r="S218" s="29">
@@ -15676,7 +15676,7 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>6</v>
@@ -15688,7 +15688,7 @@
         <v>47</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F219" s="5">
         <v>2</v>
@@ -15705,7 +15705,7 @@
       <c r="J219" s="14">
         <v>4410</v>
       </c>
-      <c r="K219" s="41">
+      <c r="K219" s="42">
         <v>52920</v>
       </c>
       <c r="L219" s="5" t="s">
@@ -15720,13 +15720,13 @@
       <c r="O219" s="11">
         <v>0.29342051491622395</v>
       </c>
-      <c r="P219" s="50">
+      <c r="P219" s="51">
         <v>0.1741</v>
       </c>
       <c r="Q219" s="14">
         <v>36.852367688022284</v>
       </c>
-      <c r="R219" s="51">
+      <c r="R219" s="41">
         <v>3000</v>
       </c>
       <c r="S219" s="17">
@@ -15745,7 +15745,7 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>6</v>
@@ -15757,7 +15757,7 @@
         <v>47</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F220" s="5">
         <v>3</v>
@@ -15774,7 +15774,7 @@
       <c r="J220" s="14">
         <v>4410</v>
       </c>
-      <c r="K220" s="41">
+      <c r="K220" s="42">
         <v>52920</v>
       </c>
       <c r="L220" s="5" t="s">
@@ -15789,13 +15789,13 @@
       <c r="O220" s="11">
         <v>0.29342051491622395</v>
       </c>
-      <c r="P220" s="50">
+      <c r="P220" s="51">
         <v>0.1741</v>
       </c>
       <c r="Q220" s="14">
         <v>36.852367688022284</v>
       </c>
-      <c r="R220" s="51">
+      <c r="R220" s="41">
         <v>3000</v>
       </c>
       <c r="S220" s="17">
@@ -15814,7 +15814,7 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>6</v>
@@ -15826,7 +15826,7 @@
         <v>47</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F221" s="5">
         <v>4</v>
@@ -15843,7 +15843,7 @@
       <c r="J221" s="14">
         <v>4630.5</v>
       </c>
-      <c r="K221" s="41">
+      <c r="K221" s="42">
         <v>55566</v>
       </c>
       <c r="L221" s="5" t="s">
@@ -15858,13 +15858,13 @@
       <c r="O221" s="11">
         <v>0.29342051491622395</v>
       </c>
-      <c r="P221" s="50">
+      <c r="P221" s="51">
         <v>0.1741</v>
       </c>
       <c r="Q221" s="14">
         <v>38.694986072423397</v>
       </c>
-      <c r="R221" s="51">
+      <c r="R221" s="41">
         <v>3000</v>
       </c>
       <c r="S221" s="17">
@@ -15883,7 +15883,7 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>6</v>
@@ -15895,7 +15895,7 @@
         <v>47</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F222" s="5">
         <v>5</v>
@@ -15912,7 +15912,7 @@
       <c r="J222" s="14">
         <v>4630.5</v>
       </c>
-      <c r="K222" s="41">
+      <c r="K222" s="42">
         <v>55566</v>
       </c>
       <c r="L222" s="5" t="s">
@@ -15927,13 +15927,13 @@
       <c r="O222" s="11">
         <v>0.29342051491622395</v>
       </c>
-      <c r="P222" s="50">
+      <c r="P222" s="51">
         <v>0.1741</v>
       </c>
       <c r="Q222" s="14">
         <v>38.694986072423397</v>
       </c>
-      <c r="R222" s="51">
+      <c r="R222" s="41">
         <v>3000</v>
       </c>
       <c r="S222" s="17">
@@ -15952,7 +15952,7 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>6</v>
@@ -15964,7 +15964,7 @@
         <v>47</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F223" s="5">
         <v>6</v>
@@ -15981,7 +15981,7 @@
       <c r="J223" s="14">
         <v>4630.5</v>
       </c>
-      <c r="K223" s="41">
+      <c r="K223" s="42">
         <v>55566</v>
       </c>
       <c r="L223" s="5" t="s">
@@ -15996,13 +15996,13 @@
       <c r="O223" s="11">
         <v>0.29342051491622395</v>
       </c>
-      <c r="P223" s="50">
+      <c r="P223" s="51">
         <v>0.1741</v>
       </c>
       <c r="Q223" s="14">
         <v>38.694986072423397</v>
       </c>
-      <c r="R223" s="51">
+      <c r="R223" s="41">
         <v>3000</v>
       </c>
       <c r="S223" s="17">
@@ -16021,76 +16021,76 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V224" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W224" s="40"/>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>6</v>
@@ -16102,7 +16102,7 @@
         <v>48</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F225" s="5">
         <v>1</v>
@@ -16119,7 +16119,7 @@
       <c r="J225" s="14">
         <v>932</v>
       </c>
-      <c r="K225" s="41">
+      <c r="K225" s="42">
         <v>11184</v>
       </c>
       <c r="L225" s="5" t="s">
@@ -16159,76 +16159,76 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V226" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W226" s="40"/>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>6</v>
@@ -16237,10 +16237,10 @@
         <v>202</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F227" s="5">
         <v>1</v>
@@ -16257,7 +16257,7 @@
       <c r="J227" s="14">
         <v>958</v>
       </c>
-      <c r="K227" s="41">
+      <c r="K227" s="42">
         <v>11496</v>
       </c>
       <c r="L227" s="5" t="s">
@@ -16297,7 +16297,7 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>6</v>
@@ -16306,10 +16306,10 @@
         <v>202</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F228" s="5">
         <v>1</v>
@@ -16326,7 +16326,7 @@
       <c r="J228" s="14">
         <v>1050</v>
       </c>
-      <c r="K228" s="41">
+      <c r="K228" s="42">
         <v>12600</v>
       </c>
       <c r="L228" s="5" t="s">
@@ -16366,7 +16366,7 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="30" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B229" s="30" t="s">
         <v>6</v>
@@ -16375,10 +16375,10 @@
         <v>202</v>
       </c>
       <c r="D229" s="30" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="E229" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F229" s="30">
         <v>1</v>
@@ -16395,7 +16395,7 @@
       <c r="J229" s="33">
         <v>1300</v>
       </c>
-      <c r="K229" s="42">
+      <c r="K229" s="43">
         <v>15600</v>
       </c>
       <c r="L229" s="30" t="s">
@@ -16416,7 +16416,7 @@
       <c r="Q229" s="33">
         <v>25.7001647446458</v>
       </c>
-      <c r="R229" s="51">
+      <c r="R229" s="41">
         <v>1300</v>
       </c>
       <c r="S229" s="31">
@@ -16435,76 +16435,76 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V230" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W230" s="40"/>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>6</v>
@@ -16513,10 +16513,10 @@
         <v>203</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F231" s="5">
         <v>1</v>
@@ -16533,7 +16533,7 @@
       <c r="J231" s="14">
         <v>1400</v>
       </c>
-      <c r="K231" s="41">
+      <c r="K231" s="42">
         <v>16800</v>
       </c>
       <c r="L231" s="5" t="s">
@@ -16573,7 +16573,7 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>6</v>
@@ -16582,10 +16582,10 @@
         <v>203</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F232" s="5">
         <v>2</v>
@@ -16602,7 +16602,7 @@
       <c r="J232" s="14">
         <v>1400</v>
       </c>
-      <c r="K232" s="41">
+      <c r="K232" s="42">
         <v>16800</v>
       </c>
       <c r="L232" s="5" t="s">
@@ -16623,7 +16623,7 @@
       <c r="Q232" s="14">
         <v>27.009646302250804</v>
       </c>
-      <c r="R232" s="51">
+      <c r="R232" s="41">
         <v>2800</v>
       </c>
       <c r="S232" s="17">
@@ -16642,7 +16642,7 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="30" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B233" s="30" t="s">
         <v>6</v>
@@ -16651,10 +16651,10 @@
         <v>203</v>
       </c>
       <c r="D233" s="30" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E233" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F233" s="30">
         <v>3</v>
@@ -16671,7 +16671,7 @@
       <c r="J233" s="33">
         <v>1470</v>
       </c>
-      <c r="K233" s="42">
+      <c r="K233" s="43">
         <v>17640</v>
       </c>
       <c r="L233" s="30" t="s">
@@ -16692,7 +16692,7 @@
       <c r="Q233" s="33">
         <v>28.360128617363344</v>
       </c>
-      <c r="R233" s="51">
+      <c r="R233" s="41">
         <v>2800</v>
       </c>
       <c r="S233" s="31">
@@ -16711,7 +16711,7 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="35" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B234" s="35" t="s">
         <v>6</v>
@@ -16720,10 +16720,10 @@
         <v>203</v>
       </c>
       <c r="D234" s="35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E234" s="35" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F234" s="35">
         <v>4</v>
@@ -16740,7 +16740,7 @@
       <c r="J234" s="38">
         <v>1515</v>
       </c>
-      <c r="K234" s="43">
+      <c r="K234" s="44">
         <v>18180</v>
       </c>
       <c r="L234" s="35" t="s">
@@ -16761,7 +16761,7 @@
       <c r="Q234" s="38">
         <v>29.228295819935692</v>
       </c>
-      <c r="R234" s="51">
+      <c r="R234" s="41">
         <v>2800</v>
       </c>
       <c r="S234" s="36">
@@ -16780,76 +16780,76 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V235" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W235" s="40"/>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>6</v>
@@ -16858,19 +16858,19 @@
         <v>204</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F236" s="5">
         <v>1</v>
       </c>
       <c r="G236" s="52">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="H236" s="52">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="I236" s="11">
         <v>0</v>
@@ -16878,7 +16878,7 @@
       <c r="J236" s="14">
         <v>0</v>
       </c>
-      <c r="K236" s="41">
+      <c r="K236" s="42">
         <v>0</v>
       </c>
       <c r="L236" s="5" t="s">
@@ -16903,13 +16903,13 @@
         <v>0</v>
       </c>
       <c r="S236" s="29">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="T236" s="29">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="U236" s="29">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="V236" s="14">
         <v>0</v>
@@ -16918,76 +16918,76 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V237" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W237" s="40"/>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>6</v>
@@ -16996,10 +16996,10 @@
         <v>205</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F238" s="5">
         <v>1</v>
@@ -17016,7 +17016,7 @@
       <c r="J238" s="14">
         <v>875</v>
       </c>
-      <c r="K238" s="41">
+      <c r="K238" s="42">
         <v>10500</v>
       </c>
       <c r="L238" s="5" t="s">
@@ -17056,7 +17056,7 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>6</v>
@@ -17065,10 +17065,10 @@
         <v>205</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F239" s="5">
         <v>2</v>
@@ -17085,7 +17085,7 @@
       <c r="J239" s="14">
         <v>900</v>
       </c>
-      <c r="K239" s="41">
+      <c r="K239" s="42">
         <v>10800</v>
       </c>
       <c r="L239" s="5" t="s">
@@ -17125,7 +17125,7 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>6</v>
@@ -17134,10 +17134,10 @@
         <v>205</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F240" s="5">
         <v>3</v>
@@ -17154,7 +17154,7 @@
       <c r="J240" s="14">
         <v>925</v>
       </c>
-      <c r="K240" s="41">
+      <c r="K240" s="42">
         <v>11100</v>
       </c>
       <c r="L240" s="5" t="s">
@@ -17194,76 +17194,76 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V241" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W241" s="40"/>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>6</v>
@@ -17272,10 +17272,10 @@
         <v>209</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F242" s="5">
         <v>1</v>
@@ -17292,7 +17292,7 @@
       <c r="J242" s="14">
         <v>625</v>
       </c>
-      <c r="K242" s="41">
+      <c r="K242" s="42">
         <v>7500</v>
       </c>
       <c r="L242" s="5" t="s">
@@ -17332,7 +17332,7 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>6</v>
@@ -17341,10 +17341,10 @@
         <v>209</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F243" s="5">
         <v>2</v>
@@ -17361,7 +17361,7 @@
       <c r="J243" s="14">
         <v>650</v>
       </c>
-      <c r="K243" s="41">
+      <c r="K243" s="42">
         <v>7800</v>
       </c>
       <c r="L243" s="5" t="s">
@@ -17401,7 +17401,7 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>6</v>
@@ -17410,10 +17410,10 @@
         <v>209</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F244" s="5">
         <v>3</v>
@@ -17430,7 +17430,7 @@
       <c r="J244" s="14">
         <v>675</v>
       </c>
-      <c r="K244" s="41">
+      <c r="K244" s="42">
         <v>8100</v>
       </c>
       <c r="L244" s="5" t="s">
@@ -17470,76 +17470,76 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V245" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W245" s="40"/>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>6</v>
@@ -17548,10 +17548,10 @@
         <v>206</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F246" s="5">
         <v>1</v>
@@ -17568,7 +17568,7 @@
       <c r="J246" s="14">
         <v>1150</v>
       </c>
-      <c r="K246" s="41">
+      <c r="K246" s="42">
         <v>13800</v>
       </c>
       <c r="L246" s="5" t="s">
@@ -17589,7 +17589,7 @@
       <c r="Q246" s="14">
         <v>23.549488054607508</v>
       </c>
-      <c r="R246" s="51">
+      <c r="R246" s="41">
         <v>2000</v>
       </c>
       <c r="S246" s="29">
@@ -17608,7 +17608,7 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>6</v>
@@ -17617,10 +17617,10 @@
         <v>206</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F247" s="5">
         <v>1</v>
@@ -17637,7 +17637,7 @@
       <c r="J247" s="14">
         <v>1250</v>
       </c>
-      <c r="K247" s="41">
+      <c r="K247" s="42">
         <v>15000</v>
       </c>
       <c r="L247" s="5" t="s">
@@ -17658,7 +17658,7 @@
       <c r="Q247" s="14">
         <v>25.597269624573379</v>
       </c>
-      <c r="R247" s="51">
+      <c r="R247" s="41">
         <v>2000</v>
       </c>
       <c r="S247" s="29">
@@ -17679,7 +17679,7 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>6</v>
@@ -17688,10 +17688,10 @@
         <v>206</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F248" s="5">
         <v>1</v>
@@ -17708,7 +17708,7 @@
       <c r="J248" s="14">
         <v>1312.5</v>
       </c>
-      <c r="K248" s="41">
+      <c r="K248" s="42">
         <v>15750</v>
       </c>
       <c r="L248" s="5" t="s">
@@ -17729,7 +17729,7 @@
       <c r="Q248" s="14">
         <v>26.877133105802049</v>
       </c>
-      <c r="R248" s="51">
+      <c r="R248" s="41">
         <v>2000</v>
       </c>
       <c r="S248" s="29">
@@ -17750,7 +17750,7 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>6</v>
@@ -17759,10 +17759,10 @@
         <v>206</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F249" s="5">
         <v>1</v>
@@ -17779,7 +17779,7 @@
       <c r="J249" s="14">
         <v>1378.125</v>
       </c>
-      <c r="K249" s="41">
+      <c r="K249" s="42">
         <v>16537.5</v>
       </c>
       <c r="L249" s="5" t="s">
@@ -17800,7 +17800,7 @@
       <c r="Q249" s="14">
         <v>28.220989761092149</v>
       </c>
-      <c r="R249" s="51">
+      <c r="R249" s="41">
         <v>2000</v>
       </c>
       <c r="S249" s="29">
@@ -17821,7 +17821,7 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>6</v>
@@ -17830,10 +17830,10 @@
         <v>206</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F250" s="5">
         <v>1</v>
@@ -17850,7 +17850,7 @@
       <c r="J250" s="14">
         <v>1447.03125</v>
       </c>
-      <c r="K250" s="41">
+      <c r="K250" s="42">
         <v>17364.375</v>
       </c>
       <c r="L250" s="5" t="s">
@@ -17871,7 +17871,7 @@
       <c r="Q250" s="14">
         <v>29.632039249146757</v>
       </c>
-      <c r="R250" s="51">
+      <c r="R250" s="41">
         <v>2000</v>
       </c>
       <c r="S250" s="29">
@@ -17892,7 +17892,7 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>6</v>
@@ -17901,10 +17901,10 @@
         <v>206</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F251" s="5">
         <v>1</v>
@@ -17921,7 +17921,7 @@
       <c r="J251" s="14">
         <v>1519.3828125</v>
       </c>
-      <c r="K251" s="41">
+      <c r="K251" s="42">
         <v>18232.59375</v>
       </c>
       <c r="L251" s="5" t="s">
@@ -17942,7 +17942,7 @@
       <c r="Q251" s="14">
         <v>31.113641211604097</v>
       </c>
-      <c r="R251" s="51">
+      <c r="R251" s="41">
         <v>2000</v>
       </c>
       <c r="S251" s="29">
@@ -17963,76 +17963,76 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V252" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W252" s="40"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>6</v>
@@ -18041,10 +18041,10 @@
         <v>207</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F253" s="5">
         <v>1</v>
@@ -18061,7 +18061,7 @@
       <c r="J253" s="14">
         <v>1150</v>
       </c>
-      <c r="K253" s="41">
+      <c r="K253" s="42">
         <v>13800</v>
       </c>
       <c r="L253" s="5" t="s">
@@ -18101,7 +18101,7 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>6</v>
@@ -18110,10 +18110,10 @@
         <v>207</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F254" s="5">
         <v>2</v>
@@ -18130,7 +18130,7 @@
       <c r="J254" s="14">
         <v>1700</v>
       </c>
-      <c r="K254" s="41">
+      <c r="K254" s="42">
         <v>20400</v>
       </c>
       <c r="L254" s="5" t="s">
@@ -18170,7 +18170,7 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>6</v>
@@ -18179,10 +18179,10 @@
         <v>207</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F255" s="5">
         <v>3</v>
@@ -18199,7 +18199,7 @@
       <c r="J255" s="14">
         <v>1751</v>
       </c>
-      <c r="K255" s="41">
+      <c r="K255" s="42">
         <v>21012</v>
       </c>
       <c r="L255" s="5" t="s">
@@ -18239,7 +18239,7 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>6</v>
@@ -18248,10 +18248,10 @@
         <v>207</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F256" s="5">
         <v>4</v>
@@ -18268,7 +18268,7 @@
       <c r="J256" s="14">
         <v>1803.53</v>
       </c>
-      <c r="K256" s="41">
+      <c r="K256" s="42">
         <v>21642.36</v>
       </c>
       <c r="L256" s="5" t="s">
@@ -18308,7 +18308,7 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="30" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B257" s="30" t="s">
         <v>6</v>
@@ -18317,10 +18317,10 @@
         <v>207</v>
       </c>
       <c r="D257" s="30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E257" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F257" s="30">
         <v>5</v>
@@ -18337,7 +18337,7 @@
       <c r="J257" s="33">
         <v>1893.7066666666667</v>
       </c>
-      <c r="K257" s="42">
+      <c r="K257" s="43">
         <v>22724.48</v>
       </c>
       <c r="L257" s="30" t="s">
@@ -18377,7 +18377,7 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="30" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B258" s="30" t="s">
         <v>6</v>
@@ -18386,10 +18386,10 @@
         <v>207</v>
       </c>
       <c r="D258" s="30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E258" s="30" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F258" s="30">
         <v>6</v>
@@ -18406,7 +18406,7 @@
       <c r="J258" s="33">
         <v>1950.5216666666665</v>
       </c>
-      <c r="K258" s="42">
+      <c r="K258" s="43">
         <v>23406.26</v>
       </c>
       <c r="L258" s="30" t="s">
@@ -18446,76 +18446,76 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="O259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="P259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="R259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="S259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="U259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="V259" s="40" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="W259" s="40"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>6</v>
@@ -18524,10 +18524,10 @@
         <v>208</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F260" s="5">
         <v>1</v>
@@ -18544,7 +18544,7 @@
       <c r="J260" s="14">
         <v>550</v>
       </c>
-      <c r="K260" s="41">
+      <c r="K260" s="42">
         <v>6600</v>
       </c>
       <c r="L260" s="5" t="s">

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1C6774F-EECC-4CE7-B1DE-F5A099FBC9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54F39AF6-CA74-49D9-8934-AC06CF937A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="51615" windowHeight="27570" xr2:uid="{E3CDC22C-56CE-4F9B-82DA-520B345C859B}"/>
+    <workbookView xWindow="5985" yWindow="4830" windowWidth="51615" windowHeight="27570" xr2:uid="{D063092B-3390-4D24-96FA-3EAC3E90B8A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -647,6 +647,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -658,7 +659,6 @@
     <xf numFmtId="44" fontId="0" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1007,7 +1007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15774CFB-F4DC-488E-AFD7-E6B72E2613CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC400FDE-52B1-4CEB-9701-92C5A0999235}">
   <dimension ref="A1:AD260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2771,7 +2771,7 @@
         <v>76</v>
       </c>
       <c r="AB29" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC29" s="20">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>79</v>
       </c>
       <c r="AB30" s="20">
-        <v>1.9988242210464433</v>
+        <v>2</v>
       </c>
       <c r="AC30" s="20"/>
       <c r="AD30" s="23"/>
@@ -3861,7 +3861,7 @@
         <v>21.500004921259844</v>
       </c>
       <c r="R47" s="14">
-        <v>0</v>
+        <v>43688.01</v>
       </c>
       <c r="S47" s="29">
         <v>45383</v>
@@ -3929,8 +3929,8 @@
       <c r="Q48" s="14">
         <v>44.29</v>
       </c>
-      <c r="R48" s="14">
-        <v>0</v>
+      <c r="R48" s="30">
+        <v>43688.01</v>
       </c>
       <c r="S48" s="17">
         <v>45383</v>
@@ -3999,7 +3999,7 @@
         <v>45.618700000000004</v>
       </c>
       <c r="R49" s="14">
-        <v>0</v>
+        <v>46348.599200000004</v>
       </c>
       <c r="S49" s="17">
         <v>45383</v>
@@ -4068,7 +4068,7 @@
         <v>46.987261000000004</v>
       </c>
       <c r="R50" s="14">
-        <v>0</v>
+        <v>47739.057176000002</v>
       </c>
       <c r="S50" s="17">
         <v>45383</v>
@@ -4137,7 +4137,7 @@
         <v>48.396878830000006</v>
       </c>
       <c r="R51" s="14">
-        <v>0</v>
+        <v>49171.22889128</v>
       </c>
       <c r="S51" s="17">
         <v>45383</v>
@@ -4206,7 +4206,7 @@
         <v>49.84878519490001</v>
       </c>
       <c r="R52" s="14">
-        <v>0</v>
+        <v>50646.365758018408</v>
       </c>
       <c r="S52" s="17">
         <v>45383</v>
@@ -4275,7 +4275,7 @@
         <v>51.344248750747013</v>
       </c>
       <c r="R53" s="14">
-        <v>0</v>
+        <v>52165.756730758963</v>
       </c>
       <c r="S53" s="17">
         <v>45383</v>
@@ -4344,7 +4344,7 @@
         <v>52.884576213269426</v>
       </c>
       <c r="R54" s="14">
-        <v>0</v>
+        <v>53730.729432681735</v>
       </c>
       <c r="S54" s="17">
         <v>45383</v>
@@ -4413,7 +4413,7 @@
         <v>54.47111349966751</v>
       </c>
       <c r="R55" s="14">
-        <v>0</v>
+        <v>55342.651315662188</v>
       </c>
       <c r="S55" s="17">
         <v>45383</v>
@@ -4482,7 +4482,7 @@
         <v>56.105246904657534</v>
       </c>
       <c r="R56" s="14">
-        <v>0</v>
+        <v>57002.930855132057</v>
       </c>
       <c r="S56" s="17">
         <v>45383</v>
@@ -4499,763 +4499,763 @@
       <c r="W56" s="14"/>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B57" s="30" t="s">
+      <c r="B57" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="30">
-        <v>1</v>
-      </c>
-      <c r="D57" s="30" t="s">
+      <c r="C57" s="31">
+        <v>1</v>
+      </c>
+      <c r="D57" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="E57" s="30" t="s">
+      <c r="E57" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F57" s="30">
+      <c r="F57" s="31">
         <v>11</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <v>49035</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="32">
         <v>49399</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="33">
         <v>0.03</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>19571.006260262006</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>234852.07512314408</v>
       </c>
-      <c r="L57" s="30" t="s">
+      <c r="L57" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M57" s="34">
+      <c r="M57" s="35">
         <v>4064</v>
       </c>
-      <c r="N57" s="32">
-        <v>1</v>
-      </c>
-      <c r="O57" s="32">
-        <v>1</v>
-      </c>
-      <c r="P57" s="32">
+      <c r="N57" s="33">
+        <v>1</v>
+      </c>
+      <c r="O57" s="33">
+        <v>1</v>
+      </c>
+      <c r="P57" s="33">
         <v>0.6</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="34">
         <v>57.788404311797265</v>
       </c>
-      <c r="R57" s="33">
-        <v>0</v>
-      </c>
-      <c r="S57" s="31">
+      <c r="R57" s="34">
+        <v>58713.01878078602</v>
+      </c>
+      <c r="S57" s="32">
         <v>45383</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="32">
         <v>45566</v>
       </c>
       <c r="U57" s="29">
         <v>49034</v>
       </c>
-      <c r="V57" s="33">
-        <v>0</v>
-      </c>
-      <c r="W57" s="33"/>
+      <c r="V57" s="34">
+        <v>0</v>
+      </c>
+      <c r="W57" s="34"/>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B58" s="30" t="s">
+      <c r="B58" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="30">
-        <v>1</v>
-      </c>
-      <c r="D58" s="30" t="s">
+      <c r="C58" s="31">
+        <v>1</v>
+      </c>
+      <c r="D58" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="E58" s="30" t="s">
+      <c r="E58" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F58" s="30">
+      <c r="F58" s="31">
         <v>12</v>
       </c>
-      <c r="G58" s="31">
+      <c r="G58" s="32">
         <v>49400</v>
       </c>
-      <c r="H58" s="31">
+      <c r="H58" s="32">
         <v>49765</v>
       </c>
-      <c r="I58" s="32">
+      <c r="I58" s="33">
         <v>0.03</v>
       </c>
-      <c r="J58" s="33">
+      <c r="J58" s="34">
         <v>20158.136448069868</v>
       </c>
-      <c r="K58" s="33">
+      <c r="K58" s="34">
         <v>241897.63737683842</v>
       </c>
-      <c r="L58" s="30" t="s">
+      <c r="L58" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M58" s="34">
+      <c r="M58" s="35">
         <v>4064</v>
       </c>
-      <c r="N58" s="32">
-        <v>1</v>
-      </c>
-      <c r="O58" s="32">
-        <v>1</v>
-      </c>
-      <c r="P58" s="32">
+      <c r="N58" s="33">
+        <v>1</v>
+      </c>
+      <c r="O58" s="33">
+        <v>1</v>
+      </c>
+      <c r="P58" s="33">
         <v>0.6</v>
       </c>
-      <c r="Q58" s="33">
+      <c r="Q58" s="34">
         <v>59.522056441151186</v>
       </c>
-      <c r="R58" s="33">
-        <v>0</v>
-      </c>
-      <c r="S58" s="31">
+      <c r="R58" s="34">
+        <v>60474.409344209605</v>
+      </c>
+      <c r="S58" s="32">
         <v>45383</v>
       </c>
-      <c r="T58" s="31">
+      <c r="T58" s="32">
         <v>45566</v>
       </c>
       <c r="U58" s="29">
         <v>49034</v>
       </c>
-      <c r="V58" s="33">
-        <v>0</v>
-      </c>
-      <c r="W58" s="33"/>
+      <c r="V58" s="34">
+        <v>0</v>
+      </c>
+      <c r="W58" s="34"/>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B59" s="30" t="s">
+      <c r="B59" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="30">
-        <v>1</v>
-      </c>
-      <c r="D59" s="30" t="s">
+      <c r="C59" s="31">
+        <v>1</v>
+      </c>
+      <c r="D59" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="E59" s="30" t="s">
+      <c r="E59" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F59" s="30">
+      <c r="F59" s="31">
         <v>13</v>
       </c>
-      <c r="G59" s="31">
+      <c r="G59" s="32">
         <v>49766</v>
       </c>
-      <c r="H59" s="31">
+      <c r="H59" s="32">
         <v>50130</v>
       </c>
-      <c r="I59" s="32">
+      <c r="I59" s="33">
         <v>0.03</v>
       </c>
-      <c r="J59" s="33">
+      <c r="J59" s="34">
         <v>20762.880541511964</v>
       </c>
-      <c r="K59" s="33">
+      <c r="K59" s="34">
         <v>249154.56649814357</v>
       </c>
-      <c r="L59" s="30" t="s">
+      <c r="L59" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="35">
         <v>4064</v>
       </c>
-      <c r="N59" s="32">
-        <v>1</v>
-      </c>
-      <c r="O59" s="32">
-        <v>1</v>
-      </c>
-      <c r="P59" s="32">
+      <c r="N59" s="33">
+        <v>1</v>
+      </c>
+      <c r="O59" s="33">
+        <v>1</v>
+      </c>
+      <c r="P59" s="33">
         <v>0.6</v>
       </c>
-      <c r="Q59" s="33">
+      <c r="Q59" s="34">
         <v>61.307718134385723</v>
       </c>
-      <c r="R59" s="33">
-        <v>0</v>
-      </c>
-      <c r="S59" s="31">
+      <c r="R59" s="34">
+        <v>62288.641624535892</v>
+      </c>
+      <c r="S59" s="32">
         <v>45383</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="32">
         <v>45566</v>
       </c>
       <c r="U59" s="29">
         <v>49034</v>
       </c>
-      <c r="V59" s="33">
-        <v>0</v>
-      </c>
-      <c r="W59" s="33"/>
+      <c r="V59" s="34">
+        <v>0</v>
+      </c>
+      <c r="W59" s="34"/>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="30" t="s">
+      <c r="B60" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C60" s="30">
-        <v>1</v>
-      </c>
-      <c r="D60" s="30" t="s">
+      <c r="C60" s="31">
+        <v>1</v>
+      </c>
+      <c r="D60" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="E60" s="30" t="s">
+      <c r="E60" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F60" s="30">
+      <c r="F60" s="31">
         <v>14</v>
       </c>
-      <c r="G60" s="31">
+      <c r="G60" s="32">
         <v>50131</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="32">
         <v>50495</v>
       </c>
-      <c r="I60" s="32">
+      <c r="I60" s="33">
         <v>0.03</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J60" s="34">
         <v>21385.766957757322</v>
       </c>
-      <c r="K60" s="33">
+      <c r="K60" s="34">
         <v>256629.20349308787</v>
       </c>
-      <c r="L60" s="30" t="s">
+      <c r="L60" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M60" s="34">
+      <c r="M60" s="35">
         <v>4064</v>
       </c>
-      <c r="N60" s="32">
-        <v>1</v>
-      </c>
-      <c r="O60" s="32">
-        <v>1</v>
-      </c>
-      <c r="P60" s="32">
+      <c r="N60" s="33">
+        <v>1</v>
+      </c>
+      <c r="O60" s="33">
+        <v>1</v>
+      </c>
+      <c r="P60" s="33">
         <v>0.6</v>
       </c>
-      <c r="Q60" s="33">
+      <c r="Q60" s="34">
         <v>63.146949678417293</v>
       </c>
-      <c r="R60" s="33">
-        <v>0</v>
-      </c>
-      <c r="S60" s="31">
+      <c r="R60" s="34">
+        <v>64157.300873271961</v>
+      </c>
+      <c r="S60" s="32">
         <v>45383</v>
       </c>
-      <c r="T60" s="31">
+      <c r="T60" s="32">
         <v>45566</v>
       </c>
       <c r="U60" s="29">
         <v>49034</v>
       </c>
-      <c r="V60" s="33">
-        <v>0</v>
-      </c>
-      <c r="W60" s="33"/>
+      <c r="V60" s="34">
+        <v>0</v>
+      </c>
+      <c r="W60" s="34"/>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="30" t="s">
+      <c r="A61" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B61" s="30" t="s">
+      <c r="B61" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="30">
-        <v>1</v>
-      </c>
-      <c r="D61" s="30" t="s">
+      <c r="C61" s="31">
+        <v>1</v>
+      </c>
+      <c r="D61" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="E61" s="30" t="s">
+      <c r="E61" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F61" s="30">
+      <c r="F61" s="31">
         <v>15</v>
       </c>
-      <c r="G61" s="31">
+      <c r="G61" s="32">
         <v>50496</v>
       </c>
-      <c r="H61" s="31">
+      <c r="H61" s="32">
         <v>50860</v>
       </c>
-      <c r="I61" s="32">
+      <c r="I61" s="33">
         <v>0.03</v>
       </c>
-      <c r="J61" s="33">
+      <c r="J61" s="34">
         <v>22027.339966490046</v>
       </c>
-      <c r="K61" s="33">
+      <c r="K61" s="34">
         <v>264328.07959788054</v>
       </c>
-      <c r="L61" s="30" t="s">
+      <c r="L61" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M61" s="34">
+      <c r="M61" s="35">
         <v>4064</v>
       </c>
-      <c r="N61" s="32">
-        <v>1</v>
-      </c>
-      <c r="O61" s="32">
-        <v>1</v>
-      </c>
-      <c r="P61" s="32">
+      <c r="N61" s="33">
+        <v>1</v>
+      </c>
+      <c r="O61" s="33">
+        <v>1</v>
+      </c>
+      <c r="P61" s="33">
         <v>0.6</v>
       </c>
-      <c r="Q61" s="33">
+      <c r="Q61" s="34">
         <v>65.041358168769818</v>
       </c>
-      <c r="R61" s="33">
-        <v>0</v>
-      </c>
-      <c r="S61" s="31">
+      <c r="R61" s="34">
+        <v>66082.019899470135</v>
+      </c>
+      <c r="S61" s="32">
         <v>45383</v>
       </c>
-      <c r="T61" s="31">
+      <c r="T61" s="32">
         <v>45566</v>
       </c>
       <c r="U61" s="29">
         <v>49034</v>
       </c>
-      <c r="V61" s="33">
-        <v>0</v>
-      </c>
-      <c r="W61" s="33"/>
+      <c r="V61" s="34">
+        <v>0</v>
+      </c>
+      <c r="W61" s="34"/>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="35">
-        <v>1</v>
-      </c>
-      <c r="D62" s="35" t="s">
+      <c r="C62" s="36">
+        <v>1</v>
+      </c>
+      <c r="D62" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E62" s="35" t="s">
+      <c r="E62" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="35">
+      <c r="F62" s="36">
         <v>16</v>
       </c>
-      <c r="G62" s="36">
+      <c r="G62" s="37">
         <v>50861</v>
       </c>
-      <c r="H62" s="36">
+      <c r="H62" s="37">
         <v>51226</v>
       </c>
-      <c r="I62" s="37">
+      <c r="I62" s="38">
         <v>0.03</v>
       </c>
-      <c r="J62" s="38">
+      <c r="J62" s="39">
         <v>22688.160165484747</v>
       </c>
-      <c r="K62" s="38">
+      <c r="K62" s="39">
         <v>272257.92198581697</v>
       </c>
-      <c r="L62" s="35" t="s">
+      <c r="L62" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M62" s="39">
+      <c r="M62" s="40">
         <v>4064</v>
       </c>
-      <c r="N62" s="37">
-        <v>1</v>
-      </c>
-      <c r="O62" s="37">
-        <v>1</v>
-      </c>
-      <c r="P62" s="37">
+      <c r="N62" s="38">
+        <v>1</v>
+      </c>
+      <c r="O62" s="38">
+        <v>1</v>
+      </c>
+      <c r="P62" s="38">
         <v>0.6</v>
       </c>
-      <c r="Q62" s="38">
+      <c r="Q62" s="39">
         <v>66.992598913832921</v>
       </c>
-      <c r="R62" s="38">
-        <v>0</v>
-      </c>
-      <c r="S62" s="36">
+      <c r="R62" s="39">
+        <v>68064.480496454242</v>
+      </c>
+      <c r="S62" s="37">
         <v>45383</v>
       </c>
-      <c r="T62" s="36">
+      <c r="T62" s="37">
         <v>45566</v>
       </c>
       <c r="U62" s="29">
         <v>49034</v>
       </c>
-      <c r="V62" s="38">
-        <v>0</v>
-      </c>
-      <c r="W62" s="38"/>
+      <c r="V62" s="39">
+        <v>0</v>
+      </c>
+      <c r="W62" s="39"/>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B63" s="35" t="s">
+      <c r="B63" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="35">
-        <v>1</v>
-      </c>
-      <c r="D63" s="35" t="s">
+      <c r="C63" s="36">
+        <v>1</v>
+      </c>
+      <c r="D63" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E63" s="35" t="s">
+      <c r="E63" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F63" s="35">
+      <c r="F63" s="36">
         <v>17</v>
       </c>
-      <c r="G63" s="36">
+      <c r="G63" s="37">
         <v>51227</v>
       </c>
-      <c r="H63" s="36">
+      <c r="H63" s="37">
         <v>51591</v>
       </c>
-      <c r="I63" s="37">
+      <c r="I63" s="38">
         <v>0.03</v>
       </c>
-      <c r="J63" s="38">
+      <c r="J63" s="39">
         <v>23368.804970449291</v>
       </c>
-      <c r="K63" s="38">
+      <c r="K63" s="39">
         <v>280425.65964539151</v>
       </c>
-      <c r="L63" s="35" t="s">
+      <c r="L63" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M63" s="39">
+      <c r="M63" s="40">
         <v>4064</v>
       </c>
-      <c r="N63" s="37">
-        <v>1</v>
-      </c>
-      <c r="O63" s="37">
-        <v>1</v>
-      </c>
-      <c r="P63" s="37">
+      <c r="N63" s="38">
+        <v>1</v>
+      </c>
+      <c r="O63" s="38">
+        <v>1</v>
+      </c>
+      <c r="P63" s="38">
         <v>0.6</v>
       </c>
-      <c r="Q63" s="38">
+      <c r="Q63" s="39">
         <v>69.002376881247912</v>
       </c>
-      <c r="R63" s="38">
-        <v>0</v>
-      </c>
-      <c r="S63" s="36">
+      <c r="R63" s="39">
+        <v>70106.414911347878</v>
+      </c>
+      <c r="S63" s="37">
         <v>45383</v>
       </c>
-      <c r="T63" s="36">
+      <c r="T63" s="37">
         <v>45566</v>
       </c>
       <c r="U63" s="29">
         <v>49034</v>
       </c>
-      <c r="V63" s="38">
-        <v>0</v>
-      </c>
-      <c r="W63" s="38"/>
+      <c r="V63" s="39">
+        <v>0</v>
+      </c>
+      <c r="W63" s="39"/>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A64" s="35" t="s">
+      <c r="A64" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B64" s="35" t="s">
+      <c r="B64" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="35">
-        <v>1</v>
-      </c>
-      <c r="D64" s="35" t="s">
+      <c r="C64" s="36">
+        <v>1</v>
+      </c>
+      <c r="D64" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E64" s="35" t="s">
+      <c r="E64" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F64" s="35">
+      <c r="F64" s="36">
         <v>18</v>
       </c>
-      <c r="G64" s="36">
+      <c r="G64" s="37">
         <v>51592</v>
       </c>
-      <c r="H64" s="36">
+      <c r="H64" s="37">
         <v>51956</v>
       </c>
-      <c r="I64" s="37">
+      <c r="I64" s="38">
         <v>0.03</v>
       </c>
-      <c r="J64" s="38">
+      <c r="J64" s="39">
         <v>24069.869119562773</v>
       </c>
-      <c r="K64" s="38">
+      <c r="K64" s="39">
         <v>288838.42943475326</v>
       </c>
-      <c r="L64" s="35" t="s">
+      <c r="L64" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M64" s="39">
+      <c r="M64" s="40">
         <v>4064</v>
       </c>
-      <c r="N64" s="37">
-        <v>1</v>
-      </c>
-      <c r="O64" s="37">
-        <v>1</v>
-      </c>
-      <c r="P64" s="37">
+      <c r="N64" s="38">
+        <v>1</v>
+      </c>
+      <c r="O64" s="38">
+        <v>1</v>
+      </c>
+      <c r="P64" s="38">
         <v>0.6</v>
       </c>
-      <c r="Q64" s="38">
+      <c r="Q64" s="39">
         <v>71.072448187685353</v>
       </c>
-      <c r="R64" s="38">
-        <v>0</v>
-      </c>
-      <c r="S64" s="36">
+      <c r="R64" s="39">
+        <v>72209.607358688314</v>
+      </c>
+      <c r="S64" s="37">
         <v>45383</v>
       </c>
-      <c r="T64" s="36">
+      <c r="T64" s="37">
         <v>45566</v>
       </c>
       <c r="U64" s="29">
         <v>49034</v>
       </c>
-      <c r="V64" s="38">
-        <v>0</v>
-      </c>
-      <c r="W64" s="38"/>
+      <c r="V64" s="39">
+        <v>0</v>
+      </c>
+      <c r="W64" s="39"/>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A65" s="35" t="s">
+      <c r="A65" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="35">
-        <v>1</v>
-      </c>
-      <c r="D65" s="35" t="s">
+      <c r="C65" s="36">
+        <v>1</v>
+      </c>
+      <c r="D65" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E65" s="35" t="s">
+      <c r="E65" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F65" s="35">
+      <c r="F65" s="36">
         <v>19</v>
       </c>
-      <c r="G65" s="36">
+      <c r="G65" s="37">
         <v>51957</v>
       </c>
-      <c r="H65" s="36">
+      <c r="H65" s="37">
         <v>52321</v>
       </c>
-      <c r="I65" s="37">
+      <c r="I65" s="38">
         <v>0.03</v>
       </c>
-      <c r="J65" s="38">
+      <c r="J65" s="39">
         <v>24791.965193149652</v>
       </c>
-      <c r="K65" s="38">
+      <c r="K65" s="39">
         <v>297503.58231779584</v>
       </c>
-      <c r="L65" s="35" t="s">
+      <c r="L65" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M65" s="39">
+      <c r="M65" s="40">
         <v>4064</v>
       </c>
-      <c r="N65" s="37">
-        <v>1</v>
-      </c>
-      <c r="O65" s="37">
-        <v>1</v>
-      </c>
-      <c r="P65" s="37">
+      <c r="N65" s="38">
+        <v>1</v>
+      </c>
+      <c r="O65" s="38">
+        <v>1</v>
+      </c>
+      <c r="P65" s="38">
         <v>0.6</v>
       </c>
-      <c r="Q65" s="38">
+      <c r="Q65" s="39">
         <v>73.204621633315909</v>
       </c>
-      <c r="R65" s="38">
-        <v>0</v>
-      </c>
-      <c r="S65" s="36">
+      <c r="R65" s="39">
+        <v>74375.895579448959</v>
+      </c>
+      <c r="S65" s="37">
         <v>45383</v>
       </c>
-      <c r="T65" s="36">
+      <c r="T65" s="37">
         <v>45566</v>
       </c>
       <c r="U65" s="29">
         <v>49034</v>
       </c>
-      <c r="V65" s="38">
-        <v>0</v>
-      </c>
-      <c r="W65" s="38"/>
+      <c r="V65" s="39">
+        <v>0</v>
+      </c>
+      <c r="W65" s="39"/>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A66" s="35" t="s">
+      <c r="A66" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B66" s="35" t="s">
+      <c r="B66" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C66" s="35">
-        <v>1</v>
-      </c>
-      <c r="D66" s="35" t="s">
+      <c r="C66" s="36">
+        <v>1</v>
+      </c>
+      <c r="D66" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E66" s="35" t="s">
+      <c r="E66" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F66" s="35">
+      <c r="F66" s="36">
         <v>20</v>
       </c>
-      <c r="G66" s="36">
+      <c r="G66" s="37">
         <v>52322</v>
       </c>
-      <c r="H66" s="36">
+      <c r="H66" s="37">
         <v>52687</v>
       </c>
-      <c r="I66" s="37">
+      <c r="I66" s="38">
         <v>0.03</v>
       </c>
-      <c r="J66" s="38">
+      <c r="J66" s="39">
         <v>25535.72414894414</v>
       </c>
-      <c r="K66" s="38">
+      <c r="K66" s="39">
         <v>306428.6897873297</v>
       </c>
-      <c r="L66" s="35" t="s">
+      <c r="L66" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M66" s="39">
+      <c r="M66" s="40">
         <v>4064</v>
       </c>
-      <c r="N66" s="37">
-        <v>1</v>
-      </c>
-      <c r="O66" s="37">
-        <v>1</v>
-      </c>
-      <c r="P66" s="37">
+      <c r="N66" s="38">
+        <v>1</v>
+      </c>
+      <c r="O66" s="38">
+        <v>1</v>
+      </c>
+      <c r="P66" s="38">
         <v>0.6</v>
       </c>
-      <c r="Q66" s="38">
+      <c r="Q66" s="39">
         <v>75.400760282315375</v>
       </c>
-      <c r="R66" s="38">
-        <v>0</v>
-      </c>
-      <c r="S66" s="36">
+      <c r="R66" s="39">
+        <v>76607.172446832425</v>
+      </c>
+      <c r="S66" s="37">
         <v>45383</v>
       </c>
-      <c r="T66" s="36">
+      <c r="T66" s="37">
         <v>45566</v>
       </c>
       <c r="U66" s="29">
         <v>49034</v>
       </c>
-      <c r="V66" s="38">
-        <v>0</v>
-      </c>
-      <c r="W66" s="38"/>
+      <c r="V66" s="39">
+        <v>0</v>
+      </c>
+      <c r="W66" s="39"/>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W67" s="40"/>
+      <c r="A67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V67" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W67" s="41"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
@@ -5309,8 +5309,8 @@
       <c r="Q68" s="14">
         <v>25.077399380804952</v>
       </c>
-      <c r="R68" s="41">
-        <v>17000</v>
+      <c r="R68" s="14">
+        <v>17550</v>
       </c>
       <c r="S68" s="29">
         <v>38504</v>
@@ -5378,8 +5378,8 @@
       <c r="Q69" s="14">
         <v>26.43486544415337</v>
       </c>
-      <c r="R69" s="41">
-        <v>17000</v>
+      <c r="R69" s="14">
+        <v>18500</v>
       </c>
       <c r="S69" s="17">
         <v>38504</v>
@@ -5447,8 +5447,8 @@
       <c r="Q70" s="14">
         <v>27.75660871636104</v>
       </c>
-      <c r="R70" s="41">
-        <v>17000</v>
+      <c r="R70" s="14">
+        <v>19425</v>
       </c>
       <c r="S70" s="17">
         <v>38504</v>
@@ -5516,8 +5516,8 @@
       <c r="Q71" s="14">
         <v>29.144439152179089</v>
       </c>
-      <c r="R71" s="41">
-        <v>17000</v>
+      <c r="R71" s="14">
+        <v>20396.25</v>
       </c>
       <c r="S71" s="17">
         <v>38504</v>
@@ -5534,73 +5534,73 @@
       <c r="W71" s="14"/>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V72" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W72" s="40"/>
+      <c r="A72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V72" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W72" s="41"/>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
@@ -6569,73 +6569,73 @@
       <c r="W86" s="14"/>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V87" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W87" s="40"/>
+      <c r="A87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V87" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W87" s="41"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
@@ -7397,73 +7397,73 @@
       <c r="W98" s="14"/>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V99" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W99" s="40"/>
+      <c r="A99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V99" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W99" s="41"/>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
@@ -8156,418 +8156,418 @@
       <c r="W109" s="14"/>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A110" s="30" t="s">
+      <c r="A110" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B110" s="30" t="s">
+      <c r="B110" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C110" s="30">
-        <v>1</v>
-      </c>
-      <c r="D110" s="30" t="s">
+      <c r="C110" s="31">
+        <v>1</v>
+      </c>
+      <c r="D110" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E110" s="30" t="s">
+      <c r="E110" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F110" s="30">
+      <c r="F110" s="31">
         <v>11</v>
       </c>
-      <c r="G110" s="31">
+      <c r="G110" s="32">
         <v>49065</v>
       </c>
-      <c r="H110" s="31">
+      <c r="H110" s="32">
         <v>49429</v>
       </c>
-      <c r="I110" s="32">
+      <c r="I110" s="33">
         <v>0.1</v>
       </c>
-      <c r="J110" s="33">
+      <c r="J110" s="34">
         <v>19158.337</v>
       </c>
-      <c r="K110" s="33">
+      <c r="K110" s="34">
         <v>229900.04399999999</v>
       </c>
-      <c r="L110" s="30" t="s">
+      <c r="L110" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M110" s="34">
+      <c r="M110" s="35">
         <v>4000</v>
       </c>
-      <c r="N110" s="32">
+      <c r="N110" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="O110" s="32">
+      <c r="O110" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="P110" s="32">
-        <v>1</v>
-      </c>
-      <c r="Q110" s="33">
+      <c r="P110" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q110" s="34">
         <v>57.475011000000002</v>
       </c>
-      <c r="R110" s="33">
-        <v>0</v>
-      </c>
-      <c r="S110" s="31">
+      <c r="R110" s="34">
+        <v>0</v>
+      </c>
+      <c r="S110" s="32">
         <v>45231</v>
       </c>
-      <c r="T110" s="31">
+      <c r="T110" s="32">
         <v>45413</v>
       </c>
       <c r="U110" s="29">
         <v>49064</v>
       </c>
-      <c r="V110" s="33">
-        <v>0</v>
-      </c>
-      <c r="W110" s="33"/>
+      <c r="V110" s="34">
+        <v>0</v>
+      </c>
+      <c r="W110" s="34"/>
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A111" s="30" t="s">
+      <c r="A111" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="30" t="s">
+      <c r="B111" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C111" s="30">
-        <v>1</v>
-      </c>
-      <c r="D111" s="30" t="s">
+      <c r="C111" s="31">
+        <v>1</v>
+      </c>
+      <c r="D111" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E111" s="30" t="s">
+      <c r="E111" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F111" s="30">
+      <c r="F111" s="31">
         <v>12</v>
       </c>
-      <c r="G111" s="31">
+      <c r="G111" s="32">
         <v>49430</v>
       </c>
-      <c r="H111" s="31">
+      <c r="H111" s="32">
         <v>49795</v>
       </c>
-      <c r="I111" s="32">
-        <v>0</v>
-      </c>
-      <c r="J111" s="33">
+      <c r="I111" s="33">
+        <v>0</v>
+      </c>
+      <c r="J111" s="34">
         <v>19158.337</v>
       </c>
-      <c r="K111" s="33">
+      <c r="K111" s="34">
         <v>229900.04399999999</v>
       </c>
-      <c r="L111" s="30" t="s">
+      <c r="L111" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M111" s="34">
+      <c r="M111" s="35">
         <v>4000</v>
       </c>
-      <c r="N111" s="32">
+      <c r="N111" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="O111" s="32">
+      <c r="O111" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="P111" s="32">
-        <v>1</v>
-      </c>
-      <c r="Q111" s="33">
+      <c r="P111" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q111" s="34">
         <v>57.475011000000002</v>
       </c>
-      <c r="R111" s="33">
-        <v>0</v>
-      </c>
-      <c r="S111" s="31">
+      <c r="R111" s="34">
+        <v>0</v>
+      </c>
+      <c r="S111" s="32">
         <v>45231</v>
       </c>
-      <c r="T111" s="31">
+      <c r="T111" s="32">
         <v>45413</v>
       </c>
       <c r="U111" s="29">
         <v>49064</v>
       </c>
-      <c r="V111" s="33">
-        <v>0</v>
-      </c>
-      <c r="W111" s="33"/>
+      <c r="V111" s="34">
+        <v>0</v>
+      </c>
+      <c r="W111" s="34"/>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A112" s="30" t="s">
+      <c r="A112" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C112" s="30">
-        <v>1</v>
-      </c>
-      <c r="D112" s="30" t="s">
+      <c r="C112" s="31">
+        <v>1</v>
+      </c>
+      <c r="D112" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E112" s="30" t="s">
+      <c r="E112" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F112" s="30">
+      <c r="F112" s="31">
         <v>13</v>
       </c>
-      <c r="G112" s="31">
+      <c r="G112" s="32">
         <v>49796</v>
       </c>
-      <c r="H112" s="31">
+      <c r="H112" s="32">
         <v>50160</v>
       </c>
-      <c r="I112" s="32">
-        <v>0</v>
-      </c>
-      <c r="J112" s="33">
+      <c r="I112" s="33">
+        <v>0</v>
+      </c>
+      <c r="J112" s="34">
         <v>19158.337</v>
       </c>
-      <c r="K112" s="33">
+      <c r="K112" s="34">
         <v>229900.04399999999</v>
       </c>
-      <c r="L112" s="30" t="s">
+      <c r="L112" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M112" s="34">
+      <c r="M112" s="35">
         <v>4000</v>
       </c>
-      <c r="N112" s="32">
+      <c r="N112" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="O112" s="32">
+      <c r="O112" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="P112" s="32">
-        <v>1</v>
-      </c>
-      <c r="Q112" s="33">
+      <c r="P112" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q112" s="34">
         <v>57.475011000000002</v>
       </c>
-      <c r="R112" s="33">
-        <v>0</v>
-      </c>
-      <c r="S112" s="31">
+      <c r="R112" s="34">
+        <v>0</v>
+      </c>
+      <c r="S112" s="32">
         <v>45231</v>
       </c>
-      <c r="T112" s="31">
+      <c r="T112" s="32">
         <v>45413</v>
       </c>
       <c r="U112" s="29">
         <v>49064</v>
       </c>
-      <c r="V112" s="33">
-        <v>0</v>
-      </c>
-      <c r="W112" s="33"/>
+      <c r="V112" s="34">
+        <v>0</v>
+      </c>
+      <c r="W112" s="34"/>
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A113" s="30" t="s">
+      <c r="A113" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B113" s="30" t="s">
+      <c r="B113" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C113" s="30">
-        <v>1</v>
-      </c>
-      <c r="D113" s="30" t="s">
+      <c r="C113" s="31">
+        <v>1</v>
+      </c>
+      <c r="D113" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E113" s="30" t="s">
+      <c r="E113" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F113" s="30">
+      <c r="F113" s="31">
         <v>14</v>
       </c>
-      <c r="G113" s="31">
+      <c r="G113" s="32">
         <v>50161</v>
       </c>
-      <c r="H113" s="31">
+      <c r="H113" s="32">
         <v>50525</v>
       </c>
-      <c r="I113" s="32">
-        <v>0</v>
-      </c>
-      <c r="J113" s="33">
+      <c r="I113" s="33">
+        <v>0</v>
+      </c>
+      <c r="J113" s="34">
         <v>19158.337</v>
       </c>
-      <c r="K113" s="33">
+      <c r="K113" s="34">
         <v>229900.04399999999</v>
       </c>
-      <c r="L113" s="30" t="s">
+      <c r="L113" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M113" s="34">
+      <c r="M113" s="35">
         <v>4000</v>
       </c>
-      <c r="N113" s="32">
+      <c r="N113" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="O113" s="32">
+      <c r="O113" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="P113" s="32">
-        <v>1</v>
-      </c>
-      <c r="Q113" s="33">
+      <c r="P113" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="34">
         <v>57.475011000000002</v>
       </c>
-      <c r="R113" s="33">
-        <v>0</v>
-      </c>
-      <c r="S113" s="31">
+      <c r="R113" s="34">
+        <v>0</v>
+      </c>
+      <c r="S113" s="32">
         <v>45231</v>
       </c>
-      <c r="T113" s="31">
+      <c r="T113" s="32">
         <v>45413</v>
       </c>
       <c r="U113" s="29">
         <v>49064</v>
       </c>
-      <c r="V113" s="33">
-        <v>0</v>
-      </c>
-      <c r="W113" s="33"/>
+      <c r="V113" s="34">
+        <v>0</v>
+      </c>
+      <c r="W113" s="34"/>
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A114" s="30" t="s">
+      <c r="A114" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B114" s="30" t="s">
+      <c r="B114" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C114" s="30">
-        <v>1</v>
-      </c>
-      <c r="D114" s="30" t="s">
+      <c r="C114" s="31">
+        <v>1</v>
+      </c>
+      <c r="D114" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E114" s="30" t="s">
+      <c r="E114" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F114" s="30">
+      <c r="F114" s="31">
         <v>15</v>
       </c>
-      <c r="G114" s="31">
+      <c r="G114" s="32">
         <v>50526</v>
       </c>
-      <c r="H114" s="31">
+      <c r="H114" s="32">
         <v>50890</v>
       </c>
-      <c r="I114" s="32">
-        <v>0</v>
-      </c>
-      <c r="J114" s="33">
+      <c r="I114" s="33">
+        <v>0</v>
+      </c>
+      <c r="J114" s="34">
         <v>19158.337</v>
       </c>
-      <c r="K114" s="33">
+      <c r="K114" s="34">
         <v>229900.04399999999</v>
       </c>
-      <c r="L114" s="30" t="s">
+      <c r="L114" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M114" s="34">
+      <c r="M114" s="35">
         <v>4000</v>
       </c>
-      <c r="N114" s="32">
+      <c r="N114" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="O114" s="32">
+      <c r="O114" s="33">
         <v>0.99950024987506247</v>
       </c>
-      <c r="P114" s="32">
-        <v>1</v>
-      </c>
-      <c r="Q114" s="33">
+      <c r="P114" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="34">
         <v>57.475011000000002</v>
       </c>
-      <c r="R114" s="33">
-        <v>0</v>
-      </c>
-      <c r="S114" s="31">
+      <c r="R114" s="34">
+        <v>0</v>
+      </c>
+      <c r="S114" s="32">
         <v>45231</v>
       </c>
-      <c r="T114" s="31">
+      <c r="T114" s="32">
         <v>45413</v>
       </c>
       <c r="U114" s="29">
         <v>49064</v>
       </c>
-      <c r="V114" s="33">
-        <v>0</v>
-      </c>
-      <c r="W114" s="33"/>
+      <c r="V114" s="34">
+        <v>0</v>
+      </c>
+      <c r="W114" s="34"/>
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V115" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W115" s="40"/>
+      <c r="A115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V115" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W115" s="41"/>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
@@ -8915,418 +8915,418 @@
       <c r="W120" s="14"/>
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A121" s="30" t="s">
+      <c r="A121" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B121" s="30" t="s">
+      <c r="B121" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C121" s="30">
+      <c r="C121" s="31">
         <v>2</v>
       </c>
-      <c r="D121" s="30" t="s">
+      <c r="D121" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E121" s="30" t="s">
+      <c r="E121" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F121" s="30">
+      <c r="F121" s="31">
         <v>6</v>
       </c>
-      <c r="G121" s="31">
+      <c r="G121" s="32">
         <v>47604</v>
       </c>
-      <c r="H121" s="31">
+      <c r="H121" s="32">
         <v>47968</v>
       </c>
-      <c r="I121" s="32">
+      <c r="I121" s="33">
         <v>0.1</v>
       </c>
-      <c r="J121" s="33">
+      <c r="J121" s="34">
         <v>2860</v>
       </c>
-      <c r="K121" s="33">
+      <c r="K121" s="34">
         <v>34320</v>
       </c>
-      <c r="L121" s="30" t="s">
+      <c r="L121" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M121" s="34">
-        <v>1</v>
-      </c>
-      <c r="N121" s="32">
+      <c r="M121" s="35">
+        <v>1</v>
+      </c>
+      <c r="N121" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="O121" s="32">
+      <c r="O121" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="P121" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="33">
+      <c r="P121" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="34">
         <v>34320</v>
       </c>
-      <c r="R121" s="33">
-        <v>0</v>
-      </c>
-      <c r="S121" s="31">
+      <c r="R121" s="34">
+        <v>0</v>
+      </c>
+      <c r="S121" s="32">
         <v>45562</v>
       </c>
-      <c r="T121" s="31">
+      <c r="T121" s="32">
         <v>45778</v>
       </c>
       <c r="U121" s="29">
         <v>47603</v>
       </c>
-      <c r="V121" s="33">
-        <v>0</v>
-      </c>
-      <c r="W121" s="33"/>
+      <c r="V121" s="34">
+        <v>0</v>
+      </c>
+      <c r="W121" s="34"/>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A122" s="30" t="s">
+      <c r="A122" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B122" s="30" t="s">
+      <c r="B122" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C122" s="30">
+      <c r="C122" s="31">
         <v>2</v>
       </c>
-      <c r="D122" s="30" t="s">
+      <c r="D122" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E122" s="30" t="s">
+      <c r="E122" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F122" s="30">
+      <c r="F122" s="31">
         <v>7</v>
       </c>
-      <c r="G122" s="31">
+      <c r="G122" s="32">
         <v>47969</v>
       </c>
-      <c r="H122" s="31">
+      <c r="H122" s="32">
         <v>48334</v>
       </c>
-      <c r="I122" s="32">
-        <v>0</v>
-      </c>
-      <c r="J122" s="33">
+      <c r="I122" s="33">
+        <v>0</v>
+      </c>
+      <c r="J122" s="34">
         <v>2860</v>
       </c>
-      <c r="K122" s="33">
+      <c r="K122" s="34">
         <v>34320</v>
       </c>
-      <c r="L122" s="30" t="s">
+      <c r="L122" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M122" s="34">
-        <v>1</v>
-      </c>
-      <c r="N122" s="32">
+      <c r="M122" s="35">
+        <v>1</v>
+      </c>
+      <c r="N122" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="O122" s="32">
+      <c r="O122" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="P122" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q122" s="33">
+      <c r="P122" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="34">
         <v>34320</v>
       </c>
-      <c r="R122" s="33">
-        <v>0</v>
-      </c>
-      <c r="S122" s="31">
+      <c r="R122" s="34">
+        <v>0</v>
+      </c>
+      <c r="S122" s="32">
         <v>45562</v>
       </c>
-      <c r="T122" s="31">
+      <c r="T122" s="32">
         <v>45778</v>
       </c>
       <c r="U122" s="29">
         <v>47603</v>
       </c>
-      <c r="V122" s="33">
-        <v>0</v>
-      </c>
-      <c r="W122" s="33"/>
+      <c r="V122" s="34">
+        <v>0</v>
+      </c>
+      <c r="W122" s="34"/>
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A123" s="30" t="s">
+      <c r="A123" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B123" s="30" t="s">
+      <c r="B123" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C123" s="30">
+      <c r="C123" s="31">
         <v>2</v>
       </c>
-      <c r="D123" s="30" t="s">
+      <c r="D123" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E123" s="30" t="s">
+      <c r="E123" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F123" s="30">
+      <c r="F123" s="31">
         <v>8</v>
       </c>
-      <c r="G123" s="31">
+      <c r="G123" s="32">
         <v>48335</v>
       </c>
-      <c r="H123" s="31">
+      <c r="H123" s="32">
         <v>48699</v>
       </c>
-      <c r="I123" s="32">
-        <v>0</v>
-      </c>
-      <c r="J123" s="33">
+      <c r="I123" s="33">
+        <v>0</v>
+      </c>
+      <c r="J123" s="34">
         <v>2860</v>
       </c>
-      <c r="K123" s="33">
+      <c r="K123" s="34">
         <v>34320</v>
       </c>
-      <c r="L123" s="30" t="s">
+      <c r="L123" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M123" s="34">
-        <v>1</v>
-      </c>
-      <c r="N123" s="32">
+      <c r="M123" s="35">
+        <v>1</v>
+      </c>
+      <c r="N123" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="O123" s="32">
+      <c r="O123" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="P123" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="33">
+      <c r="P123" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="34">
         <v>34320</v>
       </c>
-      <c r="R123" s="33">
-        <v>0</v>
-      </c>
-      <c r="S123" s="31">
+      <c r="R123" s="34">
+        <v>0</v>
+      </c>
+      <c r="S123" s="32">
         <v>45562</v>
       </c>
-      <c r="T123" s="31">
+      <c r="T123" s="32">
         <v>45778</v>
       </c>
       <c r="U123" s="29">
         <v>47603</v>
       </c>
-      <c r="V123" s="33">
-        <v>0</v>
-      </c>
-      <c r="W123" s="33"/>
+      <c r="V123" s="34">
+        <v>0</v>
+      </c>
+      <c r="W123" s="34"/>
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A124" s="30" t="s">
+      <c r="A124" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B124" s="30" t="s">
+      <c r="B124" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C124" s="30">
+      <c r="C124" s="31">
         <v>2</v>
       </c>
-      <c r="D124" s="30" t="s">
+      <c r="D124" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E124" s="30" t="s">
+      <c r="E124" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F124" s="30">
+      <c r="F124" s="31">
         <v>9</v>
       </c>
-      <c r="G124" s="31">
+      <c r="G124" s="32">
         <v>48700</v>
       </c>
-      <c r="H124" s="31">
+      <c r="H124" s="32">
         <v>49064</v>
       </c>
-      <c r="I124" s="32">
-        <v>0</v>
-      </c>
-      <c r="J124" s="33">
+      <c r="I124" s="33">
+        <v>0</v>
+      </c>
+      <c r="J124" s="34">
         <v>2860</v>
       </c>
-      <c r="K124" s="33">
+      <c r="K124" s="34">
         <v>34320</v>
       </c>
-      <c r="L124" s="30" t="s">
+      <c r="L124" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M124" s="34">
-        <v>1</v>
-      </c>
-      <c r="N124" s="32">
+      <c r="M124" s="35">
+        <v>1</v>
+      </c>
+      <c r="N124" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="O124" s="32">
+      <c r="O124" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="P124" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="33">
+      <c r="P124" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="34">
         <v>34320</v>
       </c>
-      <c r="R124" s="33">
-        <v>0</v>
-      </c>
-      <c r="S124" s="31">
+      <c r="R124" s="34">
+        <v>0</v>
+      </c>
+      <c r="S124" s="32">
         <v>45562</v>
       </c>
-      <c r="T124" s="31">
+      <c r="T124" s="32">
         <v>45778</v>
       </c>
       <c r="U124" s="29">
         <v>47603</v>
       </c>
-      <c r="V124" s="33">
-        <v>0</v>
-      </c>
-      <c r="W124" s="33"/>
+      <c r="V124" s="34">
+        <v>0</v>
+      </c>
+      <c r="W124" s="34"/>
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A125" s="30" t="s">
+      <c r="A125" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B125" s="30" t="s">
+      <c r="B125" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C125" s="30">
+      <c r="C125" s="31">
         <v>2</v>
       </c>
-      <c r="D125" s="30" t="s">
+      <c r="D125" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E125" s="30" t="s">
+      <c r="E125" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F125" s="30">
+      <c r="F125" s="31">
         <v>10</v>
       </c>
-      <c r="G125" s="31">
+      <c r="G125" s="32">
         <v>49065</v>
       </c>
-      <c r="H125" s="31">
+      <c r="H125" s="32">
         <v>49429</v>
       </c>
-      <c r="I125" s="32">
-        <v>0</v>
-      </c>
-      <c r="J125" s="33">
+      <c r="I125" s="33">
+        <v>0</v>
+      </c>
+      <c r="J125" s="34">
         <v>2860</v>
       </c>
-      <c r="K125" s="33">
+      <c r="K125" s="34">
         <v>34320</v>
       </c>
-      <c r="L125" s="30" t="s">
+      <c r="L125" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M125" s="34">
-        <v>1</v>
-      </c>
-      <c r="N125" s="32">
+      <c r="M125" s="35">
+        <v>1</v>
+      </c>
+      <c r="N125" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="O125" s="32">
+      <c r="O125" s="33">
         <v>2.4987506246876561E-4</v>
       </c>
-      <c r="P125" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="33">
+      <c r="P125" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="34">
         <v>34320</v>
       </c>
-      <c r="R125" s="33">
-        <v>0</v>
-      </c>
-      <c r="S125" s="31">
+      <c r="R125" s="34">
+        <v>0</v>
+      </c>
+      <c r="S125" s="32">
         <v>45562</v>
       </c>
-      <c r="T125" s="31">
+      <c r="T125" s="32">
         <v>45778</v>
       </c>
       <c r="U125" s="29">
         <v>47603</v>
       </c>
-      <c r="V125" s="33">
-        <v>0</v>
-      </c>
-      <c r="W125" s="33"/>
+      <c r="V125" s="34">
+        <v>0</v>
+      </c>
+      <c r="W125" s="34"/>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V126" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W126" s="40"/>
+      <c r="A126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V126" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W126" s="41"/>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
@@ -10088,73 +10088,73 @@
       <c r="W137" s="14"/>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V138" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W138" s="40"/>
+      <c r="A138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V138" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W138" s="41"/>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
@@ -10502,73 +10502,73 @@
       <c r="W143" s="14"/>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V144" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W144" s="40"/>
+      <c r="A144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V144" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W144" s="41"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
@@ -10914,73 +10914,73 @@
       <c r="W149" s="14"/>
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V150" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W150" s="40"/>
+      <c r="A150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V150" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W150" s="41"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
@@ -11328,73 +11328,73 @@
       <c r="W155" s="14"/>
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V156" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W156" s="40"/>
+      <c r="A156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V156" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W156" s="41"/>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
@@ -12087,694 +12087,694 @@
       <c r="W166" s="14"/>
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A167" s="30" t="s">
+      <c r="A167" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B167" s="30" t="s">
+      <c r="B167" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C167" s="30">
+      <c r="C167" s="31">
         <v>4</v>
       </c>
-      <c r="D167" s="30" t="s">
+      <c r="D167" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="E167" s="30" t="s">
+      <c r="E167" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F167" s="30">
+      <c r="F167" s="31">
         <v>11</v>
       </c>
-      <c r="G167" s="31">
+      <c r="G167" s="32">
         <v>47574</v>
       </c>
-      <c r="H167" s="31">
+      <c r="H167" s="32">
         <v>47938</v>
       </c>
-      <c r="I167" s="32">
+      <c r="I167" s="33">
         <v>1.999954169161966E-2</v>
       </c>
-      <c r="J167" s="33">
+      <c r="J167" s="34">
         <v>9681.25</v>
       </c>
       <c r="K167" s="43">
         <v>116175</v>
       </c>
-      <c r="L167" s="30" t="s">
+      <c r="L167" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M167" s="34">
+      <c r="M167" s="35">
         <v>2508</v>
       </c>
-      <c r="N167" s="32">
+      <c r="N167" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O167" s="32">
+      <c r="O167" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P167" s="32">
+      <c r="P167" s="33">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q167" s="33">
+      <c r="Q167" s="34">
         <v>46.321770334928232</v>
       </c>
-      <c r="R167" s="33">
+      <c r="R167" s="34">
         <v>29043.75</v>
       </c>
-      <c r="S167" s="31">
+      <c r="S167" s="32">
         <v>43866</v>
       </c>
-      <c r="T167" s="31">
+      <c r="T167" s="32">
         <v>44044</v>
       </c>
       <c r="U167" s="29">
         <v>47573</v>
       </c>
-      <c r="V167" s="33">
-        <v>0</v>
-      </c>
-      <c r="W167" s="33"/>
+      <c r="V167" s="34">
+        <v>0</v>
+      </c>
+      <c r="W167" s="34"/>
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A168" s="30" t="s">
+      <c r="A168" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B168" s="30" t="s">
+      <c r="B168" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C168" s="30">
+      <c r="C168" s="31">
         <v>4</v>
       </c>
-      <c r="D168" s="30" t="s">
+      <c r="D168" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="E168" s="30" t="s">
+      <c r="E168" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F168" s="30">
+      <c r="F168" s="31">
         <v>12</v>
       </c>
-      <c r="G168" s="31">
+      <c r="G168" s="32">
         <v>47939</v>
       </c>
-      <c r="H168" s="31">
+      <c r="H168" s="32">
         <v>48304</v>
       </c>
-      <c r="I168" s="32">
+      <c r="I168" s="33">
         <v>1.9999483537766372E-2</v>
       </c>
-      <c r="J168" s="33">
+      <c r="J168" s="34">
         <v>9874.8700000000008</v>
       </c>
       <c r="K168" s="43">
         <v>118498.44</v>
       </c>
-      <c r="L168" s="30" t="s">
+      <c r="L168" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M168" s="34">
+      <c r="M168" s="35">
         <v>2508</v>
       </c>
-      <c r="N168" s="32">
+      <c r="N168" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O168" s="32">
+      <c r="O168" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P168" s="32">
+      <c r="P168" s="33">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q168" s="33">
+      <c r="Q168" s="34">
         <v>47.24818181818182</v>
       </c>
-      <c r="R168" s="33">
+      <c r="R168" s="34">
         <v>29624.61</v>
       </c>
-      <c r="S168" s="31">
+      <c r="S168" s="32">
         <v>43866</v>
       </c>
-      <c r="T168" s="31">
+      <c r="T168" s="32">
         <v>44044</v>
       </c>
       <c r="U168" s="29">
         <v>47573</v>
       </c>
-      <c r="V168" s="33">
-        <v>0</v>
-      </c>
-      <c r="W168" s="33"/>
+      <c r="V168" s="34">
+        <v>0</v>
+      </c>
+      <c r="W168" s="34"/>
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A169" s="30" t="s">
+      <c r="A169" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B169" s="30" t="s">
+      <c r="B169" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C169" s="30">
+      <c r="C169" s="31">
         <v>4</v>
       </c>
-      <c r="D169" s="30" t="s">
+      <c r="D169" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="E169" s="30" t="s">
+      <c r="E169" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F169" s="30">
+      <c r="F169" s="31">
         <v>13</v>
       </c>
-      <c r="G169" s="31">
+      <c r="G169" s="32">
         <v>48305</v>
       </c>
-      <c r="H169" s="31">
+      <c r="H169" s="32">
         <v>48669</v>
       </c>
-      <c r="I169" s="32">
+      <c r="I169" s="33">
         <v>2.0000263294605469E-2</v>
       </c>
-      <c r="J169" s="33">
+      <c r="J169" s="34">
         <v>10072.370000000001</v>
       </c>
       <c r="K169" s="43">
         <v>120868.44</v>
       </c>
-      <c r="L169" s="30" t="s">
+      <c r="L169" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M169" s="34">
+      <c r="M169" s="35">
         <v>2508</v>
       </c>
-      <c r="N169" s="32">
+      <c r="N169" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O169" s="32">
+      <c r="O169" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P169" s="32">
+      <c r="P169" s="33">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q169" s="33">
+      <c r="Q169" s="34">
         <v>48.193157894736842</v>
       </c>
-      <c r="R169" s="33">
+      <c r="R169" s="34">
         <v>30217.11</v>
       </c>
-      <c r="S169" s="31">
+      <c r="S169" s="32">
         <v>43866</v>
       </c>
-      <c r="T169" s="31">
+      <c r="T169" s="32">
         <v>44044</v>
       </c>
       <c r="U169" s="29">
         <v>47573</v>
       </c>
-      <c r="V169" s="33">
-        <v>0</v>
-      </c>
-      <c r="W169" s="33"/>
+      <c r="V169" s="34">
+        <v>0</v>
+      </c>
+      <c r="W169" s="34"/>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A170" s="30" t="s">
+      <c r="A170" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B170" s="30" t="s">
+      <c r="B170" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C170" s="30">
+      <c r="C170" s="31">
         <v>4</v>
       </c>
-      <c r="D170" s="30" t="s">
+      <c r="D170" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="E170" s="30" t="s">
+      <c r="E170" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F170" s="30">
+      <c r="F170" s="31">
         <v>14</v>
       </c>
-      <c r="G170" s="31">
+      <c r="G170" s="32">
         <v>48670</v>
       </c>
-      <c r="H170" s="31">
+      <c r="H170" s="32">
         <v>49034</v>
       </c>
-      <c r="I170" s="32">
+      <c r="I170" s="33">
         <v>2.0000258131899429E-2</v>
       </c>
-      <c r="J170" s="33">
+      <c r="J170" s="34">
         <v>10273.82</v>
       </c>
       <c r="K170" s="43">
         <v>123285.84</v>
       </c>
-      <c r="L170" s="30" t="s">
+      <c r="L170" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M170" s="34">
+      <c r="M170" s="35">
         <v>2508</v>
       </c>
-      <c r="N170" s="32">
+      <c r="N170" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O170" s="32">
+      <c r="O170" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P170" s="32">
+      <c r="P170" s="33">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q170" s="33">
+      <c r="Q170" s="34">
         <v>49.157033492822968</v>
       </c>
-      <c r="R170" s="33">
+      <c r="R170" s="34">
         <v>30821.46</v>
       </c>
-      <c r="S170" s="31">
+      <c r="S170" s="32">
         <v>43866</v>
       </c>
-      <c r="T170" s="31">
+      <c r="T170" s="32">
         <v>44044</v>
       </c>
       <c r="U170" s="29">
         <v>47573</v>
       </c>
-      <c r="V170" s="33">
-        <v>0</v>
-      </c>
-      <c r="W170" s="33"/>
+      <c r="V170" s="34">
+        <v>0</v>
+      </c>
+      <c r="W170" s="34"/>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A171" s="30" t="s">
+      <c r="A171" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B171" s="30" t="s">
+      <c r="B171" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C171" s="30">
+      <c r="C171" s="31">
         <v>4</v>
       </c>
-      <c r="D171" s="30" t="s">
+      <c r="D171" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="E171" s="30" t="s">
+      <c r="E171" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F171" s="30">
+      <c r="F171" s="31">
         <v>15</v>
       </c>
-      <c r="G171" s="31">
+      <c r="G171" s="32">
         <v>49035</v>
       </c>
-      <c r="H171" s="31">
+      <c r="H171" s="32">
         <v>49399</v>
       </c>
-      <c r="I171" s="32">
+      <c r="I171" s="33">
         <v>1.9999377057413836E-2</v>
       </c>
-      <c r="J171" s="33">
+      <c r="J171" s="34">
         <v>10479.289999999999</v>
       </c>
       <c r="K171" s="43">
         <v>125751.48</v>
       </c>
-      <c r="L171" s="30" t="s">
+      <c r="L171" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M171" s="34">
+      <c r="M171" s="35">
         <v>2508</v>
       </c>
-      <c r="N171" s="32">
+      <c r="N171" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O171" s="32">
+      <c r="O171" s="33">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P171" s="32">
+      <c r="P171" s="33">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q171" s="33">
+      <c r="Q171" s="34">
         <v>50.140143540669854</v>
       </c>
-      <c r="R171" s="33">
+      <c r="R171" s="34">
         <v>31437.869999999995</v>
       </c>
-      <c r="S171" s="31">
+      <c r="S171" s="32">
         <v>43866</v>
       </c>
-      <c r="T171" s="31">
+      <c r="T171" s="32">
         <v>44044</v>
       </c>
       <c r="U171" s="29">
         <v>47573</v>
       </c>
-      <c r="V171" s="33">
-        <v>0</v>
-      </c>
-      <c r="W171" s="33"/>
+      <c r="V171" s="34">
+        <v>0</v>
+      </c>
+      <c r="W171" s="34"/>
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A172" s="35" t="s">
+      <c r="A172" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="B172" s="35" t="s">
+      <c r="B172" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C172" s="35">
+      <c r="C172" s="36">
         <v>4</v>
       </c>
-      <c r="D172" s="35" t="s">
+      <c r="D172" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E172" s="35" t="s">
+      <c r="E172" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F172" s="35">
+      <c r="F172" s="36">
         <v>16</v>
       </c>
-      <c r="G172" s="36">
+      <c r="G172" s="37">
         <v>49400</v>
       </c>
-      <c r="H172" s="36">
+      <c r="H172" s="37">
         <v>49765</v>
       </c>
-      <c r="I172" s="37">
+      <c r="I172" s="38">
         <v>2.0000400790511685E-2</v>
       </c>
-      <c r="J172" s="38">
+      <c r="J172" s="39">
         <v>10688.88</v>
       </c>
       <c r="K172" s="44">
         <v>128266.56</v>
       </c>
-      <c r="L172" s="35" t="s">
+      <c r="L172" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M172" s="39">
+      <c r="M172" s="40">
         <v>2508</v>
       </c>
-      <c r="N172" s="37">
+      <c r="N172" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O172" s="37">
+      <c r="O172" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P172" s="37">
+      <c r="P172" s="38">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q172" s="38">
+      <c r="Q172" s="39">
         <v>51.142966507177036</v>
       </c>
-      <c r="R172" s="38">
+      <c r="R172" s="39">
         <v>32066.639999999999</v>
       </c>
-      <c r="S172" s="36">
+      <c r="S172" s="37">
         <v>43866</v>
       </c>
-      <c r="T172" s="36">
+      <c r="T172" s="37">
         <v>44044</v>
       </c>
       <c r="U172" s="29">
         <v>47573</v>
       </c>
-      <c r="V172" s="38">
-        <v>0</v>
-      </c>
-      <c r="W172" s="38"/>
+      <c r="V172" s="39">
+        <v>0</v>
+      </c>
+      <c r="W172" s="39"/>
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A173" s="35" t="s">
+      <c r="A173" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="B173" s="35" t="s">
+      <c r="B173" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C173" s="35">
+      <c r="C173" s="36">
         <v>4</v>
       </c>
-      <c r="D173" s="35" t="s">
+      <c r="D173" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E173" s="35" t="s">
+      <c r="E173" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F173" s="35">
+      <c r="F173" s="36">
         <v>17</v>
       </c>
-      <c r="G173" s="36">
+      <c r="G173" s="37">
         <v>49766</v>
       </c>
-      <c r="H173" s="36">
+      <c r="H173" s="37">
         <v>50130</v>
       </c>
-      <c r="I173" s="37">
+      <c r="I173" s="38">
         <v>2.0000224532411348E-2</v>
       </c>
-      <c r="J173" s="38">
+      <c r="J173" s="39">
         <v>10902.66</v>
       </c>
       <c r="K173" s="44">
         <v>130831.92</v>
       </c>
-      <c r="L173" s="35" t="s">
+      <c r="L173" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M173" s="39">
+      <c r="M173" s="40">
         <v>2508</v>
       </c>
-      <c r="N173" s="37">
+      <c r="N173" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O173" s="37">
+      <c r="O173" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P173" s="37">
+      <c r="P173" s="38">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q173" s="38">
+      <c r="Q173" s="39">
         <v>52.165837320574163</v>
       </c>
-      <c r="R173" s="38">
+      <c r="R173" s="39">
         <v>32707.98</v>
       </c>
-      <c r="S173" s="36">
+      <c r="S173" s="37">
         <v>43866</v>
       </c>
-      <c r="T173" s="36">
+      <c r="T173" s="37">
         <v>44044</v>
       </c>
       <c r="U173" s="29">
         <v>47573</v>
       </c>
-      <c r="V173" s="38">
-        <v>0</v>
-      </c>
-      <c r="W173" s="38"/>
+      <c r="V173" s="39">
+        <v>0</v>
+      </c>
+      <c r="W173" s="39"/>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A174" s="35" t="s">
+      <c r="A174" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="B174" s="35" t="s">
+      <c r="B174" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C174" s="35">
+      <c r="C174" s="36">
         <v>4</v>
       </c>
-      <c r="D174" s="35" t="s">
+      <c r="D174" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E174" s="35" t="s">
+      <c r="E174" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F174" s="35">
+      <c r="F174" s="36">
         <v>18</v>
       </c>
-      <c r="G174" s="36">
+      <c r="G174" s="37">
         <v>50131</v>
       </c>
-      <c r="H174" s="36">
+      <c r="H174" s="37">
         <v>50495</v>
       </c>
-      <c r="I174" s="37">
+      <c r="I174" s="38">
         <v>1.9999706493644576E-2</v>
       </c>
-      <c r="J174" s="38">
+      <c r="J174" s="39">
         <v>11120.71</v>
       </c>
       <c r="K174" s="44">
         <v>133448.51999999999</v>
       </c>
-      <c r="L174" s="35" t="s">
+      <c r="L174" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M174" s="39">
+      <c r="M174" s="40">
         <v>2508</v>
       </c>
-      <c r="N174" s="37">
+      <c r="N174" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O174" s="37">
+      <c r="O174" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P174" s="37">
+      <c r="P174" s="38">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q174" s="38">
+      <c r="Q174" s="39">
         <v>53.20913875598086</v>
       </c>
-      <c r="R174" s="38">
+      <c r="R174" s="39">
         <v>33362.129999999997</v>
       </c>
-      <c r="S174" s="36">
+      <c r="S174" s="37">
         <v>43866</v>
       </c>
-      <c r="T174" s="36">
+      <c r="T174" s="37">
         <v>44044</v>
       </c>
       <c r="U174" s="29">
         <v>47573</v>
       </c>
-      <c r="V174" s="38">
-        <v>0</v>
-      </c>
-      <c r="W174" s="38"/>
+      <c r="V174" s="39">
+        <v>0</v>
+      </c>
+      <c r="W174" s="39"/>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A175" s="35" t="s">
+      <c r="A175" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="B175" s="35" t="s">
+      <c r="B175" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C175" s="35">
+      <c r="C175" s="36">
         <v>4</v>
       </c>
-      <c r="D175" s="35" t="s">
+      <c r="D175" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E175" s="35" t="s">
+      <c r="E175" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F175" s="35">
+      <c r="F175" s="36">
         <v>19</v>
       </c>
-      <c r="G175" s="36">
+      <c r="G175" s="37">
         <v>50496</v>
       </c>
-      <c r="H175" s="36">
+      <c r="H175" s="37">
         <v>50860</v>
       </c>
-      <c r="I175" s="37">
+      <c r="I175" s="38">
         <v>2.0000521549433437E-2</v>
       </c>
-      <c r="J175" s="38">
+      <c r="J175" s="39">
         <v>11343.13</v>
       </c>
       <c r="K175" s="44">
         <v>136117.56</v>
       </c>
-      <c r="L175" s="35" t="s">
+      <c r="L175" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M175" s="39">
+      <c r="M175" s="40">
         <v>2508</v>
       </c>
-      <c r="N175" s="37">
+      <c r="N175" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O175" s="37">
+      <c r="O175" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P175" s="37">
+      <c r="P175" s="38">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q175" s="38">
+      <c r="Q175" s="39">
         <v>54.27334928229665</v>
       </c>
-      <c r="R175" s="38">
+      <c r="R175" s="39">
         <v>34029.39</v>
       </c>
-      <c r="S175" s="36">
+      <c r="S175" s="37">
         <v>43866</v>
       </c>
-      <c r="T175" s="36">
+      <c r="T175" s="37">
         <v>44044</v>
       </c>
       <c r="U175" s="29">
         <v>47573</v>
       </c>
-      <c r="V175" s="38">
-        <v>0</v>
-      </c>
-      <c r="W175" s="38"/>
+      <c r="V175" s="39">
+        <v>0</v>
+      </c>
+      <c r="W175" s="39"/>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A176" s="35" t="s">
+      <c r="A176" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="B176" s="35" t="s">
+      <c r="B176" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C176" s="35">
+      <c r="C176" s="36">
         <v>4</v>
       </c>
-      <c r="D176" s="35" t="s">
+      <c r="D176" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E176" s="35" t="s">
+      <c r="E176" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F176" s="35">
+      <c r="F176" s="36">
         <v>20</v>
       </c>
-      <c r="G176" s="36">
+      <c r="G176" s="37">
         <v>50861</v>
       </c>
-      <c r="H176" s="36">
+      <c r="H176" s="37">
         <v>51226</v>
       </c>
-      <c r="I176" s="37">
+      <c r="I176" s="38">
         <v>1.9999770786370386E-2</v>
       </c>
-      <c r="J176" s="38">
+      <c r="J176" s="39">
         <v>11569.99</v>
       </c>
       <c r="K176" s="44">
         <v>138839.88</v>
       </c>
-      <c r="L176" s="35" t="s">
+      <c r="L176" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M176" s="39">
+      <c r="M176" s="40">
         <v>2508</v>
       </c>
-      <c r="N176" s="37">
+      <c r="N176" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="O176" s="37">
+      <c r="O176" s="38">
         <v>0.43556790552275093</v>
       </c>
-      <c r="P176" s="37">
+      <c r="P176" s="38">
         <v>0.33722850344224098</v>
       </c>
-      <c r="Q176" s="38">
+      <c r="Q176" s="39">
         <v>55.358803827751196</v>
       </c>
-      <c r="R176" s="38">
+      <c r="R176" s="39">
         <v>34709.97</v>
       </c>
-      <c r="S176" s="36">
+      <c r="S176" s="37">
         <v>43866</v>
       </c>
-      <c r="T176" s="36">
+      <c r="T176" s="37">
         <v>44044</v>
       </c>
       <c r="U176" s="29">
         <v>47573</v>
       </c>
-      <c r="V176" s="38">
-        <v>0</v>
-      </c>
-      <c r="W176" s="38"/>
+      <c r="V176" s="39">
+        <v>0</v>
+      </c>
+      <c r="W176" s="39"/>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" s="45" t="s">
@@ -13122,73 +13122,73 @@
       <c r="W181" s="48"/>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V182" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W182" s="40"/>
+      <c r="A182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V182" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W182" s="41"/>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
@@ -13605,211 +13605,211 @@
       <c r="W188" s="14"/>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A189" s="35" t="s">
+      <c r="A189" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="B189" s="35" t="s">
+      <c r="B189" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C189" s="35">
+      <c r="C189" s="36">
         <v>5</v>
       </c>
-      <c r="D189" s="35" t="s">
+      <c r="D189" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="E189" s="35" t="s">
+      <c r="E189" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F189" s="35">
+      <c r="F189" s="36">
         <v>7</v>
       </c>
-      <c r="G189" s="36">
+      <c r="G189" s="37">
         <v>46997</v>
       </c>
-      <c r="H189" s="36">
+      <c r="H189" s="37">
         <v>47361</v>
       </c>
-      <c r="I189" s="37">
+      <c r="I189" s="38">
         <v>6.4516129032258007E-2</v>
       </c>
-      <c r="J189" s="38">
+      <c r="J189" s="39">
         <v>3300</v>
       </c>
       <c r="K189" s="44">
         <v>39600</v>
       </c>
-      <c r="L189" s="35" t="s">
+      <c r="L189" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="M189" s="39">
+      <c r="M189" s="40">
         <v>1189</v>
       </c>
-      <c r="N189" s="37">
+      <c r="N189" s="38">
         <v>0.39</v>
       </c>
-      <c r="O189" s="37">
+      <c r="O189" s="38">
         <v>0.39</v>
       </c>
-      <c r="P189" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q189" s="38">
+      <c r="P189" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q189" s="39">
         <v>33.30529857022708</v>
       </c>
-      <c r="R189" s="38">
+      <c r="R189" s="39">
         <v>9900</v>
       </c>
-      <c r="S189" s="36">
+      <c r="S189" s="37">
         <v>45066</v>
       </c>
-      <c r="T189" s="36">
+      <c r="T189" s="37">
         <v>45108</v>
       </c>
       <c r="U189" s="29">
         <v>46996</v>
       </c>
-      <c r="V189" s="38">
-        <v>0</v>
-      </c>
-      <c r="W189" s="38"/>
+      <c r="V189" s="39">
+        <v>0</v>
+      </c>
+      <c r="W189" s="39"/>
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A190" s="35" t="s">
+      <c r="A190" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="B190" s="35" t="s">
+      <c r="B190" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C190" s="35">
+      <c r="C190" s="36">
         <v>5</v>
       </c>
-      <c r="D190" s="35" t="s">
+      <c r="D190" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="E190" s="35" t="s">
+      <c r="E190" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F190" s="35">
+      <c r="F190" s="36">
         <v>8</v>
       </c>
-      <c r="G190" s="36">
+      <c r="G190" s="37">
         <v>47362</v>
       </c>
-      <c r="H190" s="36">
+      <c r="H190" s="37">
         <v>47726</v>
       </c>
-      <c r="I190" s="37">
+      <c r="I190" s="38">
         <v>3.0303030303030276E-2</v>
       </c>
-      <c r="J190" s="38">
+      <c r="J190" s="39">
         <v>3400</v>
       </c>
       <c r="K190" s="44">
         <v>40800</v>
       </c>
-      <c r="L190" s="35" t="s">
+      <c r="L190" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="M190" s="39">
+      <c r="M190" s="40">
         <v>1189</v>
       </c>
-      <c r="N190" s="37">
+      <c r="N190" s="38">
         <v>0.39</v>
       </c>
-      <c r="O190" s="37">
+      <c r="O190" s="38">
         <v>0.39</v>
       </c>
-      <c r="P190" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q190" s="38">
+      <c r="P190" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="39">
         <v>34.314550042052147</v>
       </c>
-      <c r="R190" s="38">
+      <c r="R190" s="39">
         <v>10200</v>
       </c>
-      <c r="S190" s="36">
+      <c r="S190" s="37">
         <v>45066</v>
       </c>
-      <c r="T190" s="36">
+      <c r="T190" s="37">
         <v>45108</v>
       </c>
       <c r="U190" s="29">
         <v>46996</v>
       </c>
-      <c r="V190" s="38">
-        <v>0</v>
-      </c>
-      <c r="W190" s="38"/>
+      <c r="V190" s="39">
+        <v>0</v>
+      </c>
+      <c r="W190" s="39"/>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V191" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W191" s="40"/>
+      <c r="A191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V191" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W191" s="41"/>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
@@ -13881,73 +13881,73 @@
       <c r="W192" s="14"/>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V193" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W193" s="40"/>
+      <c r="A193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V193" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W193" s="41"/>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
@@ -14019,73 +14019,73 @@
       <c r="W194" s="14"/>
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V195" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W195" s="40"/>
+      <c r="A195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V195" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W195" s="41"/>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
@@ -14139,7 +14139,7 @@
       <c r="Q196" s="14">
         <v>36.124176857949202</v>
       </c>
-      <c r="R196" s="41">
+      <c r="R196" s="30">
         <v>5600</v>
       </c>
       <c r="S196" s="29">
@@ -14157,73 +14157,73 @@
       <c r="W196" s="14"/>
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V197" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W197" s="40"/>
+      <c r="A197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V197" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W197" s="41"/>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
@@ -14277,7 +14277,7 @@
       <c r="Q198" s="14">
         <v>31.838382352941174</v>
       </c>
-      <c r="R198" s="41">
+      <c r="R198" s="30">
         <v>3228</v>
       </c>
       <c r="S198" s="29">
@@ -14346,7 +14346,7 @@
       <c r="Q199" s="14">
         <v>31.838382352941174</v>
       </c>
-      <c r="R199" s="41">
+      <c r="R199" s="30">
         <v>3228</v>
       </c>
       <c r="S199" s="29">
@@ -14364,73 +14364,73 @@
       <c r="W199" s="14"/>
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V200" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W200" s="40"/>
+      <c r="A200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V200" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W200" s="41"/>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
@@ -14553,7 +14553,7 @@
       <c r="Q202" s="14">
         <v>46.764985507246379</v>
       </c>
-      <c r="R202" s="41">
+      <c r="R202" s="30">
         <v>7832</v>
       </c>
       <c r="S202" s="17">
@@ -14622,7 +14622,7 @@
       <c r="Q203" s="14">
         <v>48.164908212560384</v>
       </c>
-      <c r="R203" s="41">
+      <c r="R203" s="30">
         <v>7832</v>
       </c>
       <c r="S203" s="17">
@@ -14691,7 +14691,7 @@
       <c r="Q204" s="14">
         <v>49.61212560386474</v>
       </c>
-      <c r="R204" s="41">
+      <c r="R204" s="30">
         <v>7832</v>
       </c>
       <c r="S204" s="17">
@@ -14760,7 +14760,7 @@
       <c r="Q205" s="14">
         <v>51.097159420289856</v>
       </c>
-      <c r="R205" s="41">
+      <c r="R205" s="30">
         <v>7832</v>
       </c>
       <c r="S205" s="17">
@@ -14829,7 +14829,7 @@
       <c r="Q206" s="14">
         <v>51.097159420289856</v>
       </c>
-      <c r="R206" s="41">
+      <c r="R206" s="30">
         <v>7832</v>
       </c>
       <c r="S206" s="17">
@@ -14847,763 +14847,763 @@
       <c r="W206" s="14"/>
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A207" s="30" t="s">
+      <c r="A207" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B207" s="30" t="s">
+      <c r="B207" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C207" s="30">
+      <c r="C207" s="31">
         <v>3</v>
       </c>
-      <c r="D207" s="30" t="s">
+      <c r="D207" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E207" s="30" t="s">
+      <c r="E207" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F207" s="30">
+      <c r="F207" s="31">
         <v>7</v>
       </c>
-      <c r="G207" s="31">
+      <c r="G207" s="32">
         <v>46811</v>
       </c>
-      <c r="H207" s="31">
+      <c r="H207" s="32">
         <v>47176</v>
       </c>
-      <c r="I207" s="32">
+      <c r="I207" s="33">
         <v>3.0174399212185676E-2</v>
       </c>
-      <c r="J207" s="33">
+      <c r="J207" s="34">
         <v>4540.1125000000002</v>
       </c>
       <c r="K207" s="43">
         <v>54481.35</v>
       </c>
-      <c r="L207" s="30" t="s">
+      <c r="L207" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M207" s="34">
+      <c r="M207" s="35">
         <v>1035</v>
       </c>
-      <c r="N207" s="32">
+      <c r="N207" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O207" s="32">
+      <c r="O207" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P207" s="32">
+      <c r="P207" s="33">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q207" s="33">
+      <c r="Q207" s="34">
         <v>52.638985507246375</v>
       </c>
-      <c r="R207" s="41">
+      <c r="R207" s="30">
         <v>7832</v>
       </c>
-      <c r="S207" s="31">
+      <c r="S207" s="32">
         <v>44685</v>
       </c>
-      <c r="T207" s="31">
+      <c r="T207" s="32">
         <v>44838</v>
       </c>
       <c r="U207" s="29">
         <v>46810</v>
       </c>
-      <c r="V207" s="33">
-        <v>0</v>
-      </c>
-      <c r="W207" s="33"/>
+      <c r="V207" s="34">
+        <v>0</v>
+      </c>
+      <c r="W207" s="34"/>
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A208" s="30" t="s">
+      <c r="A208" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B208" s="30" t="s">
+      <c r="B208" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C208" s="30">
+      <c r="C208" s="31">
         <v>3</v>
       </c>
-      <c r="D208" s="30" t="s">
+      <c r="D208" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E208" s="30" t="s">
+      <c r="E208" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F208" s="30">
+      <c r="F208" s="31">
         <v>8</v>
       </c>
-      <c r="G208" s="31">
+      <c r="G208" s="32">
         <v>47177</v>
       </c>
-      <c r="H208" s="31">
+      <c r="H208" s="32">
         <v>47541</v>
       </c>
-      <c r="I208" s="32">
+      <c r="I208" s="33">
         <v>2.9829290206648595E-2</v>
       </c>
-      <c r="J208" s="33">
+      <c r="J208" s="34">
         <v>4675.5408333333335</v>
       </c>
       <c r="K208" s="43">
         <v>56106.49</v>
       </c>
-      <c r="L208" s="30" t="s">
+      <c r="L208" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M208" s="34">
+      <c r="M208" s="35">
         <v>1035</v>
       </c>
-      <c r="N208" s="32">
+      <c r="N208" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O208" s="32">
+      <c r="O208" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P208" s="32">
+      <c r="P208" s="33">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q208" s="33">
+      <c r="Q208" s="34">
         <v>54.209169082125605</v>
       </c>
-      <c r="R208" s="41">
+      <c r="R208" s="30">
         <v>7832</v>
       </c>
-      <c r="S208" s="31">
+      <c r="S208" s="32">
         <v>44685</v>
       </c>
-      <c r="T208" s="31">
+      <c r="T208" s="32">
         <v>44838</v>
       </c>
       <c r="U208" s="29">
         <v>46810</v>
       </c>
-      <c r="V208" s="33">
-        <v>0</v>
-      </c>
-      <c r="W208" s="33"/>
+      <c r="V208" s="34">
+        <v>0</v>
+      </c>
+      <c r="W208" s="34"/>
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A209" s="30" t="s">
+      <c r="A209" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B209" s="30" t="s">
+      <c r="B209" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C209" s="30">
+      <c r="C209" s="31">
         <v>3</v>
       </c>
-      <c r="D209" s="30" t="s">
+      <c r="D209" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E209" s="30" t="s">
+      <c r="E209" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F209" s="30">
+      <c r="F209" s="31">
         <v>9</v>
       </c>
-      <c r="G209" s="31">
+      <c r="G209" s="32">
         <v>47542</v>
       </c>
-      <c r="H209" s="31">
+      <c r="H209" s="32">
         <v>47906</v>
       </c>
-      <c r="I209" s="32">
+      <c r="I209" s="33">
         <v>3.0012214273250848E-2</v>
       </c>
-      <c r="J209" s="33">
+      <c r="J209" s="34">
         <v>4815.8641666666672</v>
       </c>
       <c r="K209" s="43">
         <v>57790.37</v>
       </c>
-      <c r="L209" s="30" t="s">
+      <c r="L209" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M209" s="34">
+      <c r="M209" s="35">
         <v>1035</v>
       </c>
-      <c r="N209" s="32">
+      <c r="N209" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O209" s="32">
+      <c r="O209" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P209" s="32">
+      <c r="P209" s="33">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q209" s="33">
+      <c r="Q209" s="34">
         <v>55.836106280193242</v>
       </c>
-      <c r="R209" s="41">
+      <c r="R209" s="30">
         <v>7832</v>
       </c>
-      <c r="S209" s="31">
+      <c r="S209" s="32">
         <v>44685</v>
       </c>
-      <c r="T209" s="31">
+      <c r="T209" s="32">
         <v>44838</v>
       </c>
       <c r="U209" s="29">
         <v>46810</v>
       </c>
-      <c r="V209" s="33">
-        <v>0</v>
-      </c>
-      <c r="W209" s="33"/>
+      <c r="V209" s="34">
+        <v>0</v>
+      </c>
+      <c r="W209" s="34"/>
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A210" s="30" t="s">
+      <c r="A210" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B210" s="30" t="s">
+      <c r="B210" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C210" s="30">
+      <c r="C210" s="31">
         <v>3</v>
       </c>
-      <c r="D210" s="30" t="s">
+      <c r="D210" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E210" s="30" t="s">
+      <c r="E210" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F210" s="30">
+      <c r="F210" s="31">
         <v>10</v>
       </c>
-      <c r="G210" s="31">
+      <c r="G210" s="32">
         <v>47907</v>
       </c>
-      <c r="H210" s="31">
+      <c r="H210" s="32">
         <v>48271</v>
       </c>
-      <c r="I210" s="32">
+      <c r="I210" s="33">
         <v>2.9984753515161611E-2</v>
       </c>
-      <c r="J210" s="33">
+      <c r="J210" s="34">
         <v>4960.2666666666664</v>
       </c>
       <c r="K210" s="43">
         <v>59523.199999999997</v>
       </c>
-      <c r="L210" s="30" t="s">
+      <c r="L210" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M210" s="34">
+      <c r="M210" s="35">
         <v>1035</v>
       </c>
-      <c r="N210" s="32">
+      <c r="N210" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O210" s="32">
+      <c r="O210" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P210" s="32">
+      <c r="P210" s="33">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q210" s="33">
+      <c r="Q210" s="34">
         <v>57.510338164251202</v>
       </c>
-      <c r="R210" s="41">
+      <c r="R210" s="30">
         <v>7832</v>
       </c>
-      <c r="S210" s="31">
+      <c r="S210" s="32">
         <v>44685</v>
       </c>
-      <c r="T210" s="31">
+      <c r="T210" s="32">
         <v>44838</v>
       </c>
       <c r="U210" s="29">
         <v>46810</v>
       </c>
-      <c r="V210" s="33">
-        <v>0</v>
-      </c>
-      <c r="W210" s="33"/>
+      <c r="V210" s="34">
+        <v>0</v>
+      </c>
+      <c r="W210" s="34"/>
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A211" s="30" t="s">
+      <c r="A211" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B211" s="30" t="s">
+      <c r="B211" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C211" s="30">
+      <c r="C211" s="31">
         <v>3</v>
       </c>
-      <c r="D211" s="30" t="s">
+      <c r="D211" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E211" s="30" t="s">
+      <c r="E211" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F211" s="30">
+      <c r="F211" s="31">
         <v>11</v>
       </c>
-      <c r="G211" s="31">
+      <c r="G211" s="32">
         <v>48272</v>
       </c>
-      <c r="H211" s="31">
+      <c r="H211" s="32">
         <v>48637</v>
       </c>
-      <c r="I211" s="32">
+      <c r="I211" s="33">
         <v>3.0098684210526416E-2</v>
       </c>
-      <c r="J211" s="33">
+      <c r="J211" s="34">
         <v>5109.5641666666661</v>
       </c>
       <c r="K211" s="43">
         <v>61314.77</v>
       </c>
-      <c r="L211" s="30" t="s">
+      <c r="L211" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M211" s="34">
+      <c r="M211" s="35">
         <v>1035</v>
       </c>
-      <c r="N211" s="32">
+      <c r="N211" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O211" s="32">
+      <c r="O211" s="33">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P211" s="32">
+      <c r="P211" s="33">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q211" s="33">
+      <c r="Q211" s="34">
         <v>59.241323671497582</v>
       </c>
-      <c r="R211" s="41">
+      <c r="R211" s="30">
         <v>7832</v>
       </c>
-      <c r="S211" s="31">
+      <c r="S211" s="32">
         <v>44685</v>
       </c>
-      <c r="T211" s="31">
+      <c r="T211" s="32">
         <v>44838</v>
       </c>
       <c r="U211" s="29">
         <v>46810</v>
       </c>
-      <c r="V211" s="33">
-        <v>0</v>
-      </c>
-      <c r="W211" s="33"/>
+      <c r="V211" s="34">
+        <v>0</v>
+      </c>
+      <c r="W211" s="34"/>
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A212" s="35" t="s">
+      <c r="A212" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="B212" s="35" t="s">
+      <c r="B212" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C212" s="35">
+      <c r="C212" s="36">
         <v>3</v>
       </c>
-      <c r="D212" s="35" t="s">
+      <c r="D212" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E212" s="35" t="s">
+      <c r="E212" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F212" s="35">
+      <c r="F212" s="36">
         <v>12</v>
       </c>
-      <c r="G212" s="36">
+      <c r="G212" s="37">
         <v>48638</v>
       </c>
-      <c r="H212" s="36">
+      <c r="H212" s="37">
         <v>49002</v>
       </c>
-      <c r="I212" s="37">
+      <c r="I212" s="38">
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="J212" s="38">
+      <c r="J212" s="39">
         <v>5211.7554499999997</v>
       </c>
       <c r="K212" s="44">
         <v>62541.065399999999</v>
       </c>
-      <c r="L212" s="35" t="s">
+      <c r="L212" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M212" s="39">
+      <c r="M212" s="40">
         <v>1035</v>
       </c>
-      <c r="N212" s="37">
+      <c r="N212" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O212" s="37">
+      <c r="O212" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P212" s="37">
+      <c r="P212" s="38">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q212" s="38">
+      <c r="Q212" s="39">
         <v>60.426150144927533</v>
       </c>
-      <c r="R212" s="41">
+      <c r="R212" s="30">
         <v>7832</v>
       </c>
-      <c r="S212" s="36">
+      <c r="S212" s="37">
         <v>44685</v>
       </c>
-      <c r="T212" s="36">
+      <c r="T212" s="37">
         <v>44838</v>
       </c>
       <c r="U212" s="29">
         <v>46810</v>
       </c>
-      <c r="V212" s="38">
-        <v>0</v>
-      </c>
-      <c r="W212" s="38"/>
+      <c r="V212" s="39">
+        <v>0</v>
+      </c>
+      <c r="W212" s="39"/>
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A213" s="35" t="s">
+      <c r="A213" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="B213" s="35" t="s">
+      <c r="B213" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C213" s="35">
+      <c r="C213" s="36">
         <v>3</v>
       </c>
-      <c r="D213" s="35" t="s">
+      <c r="D213" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E213" s="35" t="s">
+      <c r="E213" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F213" s="35">
+      <c r="F213" s="36">
         <v>13</v>
       </c>
-      <c r="G213" s="36">
+      <c r="G213" s="37">
         <v>49003</v>
       </c>
-      <c r="H213" s="36">
+      <c r="H213" s="37">
         <v>49367</v>
       </c>
-      <c r="I213" s="37">
+      <c r="I213" s="38">
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="J213" s="38">
+      <c r="J213" s="39">
         <v>5315.9905589999998</v>
       </c>
       <c r="K213" s="44">
         <v>63791.886707999998</v>
       </c>
-      <c r="L213" s="35" t="s">
+      <c r="L213" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M213" s="39">
+      <c r="M213" s="40">
         <v>1035</v>
       </c>
-      <c r="N213" s="37">
+      <c r="N213" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O213" s="37">
+      <c r="O213" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P213" s="37">
+      <c r="P213" s="38">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q213" s="38">
+      <c r="Q213" s="39">
         <v>61.634673147826085</v>
       </c>
-      <c r="R213" s="41">
+      <c r="R213" s="30">
         <v>7832</v>
       </c>
-      <c r="S213" s="36">
+      <c r="S213" s="37">
         <v>44685</v>
       </c>
-      <c r="T213" s="36">
+      <c r="T213" s="37">
         <v>44838</v>
       </c>
       <c r="U213" s="29">
         <v>46810</v>
       </c>
-      <c r="V213" s="38">
-        <v>0</v>
-      </c>
-      <c r="W213" s="38"/>
+      <c r="V213" s="39">
+        <v>0</v>
+      </c>
+      <c r="W213" s="39"/>
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A214" s="35" t="s">
+      <c r="A214" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="B214" s="35" t="s">
+      <c r="B214" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C214" s="35">
+      <c r="C214" s="36">
         <v>3</v>
       </c>
-      <c r="D214" s="35" t="s">
+      <c r="D214" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E214" s="35" t="s">
+      <c r="E214" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F214" s="35">
+      <c r="F214" s="36">
         <v>14</v>
       </c>
-      <c r="G214" s="36">
+      <c r="G214" s="37">
         <v>49368</v>
       </c>
-      <c r="H214" s="36">
+      <c r="H214" s="37">
         <v>49732</v>
       </c>
-      <c r="I214" s="37">
+      <c r="I214" s="38">
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="J214" s="38">
+      <c r="J214" s="39">
         <v>5422.3103701800001</v>
       </c>
       <c r="K214" s="44">
         <v>65067.724442159997</v>
       </c>
-      <c r="L214" s="35" t="s">
+      <c r="L214" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M214" s="39">
+      <c r="M214" s="40">
         <v>1035</v>
       </c>
-      <c r="N214" s="37">
+      <c r="N214" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O214" s="37">
+      <c r="O214" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P214" s="37">
+      <c r="P214" s="38">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q214" s="38">
+      <c r="Q214" s="39">
         <v>62.867366610782604</v>
       </c>
-      <c r="R214" s="41">
+      <c r="R214" s="30">
         <v>7832</v>
       </c>
-      <c r="S214" s="36">
+      <c r="S214" s="37">
         <v>44685</v>
       </c>
-      <c r="T214" s="36">
+      <c r="T214" s="37">
         <v>44838</v>
       </c>
       <c r="U214" s="29">
         <v>46810</v>
       </c>
-      <c r="V214" s="38">
-        <v>0</v>
-      </c>
-      <c r="W214" s="38"/>
+      <c r="V214" s="39">
+        <v>0</v>
+      </c>
+      <c r="W214" s="39"/>
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A215" s="35" t="s">
+      <c r="A215" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="B215" s="35" t="s">
+      <c r="B215" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C215" s="35">
+      <c r="C215" s="36">
         <v>3</v>
       </c>
-      <c r="D215" s="35" t="s">
+      <c r="D215" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E215" s="35" t="s">
+      <c r="E215" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F215" s="35">
+      <c r="F215" s="36">
         <v>15</v>
       </c>
-      <c r="G215" s="36">
+      <c r="G215" s="37">
         <v>49733</v>
       </c>
-      <c r="H215" s="36">
+      <c r="H215" s="37">
         <v>50098</v>
       </c>
-      <c r="I215" s="37">
+      <c r="I215" s="38">
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="J215" s="38">
+      <c r="J215" s="39">
         <v>5530.7565775836001</v>
       </c>
       <c r="K215" s="44">
         <v>66369.078931003198</v>
       </c>
-      <c r="L215" s="35" t="s">
+      <c r="L215" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M215" s="39">
+      <c r="M215" s="40">
         <v>1035</v>
       </c>
-      <c r="N215" s="37">
+      <c r="N215" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O215" s="37">
+      <c r="O215" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P215" s="37">
+      <c r="P215" s="38">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q215" s="38">
+      <c r="Q215" s="39">
         <v>64.124713942998255</v>
       </c>
-      <c r="R215" s="41">
+      <c r="R215" s="30">
         <v>7832</v>
       </c>
-      <c r="S215" s="36">
+      <c r="S215" s="37">
         <v>44685</v>
       </c>
-      <c r="T215" s="36">
+      <c r="T215" s="37">
         <v>44838</v>
       </c>
       <c r="U215" s="29">
         <v>46810</v>
       </c>
-      <c r="V215" s="38">
-        <v>0</v>
-      </c>
-      <c r="W215" s="38"/>
+      <c r="V215" s="39">
+        <v>0</v>
+      </c>
+      <c r="W215" s="39"/>
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A216" s="35" t="s">
+      <c r="A216" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="B216" s="35" t="s">
+      <c r="B216" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C216" s="35">
+      <c r="C216" s="36">
         <v>3</v>
       </c>
-      <c r="D216" s="35" t="s">
+      <c r="D216" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E216" s="35" t="s">
+      <c r="E216" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F216" s="35">
+      <c r="F216" s="36">
         <v>16</v>
       </c>
-      <c r="G216" s="36">
+      <c r="G216" s="37">
         <v>50099</v>
       </c>
-      <c r="H216" s="36">
+      <c r="H216" s="37">
         <v>50463</v>
       </c>
-      <c r="I216" s="37">
+      <c r="I216" s="38">
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="J216" s="38">
+      <c r="J216" s="39">
         <v>5641.3717091352728</v>
       </c>
       <c r="K216" s="44">
         <v>67696.46050962327</v>
       </c>
-      <c r="L216" s="35" t="s">
+      <c r="L216" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M216" s="39">
+      <c r="M216" s="40">
         <v>1035</v>
       </c>
-      <c r="N216" s="37">
+      <c r="N216" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="O216" s="37">
+      <c r="O216" s="38">
         <v>0.21148344912137312</v>
       </c>
-      <c r="P216" s="37">
+      <c r="P216" s="38">
         <v>0.12689006947282386</v>
       </c>
-      <c r="Q216" s="38">
+      <c r="Q216" s="39">
         <v>65.407208221858227</v>
       </c>
-      <c r="R216" s="41">
+      <c r="R216" s="30">
         <v>7832</v>
       </c>
-      <c r="S216" s="36">
+      <c r="S216" s="37">
         <v>44685</v>
       </c>
-      <c r="T216" s="36">
+      <c r="T216" s="37">
         <v>44838</v>
       </c>
       <c r="U216" s="29">
         <v>46810</v>
       </c>
-      <c r="V216" s="38">
-        <v>0</v>
-      </c>
-      <c r="W216" s="38"/>
+      <c r="V216" s="39">
+        <v>0</v>
+      </c>
+      <c r="W216" s="39"/>
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V217" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W217" s="40"/>
+      <c r="A217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V217" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W217" s="41"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
@@ -15657,7 +15657,7 @@
       <c r="Q218" s="14">
         <v>36.852367688022284</v>
       </c>
-      <c r="R218" s="41">
+      <c r="R218" s="30">
         <v>3000</v>
       </c>
       <c r="S218" s="29">
@@ -15726,7 +15726,7 @@
       <c r="Q219" s="14">
         <v>36.852367688022284</v>
       </c>
-      <c r="R219" s="41">
+      <c r="R219" s="30">
         <v>3000</v>
       </c>
       <c r="S219" s="17">
@@ -15795,7 +15795,7 @@
       <c r="Q220" s="14">
         <v>36.852367688022284</v>
       </c>
-      <c r="R220" s="41">
+      <c r="R220" s="30">
         <v>3000</v>
       </c>
       <c r="S220" s="17">
@@ -15864,7 +15864,7 @@
       <c r="Q221" s="14">
         <v>38.694986072423397</v>
       </c>
-      <c r="R221" s="41">
+      <c r="R221" s="30">
         <v>3000</v>
       </c>
       <c r="S221" s="17">
@@ -15933,7 +15933,7 @@
       <c r="Q222" s="14">
         <v>38.694986072423397</v>
       </c>
-      <c r="R222" s="41">
+      <c r="R222" s="30">
         <v>3000</v>
       </c>
       <c r="S222" s="17">
@@ -16002,7 +16002,7 @@
       <c r="Q223" s="14">
         <v>38.694986072423397</v>
       </c>
-      <c r="R223" s="41">
+      <c r="R223" s="30">
         <v>3000</v>
       </c>
       <c r="S223" s="17">
@@ -16020,73 +16020,73 @@
       <c r="W223" s="14"/>
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V224" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W224" s="40"/>
+      <c r="A224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V224" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W224" s="41"/>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
@@ -16158,73 +16158,73 @@
       <c r="W225" s="14"/>
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V226" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W226" s="40"/>
+      <c r="A226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V226" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W226" s="41"/>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
@@ -16365,142 +16365,142 @@
       <c r="W228" s="14"/>
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A229" s="30" t="s">
+      <c r="A229" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="B229" s="30" t="s">
+      <c r="B229" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C229" s="30">
+      <c r="C229" s="31">
         <v>202</v>
       </c>
-      <c r="D229" s="30" t="s">
+      <c r="D229" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E229" s="30" t="s">
+      <c r="E229" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F229" s="30">
-        <v>1</v>
-      </c>
-      <c r="G229" s="31">
+      <c r="F229" s="31">
+        <v>1</v>
+      </c>
+      <c r="G229" s="32">
         <v>46539</v>
       </c>
-      <c r="H229" s="31">
+      <c r="H229" s="32">
         <v>46904</v>
       </c>
-      <c r="I229" s="32">
+      <c r="I229" s="33">
         <v>1.2380952380952381</v>
       </c>
-      <c r="J229" s="33">
+      <c r="J229" s="34">
         <v>1300</v>
       </c>
       <c r="K229" s="43">
         <v>15600</v>
       </c>
-      <c r="L229" s="30" t="s">
+      <c r="L229" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M229" s="34">
+      <c r="M229" s="35">
         <v>607</v>
       </c>
-      <c r="N229" s="32">
+      <c r="N229" s="33">
         <v>0.12339906485057939</v>
       </c>
-      <c r="O229" s="32">
+      <c r="O229" s="33">
         <v>0.12339906485057939</v>
       </c>
-      <c r="P229" s="32">
+      <c r="P229" s="33">
         <v>4.9359625940231758E-2</v>
       </c>
-      <c r="Q229" s="33">
+      <c r="Q229" s="34">
         <v>25.7001647446458</v>
       </c>
-      <c r="R229" s="41">
+      <c r="R229" s="30">
         <v>1300</v>
       </c>
-      <c r="S229" s="31">
+      <c r="S229" s="32">
         <v>41640</v>
       </c>
-      <c r="T229" s="31">
+      <c r="T229" s="32">
         <v>41640</v>
       </c>
       <c r="U229" s="29">
         <v>46538</v>
       </c>
-      <c r="V229" s="33">
-        <v>0</v>
-      </c>
-      <c r="W229" s="33"/>
+      <c r="V229" s="34">
+        <v>0</v>
+      </c>
+      <c r="W229" s="34"/>
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V230" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W230" s="40"/>
+      <c r="A230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V230" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W230" s="41"/>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
@@ -16623,7 +16623,7 @@
       <c r="Q232" s="14">
         <v>27.009646302250804</v>
       </c>
-      <c r="R232" s="41">
+      <c r="R232" s="30">
         <v>2800</v>
       </c>
       <c r="S232" s="17">
@@ -16641,211 +16641,211 @@
       <c r="W232" s="14"/>
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A233" s="30" t="s">
+      <c r="A233" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="B233" s="30" t="s">
+      <c r="B233" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C233" s="30">
+      <c r="C233" s="31">
         <v>203</v>
       </c>
-      <c r="D233" s="30" t="s">
+      <c r="D233" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E233" s="30" t="s">
+      <c r="E233" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F233" s="30">
+      <c r="F233" s="31">
         <v>3</v>
       </c>
-      <c r="G233" s="31">
+      <c r="G233" s="32">
         <v>46539</v>
       </c>
-      <c r="H233" s="31">
+      <c r="H233" s="32">
         <v>46904</v>
       </c>
-      <c r="I233" s="32">
+      <c r="I233" s="33">
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="J233" s="33">
+      <c r="J233" s="34">
         <v>1470</v>
       </c>
       <c r="K233" s="43">
         <v>17640</v>
       </c>
-      <c r="L233" s="30" t="s">
+      <c r="L233" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M233" s="34">
+      <c r="M233" s="35">
         <v>622</v>
       </c>
-      <c r="N233" s="32">
+      <c r="N233" s="33">
         <v>0.12644846513519009</v>
       </c>
-      <c r="O233" s="32">
+      <c r="O233" s="33">
         <v>0.12644846513519009</v>
       </c>
-      <c r="P233" s="32">
+      <c r="P233" s="33">
         <v>5.0579386054076039E-2</v>
       </c>
-      <c r="Q233" s="33">
+      <c r="Q233" s="34">
         <v>28.360128617363344</v>
       </c>
-      <c r="R233" s="41">
+      <c r="R233" s="30">
         <v>2800</v>
       </c>
-      <c r="S233" s="31">
+      <c r="S233" s="32">
         <v>45762</v>
       </c>
-      <c r="T233" s="31">
+      <c r="T233" s="32">
         <v>45782</v>
       </c>
       <c r="U233" s="29">
         <v>46538</v>
       </c>
-      <c r="V233" s="33">
-        <v>0</v>
-      </c>
-      <c r="W233" s="33"/>
+      <c r="V233" s="34">
+        <v>0</v>
+      </c>
+      <c r="W233" s="34"/>
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A234" s="35" t="s">
+      <c r="A234" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="B234" s="35" t="s">
+      <c r="B234" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C234" s="35">
+      <c r="C234" s="36">
         <v>203</v>
       </c>
-      <c r="D234" s="35" t="s">
+      <c r="D234" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E234" s="35" t="s">
+      <c r="E234" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="F234" s="35">
+      <c r="F234" s="36">
         <v>4</v>
       </c>
-      <c r="G234" s="36">
+      <c r="G234" s="37">
         <v>46905</v>
       </c>
-      <c r="H234" s="36">
+      <c r="H234" s="37">
         <v>47269</v>
       </c>
-      <c r="I234" s="37">
+      <c r="I234" s="38">
         <v>3.0612244897959107E-2</v>
       </c>
-      <c r="J234" s="38">
+      <c r="J234" s="39">
         <v>1515</v>
       </c>
       <c r="K234" s="44">
         <v>18180</v>
       </c>
-      <c r="L234" s="35" t="s">
+      <c r="L234" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="M234" s="39">
+      <c r="M234" s="40">
         <v>622</v>
       </c>
-      <c r="N234" s="37">
+      <c r="N234" s="38">
         <v>0.12644846513519009</v>
       </c>
-      <c r="O234" s="37">
+      <c r="O234" s="38">
         <v>0.12644846513519009</v>
       </c>
-      <c r="P234" s="37">
+      <c r="P234" s="38">
         <v>5.0579386054076039E-2</v>
       </c>
-      <c r="Q234" s="38">
+      <c r="Q234" s="39">
         <v>29.228295819935692</v>
       </c>
-      <c r="R234" s="41">
+      <c r="R234" s="30">
         <v>2800</v>
       </c>
-      <c r="S234" s="36">
+      <c r="S234" s="37">
         <v>45762</v>
       </c>
-      <c r="T234" s="36">
+      <c r="T234" s="37">
         <v>45782</v>
       </c>
       <c r="U234" s="29">
         <v>46538</v>
       </c>
-      <c r="V234" s="38">
-        <v>0</v>
-      </c>
-      <c r="W234" s="38"/>
+      <c r="V234" s="39">
+        <v>0</v>
+      </c>
+      <c r="W234" s="39"/>
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V235" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W235" s="40"/>
+      <c r="A235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V235" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W235" s="41"/>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
@@ -16917,73 +16917,73 @@
       <c r="W236" s="14"/>
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V237" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W237" s="40"/>
+      <c r="A237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V237" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W237" s="41"/>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
@@ -17193,73 +17193,73 @@
       <c r="W240" s="14"/>
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V241" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W241" s="40"/>
+      <c r="A241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V241" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W241" s="41"/>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
@@ -17469,73 +17469,73 @@
       <c r="W244" s="14"/>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V245" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W245" s="40"/>
+      <c r="A245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V245" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W245" s="41"/>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
@@ -17589,7 +17589,7 @@
       <c r="Q246" s="14">
         <v>23.549488054607508</v>
       </c>
-      <c r="R246" s="41">
+      <c r="R246" s="30">
         <v>2000</v>
       </c>
       <c r="S246" s="29">
@@ -17658,7 +17658,7 @@
       <c r="Q247" s="14">
         <v>25.597269624573379</v>
       </c>
-      <c r="R247" s="41">
+      <c r="R247" s="30">
         <v>2000</v>
       </c>
       <c r="S247" s="29">
@@ -17729,7 +17729,7 @@
       <c r="Q248" s="14">
         <v>26.877133105802049</v>
       </c>
-      <c r="R248" s="41">
+      <c r="R248" s="30">
         <v>2000</v>
       </c>
       <c r="S248" s="29">
@@ -17800,7 +17800,7 @@
       <c r="Q249" s="14">
         <v>28.220989761092149</v>
       </c>
-      <c r="R249" s="41">
+      <c r="R249" s="30">
         <v>2000</v>
       </c>
       <c r="S249" s="29">
@@ -17871,7 +17871,7 @@
       <c r="Q250" s="14">
         <v>29.632039249146757</v>
       </c>
-      <c r="R250" s="41">
+      <c r="R250" s="30">
         <v>2000</v>
       </c>
       <c r="S250" s="29">
@@ -17942,7 +17942,7 @@
       <c r="Q251" s="14">
         <v>31.113641211604097</v>
       </c>
-      <c r="R251" s="41">
+      <c r="R251" s="30">
         <v>2000</v>
       </c>
       <c r="S251" s="29">
@@ -17962,73 +17962,73 @@
       </c>
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V252" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W252" s="40"/>
+      <c r="A252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V252" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W252" s="41"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
@@ -18307,211 +18307,211 @@
       <c r="W256" s="14"/>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A257" s="30" t="s">
+      <c r="A257" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B257" s="30" t="s">
+      <c r="B257" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C257" s="30">
+      <c r="C257" s="31">
         <v>207</v>
       </c>
-      <c r="D257" s="30" t="s">
+      <c r="D257" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E257" s="30" t="s">
+      <c r="E257" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F257" s="30">
+      <c r="F257" s="31">
         <v>5</v>
       </c>
-      <c r="G257" s="31">
+      <c r="G257" s="32">
         <v>47484</v>
       </c>
-      <c r="H257" s="31">
+      <c r="H257" s="32">
         <v>47848</v>
       </c>
-      <c r="I257" s="32">
+      <c r="I257" s="33">
         <v>5.0000092411363495E-2</v>
       </c>
-      <c r="J257" s="33">
+      <c r="J257" s="34">
         <v>1893.7066666666667</v>
       </c>
       <c r="K257" s="43">
         <v>22724.48</v>
       </c>
-      <c r="L257" s="30" t="s">
+      <c r="L257" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M257" s="34">
+      <c r="M257" s="35">
         <v>793</v>
       </c>
-      <c r="N257" s="32">
+      <c r="N257" s="33">
         <v>0.16121162837975198</v>
       </c>
-      <c r="O257" s="32">
+      <c r="O257" s="33">
         <v>0.16121162837975198</v>
       </c>
-      <c r="P257" s="32">
+      <c r="P257" s="33">
         <v>6.448465135190079E-2</v>
       </c>
-      <c r="Q257" s="33">
+      <c r="Q257" s="34">
         <v>28.656343001261032</v>
       </c>
-      <c r="R257" s="33">
+      <c r="R257" s="34">
         <v>1893.7066666666667</v>
       </c>
-      <c r="S257" s="31">
+      <c r="S257" s="32">
         <v>39520</v>
       </c>
-      <c r="T257" s="31">
+      <c r="T257" s="32">
         <v>39520</v>
       </c>
       <c r="U257" s="29">
         <v>47483</v>
       </c>
-      <c r="V257" s="33">
-        <v>0</v>
-      </c>
-      <c r="W257" s="33"/>
+      <c r="V257" s="34">
+        <v>0</v>
+      </c>
+      <c r="W257" s="34"/>
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A258" s="30" t="s">
+      <c r="A258" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B258" s="30" t="s">
+      <c r="B258" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C258" s="30">
+      <c r="C258" s="31">
         <v>207</v>
       </c>
-      <c r="D258" s="30" t="s">
+      <c r="D258" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E258" s="30" t="s">
+      <c r="E258" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F258" s="30">
+      <c r="F258" s="31">
         <v>6</v>
       </c>
-      <c r="G258" s="31">
+      <c r="G258" s="32">
         <v>47849</v>
       </c>
-      <c r="H258" s="31">
+      <c r="H258" s="32">
         <v>48213</v>
       </c>
-      <c r="I258" s="32">
+      <c r="I258" s="33">
         <v>3.0002006646576707E-2</v>
       </c>
-      <c r="J258" s="33">
+      <c r="J258" s="34">
         <v>1950.5216666666665</v>
       </c>
       <c r="K258" s="43">
         <v>23406.26</v>
       </c>
-      <c r="L258" s="30" t="s">
+      <c r="L258" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M258" s="34">
+      <c r="M258" s="35">
         <v>793</v>
       </c>
-      <c r="N258" s="32">
+      <c r="N258" s="33">
         <v>0.16121162837975198</v>
       </c>
-      <c r="O258" s="32">
+      <c r="O258" s="33">
         <v>0.16121162837975198</v>
       </c>
-      <c r="P258" s="32">
+      <c r="P258" s="33">
         <v>6.448465135190079E-2</v>
       </c>
-      <c r="Q258" s="33">
+      <c r="Q258" s="34">
         <v>29.516090794451447</v>
       </c>
-      <c r="R258" s="33">
+      <c r="R258" s="34">
         <v>1950.5216666666665</v>
       </c>
-      <c r="S258" s="31">
+      <c r="S258" s="32">
         <v>39520</v>
       </c>
-      <c r="T258" s="31">
+      <c r="T258" s="32">
         <v>39520</v>
       </c>
       <c r="U258" s="29">
         <v>47483</v>
       </c>
-      <c r="V258" s="33">
-        <v>0</v>
-      </c>
-      <c r="W258" s="33"/>
+      <c r="V258" s="34">
+        <v>0</v>
+      </c>
+      <c r="W258" s="34"/>
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="B259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="I259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="K259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="L259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="M259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="N259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="O259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="P259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="R259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="S259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="U259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="V259" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="W259" s="40"/>
+      <c r="A259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="K259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="L259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="M259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="O259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="P259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="R259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="S259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="T259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="U259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="V259" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W259" s="41"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A71F962-7529-46C5-A092-563D7194B201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C428DD5D-2C05-4E61-AD93-DED4470F1432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1560" windowWidth="69795" windowHeight="29895" xr2:uid="{F2AD7EB6-AB81-41AA-B966-6E7976896F31}"/>
+    <workbookView xWindow="0" yWindow="2505" windowWidth="57810" windowHeight="29895" xr2:uid="{8A02A6E0-EEF3-4C0D-8740-D5447D1DA22A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="191">
   <si>
     <t>Building</t>
   </si>
@@ -191,7 +191,7 @@
     <t>Select Tenant:</t>
   </si>
   <si>
-    <t>114 Central_207_Westfield Education Association</t>
+    <t xml:space="preserve">114 Central_202_Tang Pacific LLC D/BA ARSA </t>
   </si>
   <si>
     <t>EJS Westfield Toybox, LLC d/b/a Learning Express</t>
@@ -203,7 +203,7 @@
     <t>Tenant</t>
   </si>
   <si>
-    <t>Westfield Education Association</t>
+    <t xml:space="preserve">Tang Pacific LLC D/BA ARSA </t>
   </si>
   <si>
     <t>Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
@@ -240,9 +240,6 @@
   </si>
   <si>
     <t>Mths Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tang Pacific LLC D/BA ARSA </t>
   </si>
   <si>
     <t>Annual Variable</t>
@@ -297,6 +294,9 @@
   </si>
   <si>
     <t>Clauses</t>
+  </si>
+  <si>
+    <t>Westfield Education Association</t>
   </si>
   <si>
     <t>One-Two Year</t>
@@ -392,6 +392,9 @@
     <t>Two 5-Year 3% Annual Inc</t>
   </si>
   <si>
+    <t>Option_1</t>
+  </si>
+  <si>
     <t>Longo Architects &amp; Associates, LLC</t>
   </si>
   <si>
@@ -411,9 +414,6 @@
   </si>
   <si>
     <t>Two 5-Year 7.5% Jump then Flat</t>
-  </si>
-  <si>
-    <t>Option_1</t>
   </si>
   <si>
     <t>George's Appliance, LLC</t>
@@ -593,9 +593,6 @@
     <t>114 Central_201_Ashford - Schael, LLC</t>
   </si>
   <si>
-    <t xml:space="preserve">114 Central_202_Tang Pacific LLC D/BA ARSA </t>
-  </si>
-  <si>
     <t>114 Central_203_Rentokil North America dba Terminix</t>
   </si>
   <si>
@@ -609,6 +606,9 @@
   </si>
   <si>
     <t>114 Central_206_Dave Rossi Photography, LLC</t>
+  </si>
+  <si>
+    <t>114 Central_207_Westfield Education Association</t>
   </si>
   <si>
     <t>114 Central_208_SRD Capital Management, LLC</t>
@@ -1349,7 +1349,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD14F0B-91B4-4C6E-A4EC-64272DDBC3CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444630EB-1CC8-4A81-9DDA-D3668A4DB0D3}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1429,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="7">
-        <v>130000</v>
+        <v>130001</v>
       </c>
       <c r="C2" s="8">
         <v>4894</v>
@@ -1951,7 +1951,7 @@
         <v>58</v>
       </c>
       <c r="AT13" s="27">
-        <v>793</v>
+        <v>607</v>
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
@@ -2060,7 +2060,7 @@
         <v>60</v>
       </c>
       <c r="AT14" s="28">
-        <v>47483</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
@@ -2163,13 +2163,13 @@
         <v>65</v>
       </c>
       <c r="AL15" s="22">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AS15" s="23" t="s">
         <v>66</v>
       </c>
       <c r="AT15" s="30">
-        <v>44.333333333333336</v>
+        <v>11.766666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
@@ -2180,7 +2180,7 @@
         <v>202</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>62</v>
@@ -2247,7 +2247,7 @@
         <v>46507</v>
       </c>
       <c r="Z16" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA16" s="18">
         <v>46327</v>
@@ -2257,10 +2257,10 @@
       </c>
       <c r="AC16" s="19"/>
       <c r="AD16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE16" s="16" t="s">
         <v>69</v>
-      </c>
-      <c r="AE16" s="16" t="s">
-        <v>70</v>
       </c>
       <c r="AF16" s="13">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>27</v>
       </c>
       <c r="AS16" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AT16" s="31">
-        <v>17.402269861286253</v>
+        <v>20.757825370675452</v>
       </c>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
@@ -2295,7 +2295,7 @@
         <v>203</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>62</v>
@@ -2371,7 +2371,7 @@
       <c r="AC17" s="19"/>
       <c r="AD17" s="32"/>
       <c r="AE17" s="32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AF17" s="13">
         <v>0</v>
@@ -2389,19 +2389,19 @@
         <v>58</v>
       </c>
       <c r="AL17" s="27">
-        <v>793</v>
+        <v>607</v>
       </c>
       <c r="AM17" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN17" s="31">
+        <v>1050</v>
+      </c>
+      <c r="AS17" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="AN17" s="31">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="23" t="s">
-        <v>75</v>
-      </c>
       <c r="AT17" s="33">
-        <v>6.448465135190079E-2</v>
+        <v>4.9359625940231758E-2</v>
       </c>
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
@@ -2412,7 +2412,7 @@
         <v>204</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>62</v>
@@ -2470,13 +2470,13 @@
         <v>-10.571254319983737</v>
       </c>
       <c r="W18" s="16">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="X18" s="16">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="Y18" s="16">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="Z18" s="17"/>
       <c r="AA18" s="18" t="s">
@@ -2502,19 +2502,19 @@
         <v>19</v>
       </c>
       <c r="AL18" s="34">
-        <v>0.16121162837975198</v>
+        <v>0.12339906485057939</v>
       </c>
       <c r="AM18" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN18" s="34">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="AN18" s="34">
-        <v>0</v>
-      </c>
-      <c r="AS18" s="23" t="s">
-        <v>78</v>
-      </c>
       <c r="AT18" s="35">
-        <v>47303</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
@@ -2525,7 +2525,7 @@
         <v>205</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>62</v>
@@ -2614,22 +2614,22 @@
         <v>1225</v>
       </c>
       <c r="AK19" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL19" s="34">
-        <v>6.448465135190079E-2</v>
+        <v>4.9359625940231758E-2</v>
       </c>
       <c r="AM19" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AN19" s="34">
-        <v>6.448465135190079E-2</v>
+        <v>4.9359625940231758E-2</v>
       </c>
       <c r="AS19" s="23" t="s">
         <v>35</v>
       </c>
       <c r="AT19" s="36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
@@ -2640,7 +2640,7 @@
         <v>206</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>62</v>
@@ -2707,7 +2707,7 @@
         <v>47968</v>
       </c>
       <c r="Z20" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA20" s="18">
         <v>46417</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AC20" s="19"/>
       <c r="AD20" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AE20" s="16"/>
       <c r="AF20" s="13">
@@ -2733,22 +2733,22 @@
         <v>1465</v>
       </c>
       <c r="AK20" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL20" s="28">
+        <v>41640</v>
+      </c>
+      <c r="AM20" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="AL20" s="28">
-        <v>39520</v>
-      </c>
-      <c r="AM20" s="26" t="s">
+      <c r="AN20" s="34">
+        <v>-4.9359625940231758E-2</v>
+      </c>
+      <c r="AS20" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="AN20" s="34">
-        <v>-6.448465135190079E-2</v>
-      </c>
-      <c r="AS20" s="23" t="s">
-        <v>85</v>
-      </c>
       <c r="AT20" s="27" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
@@ -2759,7 +2759,7 @@
         <v>207</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>62</v>
@@ -2853,7 +2853,7 @@
         <v>87</v>
       </c>
       <c r="AL21" s="28">
-        <v>39520</v>
+        <v>41640</v>
       </c>
       <c r="AM21" s="26" t="s">
         <v>88</v>
@@ -2968,19 +2968,19 @@
         <v>60</v>
       </c>
       <c r="AL22" s="38">
-        <v>47483</v>
+        <v>46507</v>
       </c>
       <c r="AM22" s="26" t="s">
         <v>66</v>
       </c>
       <c r="AN22" s="30">
-        <v>44.333333333333336</v>
+        <v>11.766666666666667</v>
       </c>
       <c r="AS22" s="23" t="s">
         <v>66</v>
       </c>
       <c r="AT22" s="39">
-        <v>4.9333333333333336</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
@@ -3361,7 +3361,7 @@
         <v>108</v>
       </c>
       <c r="AR26" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AS26" s="56" t="s">
         <v>26</v>
@@ -3472,43 +3472,43 @@
         <v>0</v>
       </c>
       <c r="AK27" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL27" s="58">
-        <v>1</v>
-      </c>
-      <c r="AM27" s="28">
-        <v>46023</v>
-      </c>
-      <c r="AN27" s="28">
-        <v>46387</v>
-      </c>
-      <c r="AO27" s="34">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="59">
-        <v>1150</v>
-      </c>
-      <c r="AQ27" s="60">
-        <v>13800</v>
-      </c>
-      <c r="AR27" s="59">
-        <v>17.402269861286253</v>
-      </c>
-      <c r="AS27" s="60">
-        <v>6.448465135190079E-2</v>
-      </c>
-      <c r="AT27" s="60">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="AL27" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM27" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN27" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO27" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP27" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ27" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR27" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS27" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT27" s="60" t="s">
+        <v>94</v>
       </c>
       <c r="AU27" s="60" t="s">
         <v>94</v>
       </c>
       <c r="AV27" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW27" s="59">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="AW27" s="59" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
@@ -3557,34 +3557,34 @@
         <v>113</v>
       </c>
       <c r="AL28" s="62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM28" s="63">
-        <v>46388</v>
+        <v>46143</v>
       </c>
       <c r="AN28" s="63">
-        <v>46752</v>
+        <v>46507</v>
       </c>
       <c r="AO28" s="64">
-        <v>0.47826086956521729</v>
+        <v>1.0960334029227556</v>
       </c>
       <c r="AP28" s="65">
-        <v>1700</v>
+        <v>1050</v>
       </c>
       <c r="AQ28" s="66">
-        <v>20400</v>
+        <v>12600</v>
       </c>
       <c r="AR28" s="65">
-        <v>25.725094577553595</v>
+        <v>20.757825370675452</v>
       </c>
       <c r="AS28" s="66">
-        <v>6.448465135190079E-2</v>
+        <v>4.9359625940231758E-2</v>
       </c>
       <c r="AT28" s="66">
-        <v>1700</v>
-      </c>
-      <c r="AU28" s="66">
-        <v>1700</v>
+        <v>1050</v>
+      </c>
+      <c r="AU28" s="66" t="s">
+        <v>94</v>
       </c>
       <c r="AV28" s="67" t="s">
         <v>27</v>
@@ -3694,37 +3694,37 @@
         <v>16933.333333333332</v>
       </c>
       <c r="AK29" s="22" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL29" s="58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM29" s="28">
-        <v>46753</v>
+        <v>46508</v>
       </c>
       <c r="AN29" s="28">
-        <v>47118</v>
+        <v>46873</v>
       </c>
       <c r="AO29" s="34">
-        <v>3.0000000000000027E-2</v>
+        <v>1.2380952380952381</v>
       </c>
       <c r="AP29" s="59">
-        <v>1751</v>
+        <v>1300</v>
       </c>
       <c r="AQ29" s="60">
-        <v>21012</v>
+        <v>15600</v>
       </c>
       <c r="AR29" s="59">
-        <v>26.4968474148802</v>
+        <v>25.7001647446458</v>
       </c>
       <c r="AS29" s="60">
-        <v>6.448465135190079E-2</v>
+        <v>4.9359625940231758E-2</v>
       </c>
       <c r="AT29" s="60">
-        <v>1751</v>
+        <v>1300</v>
       </c>
       <c r="AU29" s="60">
-        <v>51</v>
+        <v>250</v>
       </c>
       <c r="AV29" s="61" t="s">
         <v>27</v>
@@ -3741,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>62</v>
@@ -3750,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
@@ -3811,7 +3811,7 @@
         <v>0.05</v>
       </c>
       <c r="AA30" s="32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AB30" s="19">
         <v>2</v>
@@ -3832,43 +3832,43 @@
         <v>8747.9166666666661</v>
       </c>
       <c r="AK30" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL30" s="62">
-        <v>4</v>
-      </c>
-      <c r="AM30" s="63">
-        <v>47119</v>
-      </c>
-      <c r="AN30" s="63">
-        <v>47483</v>
-      </c>
-      <c r="AO30" s="64">
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AP30" s="65">
-        <v>1803.53</v>
-      </c>
-      <c r="AQ30" s="66">
-        <v>21642.36</v>
-      </c>
-      <c r="AR30" s="65">
-        <v>27.291752837326609</v>
-      </c>
-      <c r="AS30" s="66">
-        <v>6.448465135190079E-2</v>
-      </c>
-      <c r="AT30" s="66">
-        <v>1803.53</v>
-      </c>
-      <c r="AU30" s="66">
-        <v>52.529999999999973</v>
+        <v>94</v>
+      </c>
+      <c r="AL30" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM30" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN30" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO30" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP30" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ30" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR30" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS30" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT30" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU30" s="66" t="s">
+        <v>94</v>
       </c>
       <c r="AV30" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW30" s="65">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="AW30" s="65" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
@@ -3879,16 +3879,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E31" s="6">
         <v>3</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AB31" s="19"/>
       <c r="AC31" s="19"/>
@@ -3968,43 +3968,43 @@
         <v>0</v>
       </c>
       <c r="AK31" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL31" s="58">
-        <v>5</v>
-      </c>
-      <c r="AM31" s="28">
-        <v>47484</v>
-      </c>
-      <c r="AN31" s="28">
-        <v>47848</v>
-      </c>
-      <c r="AO31" s="34">
-        <v>5.0000092411363495E-2</v>
-      </c>
-      <c r="AP31" s="59">
-        <v>1893.7066666666667</v>
-      </c>
-      <c r="AQ31" s="60">
-        <v>22724.48</v>
-      </c>
-      <c r="AR31" s="59">
-        <v>28.656343001261032</v>
-      </c>
-      <c r="AS31" s="60">
-        <v>6.448465135190079E-2</v>
-      </c>
-      <c r="AT31" s="60">
-        <v>1893.7066666666667</v>
-      </c>
-      <c r="AU31" s="60">
-        <v>90.176666666666733</v>
+        <v>94</v>
+      </c>
+      <c r="AL31" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM31" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN31" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO31" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP31" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ31" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR31" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS31" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT31" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU31" s="60" t="s">
+        <v>94</v>
       </c>
       <c r="AV31" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW31" s="59">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="AW31" s="59" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
@@ -4024,7 +4024,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
@@ -4100,43 +4100,43 @@
         <v>0</v>
       </c>
       <c r="AK32" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL32" s="62">
-        <v>6</v>
-      </c>
-      <c r="AM32" s="63">
-        <v>47849</v>
-      </c>
-      <c r="AN32" s="63">
-        <v>48213</v>
-      </c>
-      <c r="AO32" s="64">
-        <v>3.0002006646576707E-2</v>
-      </c>
-      <c r="AP32" s="65">
-        <v>1950.5216666666665</v>
-      </c>
-      <c r="AQ32" s="66">
-        <v>23406.26</v>
-      </c>
-      <c r="AR32" s="65">
-        <v>29.516090794451447</v>
-      </c>
-      <c r="AS32" s="66">
-        <v>6.448465135190079E-2</v>
-      </c>
-      <c r="AT32" s="66">
-        <v>1950.5216666666665</v>
-      </c>
-      <c r="AU32" s="66">
-        <v>56.814999999999827</v>
+        <v>94</v>
+      </c>
+      <c r="AL32" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM32" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN32" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO32" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP32" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ32" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR32" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS32" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT32" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU32" s="66" t="s">
+        <v>94</v>
       </c>
       <c r="AV32" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW32" s="65">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="AW32" s="65" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
@@ -6468,25 +6468,25 @@
         <v>113</v>
       </c>
       <c r="AL55" s="58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM55" s="28">
-        <v>46023</v>
+        <v>45778</v>
       </c>
       <c r="AN55" s="28">
-        <v>47483</v>
+        <v>46507</v>
       </c>
       <c r="AO55" s="59">
-        <v>1150</v>
+        <v>958</v>
       </c>
       <c r="AP55" s="60">
-        <v>13800</v>
+        <v>11496</v>
       </c>
       <c r="AQ55" s="59">
-        <v>1803.53</v>
+        <v>1050</v>
       </c>
       <c r="AR55" s="60">
-        <v>21642.36</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
@@ -6561,25 +6561,25 @@
         <v>160</v>
       </c>
       <c r="AL56" s="58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM56" s="28">
-        <v>47484</v>
+        <v>46508</v>
       </c>
       <c r="AN56" s="28">
-        <v>48213</v>
+        <v>46873</v>
       </c>
       <c r="AO56" s="59">
-        <v>1893.7066666666667</v>
+        <v>1300</v>
       </c>
       <c r="AP56" s="60">
-        <v>22724.48</v>
+        <v>15600</v>
       </c>
       <c r="AQ56" s="59">
-        <v>1950.5216666666665</v>
+        <v>1300</v>
       </c>
       <c r="AR56" s="60">
-        <v>23406.26</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
@@ -6596,7 +6596,7 @@
         <v>114</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F57" s="73">
         <v>11</v>
@@ -6689,7 +6689,7 @@
         <v>114</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F58" s="73">
         <v>12</v>
@@ -6782,7 +6782,7 @@
         <v>114</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F59" s="73">
         <v>13</v>
@@ -6851,7 +6851,7 @@
         <v>114</v>
       </c>
       <c r="E60" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F60" s="73">
         <v>14</v>
@@ -6920,7 +6920,7 @@
         <v>114</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F61" s="73">
         <v>15</v>
@@ -7400,7 +7400,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>113</v>
@@ -7469,7 +7469,7 @@
         <v>2</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>113</v>
@@ -7538,7 +7538,7 @@
         <v>2</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>113</v>
@@ -7607,7 +7607,7 @@
         <v>2</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>113</v>
@@ -7745,7 +7745,7 @@
         <v>3</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>113</v>
@@ -7814,7 +7814,7 @@
         <v>3</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>113</v>
@@ -7883,7 +7883,7 @@
         <v>3</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>113</v>
@@ -7952,7 +7952,7 @@
         <v>3</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>113</v>
@@ -8021,7 +8021,7 @@
         <v>3</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>113</v>
@@ -8090,7 +8090,7 @@
         <v>3</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>113</v>
@@ -8159,7 +8159,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>113</v>
@@ -8228,7 +8228,7 @@
         <v>3</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>113</v>
@@ -8297,7 +8297,7 @@
         <v>3</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>113</v>
@@ -8366,7 +8366,7 @@
         <v>3</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>113</v>
@@ -8435,7 +8435,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>113</v>
@@ -8504,7 +8504,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>113</v>
@@ -8573,7 +8573,7 @@
         <v>3</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>113</v>
@@ -8642,7 +8642,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>113</v>
@@ -10301,7 +10301,7 @@
         <v>95</v>
       </c>
       <c r="E110" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F110" s="73">
         <v>11</v>
@@ -10370,7 +10370,7 @@
         <v>95</v>
       </c>
       <c r="E111" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F111" s="73">
         <v>12</v>
@@ -10439,7 +10439,7 @@
         <v>95</v>
       </c>
       <c r="E112" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F112" s="73">
         <v>13</v>
@@ -10508,7 +10508,7 @@
         <v>95</v>
       </c>
       <c r="E113" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F113" s="73">
         <v>14</v>
@@ -10577,7 +10577,7 @@
         <v>95</v>
       </c>
       <c r="E114" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F114" s="73">
         <v>15</v>
@@ -11060,7 +11060,7 @@
         <v>100</v>
       </c>
       <c r="E121" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F121" s="73">
         <v>6</v>
@@ -11129,7 +11129,7 @@
         <v>100</v>
       </c>
       <c r="E122" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F122" s="73">
         <v>7</v>
@@ -11198,7 +11198,7 @@
         <v>100</v>
       </c>
       <c r="E123" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F123" s="73">
         <v>8</v>
@@ -11267,7 +11267,7 @@
         <v>100</v>
       </c>
       <c r="E124" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F124" s="73">
         <v>9</v>
@@ -11336,7 +11336,7 @@
         <v>100</v>
       </c>
       <c r="E125" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F125" s="73">
         <v>10</v>
@@ -14232,7 +14232,7 @@
         <v>131</v>
       </c>
       <c r="E167" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F167" s="73">
         <v>11</v>
@@ -14301,7 +14301,7 @@
         <v>131</v>
       </c>
       <c r="E168" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F168" s="73">
         <v>12</v>
@@ -14370,7 +14370,7 @@
         <v>131</v>
       </c>
       <c r="E169" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F169" s="73">
         <v>13</v>
@@ -14439,7 +14439,7 @@
         <v>131</v>
       </c>
       <c r="E170" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F170" s="73">
         <v>14</v>
@@ -14508,7 +14508,7 @@
         <v>131</v>
       </c>
       <c r="E171" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F171" s="73">
         <v>15</v>
@@ -16992,7 +16992,7 @@
         <v>55</v>
       </c>
       <c r="E207" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F207" s="73">
         <v>7</v>
@@ -17061,7 +17061,7 @@
         <v>55</v>
       </c>
       <c r="E208" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F208" s="73">
         <v>8</v>
@@ -17130,7 +17130,7 @@
         <v>55</v>
       </c>
       <c r="E209" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F209" s="73">
         <v>9</v>
@@ -17199,7 +17199,7 @@
         <v>55</v>
       </c>
       <c r="E210" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F210" s="73">
         <v>10</v>
@@ -17268,7 +17268,7 @@
         <v>55</v>
       </c>
       <c r="E211" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F211" s="73">
         <v>11</v>
@@ -18360,7 +18360,7 @@
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>6</v>
@@ -18369,7 +18369,7 @@
         <v>202</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E227" s="6" t="s">
         <v>113</v>
@@ -18429,7 +18429,7 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>6</v>
@@ -18438,7 +18438,7 @@
         <v>202</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>113</v>
@@ -18498,7 +18498,7 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="73" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="B229" s="73" t="s">
         <v>6</v>
@@ -18507,10 +18507,10 @@
         <v>202</v>
       </c>
       <c r="D229" s="73" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E229" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F229" s="73">
         <v>1</v>
@@ -18636,7 +18636,7 @@
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>6</v>
@@ -18645,7 +18645,7 @@
         <v>203</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E231" s="6" t="s">
         <v>113</v>
@@ -18705,7 +18705,7 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>6</v>
@@ -18714,7 +18714,7 @@
         <v>203</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>113</v>
@@ -18774,7 +18774,7 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B233" s="73" t="s">
         <v>6</v>
@@ -18783,10 +18783,10 @@
         <v>203</v>
       </c>
       <c r="D233" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E233" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F233" s="73">
         <v>3</v>
@@ -18843,7 +18843,7 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B234" s="78" t="s">
         <v>6</v>
@@ -18852,7 +18852,7 @@
         <v>203</v>
       </c>
       <c r="D234" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E234" s="78" t="s">
         <v>163</v>
@@ -18981,7 +18981,7 @@
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>6</v>
@@ -18990,7 +18990,7 @@
         <v>204</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>113</v>
@@ -18999,10 +18999,10 @@
         <v>1</v>
       </c>
       <c r="G236" s="93">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H236" s="93">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="I236" s="10">
         <v>0</v>
@@ -19035,13 +19035,13 @@
         <v>0</v>
       </c>
       <c r="S236" s="70">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="T236" s="70">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="U236" s="70">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="V236" s="13">
         <v>0</v>
@@ -19119,7 +19119,7 @@
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>6</v>
@@ -19128,7 +19128,7 @@
         <v>205</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>113</v>
@@ -19188,7 +19188,7 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>6</v>
@@ -19197,7 +19197,7 @@
         <v>205</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E239" s="6" t="s">
         <v>113</v>
@@ -19257,7 +19257,7 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>6</v>
@@ -19266,7 +19266,7 @@
         <v>205</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>113</v>
@@ -19395,7 +19395,7 @@
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>6</v>
@@ -19464,7 +19464,7 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>6</v>
@@ -19533,7 +19533,7 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>6</v>
@@ -19671,7 +19671,7 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>6</v>
@@ -19680,7 +19680,7 @@
         <v>206</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>113</v>
@@ -19740,7 +19740,7 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>6</v>
@@ -19749,7 +19749,7 @@
         <v>206</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E247" s="6" t="s">
         <v>113</v>
@@ -19811,7 +19811,7 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>6</v>
@@ -19820,7 +19820,7 @@
         <v>206</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>113</v>
@@ -19882,7 +19882,7 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>6</v>
@@ -19891,7 +19891,7 @@
         <v>206</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E249" s="6" t="s">
         <v>113</v>
@@ -19953,7 +19953,7 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>6</v>
@@ -19962,7 +19962,7 @@
         <v>206</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>113</v>
@@ -20024,7 +20024,7 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>6</v>
@@ -20033,7 +20033,7 @@
         <v>206</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E251" s="6" t="s">
         <v>113</v>
@@ -20164,7 +20164,7 @@
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>6</v>
@@ -20173,7 +20173,7 @@
         <v>207</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E253" s="6" t="s">
         <v>113</v>
@@ -20233,7 +20233,7 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>6</v>
@@ -20242,7 +20242,7 @@
         <v>207</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>113</v>
@@ -20302,7 +20302,7 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>6</v>
@@ -20311,7 +20311,7 @@
         <v>207</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E255" s="6" t="s">
         <v>113</v>
@@ -20371,7 +20371,7 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>6</v>
@@ -20380,7 +20380,7 @@
         <v>207</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>113</v>
@@ -20440,7 +20440,7 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="73" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="B257" s="73" t="s">
         <v>6</v>
@@ -20449,10 +20449,10 @@
         <v>207</v>
       </c>
       <c r="D257" s="73" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E257" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F257" s="73">
         <v>5</v>
@@ -20509,7 +20509,7 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="73" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="B258" s="73" t="s">
         <v>6</v>
@@ -20518,10 +20518,10 @@
         <v>207</v>
       </c>
       <c r="D258" s="73" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E258" s="73" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F258" s="73">
         <v>6</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C428DD5D-2C05-4E61-AD93-DED4470F1432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43564DC1-F923-4227-99BD-35898DD8D923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2505" windowWidth="57810" windowHeight="29895" xr2:uid="{8A02A6E0-EEF3-4C0D-8740-D5447D1DA22A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="57810" windowHeight="29895" xr2:uid="{98642A8E-0764-40C3-B15E-624F75792EAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="192">
   <si>
     <t>Building</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Tenant</t>
   </si>
   <si>
-    <t xml:space="preserve">Tang Pacific LLC D/BA ARSA </t>
-  </si>
-  <si>
     <t>Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
   </si>
   <si>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>Mths Left</t>
+  </si>
+  <si>
+    <t>Tang Pacific LLC D/BA ARSA</t>
   </si>
   <si>
     <t>Annual Variable</t>
@@ -380,9 +380,6 @@
     <t>Easement</t>
   </si>
   <si>
-    <t>Original</t>
-  </si>
-  <si>
     <t>HDR HOLDINGS LLC D/B/A WONDER</t>
   </si>
   <si>
@@ -390,9 +387,6 @@
   </si>
   <si>
     <t>Two 5-Year 3% Annual Inc</t>
-  </si>
-  <si>
-    <t>Option_1</t>
   </si>
   <si>
     <t>Longo Architects &amp; Associates, LLC</t>
@@ -494,6 +488,9 @@
     <t>36 South_1_HDR HOLDINGS LLC D/B/A WONDER</t>
   </si>
   <si>
+    <t>Original</t>
+  </si>
+  <si>
     <t>LEASE OPTIONS SUMMARY</t>
   </si>
   <si>
@@ -522,6 +519,9 @@
   </si>
   <si>
     <t>Option 1</t>
+  </si>
+  <si>
+    <t>Option_1</t>
   </si>
   <si>
     <t>Option 2</t>
@@ -578,19 +578,22 @@
     <t>1280 Springfield_7_Alan DiEsso</t>
   </si>
   <si>
-    <t>114 Central_1_Nabig Sakr</t>
+    <t>114 Central_102_Nabig Sakr</t>
   </si>
   <si>
-    <t>114 Central_2_EJS Westfield Toybox, LLC d/b/a Learning Express</t>
+    <t>114 Central_104_EJS Westfield Toybox, LLC d/b/a Learning Express</t>
   </si>
   <si>
-    <t>114 Central_3_Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
+    <t>114 Central_106_Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
   </si>
   <si>
-    <t>114 Central_4_Luna Wireless</t>
+    <t>114 Central_108_Luna Wireless</t>
   </si>
   <si>
     <t>114 Central_201_Ashford - Schael, LLC</t>
+  </si>
+  <si>
+    <t>114 Central_202_Tang Pacific LLC D/BA ARSA</t>
   </si>
   <si>
     <t>114 Central_203_Rentokil North America dba Terminix</t>
@@ -1349,7 +1352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444630EB-1CC8-4A81-9DDA-D3668A4DB0D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01BBE3BE-0B5E-41B0-9D35-E128E88B66BC}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1626,7 +1629,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>44</v>
@@ -1739,7 +1742,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="6">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>51</v>
@@ -1837,8 +1840,8 @@
       <c r="AS12" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="AT12" s="22" t="s">
-        <v>54</v>
+      <c r="AT12" s="22" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
@@ -1846,10 +1849,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="6">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>45</v>
@@ -1916,7 +1919,7 @@
         <v>46810</v>
       </c>
       <c r="Z13" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AA13" s="18">
         <v>46565</v>
@@ -1927,7 +1930,7 @@
       <c r="AC13" s="19"/>
       <c r="AD13" s="16"/>
       <c r="AE13" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AF13" s="13">
         <v>11.637681159420289</v>
@@ -1944,14 +1947,14 @@
       <c r="AK13" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="AL13" s="22" t="s">
-        <v>54</v>
+      <c r="AL13" s="22" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AS13" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="AT13" s="27">
-        <v>607</v>
+        <v>57</v>
+      </c>
+      <c r="AT13" s="27" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
@@ -1959,10 +1962,10 @@
         <v>6</v>
       </c>
       <c r="B14" s="6">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>45</v>
@@ -2053,14 +2056,14 @@
       <c r="AK14" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="AL14" s="22" t="s">
-        <v>6</v>
+      <c r="AL14" s="22" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AS14" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="AT14" s="28">
-        <v>46507</v>
+        <v>59</v>
+      </c>
+      <c r="AT14" s="28" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
@@ -2071,16 +2074,16 @@
         <v>201</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="E15" s="6">
         <v>2</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6">
@@ -2145,7 +2148,7 @@
       <c r="AC15" s="19"/>
       <c r="AD15" s="16"/>
       <c r="AE15" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AF15" s="13">
         <v>0</v>
@@ -2160,16 +2163,16 @@
         <v>1632.5</v>
       </c>
       <c r="AK15" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL15" s="22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS15" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="AL15" s="22">
-        <v>202</v>
-      </c>
-      <c r="AS15" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT15" s="30">
-        <v>11.766666666666667</v>
+      <c r="AT15" s="30" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
@@ -2180,16 +2183,16 @@
         <v>202</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="6">
         <v>2</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6">
@@ -2277,14 +2280,14 @@
       <c r="AK16" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AL16" s="22" t="s">
-        <v>27</v>
+      <c r="AL16" s="22" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AS16" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AT16" s="31">
-        <v>20.757825370675452</v>
+      <c r="AT16" s="31" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
@@ -2298,13 +2301,13 @@
         <v>71</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" s="6">
         <v>2</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6">
@@ -2386,22 +2389,22 @@
         <v>1555</v>
       </c>
       <c r="AK17" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="AL17" s="27">
-        <v>607</v>
+        <v>57</v>
+      </c>
+      <c r="AL17" s="27" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AM17" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="AN17" s="31">
-        <v>1050</v>
+      <c r="AN17" s="31" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AS17" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="AT17" s="33">
-        <v>4.9359625940231758E-2</v>
+      <c r="AT17" s="33" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
@@ -2415,13 +2418,13 @@
         <v>75</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
@@ -2501,20 +2504,20 @@
       <c r="AK18" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="AL18" s="34">
-        <v>0.12339906485057939</v>
+      <c r="AL18" s="34" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AM18" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="AN18" s="34">
-        <v>0</v>
+      <c r="AN18" s="34" t="s">
+        <v>68</v>
       </c>
       <c r="AS18" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="AT18" s="35">
-        <v>46327</v>
+      <c r="AT18" s="35" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
@@ -2528,13 +2531,13 @@
         <v>78</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="6">
         <v>2</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6">
@@ -2616,14 +2619,14 @@
       <c r="AK19" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="AL19" s="34">
-        <v>4.9359625940231758E-2</v>
+      <c r="AL19" s="34" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AM19" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="AN19" s="34">
-        <v>4.9359625940231758E-2</v>
+      <c r="AN19" s="34" t="s">
+        <v>68</v>
       </c>
       <c r="AS19" s="23" t="s">
         <v>35</v>
@@ -2643,13 +2646,13 @@
         <v>80</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6">
@@ -2735,20 +2738,20 @@
       <c r="AK20" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AL20" s="28">
-        <v>41640</v>
+      <c r="AL20" s="28" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AM20" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="AN20" s="34">
-        <v>-4.9359625940231758E-2</v>
+      <c r="AN20" s="34" t="e">
+        <v>#VALUE!</v>
       </c>
       <c r="AS20" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="AT20" s="27" t="s">
-        <v>69</v>
+      <c r="AT20" s="27" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
@@ -2762,13 +2765,13 @@
         <v>85</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" s="6">
         <v>2</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6">
@@ -2852,14 +2855,14 @@
       <c r="AK21" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="AL21" s="28">
-        <v>41640</v>
+      <c r="AL21" s="28" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AM21" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="AN21" s="31">
-        <v>0</v>
+      <c r="AN21" s="31" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AS21" s="23" t="s">
         <v>89</v>
@@ -2879,13 +2882,13 @@
         <v>90</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6">
@@ -2965,19 +2968,19 @@
         <v>680</v>
       </c>
       <c r="AK22" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL22" s="38">
-        <v>46507</v>
+        <v>59</v>
+      </c>
+      <c r="AL22" s="38" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AM22" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN22" s="30">
-        <v>11.766666666666667</v>
+        <v>65</v>
+      </c>
+      <c r="AN22" s="30" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AS22" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AT22" s="39">
         <v>4.9000000000000004</v>
@@ -2994,13 +2997,13 @@
         <v>91</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" s="6">
         <v>2</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6">
@@ -3554,43 +3557,43 @@
       </c>
       <c r="AI28" s="45"/>
       <c r="AK28" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL28" s="62">
-        <v>1</v>
-      </c>
-      <c r="AM28" s="63">
-        <v>46143</v>
-      </c>
-      <c r="AN28" s="63">
-        <v>46507</v>
-      </c>
-      <c r="AO28" s="64">
-        <v>1.0960334029227556</v>
-      </c>
-      <c r="AP28" s="65">
-        <v>1050</v>
-      </c>
-      <c r="AQ28" s="66">
-        <v>12600</v>
-      </c>
-      <c r="AR28" s="65">
-        <v>20.757825370675452</v>
-      </c>
-      <c r="AS28" s="66">
-        <v>4.9359625940231758E-2</v>
-      </c>
-      <c r="AT28" s="66">
-        <v>1050</v>
+        <v>94</v>
+      </c>
+      <c r="AL28" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM28" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN28" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO28" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP28" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ28" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR28" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS28" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT28" s="66" t="s">
+        <v>94</v>
       </c>
       <c r="AU28" s="66" t="s">
         <v>94</v>
       </c>
       <c r="AV28" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW28" s="65">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="AW28" s="65" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
@@ -3601,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>45</v>
@@ -3610,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
@@ -3671,7 +3674,7 @@
         <v>0.03</v>
       </c>
       <c r="AA29" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AB29" s="19">
         <v>3</v>
@@ -3694,43 +3697,43 @@
         <v>16933.333333333332</v>
       </c>
       <c r="AK29" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="AL29" s="58">
-        <v>1</v>
-      </c>
-      <c r="AM29" s="28">
-        <v>46508</v>
-      </c>
-      <c r="AN29" s="28">
-        <v>46873</v>
-      </c>
-      <c r="AO29" s="34">
-        <v>1.2380952380952381</v>
-      </c>
-      <c r="AP29" s="59">
-        <v>1300</v>
-      </c>
-      <c r="AQ29" s="60">
-        <v>15600</v>
-      </c>
-      <c r="AR29" s="59">
-        <v>25.7001647446458</v>
-      </c>
-      <c r="AS29" s="60">
-        <v>4.9359625940231758E-2</v>
-      </c>
-      <c r="AT29" s="60">
-        <v>1300</v>
-      </c>
-      <c r="AU29" s="60">
-        <v>250</v>
+        <v>94</v>
+      </c>
+      <c r="AL29" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM29" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN29" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO29" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP29" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ29" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR29" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS29" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT29" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU29" s="60" t="s">
+        <v>94</v>
       </c>
       <c r="AV29" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW29" s="59">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="AW29" s="59" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
@@ -3741,16 +3744,16 @@
         <v>2</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" s="6">
         <v>2</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
@@ -3811,7 +3814,7 @@
         <v>0.05</v>
       </c>
       <c r="AA30" s="32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AB30" s="19">
         <v>2</v>
@@ -3879,16 +3882,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E31" s="6">
         <v>3</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
@@ -3949,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AB31" s="19"/>
       <c r="AC31" s="19"/>
@@ -4024,7 +4027,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
@@ -4229,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>45</v>
@@ -4238,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
@@ -4296,7 +4299,7 @@
         <v>46538</v>
       </c>
       <c r="Z34" s="52" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AA34" s="32" t="s">
         <v>48</v>
@@ -4367,7 +4370,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>45</v>
@@ -4376,7 +4379,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6">
@@ -4434,7 +4437,7 @@
         <v>46706</v>
       </c>
       <c r="Z35" s="52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AA35" s="32" t="s">
         <v>48</v>
@@ -4505,7 +4508,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>45</v>
@@ -4514,7 +4517,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6">
@@ -4572,7 +4575,7 @@
         <v>47299</v>
       </c>
       <c r="Z36" s="52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AA36" s="32" t="s">
         <v>48</v>
@@ -4643,7 +4646,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>45</v>
@@ -4652,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6">
@@ -4710,10 +4713,10 @@
         <v>47573</v>
       </c>
       <c r="Z37" s="52" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AA37" s="32" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB37" s="19">
         <v>3</v>
@@ -4781,16 +4784,16 @@
         <v>5</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E38" s="6">
         <v>2</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6">
@@ -4848,10 +4851,10 @@
         <v>46996</v>
       </c>
       <c r="Z38" s="52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AA38" s="32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AB38" s="19">
         <v>3</v>
@@ -4919,16 +4922,16 @@
         <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E39" s="6">
         <v>2</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6">
@@ -5059,16 +5062,16 @@
         <v>7</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6">
@@ -5399,13 +5402,13 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>53</v>
@@ -5414,7 +5417,7 @@
         <v>102</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>104</v>
@@ -5426,19 +5429,19 @@
         <v>106</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N45" s="69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O45" s="69" t="s">
         <v>14</v>
@@ -5447,10 +5450,10 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>31</v>
@@ -5465,7 +5468,7 @@
         <v>37</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AK45" s="22" t="s">
         <v>94</v>
@@ -5509,7 +5512,7 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -5518,10 +5521,10 @@
         <v>1</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F46" s="6">
         <v>0</v>
@@ -5617,7 +5620,7 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
@@ -5626,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
@@ -5725,7 +5728,7 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
@@ -5734,10 +5737,10 @@
         <v>1</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F48" s="6">
         <v>2</v>
@@ -5833,7 +5836,7 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
@@ -5842,10 +5845,10 @@
         <v>1</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
@@ -5941,7 +5944,7 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
@@ -5950,10 +5953,10 @@
         <v>1</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F50" s="6">
         <v>4</v>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
@@ -6058,10 +6061,10 @@
         <v>1</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
@@ -6157,7 +6160,7 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
@@ -6166,10 +6169,10 @@
         <v>1</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
@@ -6226,7 +6229,7 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
@@ -6235,10 +6238,10 @@
         <v>1</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
@@ -6293,7 +6296,7 @@
       </c>
       <c r="W53" s="13"/>
       <c r="AK53" s="72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AL53" s="22"/>
       <c r="AM53" s="22"/>
@@ -6305,7 +6308,7 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>8</v>
@@ -6314,10 +6317,10 @@
         <v>1</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F54" s="6">
         <v>8</v>
@@ -6372,33 +6375,33 @@
       </c>
       <c r="W54" s="13"/>
       <c r="AK54" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL54" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AL54" s="56" t="s">
+      <c r="AM54" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="AM54" s="56" t="s">
+      <c r="AN54" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="AN54" s="56" t="s">
+      <c r="AO54" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="AO54" s="56" t="s">
+      <c r="AP54" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="AP54" s="56" t="s">
+      <c r="AQ54" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="AQ54" s="56" t="s">
+      <c r="AR54" s="56" t="s">
         <v>158</v>
-      </c>
-      <c r="AR54" s="56" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>8</v>
@@ -6407,10 +6410,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F55" s="6">
         <v>9</v>
@@ -6465,33 +6468,33 @@
       </c>
       <c r="W55" s="13"/>
       <c r="AK55" s="26" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="AL55" s="58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM55" s="28">
-        <v>45778</v>
+        <v>0</v>
       </c>
       <c r="AN55" s="28">
-        <v>46507</v>
-      </c>
-      <c r="AO55" s="59">
-        <v>958</v>
-      </c>
-      <c r="AP55" s="60">
-        <v>11496</v>
-      </c>
-      <c r="AQ55" s="59">
-        <v>1050</v>
-      </c>
-      <c r="AR55" s="60">
-        <v>12600</v>
+        <v>0</v>
+      </c>
+      <c r="AO55" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP55" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ55" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR55" s="60" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
@@ -6500,10 +6503,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F56" s="6">
         <v>10</v>
@@ -6558,33 +6561,33 @@
       </c>
       <c r="W56" s="13"/>
       <c r="AK56" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AL56" s="58">
-        <v>1</v>
-      </c>
-      <c r="AM56" s="28">
-        <v>46508</v>
-      </c>
-      <c r="AN56" s="28">
-        <v>46873</v>
-      </c>
-      <c r="AO56" s="59">
-        <v>1300</v>
-      </c>
-      <c r="AP56" s="60">
-        <v>15600</v>
-      </c>
-      <c r="AQ56" s="59">
-        <v>1300</v>
-      </c>
-      <c r="AR56" s="60">
-        <v>15600</v>
+        <v>0</v>
+      </c>
+      <c r="AM56" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN56" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO56" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP56" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ56" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR56" s="60" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B57" s="73" t="s">
         <v>8</v>
@@ -6593,10 +6596,10 @@
         <v>1</v>
       </c>
       <c r="D57" s="73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F57" s="73">
         <v>11</v>
@@ -6677,7 +6680,7 @@
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B58" s="73" t="s">
         <v>8</v>
@@ -6686,10 +6689,10 @@
         <v>1</v>
       </c>
       <c r="D58" s="73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F58" s="73">
         <v>12</v>
@@ -6770,7 +6773,7 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B59" s="73" t="s">
         <v>8</v>
@@ -6779,10 +6782,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F59" s="73">
         <v>13</v>
@@ -6839,7 +6842,7 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B60" s="73" t="s">
         <v>8</v>
@@ -6848,10 +6851,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E60" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F60" s="73">
         <v>14</v>
@@ -6908,7 +6911,7 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B61" s="73" t="s">
         <v>8</v>
@@ -6917,10 +6920,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F61" s="73">
         <v>15</v>
@@ -6977,7 +6980,7 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B62" s="78" t="s">
         <v>8</v>
@@ -6986,7 +6989,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E62" s="78" t="s">
         <v>163</v>
@@ -7046,7 +7049,7 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="78" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B63" s="78" t="s">
         <v>8</v>
@@ -7055,7 +7058,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E63" s="78" t="s">
         <v>163</v>
@@ -7115,7 +7118,7 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="78" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B64" s="78" t="s">
         <v>8</v>
@@ -7124,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="D64" s="78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E64" s="78" t="s">
         <v>163</v>
@@ -7184,7 +7187,7 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="78" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B65" s="78" t="s">
         <v>8</v>
@@ -7193,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E65" s="78" t="s">
         <v>163</v>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="78" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B66" s="78" t="s">
         <v>8</v>
@@ -7262,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E66" s="78" t="s">
         <v>163</v>
@@ -7400,10 +7403,10 @@
         <v>2</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F68" s="6">
         <v>1</v>
@@ -7469,10 +7472,10 @@
         <v>2</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F69" s="6">
         <v>2</v>
@@ -7538,10 +7541,10 @@
         <v>2</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F70" s="6">
         <v>3</v>
@@ -7607,10 +7610,10 @@
         <v>2</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F71" s="6">
         <v>4</v>
@@ -7745,10 +7748,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F73" s="6">
         <v>1</v>
@@ -7814,10 +7817,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F74" s="6">
         <v>2</v>
@@ -7883,10 +7886,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F75" s="6">
         <v>3</v>
@@ -7952,10 +7955,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F76" s="6">
         <v>4</v>
@@ -8021,10 +8024,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F77" s="6">
         <v>5</v>
@@ -8090,10 +8093,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F78" s="6">
         <v>6</v>
@@ -8159,10 +8162,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F79" s="6">
         <v>7</v>
@@ -8228,10 +8231,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F80" s="6">
         <v>8</v>
@@ -8297,10 +8300,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F81" s="6">
         <v>9</v>
@@ -8366,10 +8369,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F82" s="6">
         <v>10</v>
@@ -8435,10 +8438,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F83" s="6">
         <v>11</v>
@@ -8504,10 +8507,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F84" s="6">
         <v>12</v>
@@ -8573,10 +8576,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F85" s="6">
         <v>13</v>
@@ -8642,10 +8645,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F86" s="6">
         <v>14</v>
@@ -8783,7 +8786,7 @@
         <v>112</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F88" s="6">
         <v>1</v>
@@ -8852,7 +8855,7 @@
         <v>112</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F89" s="6">
         <v>2</v>
@@ -8921,7 +8924,7 @@
         <v>112</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F90" s="6">
         <v>3</v>
@@ -8990,7 +8993,7 @@
         <v>112</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F91" s="6">
         <v>4</v>
@@ -9059,7 +9062,7 @@
         <v>112</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F92" s="6">
         <v>5</v>
@@ -9128,7 +9131,7 @@
         <v>112</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F93" s="6">
         <v>6</v>
@@ -9197,7 +9200,7 @@
         <v>112</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F94" s="6">
         <v>7</v>
@@ -9266,7 +9269,7 @@
         <v>112</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F95" s="6">
         <v>8</v>
@@ -9335,7 +9338,7 @@
         <v>112</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F96" s="6">
         <v>9</v>
@@ -9404,7 +9407,7 @@
         <v>112</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F97" s="6">
         <v>10</v>
@@ -9473,7 +9476,7 @@
         <v>112</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F98" s="6">
         <v>11</v>
@@ -9611,7 +9614,7 @@
         <v>95</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F100" s="6">
         <v>1</v>
@@ -9680,7 +9683,7 @@
         <v>95</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F101" s="6">
         <v>2</v>
@@ -9749,7 +9752,7 @@
         <v>95</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F102" s="6">
         <v>3</v>
@@ -9818,7 +9821,7 @@
         <v>95</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F103" s="6">
         <v>4</v>
@@ -9887,7 +9890,7 @@
         <v>95</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F104" s="6">
         <v>5</v>
@@ -9956,7 +9959,7 @@
         <v>95</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F105" s="6">
         <v>6</v>
@@ -10025,7 +10028,7 @@
         <v>95</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F106" s="6">
         <v>7</v>
@@ -10094,7 +10097,7 @@
         <v>95</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F107" s="6">
         <v>8</v>
@@ -10163,7 +10166,7 @@
         <v>95</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F108" s="6">
         <v>9</v>
@@ -10232,7 +10235,7 @@
         <v>95</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F109" s="6">
         <v>10</v>
@@ -10301,7 +10304,7 @@
         <v>95</v>
       </c>
       <c r="E110" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F110" s="73">
         <v>11</v>
@@ -10370,7 +10373,7 @@
         <v>95</v>
       </c>
       <c r="E111" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F111" s="73">
         <v>12</v>
@@ -10439,7 +10442,7 @@
         <v>95</v>
       </c>
       <c r="E112" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F112" s="73">
         <v>13</v>
@@ -10508,7 +10511,7 @@
         <v>95</v>
       </c>
       <c r="E113" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F113" s="73">
         <v>14</v>
@@ -10577,7 +10580,7 @@
         <v>95</v>
       </c>
       <c r="E114" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F114" s="73">
         <v>15</v>
@@ -10715,7 +10718,7 @@
         <v>100</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F116" s="6">
         <v>1</v>
@@ -10784,7 +10787,7 @@
         <v>100</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F117" s="6">
         <v>2</v>
@@ -10853,7 +10856,7 @@
         <v>100</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F118" s="6">
         <v>3</v>
@@ -10922,7 +10925,7 @@
         <v>100</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F119" s="6">
         <v>4</v>
@@ -10991,7 +10994,7 @@
         <v>100</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F120" s="6">
         <v>5</v>
@@ -11060,7 +11063,7 @@
         <v>100</v>
       </c>
       <c r="E121" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F121" s="73">
         <v>6</v>
@@ -11129,7 +11132,7 @@
         <v>100</v>
       </c>
       <c r="E122" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F122" s="73">
         <v>7</v>
@@ -11198,7 +11201,7 @@
         <v>100</v>
       </c>
       <c r="E123" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F123" s="73">
         <v>8</v>
@@ -11267,7 +11270,7 @@
         <v>100</v>
       </c>
       <c r="E124" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F124" s="73">
         <v>9</v>
@@ -11336,7 +11339,7 @@
         <v>100</v>
       </c>
       <c r="E125" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F125" s="73">
         <v>10</v>
@@ -11474,7 +11477,7 @@
         <v>112</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F127" s="6">
         <v>1</v>
@@ -11543,7 +11546,7 @@
         <v>112</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F128" s="6">
         <v>2</v>
@@ -11612,7 +11615,7 @@
         <v>112</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F129" s="6">
         <v>3</v>
@@ -11681,7 +11684,7 @@
         <v>112</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F130" s="6">
         <v>4</v>
@@ -11750,7 +11753,7 @@
         <v>112</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F131" s="6">
         <v>5</v>
@@ -11819,7 +11822,7 @@
         <v>112</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F132" s="6">
         <v>6</v>
@@ -11888,7 +11891,7 @@
         <v>112</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F133" s="6">
         <v>7</v>
@@ -11957,7 +11960,7 @@
         <v>112</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F134" s="6">
         <v>8</v>
@@ -12026,7 +12029,7 @@
         <v>112</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F135" s="6">
         <v>9</v>
@@ -12095,7 +12098,7 @@
         <v>112</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F136" s="6">
         <v>10</v>
@@ -12164,7 +12167,7 @@
         <v>112</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F137" s="6">
         <v>11</v>
@@ -12299,10 +12302,10 @@
         <v>1</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F139" s="6">
         <v>1</v>
@@ -12368,10 +12371,10 @@
         <v>1</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F140" s="6">
         <v>2</v>
@@ -12437,10 +12440,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F141" s="6">
         <v>3</v>
@@ -12506,10 +12509,10 @@
         <v>1</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F142" s="6">
         <v>4</v>
@@ -12575,10 +12578,10 @@
         <v>1</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F143" s="6">
         <v>5</v>
@@ -12713,10 +12716,10 @@
         <v>2</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F145" s="6">
         <v>1</v>
@@ -12782,10 +12785,10 @@
         <v>2</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F146" s="6">
         <v>2</v>
@@ -12851,10 +12854,10 @@
         <v>2</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F147" s="6">
         <v>3</v>
@@ -12920,10 +12923,10 @@
         <v>2</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F148" s="6">
         <v>4</v>
@@ -12989,10 +12992,10 @@
         <v>2</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F149" s="6">
         <v>5</v>
@@ -13125,10 +13128,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F151" s="6">
         <v>1</v>
@@ -13194,10 +13197,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F152" s="6">
         <v>2</v>
@@ -13263,10 +13266,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F153" s="6">
         <v>3</v>
@@ -13332,10 +13335,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F154" s="6">
         <v>4</v>
@@ -13401,10 +13404,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F155" s="6">
         <v>5</v>
@@ -13539,10 +13542,10 @@
         <v>4</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F157" s="6">
         <v>1</v>
@@ -13608,10 +13611,10 @@
         <v>4</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F158" s="6">
         <v>2</v>
@@ -13677,10 +13680,10 @@
         <v>4</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F159" s="6">
         <v>3</v>
@@ -13746,10 +13749,10 @@
         <v>4</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F160" s="6">
         <v>4</v>
@@ -13815,10 +13818,10 @@
         <v>4</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F161" s="6">
         <v>5</v>
@@ -13884,10 +13887,10 @@
         <v>4</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F162" s="6">
         <v>6</v>
@@ -13953,10 +13956,10 @@
         <v>4</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F163" s="6">
         <v>7</v>
@@ -14022,10 +14025,10 @@
         <v>4</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F164" s="6">
         <v>8</v>
@@ -14091,10 +14094,10 @@
         <v>4</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F165" s="6">
         <v>9</v>
@@ -14160,10 +14163,10 @@
         <v>4</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F166" s="6">
         <v>10</v>
@@ -14229,10 +14232,10 @@
         <v>4</v>
       </c>
       <c r="D167" s="73" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E167" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F167" s="73">
         <v>11</v>
@@ -14298,10 +14301,10 @@
         <v>4</v>
       </c>
       <c r="D168" s="73" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E168" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F168" s="73">
         <v>12</v>
@@ -14367,10 +14370,10 @@
         <v>4</v>
       </c>
       <c r="D169" s="73" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E169" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F169" s="73">
         <v>13</v>
@@ -14436,10 +14439,10 @@
         <v>4</v>
       </c>
       <c r="D170" s="73" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E170" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F170" s="73">
         <v>14</v>
@@ -14505,10 +14508,10 @@
         <v>4</v>
       </c>
       <c r="D171" s="73" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E171" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F171" s="73">
         <v>15</v>
@@ -14574,7 +14577,7 @@
         <v>4</v>
       </c>
       <c r="D172" s="78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E172" s="78" t="s">
         <v>163</v>
@@ -14643,7 +14646,7 @@
         <v>4</v>
       </c>
       <c r="D173" s="78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E173" s="78" t="s">
         <v>163</v>
@@ -14712,7 +14715,7 @@
         <v>4</v>
       </c>
       <c r="D174" s="78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E174" s="78" t="s">
         <v>163</v>
@@ -14781,7 +14784,7 @@
         <v>4</v>
       </c>
       <c r="D175" s="78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E175" s="78" t="s">
         <v>163</v>
@@ -14850,7 +14853,7 @@
         <v>4</v>
       </c>
       <c r="D176" s="78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E176" s="78" t="s">
         <v>163</v>
@@ -14919,7 +14922,7 @@
         <v>4</v>
       </c>
       <c r="D177" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E177" s="86" t="s">
         <v>175</v>
@@ -14988,7 +14991,7 @@
         <v>4</v>
       </c>
       <c r="D178" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E178" s="86" t="s">
         <v>175</v>
@@ -15057,7 +15060,7 @@
         <v>4</v>
       </c>
       <c r="D179" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E179" s="86" t="s">
         <v>175</v>
@@ -15126,7 +15129,7 @@
         <v>4</v>
       </c>
       <c r="D180" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E180" s="86" t="s">
         <v>175</v>
@@ -15195,7 +15198,7 @@
         <v>4</v>
       </c>
       <c r="D181" s="86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E181" s="86" t="s">
         <v>175</v>
@@ -15333,10 +15336,10 @@
         <v>5</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F183" s="6">
         <v>1</v>
@@ -15402,10 +15405,10 @@
         <v>5</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F184" s="6">
         <v>2</v>
@@ -15471,10 +15474,10 @@
         <v>5</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F185" s="6">
         <v>3</v>
@@ -15540,10 +15543,10 @@
         <v>5</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F186" s="6">
         <v>4</v>
@@ -15609,10 +15612,10 @@
         <v>5</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F187" s="6">
         <v>5</v>
@@ -15678,10 +15681,10 @@
         <v>5</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F188" s="6">
         <v>6</v>
@@ -15747,7 +15750,7 @@
         <v>5</v>
       </c>
       <c r="D189" s="78" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E189" s="78" t="s">
         <v>163</v>
@@ -15816,7 +15819,7 @@
         <v>5</v>
       </c>
       <c r="D190" s="78" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E190" s="78" t="s">
         <v>163</v>
@@ -15954,10 +15957,10 @@
         <v>6</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F192" s="6">
         <v>1</v>
@@ -16092,10 +16095,10 @@
         <v>7</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F194" s="6">
         <v>1</v>
@@ -16227,13 +16230,13 @@
         <v>6</v>
       </c>
       <c r="C196" s="6">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F196" s="6">
         <v>1</v>
@@ -16365,13 +16368,13 @@
         <v>6</v>
       </c>
       <c r="C198" s="6">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="D198" s="6" t="s">
         <v>51</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F198" s="6">
         <v>1</v>
@@ -16434,13 +16437,13 @@
         <v>6</v>
       </c>
       <c r="C199" s="6">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="D199" s="6" t="s">
         <v>51</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F199" s="6">
         <v>1</v>
@@ -16572,13 +16575,13 @@
         <v>6</v>
       </c>
       <c r="C201" s="6">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F201" s="6">
         <v>1</v>
@@ -16641,13 +16644,13 @@
         <v>6</v>
       </c>
       <c r="C202" s="6">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F202" s="6">
         <v>2</v>
@@ -16710,13 +16713,13 @@
         <v>6</v>
       </c>
       <c r="C203" s="6">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F203" s="6">
         <v>3</v>
@@ -16779,13 +16782,13 @@
         <v>6</v>
       </c>
       <c r="C204" s="6">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F204" s="6">
         <v>4</v>
@@ -16848,13 +16851,13 @@
         <v>6</v>
       </c>
       <c r="C205" s="6">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F205" s="6">
         <v>5</v>
@@ -16917,13 +16920,13 @@
         <v>6</v>
       </c>
       <c r="C206" s="6">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F206" s="6">
         <v>6</v>
@@ -16986,13 +16989,13 @@
         <v>6</v>
       </c>
       <c r="C207" s="73">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D207" s="73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E207" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F207" s="73">
         <v>7</v>
@@ -17055,13 +17058,13 @@
         <v>6</v>
       </c>
       <c r="C208" s="73">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D208" s="73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E208" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F208" s="73">
         <v>8</v>
@@ -17124,13 +17127,13 @@
         <v>6</v>
       </c>
       <c r="C209" s="73">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D209" s="73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E209" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F209" s="73">
         <v>9</v>
@@ -17193,13 +17196,13 @@
         <v>6</v>
       </c>
       <c r="C210" s="73">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D210" s="73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E210" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F210" s="73">
         <v>10</v>
@@ -17262,13 +17265,13 @@
         <v>6</v>
       </c>
       <c r="C211" s="73">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D211" s="73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E211" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F211" s="73">
         <v>11</v>
@@ -17331,10 +17334,10 @@
         <v>6</v>
       </c>
       <c r="C212" s="78">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D212" s="78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E212" s="78" t="s">
         <v>163</v>
@@ -17400,10 +17403,10 @@
         <v>6</v>
       </c>
       <c r="C213" s="78">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D213" s="78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E213" s="78" t="s">
         <v>163</v>
@@ -17469,10 +17472,10 @@
         <v>6</v>
       </c>
       <c r="C214" s="78">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D214" s="78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E214" s="78" t="s">
         <v>163</v>
@@ -17538,10 +17541,10 @@
         <v>6</v>
       </c>
       <c r="C215" s="78">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D215" s="78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E215" s="78" t="s">
         <v>163</v>
@@ -17607,10 +17610,10 @@
         <v>6</v>
       </c>
       <c r="C216" s="78">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D216" s="78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E216" s="78" t="s">
         <v>163</v>
@@ -17745,13 +17748,13 @@
         <v>6</v>
       </c>
       <c r="C218" s="6">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F218" s="6">
         <v>1</v>
@@ -17814,13 +17817,13 @@
         <v>6</v>
       </c>
       <c r="C219" s="6">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F219" s="6">
         <v>2</v>
@@ -17883,13 +17886,13 @@
         <v>6</v>
       </c>
       <c r="C220" s="6">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F220" s="6">
         <v>3</v>
@@ -17952,13 +17955,13 @@
         <v>6</v>
       </c>
       <c r="C221" s="6">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F221" s="6">
         <v>4</v>
@@ -18021,13 +18024,13 @@
         <v>6</v>
       </c>
       <c r="C222" s="6">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F222" s="6">
         <v>5</v>
@@ -18090,13 +18093,13 @@
         <v>6</v>
       </c>
       <c r="C223" s="6">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F223" s="6">
         <v>6</v>
@@ -18231,10 +18234,10 @@
         <v>201</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F225" s="6">
         <v>1</v>
@@ -18360,7 +18363,7 @@
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>6</v>
@@ -18369,10 +18372,10 @@
         <v>202</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F227" s="6">
         <v>1</v>
@@ -18429,7 +18432,7 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>6</v>
@@ -18438,10 +18441,10 @@
         <v>202</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F228" s="6">
         <v>1</v>
@@ -18498,7 +18501,7 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="73" t="s">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="B229" s="73" t="s">
         <v>6</v>
@@ -18507,10 +18510,10 @@
         <v>202</v>
       </c>
       <c r="D229" s="73" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E229" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F229" s="73">
         <v>1</v>
@@ -18636,7 +18639,7 @@
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>6</v>
@@ -18648,7 +18651,7 @@
         <v>71</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F231" s="6">
         <v>1</v>
@@ -18705,7 +18708,7 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>6</v>
@@ -18717,7 +18720,7 @@
         <v>71</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F232" s="6">
         <v>2</v>
@@ -18774,7 +18777,7 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="73" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B233" s="73" t="s">
         <v>6</v>
@@ -18786,7 +18789,7 @@
         <v>71</v>
       </c>
       <c r="E233" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F233" s="73">
         <v>3</v>
@@ -18843,7 +18846,7 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B234" s="78" t="s">
         <v>6</v>
@@ -18981,7 +18984,7 @@
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>6</v>
@@ -18993,7 +18996,7 @@
         <v>75</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F236" s="6">
         <v>1</v>
@@ -19119,7 +19122,7 @@
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>6</v>
@@ -19131,7 +19134,7 @@
         <v>78</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F238" s="6">
         <v>1</v>
@@ -19188,7 +19191,7 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>6</v>
@@ -19200,7 +19203,7 @@
         <v>78</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F239" s="6">
         <v>2</v>
@@ -19257,7 +19260,7 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>6</v>
@@ -19269,7 +19272,7 @@
         <v>78</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F240" s="6">
         <v>3</v>
@@ -19395,7 +19398,7 @@
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>6</v>
@@ -19407,7 +19410,7 @@
         <v>91</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F242" s="6">
         <v>1</v>
@@ -19464,7 +19467,7 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>6</v>
@@ -19476,7 +19479,7 @@
         <v>91</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F243" s="6">
         <v>2</v>
@@ -19533,7 +19536,7 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>6</v>
@@ -19545,7 +19548,7 @@
         <v>91</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F244" s="6">
         <v>3</v>
@@ -19671,7 +19674,7 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>6</v>
@@ -19683,7 +19686,7 @@
         <v>80</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F246" s="6">
         <v>1</v>
@@ -19740,7 +19743,7 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>6</v>
@@ -19752,7 +19755,7 @@
         <v>80</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F247" s="6">
         <v>1</v>
@@ -19811,7 +19814,7 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>6</v>
@@ -19823,7 +19826,7 @@
         <v>80</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F248" s="6">
         <v>1</v>
@@ -19882,7 +19885,7 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>6</v>
@@ -19894,7 +19897,7 @@
         <v>80</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F249" s="6">
         <v>1</v>
@@ -19953,7 +19956,7 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>6</v>
@@ -19965,7 +19968,7 @@
         <v>80</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F250" s="6">
         <v>1</v>
@@ -20024,7 +20027,7 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>6</v>
@@ -20036,7 +20039,7 @@
         <v>80</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F251" s="6">
         <v>1</v>
@@ -20164,7 +20167,7 @@
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>6</v>
@@ -20176,7 +20179,7 @@
         <v>85</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F253" s="6">
         <v>1</v>
@@ -20233,7 +20236,7 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>6</v>
@@ -20245,7 +20248,7 @@
         <v>85</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F254" s="6">
         <v>2</v>
@@ -20302,7 +20305,7 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>6</v>
@@ -20314,7 +20317,7 @@
         <v>85</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F255" s="6">
         <v>3</v>
@@ -20371,7 +20374,7 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>6</v>
@@ -20383,7 +20386,7 @@
         <v>85</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F256" s="6">
         <v>4</v>
@@ -20440,7 +20443,7 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="73" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B257" s="73" t="s">
         <v>6</v>
@@ -20452,7 +20455,7 @@
         <v>85</v>
       </c>
       <c r="E257" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F257" s="73">
         <v>5</v>
@@ -20509,7 +20512,7 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="73" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B258" s="73" t="s">
         <v>6</v>
@@ -20521,7 +20524,7 @@
         <v>85</v>
       </c>
       <c r="E258" s="73" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="F258" s="73">
         <v>6</v>
@@ -20647,7 +20650,7 @@
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>6</v>
@@ -20659,7 +20662,7 @@
         <v>90</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F260" s="6">
         <v>1</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43564DC1-F923-4227-99BD-35898DD8D923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66659B97-128B-4100-8D52-E0CF82641740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="57810" windowHeight="29895" xr2:uid="{98642A8E-0764-40C3-B15E-624F75792EAD}"/>
+    <workbookView xWindow="0" yWindow="1560" windowWidth="57810" windowHeight="29895" xr2:uid="{23B40020-25F4-47F8-B0D6-D59DCED1BC7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="196">
   <si>
     <t>Building</t>
   </si>
@@ -341,6 +341,9 @@
     <t>RENT SCHEDULE &amp; SECURITY DEPOSIT BY YEAR</t>
   </si>
   <si>
+    <t>Exterior</t>
+  </si>
+  <si>
     <t>Wells Fargo</t>
   </si>
   <si>
@@ -398,10 +401,10 @@
     <t>One 3-Year 31% Jump + 3% Annual Inc</t>
   </si>
   <si>
-    <t>Verizon</t>
+    <t>Roof</t>
   </si>
   <si>
-    <t>Roof</t>
+    <t>Verizon</t>
   </si>
   <si>
     <t>36 South3</t>
@@ -437,6 +440,9 @@
     <t>Three 5-Yr w 2% Ann Inc</t>
   </si>
   <si>
+    <t>O-1</t>
+  </si>
+  <si>
     <t>Sana Yoga Studio, LLC</t>
   </si>
   <si>
@@ -452,10 +458,16 @@
     <t>Two 2-Year</t>
   </si>
   <si>
+    <t>A-1</t>
+  </si>
+  <si>
     <t>VACANT_6</t>
   </si>
   <si>
     <t>Apartment</t>
+  </si>
+  <si>
+    <t>A-2</t>
   </si>
   <si>
     <t>Alan DiEsso</t>
@@ -485,7 +497,7 @@
     <t>Cancel Date</t>
   </si>
   <si>
-    <t>36 South_1_HDR HOLDINGS LLC D/B/A WONDER</t>
+    <t>36 South_101_HDR HOLDINGS LLC D/B/A WONDER</t>
   </si>
   <si>
     <t>Original</t>
@@ -536,22 +548,22 @@
     <t>-</t>
   </si>
   <si>
-    <t>36 South_2_Longo Architects &amp; Associates, LLC</t>
+    <t>36 South_201_Longo Architects &amp; Associates, LLC</t>
   </si>
   <si>
-    <t>36 South_3_Verizon</t>
+    <t>36 South_Roof_Verizon</t>
   </si>
   <si>
-    <t>36 South_3_Easement</t>
+    <t>36 South_Easement_Easement</t>
   </si>
   <si>
     <t>15 South_1_CITY PROPERTY USA NJ, LLC</t>
   </si>
   <si>
-    <t>15 South_2_Wells Fargo</t>
+    <t>15 South_Exterior_Wells Fargo</t>
   </si>
   <si>
-    <t>15 South_3_Easement</t>
+    <t>15 South_Easement_Easement</t>
   </si>
   <si>
     <t>1280 Springfield_1_George's Appliance, LLC</t>
@@ -563,19 +575,19 @@
     <t>1280 Springfield_3_Uppleside Down Wellness, LLC D/B/A Air</t>
   </si>
   <si>
-    <t>1280 Springfield_4_SLK Enterprises, LLC D/B/A AFC Urgent Care</t>
+    <t>1280 Springfield_1286_SLK Enterprises, LLC D/B/A AFC Urgent Care</t>
   </si>
   <si>
     <t>Option_3</t>
   </si>
   <si>
-    <t>1280 Springfield_5_Sana Yoga Studio, LLC</t>
+    <t>1280 Springfield_O-1_Sana Yoga Studio, LLC</t>
   </si>
   <si>
-    <t>1280 Springfield_6_VACANT_6</t>
+    <t>1280 Springfield_A-1_VACANT_6</t>
   </si>
   <si>
-    <t>1280 Springfield_7_Alan DiEsso</t>
+    <t>1280 Springfield_A-2_Alan DiEsso</t>
   </si>
   <si>
     <t>114 Central_102_Nabig Sakr</t>
@@ -1352,7 +1364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01BBE3BE-0B5E-41B0-9D35-E128E88B66BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC2A20B-D228-4C4E-84F6-4F6471E25866}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3250,14 +3262,14 @@
       <c r="A26" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="6">
-        <v>2</v>
+      <c r="B26" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E26" s="6">
         <v>1</v>
@@ -3343,25 +3355,25 @@
         <v>2300</v>
       </c>
       <c r="AK26" s="56" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AL26" s="56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM26" s="56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AN26" s="56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AO26" s="56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AP26" s="56" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AQ26" s="56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR26" s="56" t="s">
         <v>70</v>
@@ -3370,30 +3382,30 @@
         <v>26</v>
       </c>
       <c r="AT26" s="56" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU26" s="56" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AV26" s="57" t="s">
         <v>13</v>
       </c>
       <c r="AW26" s="56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="6">
-        <v>3</v>
+      <c r="B27" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" s="6">
         <v>1</v>
@@ -3601,10 +3613,10 @@
         <v>8</v>
       </c>
       <c r="B29" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>45</v>
@@ -3613,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
@@ -3674,7 +3686,7 @@
         <v>0.03</v>
       </c>
       <c r="AA29" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AB29" s="19">
         <v>3</v>
@@ -3741,10 +3753,10 @@
         <v>8</v>
       </c>
       <c r="B30" s="6">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>61</v>
@@ -3753,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
@@ -3814,7 +3826,7 @@
         <v>0.05</v>
       </c>
       <c r="AA30" s="32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AB30" s="19">
         <v>2</v>
@@ -3878,11 +3890,11 @@
       <c r="A31" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="6">
-        <v>3</v>
+      <c r="B31" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>120</v>
@@ -3891,7 +3903,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
@@ -3952,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AB31" s="19"/>
       <c r="AC31" s="19"/>
@@ -4014,20 +4026,20 @@
       <c r="A32" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="6">
-        <v>4</v>
+      <c r="B32" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
@@ -4232,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>45</v>
@@ -4241,7 +4253,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
@@ -4299,7 +4311,7 @@
         <v>46538</v>
       </c>
       <c r="Z34" s="52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AA34" s="32" t="s">
         <v>48</v>
@@ -4370,7 +4382,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>45</v>
@@ -4379,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6">
@@ -4437,7 +4449,7 @@
         <v>46706</v>
       </c>
       <c r="Z35" s="52" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA35" s="32" t="s">
         <v>48</v>
@@ -4508,7 +4520,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>45</v>
@@ -4517,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6">
@@ -4575,7 +4587,7 @@
         <v>47299</v>
       </c>
       <c r="Z36" s="52" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA36" s="32" t="s">
         <v>48</v>
@@ -4643,10 +4655,10 @@
         <v>9</v>
       </c>
       <c r="B37" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>45</v>
@@ -4655,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6">
@@ -4713,10 +4725,10 @@
         <v>47573</v>
       </c>
       <c r="Z37" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA37" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AB37" s="19">
         <v>3</v>
@@ -4780,20 +4792,20 @@
       <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6">
-        <v>5</v>
+      <c r="B38" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E38" s="6">
         <v>2</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6">
@@ -4851,10 +4863,10 @@
         <v>46996</v>
       </c>
       <c r="Z38" s="52" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AA38" s="32" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AB38" s="19">
         <v>3</v>
@@ -4918,20 +4930,20 @@
       <c r="A39" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="6">
-        <v>6</v>
+      <c r="B39" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E39" s="6">
         <v>2</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6">
@@ -5058,20 +5070,20 @@
       <c r="A40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="6">
-        <v>7</v>
+      <c r="B40" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6">
@@ -5402,7 +5414,7 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
@@ -5414,25 +5426,25 @@
         <v>53</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
@@ -5441,7 +5453,7 @@
         <v>57</v>
       </c>
       <c r="N45" s="69" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="O45" s="69" t="s">
         <v>14</v>
@@ -5450,10 +5462,10 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>31</v>
@@ -5468,7 +5480,7 @@
         <v>37</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AK45" s="22" t="s">
         <v>94</v>
@@ -5512,19 +5524,19 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6">
         <v>0</v>
@@ -5620,19 +5632,19 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
@@ -5728,19 +5740,19 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F48" s="6">
         <v>2</v>
@@ -5836,19 +5848,19 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
@@ -5944,19 +5956,19 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F50" s="6">
         <v>4</v>
@@ -6052,19 +6064,19 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
@@ -6160,19 +6172,19 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
@@ -6229,19 +6241,19 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
@@ -6296,7 +6308,7 @@
       </c>
       <c r="W53" s="13"/>
       <c r="AK53" s="72" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AL53" s="22"/>
       <c r="AM53" s="22"/>
@@ -6308,19 +6320,19 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F54" s="6">
         <v>8</v>
@@ -6375,45 +6387,45 @@
       </c>
       <c r="W54" s="13"/>
       <c r="AK54" s="56" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AL54" s="56" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM54" s="56" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AN54" s="56" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AO54" s="56" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AP54" s="56" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AQ54" s="56" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AR54" s="56" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F55" s="6">
         <v>9</v>
@@ -6468,7 +6480,7 @@
       </c>
       <c r="W55" s="13"/>
       <c r="AK55" s="26" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AL55" s="58">
         <v>0</v>
@@ -6494,19 +6506,19 @@
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F56" s="6">
         <v>10</v>
@@ -6561,7 +6573,7 @@
       </c>
       <c r="W56" s="13"/>
       <c r="AK56" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AL56" s="58">
         <v>0</v>
@@ -6587,19 +6599,19 @@
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="73" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B57" s="73" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="73">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D57" s="73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F57" s="73">
         <v>11</v>
@@ -6654,7 +6666,7 @@
       </c>
       <c r="W57" s="76"/>
       <c r="AK57" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AL57" s="58">
         <v>0</v>
@@ -6680,19 +6692,19 @@
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="73" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B58" s="73" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="73">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D58" s="73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F58" s="73">
         <v>12</v>
@@ -6747,7 +6759,7 @@
       </c>
       <c r="W58" s="76"/>
       <c r="AK58" s="26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AL58" s="58">
         <v>0</v>
@@ -6773,19 +6785,19 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="73" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B59" s="73" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="73">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D59" s="73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F59" s="73">
         <v>13</v>
@@ -6842,19 +6854,19 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="73" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B60" s="73" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="73">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D60" s="73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E60" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F60" s="73">
         <v>14</v>
@@ -6911,19 +6923,19 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="73" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B61" s="73" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="73">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D61" s="73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F61" s="73">
         <v>15</v>
@@ -6980,19 +6992,19 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B62" s="78" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="78">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D62" s="78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E62" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F62" s="78">
         <v>16</v>
@@ -7049,19 +7061,19 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="78" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B63" s="78" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="78">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D63" s="78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E63" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F63" s="78">
         <v>17</v>
@@ -7118,19 +7130,19 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="78" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B64" s="78" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="78">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D64" s="78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E64" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F64" s="78">
         <v>18</v>
@@ -7187,19 +7199,19 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="78" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B65" s="78" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="78">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D65" s="78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E65" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F65" s="78">
         <v>19</v>
@@ -7256,19 +7268,19 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="78" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B66" s="78" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="78">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D66" s="78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E66" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F66" s="78">
         <v>20</v>
@@ -7325,88 +7337,88 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V67" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W67" s="48"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="6">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F68" s="6">
         <v>1</v>
@@ -7463,19 +7475,19 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="6">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F69" s="6">
         <v>2</v>
@@ -7532,19 +7544,19 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="6">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F70" s="6">
         <v>3</v>
@@ -7601,19 +7613,19 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="6">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F71" s="6">
         <v>4</v>
@@ -7670,88 +7682,88 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V72" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W72" s="48"/>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C73" s="6">
-        <v>3</v>
+      <c r="C73" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F73" s="6">
         <v>1</v>
@@ -7808,19 +7820,19 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="6">
-        <v>3</v>
+      <c r="C74" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F74" s="6">
         <v>2</v>
@@ -7877,19 +7889,19 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C75" s="6">
-        <v>3</v>
+      <c r="C75" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F75" s="6">
         <v>3</v>
@@ -7946,19 +7958,19 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="6">
-        <v>3</v>
+      <c r="C76" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F76" s="6">
         <v>4</v>
@@ -8015,19 +8027,19 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="6">
-        <v>3</v>
+      <c r="C77" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F77" s="6">
         <v>5</v>
@@ -8084,19 +8096,19 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C78" s="6">
-        <v>3</v>
+      <c r="C78" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F78" s="6">
         <v>6</v>
@@ -8153,19 +8165,19 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C79" s="6">
-        <v>3</v>
+      <c r="C79" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F79" s="6">
         <v>7</v>
@@ -8222,19 +8234,19 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C80" s="6">
-        <v>3</v>
+      <c r="C80" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F80" s="6">
         <v>8</v>
@@ -8291,19 +8303,19 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C81" s="6">
-        <v>3</v>
+      <c r="C81" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F81" s="6">
         <v>9</v>
@@ -8360,19 +8372,19 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C82" s="6">
-        <v>3</v>
+      <c r="C82" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F82" s="6">
         <v>10</v>
@@ -8429,19 +8441,19 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C83" s="6">
-        <v>3</v>
+      <c r="C83" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F83" s="6">
         <v>11</v>
@@ -8498,19 +8510,19 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C84" s="6">
-        <v>3</v>
+      <c r="C84" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F84" s="6">
         <v>12</v>
@@ -8567,19 +8579,19 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="6">
-        <v>3</v>
+      <c r="C85" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F85" s="6">
         <v>13</v>
@@ -8636,19 +8648,19 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C86" s="6">
-        <v>3</v>
+      <c r="C86" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F86" s="6">
         <v>14</v>
@@ -8705,88 +8717,88 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V87" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W87" s="48"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C88" s="6">
-        <v>3</v>
+      <c r="C88" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F88" s="6">
         <v>1</v>
@@ -8843,19 +8855,19 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="6">
-        <v>3</v>
+      <c r="C89" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F89" s="6">
         <v>2</v>
@@ -8912,19 +8924,19 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C90" s="6">
-        <v>3</v>
+      <c r="C90" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F90" s="6">
         <v>3</v>
@@ -8981,19 +8993,19 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C91" s="6">
-        <v>3</v>
+      <c r="C91" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F91" s="6">
         <v>4</v>
@@ -9050,19 +9062,19 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C92" s="6">
-        <v>3</v>
+      <c r="C92" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F92" s="6">
         <v>5</v>
@@ -9119,19 +9131,19 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C93" s="6">
-        <v>3</v>
+      <c r="C93" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F93" s="6">
         <v>6</v>
@@ -9188,19 +9200,19 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C94" s="6">
-        <v>3</v>
+      <c r="C94" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F94" s="6">
         <v>7</v>
@@ -9257,19 +9269,19 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C95" s="6">
-        <v>3</v>
+      <c r="C95" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F95" s="6">
         <v>8</v>
@@ -9326,19 +9338,19 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C96" s="6">
-        <v>3</v>
+      <c r="C96" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F96" s="6">
         <v>9</v>
@@ -9395,19 +9407,19 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C97" s="6">
-        <v>3</v>
+      <c r="C97" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F97" s="6">
         <v>10</v>
@@ -9464,19 +9476,19 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C98" s="6">
-        <v>3</v>
+      <c r="C98" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F98" s="6">
         <v>11</v>
@@ -9533,76 +9545,76 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V99" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W99" s="48"/>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>7</v>
@@ -9614,7 +9626,7 @@
         <v>95</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F100" s="6">
         <v>1</v>
@@ -9671,7 +9683,7 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
@@ -9683,7 +9695,7 @@
         <v>95</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F101" s="6">
         <v>2</v>
@@ -9740,7 +9752,7 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
@@ -9752,7 +9764,7 @@
         <v>95</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F102" s="6">
         <v>3</v>
@@ -9809,7 +9821,7 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
@@ -9821,7 +9833,7 @@
         <v>95</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F103" s="6">
         <v>4</v>
@@ -9878,7 +9890,7 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
@@ -9890,7 +9902,7 @@
         <v>95</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F104" s="6">
         <v>5</v>
@@ -9947,7 +9959,7 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -9959,7 +9971,7 @@
         <v>95</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F105" s="6">
         <v>6</v>
@@ -10016,7 +10028,7 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>7</v>
@@ -10028,7 +10040,7 @@
         <v>95</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F106" s="6">
         <v>7</v>
@@ -10085,7 +10097,7 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>7</v>
@@ -10097,7 +10109,7 @@
         <v>95</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F107" s="6">
         <v>8</v>
@@ -10154,7 +10166,7 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>7</v>
@@ -10166,7 +10178,7 @@
         <v>95</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F108" s="6">
         <v>9</v>
@@ -10223,7 +10235,7 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
@@ -10235,7 +10247,7 @@
         <v>95</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F109" s="6">
         <v>10</v>
@@ -10292,7 +10304,7 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="73" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B110" s="73" t="s">
         <v>7</v>
@@ -10304,7 +10316,7 @@
         <v>95</v>
       </c>
       <c r="E110" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F110" s="73">
         <v>11</v>
@@ -10361,7 +10373,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="73" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B111" s="73" t="s">
         <v>7</v>
@@ -10373,7 +10385,7 @@
         <v>95</v>
       </c>
       <c r="E111" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F111" s="73">
         <v>12</v>
@@ -10430,7 +10442,7 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="73" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B112" s="73" t="s">
         <v>7</v>
@@ -10442,7 +10454,7 @@
         <v>95</v>
       </c>
       <c r="E112" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F112" s="73">
         <v>13</v>
@@ -10499,7 +10511,7 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="73" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B113" s="73" t="s">
         <v>7</v>
@@ -10511,7 +10523,7 @@
         <v>95</v>
       </c>
       <c r="E113" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F113" s="73">
         <v>14</v>
@@ -10568,7 +10580,7 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="73" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B114" s="73" t="s">
         <v>7</v>
@@ -10580,7 +10592,7 @@
         <v>95</v>
       </c>
       <c r="E114" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F114" s="73">
         <v>15</v>
@@ -10637,88 +10649,88 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V115" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W115" s="48"/>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C116" s="6">
-        <v>2</v>
+      <c r="C116" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F116" s="6">
         <v>1</v>
@@ -10775,19 +10787,19 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C117" s="6">
-        <v>2</v>
+      <c r="C117" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F117" s="6">
         <v>2</v>
@@ -10844,19 +10856,19 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C118" s="6">
-        <v>2</v>
+      <c r="C118" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F118" s="6">
         <v>3</v>
@@ -10913,19 +10925,19 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C119" s="6">
-        <v>2</v>
+      <c r="C119" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F119" s="6">
         <v>4</v>
@@ -10982,19 +10994,19 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C120" s="6">
-        <v>2</v>
+      <c r="C120" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F120" s="6">
         <v>5</v>
@@ -11051,19 +11063,19 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="73" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B121" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="C121" s="73">
-        <v>2</v>
+      <c r="C121" s="73" t="s">
+        <v>100</v>
       </c>
       <c r="D121" s="73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E121" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F121" s="73">
         <v>6</v>
@@ -11120,19 +11132,19 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="73" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B122" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="C122" s="73">
-        <v>2</v>
+      <c r="C122" s="73" t="s">
+        <v>100</v>
       </c>
       <c r="D122" s="73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E122" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F122" s="73">
         <v>7</v>
@@ -11189,19 +11201,19 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="73" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B123" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="C123" s="73">
-        <v>2</v>
+      <c r="C123" s="73" t="s">
+        <v>100</v>
       </c>
       <c r="D123" s="73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E123" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F123" s="73">
         <v>8</v>
@@ -11258,19 +11270,19 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="73" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B124" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="C124" s="73">
-        <v>2</v>
+      <c r="C124" s="73" t="s">
+        <v>100</v>
       </c>
       <c r="D124" s="73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E124" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F124" s="73">
         <v>9</v>
@@ -11327,19 +11339,19 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="73" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B125" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="C125" s="73">
-        <v>2</v>
+      <c r="C125" s="73" t="s">
+        <v>100</v>
       </c>
       <c r="D125" s="73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E125" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F125" s="73">
         <v>10</v>
@@ -11396,88 +11408,88 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V126" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W126" s="48"/>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C127" s="6">
-        <v>3</v>
+      <c r="C127" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F127" s="6">
         <v>1</v>
@@ -11534,19 +11546,19 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C128" s="6">
-        <v>3</v>
+      <c r="C128" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F128" s="6">
         <v>2</v>
@@ -11603,19 +11615,19 @@
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C129" s="6">
-        <v>3</v>
+      <c r="C129" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F129" s="6">
         <v>3</v>
@@ -11672,19 +11684,19 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C130" s="6">
-        <v>3</v>
+      <c r="C130" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F130" s="6">
         <v>4</v>
@@ -11741,19 +11753,19 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C131" s="6">
-        <v>3</v>
+      <c r="C131" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F131" s="6">
         <v>5</v>
@@ -11810,19 +11822,19 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C132" s="6">
-        <v>3</v>
+      <c r="C132" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F132" s="6">
         <v>6</v>
@@ -11879,19 +11891,19 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C133" s="6">
-        <v>3</v>
+      <c r="C133" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F133" s="6">
         <v>7</v>
@@ -11948,19 +11960,19 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C134" s="6">
-        <v>3</v>
+      <c r="C134" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F134" s="6">
         <v>8</v>
@@ -12017,19 +12029,19 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C135" s="6">
-        <v>3</v>
+      <c r="C135" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F135" s="6">
         <v>9</v>
@@ -12086,19 +12098,19 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C136" s="6">
-        <v>3</v>
+      <c r="C136" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F136" s="6">
         <v>10</v>
@@ -12155,19 +12167,19 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C137" s="6">
-        <v>3</v>
+      <c r="C137" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F137" s="6">
         <v>11</v>
@@ -12224,76 +12236,76 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V138" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W138" s="48"/>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>9</v>
@@ -12302,10 +12314,10 @@
         <v>1</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F139" s="6">
         <v>1</v>
@@ -12362,7 +12374,7 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>9</v>
@@ -12371,10 +12383,10 @@
         <v>1</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F140" s="6">
         <v>2</v>
@@ -12431,7 +12443,7 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>9</v>
@@ -12440,10 +12452,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F141" s="6">
         <v>3</v>
@@ -12500,7 +12512,7 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>9</v>
@@ -12509,10 +12521,10 @@
         <v>1</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F142" s="6">
         <v>4</v>
@@ -12569,7 +12581,7 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>9</v>
@@ -12578,10 +12590,10 @@
         <v>1</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F143" s="6">
         <v>5</v>
@@ -12638,76 +12650,76 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W144" s="48"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>9</v>
@@ -12716,10 +12728,10 @@
         <v>2</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F145" s="6">
         <v>1</v>
@@ -12776,7 +12788,7 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>9</v>
@@ -12785,10 +12797,10 @@
         <v>2</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F146" s="6">
         <v>2</v>
@@ -12845,7 +12857,7 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>9</v>
@@ -12854,10 +12866,10 @@
         <v>2</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F147" s="6">
         <v>3</v>
@@ -12914,7 +12926,7 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>9</v>
@@ -12923,10 +12935,10 @@
         <v>2</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F148" s="6">
         <v>4</v>
@@ -12983,7 +12995,7 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>9</v>
@@ -12992,10 +13004,10 @@
         <v>2</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F149" s="6">
         <v>5</v>
@@ -13050,76 +13062,76 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V150" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W150" s="48"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>9</v>
@@ -13128,10 +13140,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F151" s="6">
         <v>1</v>
@@ -13188,7 +13200,7 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>9</v>
@@ -13197,10 +13209,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F152" s="6">
         <v>2</v>
@@ -13257,7 +13269,7 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>9</v>
@@ -13266,10 +13278,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F153" s="6">
         <v>3</v>
@@ -13326,7 +13338,7 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>9</v>
@@ -13335,10 +13347,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F154" s="6">
         <v>4</v>
@@ -13395,7 +13407,7 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>9</v>
@@ -13404,10 +13416,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F155" s="6">
         <v>5</v>
@@ -13464,88 +13476,88 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V156" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W156" s="48"/>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C157" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F157" s="6">
         <v>1</v>
@@ -13602,19 +13614,19 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C158" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F158" s="6">
         <v>2</v>
@@ -13671,19 +13683,19 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F159" s="6">
         <v>3</v>
@@ -13740,19 +13752,19 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C160" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F160" s="6">
         <v>4</v>
@@ -13809,19 +13821,19 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C161" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F161" s="6">
         <v>5</v>
@@ -13878,19 +13890,19 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C162" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F162" s="6">
         <v>6</v>
@@ -13947,19 +13959,19 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C163" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F163" s="6">
         <v>7</v>
@@ -14016,19 +14028,19 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C164" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F164" s="6">
         <v>8</v>
@@ -14085,19 +14097,19 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F165" s="6">
         <v>9</v>
@@ -14154,19 +14166,19 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="6">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F166" s="6">
         <v>10</v>
@@ -14223,19 +14235,19 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="73" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B167" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C167" s="73">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D167" s="73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E167" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F167" s="73">
         <v>11</v>
@@ -14292,19 +14304,19 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" s="73" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B168" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C168" s="73">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D168" s="73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E168" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F168" s="73">
         <v>12</v>
@@ -14361,19 +14373,19 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="73" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B169" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C169" s="73">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D169" s="73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E169" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F169" s="73">
         <v>13</v>
@@ -14430,19 +14442,19 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" s="73" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B170" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C170" s="73">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D170" s="73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E170" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F170" s="73">
         <v>14</v>
@@ -14499,19 +14511,19 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" s="73" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B171" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C171" s="73">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D171" s="73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E171" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F171" s="73">
         <v>15</v>
@@ -14568,19 +14580,19 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="78" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B172" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="78">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D172" s="78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E172" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F172" s="78">
         <v>16</v>
@@ -14637,19 +14649,19 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" s="78" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B173" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C173" s="78">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D173" s="78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E173" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F173" s="78">
         <v>17</v>
@@ -14706,19 +14718,19 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" s="78" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B174" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C174" s="78">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D174" s="78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E174" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F174" s="78">
         <v>18</v>
@@ -14775,19 +14787,19 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" s="78" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B175" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C175" s="78">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D175" s="78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E175" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F175" s="78">
         <v>19</v>
@@ -14844,19 +14856,19 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="78" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B176" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C176" s="78">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D176" s="78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E176" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F176" s="78">
         <v>20</v>
@@ -14913,19 +14925,19 @@
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" s="86" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B177" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C177" s="86">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D177" s="86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E177" s="86" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F177" s="86">
         <v>21</v>
@@ -14982,19 +14994,19 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" s="86" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B178" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C178" s="86">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D178" s="86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E178" s="86" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F178" s="86">
         <v>22</v>
@@ -15051,19 +15063,19 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" s="86" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B179" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C179" s="86">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D179" s="86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E179" s="86" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F179" s="86">
         <v>23</v>
@@ -15120,19 +15132,19 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="86" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B180" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C180" s="86">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D180" s="86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E180" s="86" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F180" s="86">
         <v>24</v>
@@ -15189,19 +15201,19 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" s="86" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B181" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C181" s="86">
-        <v>4</v>
+        <v>1286</v>
       </c>
       <c r="D181" s="86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E181" s="86" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F181" s="86">
         <v>25</v>
@@ -15258,88 +15270,88 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V182" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W182" s="48"/>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C183" s="6">
-        <v>5</v>
+      <c r="C183" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F183" s="6">
         <v>1</v>
@@ -15396,19 +15408,19 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C184" s="6">
-        <v>5</v>
+      <c r="C184" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F184" s="6">
         <v>2</v>
@@ -15465,19 +15477,19 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C185" s="6">
-        <v>5</v>
+      <c r="C185" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F185" s="6">
         <v>3</v>
@@ -15534,19 +15546,19 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C186" s="6">
-        <v>5</v>
+      <c r="C186" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F186" s="6">
         <v>4</v>
@@ -15603,19 +15615,19 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C187" s="6">
-        <v>5</v>
+      <c r="C187" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F187" s="6">
         <v>5</v>
@@ -15672,19 +15684,19 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C188" s="6">
-        <v>5</v>
+      <c r="C188" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F188" s="6">
         <v>6</v>
@@ -15741,19 +15753,19 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="78" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B189" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C189" s="78">
-        <v>5</v>
+      <c r="C189" s="78" t="s">
+        <v>133</v>
       </c>
       <c r="D189" s="78" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E189" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F189" s="78">
         <v>7</v>
@@ -15810,19 +15822,19 @@
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" s="78" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B190" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C190" s="78">
-        <v>5</v>
+      <c r="C190" s="78" t="s">
+        <v>133</v>
       </c>
       <c r="D190" s="78" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E190" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F190" s="78">
         <v>8</v>
@@ -15879,88 +15891,88 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V191" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W191" s="48"/>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C192" s="6">
-        <v>6</v>
+      <c r="C192" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F192" s="6">
         <v>1</v>
@@ -16017,88 +16029,88 @@
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V193" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W193" s="48"/>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C194" s="6">
-        <v>7</v>
+      <c r="C194" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F194" s="6">
         <v>1</v>
@@ -16155,76 +16167,76 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V195" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W195" s="48"/>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>6</v>
@@ -16236,7 +16248,7 @@
         <v>44</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F196" s="6">
         <v>1</v>
@@ -16293,76 +16305,76 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V197" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W197" s="48"/>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>6</v>
@@ -16374,7 +16386,7 @@
         <v>51</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F198" s="6">
         <v>1</v>
@@ -16431,7 +16443,7 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>6</v>
@@ -16443,7 +16455,7 @@
         <v>51</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F199" s="6">
         <v>1</v>
@@ -16500,76 +16512,76 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V200" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W200" s="48"/>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>6</v>
@@ -16581,7 +16593,7 @@
         <v>54</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F201" s="6">
         <v>1</v>
@@ -16638,7 +16650,7 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>6</v>
@@ -16650,7 +16662,7 @@
         <v>54</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F202" s="6">
         <v>2</v>
@@ -16707,7 +16719,7 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>6</v>
@@ -16719,7 +16731,7 @@
         <v>54</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F203" s="6">
         <v>3</v>
@@ -16776,7 +16788,7 @@
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>6</v>
@@ -16788,7 +16800,7 @@
         <v>54</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F204" s="6">
         <v>4</v>
@@ -16845,7 +16857,7 @@
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>6</v>
@@ -16857,7 +16869,7 @@
         <v>54</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F205" s="6">
         <v>5</v>
@@ -16914,7 +16926,7 @@
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>6</v>
@@ -16926,7 +16938,7 @@
         <v>54</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F206" s="6">
         <v>6</v>
@@ -16983,7 +16995,7 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" s="73" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B207" s="73" t="s">
         <v>6</v>
@@ -16995,7 +17007,7 @@
         <v>54</v>
       </c>
       <c r="E207" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F207" s="73">
         <v>7</v>
@@ -17052,7 +17064,7 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" s="73" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B208" s="73" t="s">
         <v>6</v>
@@ -17064,7 +17076,7 @@
         <v>54</v>
       </c>
       <c r="E208" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F208" s="73">
         <v>8</v>
@@ -17121,7 +17133,7 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" s="73" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B209" s="73" t="s">
         <v>6</v>
@@ -17133,7 +17145,7 @@
         <v>54</v>
       </c>
       <c r="E209" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F209" s="73">
         <v>9</v>
@@ -17190,7 +17202,7 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" s="73" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B210" s="73" t="s">
         <v>6</v>
@@ -17202,7 +17214,7 @@
         <v>54</v>
       </c>
       <c r="E210" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F210" s="73">
         <v>10</v>
@@ -17259,7 +17271,7 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" s="73" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B211" s="73" t="s">
         <v>6</v>
@@ -17271,7 +17283,7 @@
         <v>54</v>
       </c>
       <c r="E211" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F211" s="73">
         <v>11</v>
@@ -17328,7 +17340,7 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" s="78" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B212" s="78" t="s">
         <v>6</v>
@@ -17340,7 +17352,7 @@
         <v>54</v>
       </c>
       <c r="E212" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F212" s="78">
         <v>12</v>
@@ -17397,7 +17409,7 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" s="78" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B213" s="78" t="s">
         <v>6</v>
@@ -17409,7 +17421,7 @@
         <v>54</v>
       </c>
       <c r="E213" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F213" s="78">
         <v>13</v>
@@ -17466,7 +17478,7 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" s="78" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B214" s="78" t="s">
         <v>6</v>
@@ -17478,7 +17490,7 @@
         <v>54</v>
       </c>
       <c r="E214" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F214" s="78">
         <v>14</v>
@@ -17535,7 +17547,7 @@
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" s="78" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B215" s="78" t="s">
         <v>6</v>
@@ -17547,7 +17559,7 @@
         <v>54</v>
       </c>
       <c r="E215" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F215" s="78">
         <v>15</v>
@@ -17604,7 +17616,7 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" s="78" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B216" s="78" t="s">
         <v>6</v>
@@ -17616,7 +17628,7 @@
         <v>54</v>
       </c>
       <c r="E216" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F216" s="78">
         <v>16</v>
@@ -17673,76 +17685,76 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V217" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W217" s="48"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>6</v>
@@ -17754,7 +17766,7 @@
         <v>58</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F218" s="6">
         <v>1</v>
@@ -17811,7 +17823,7 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>6</v>
@@ -17823,7 +17835,7 @@
         <v>58</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F219" s="6">
         <v>2</v>
@@ -17880,7 +17892,7 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>6</v>
@@ -17892,7 +17904,7 @@
         <v>58</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F220" s="6">
         <v>3</v>
@@ -17949,7 +17961,7 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>6</v>
@@ -17961,7 +17973,7 @@
         <v>58</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F221" s="6">
         <v>4</v>
@@ -18018,7 +18030,7 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>6</v>
@@ -18030,7 +18042,7 @@
         <v>58</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F222" s="6">
         <v>5</v>
@@ -18087,7 +18099,7 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>6</v>
@@ -18099,7 +18111,7 @@
         <v>58</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F223" s="6">
         <v>6</v>
@@ -18156,76 +18168,76 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V224" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W224" s="48"/>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>6</v>
@@ -18237,7 +18249,7 @@
         <v>60</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F225" s="6">
         <v>1</v>
@@ -18294,76 +18306,76 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V226" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W226" s="48"/>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>6</v>
@@ -18375,7 +18387,7 @@
         <v>66</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F227" s="6">
         <v>1</v>
@@ -18432,7 +18444,7 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>6</v>
@@ -18444,7 +18456,7 @@
         <v>66</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F228" s="6">
         <v>1</v>
@@ -18501,7 +18513,7 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="73" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B229" s="73" t="s">
         <v>6</v>
@@ -18513,7 +18525,7 @@
         <v>66</v>
       </c>
       <c r="E229" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F229" s="73">
         <v>1</v>
@@ -18570,76 +18582,76 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V230" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W230" s="48"/>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>6</v>
@@ -18651,7 +18663,7 @@
         <v>71</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F231" s="6">
         <v>1</v>
@@ -18708,7 +18720,7 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>6</v>
@@ -18720,7 +18732,7 @@
         <v>71</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F232" s="6">
         <v>2</v>
@@ -18777,7 +18789,7 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="73" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B233" s="73" t="s">
         <v>6</v>
@@ -18789,7 +18801,7 @@
         <v>71</v>
       </c>
       <c r="E233" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F233" s="73">
         <v>3</v>
@@ -18846,7 +18858,7 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="78" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B234" s="78" t="s">
         <v>6</v>
@@ -18858,7 +18870,7 @@
         <v>71</v>
       </c>
       <c r="E234" s="78" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F234" s="78">
         <v>4</v>
@@ -18915,76 +18927,76 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V235" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W235" s="48"/>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>6</v>
@@ -18996,7 +19008,7 @@
         <v>75</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F236" s="6">
         <v>1</v>
@@ -19053,76 +19065,76 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V237" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W237" s="48"/>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>6</v>
@@ -19134,7 +19146,7 @@
         <v>78</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F238" s="6">
         <v>1</v>
@@ -19191,7 +19203,7 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>6</v>
@@ -19203,7 +19215,7 @@
         <v>78</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F239" s="6">
         <v>2</v>
@@ -19260,7 +19272,7 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>6</v>
@@ -19272,7 +19284,7 @@
         <v>78</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F240" s="6">
         <v>3</v>
@@ -19329,76 +19341,76 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V241" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W241" s="48"/>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>6</v>
@@ -19410,7 +19422,7 @@
         <v>91</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F242" s="6">
         <v>1</v>
@@ -19467,7 +19479,7 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>6</v>
@@ -19479,7 +19491,7 @@
         <v>91</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F243" s="6">
         <v>2</v>
@@ -19536,7 +19548,7 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>6</v>
@@ -19548,7 +19560,7 @@
         <v>91</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F244" s="6">
         <v>3</v>
@@ -19605,76 +19617,76 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V245" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W245" s="48"/>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>6</v>
@@ -19686,7 +19698,7 @@
         <v>80</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F246" s="6">
         <v>1</v>
@@ -19743,7 +19755,7 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>6</v>
@@ -19755,7 +19767,7 @@
         <v>80</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F247" s="6">
         <v>1</v>
@@ -19814,7 +19826,7 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>6</v>
@@ -19826,7 +19838,7 @@
         <v>80</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F248" s="6">
         <v>1</v>
@@ -19885,7 +19897,7 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>6</v>
@@ -19897,7 +19909,7 @@
         <v>80</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F249" s="6">
         <v>1</v>
@@ -19956,7 +19968,7 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>6</v>
@@ -19968,7 +19980,7 @@
         <v>80</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F250" s="6">
         <v>1</v>
@@ -20027,7 +20039,7 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>6</v>
@@ -20039,7 +20051,7 @@
         <v>80</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F251" s="6">
         <v>1</v>
@@ -20098,76 +20110,76 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V252" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W252" s="48"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>6</v>
@@ -20179,7 +20191,7 @@
         <v>85</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F253" s="6">
         <v>1</v>
@@ -20236,7 +20248,7 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>6</v>
@@ -20248,7 +20260,7 @@
         <v>85</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F254" s="6">
         <v>2</v>
@@ -20305,7 +20317,7 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>6</v>
@@ -20317,7 +20329,7 @@
         <v>85</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F255" s="6">
         <v>3</v>
@@ -20374,7 +20386,7 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>6</v>
@@ -20386,7 +20398,7 @@
         <v>85</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F256" s="6">
         <v>4</v>
@@ -20443,7 +20455,7 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="73" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B257" s="73" t="s">
         <v>6</v>
@@ -20455,7 +20467,7 @@
         <v>85</v>
       </c>
       <c r="E257" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F257" s="73">
         <v>5</v>
@@ -20512,7 +20524,7 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="73" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B258" s="73" t="s">
         <v>6</v>
@@ -20524,7 +20536,7 @@
         <v>85</v>
       </c>
       <c r="E258" s="73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F258" s="73">
         <v>6</v>
@@ -20581,76 +20593,76 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="R259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="T259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="U259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V259" s="48" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="W259" s="48"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>6</v>
@@ -20662,7 +20674,7 @@
         <v>90</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F260" s="6">
         <v>1</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66659B97-128B-4100-8D52-E0CF82641740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF15A9EE-BBF6-42E7-B10C-5A9FDC9E9109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1560" windowWidth="57810" windowHeight="29895" xr2:uid="{23B40020-25F4-47F8-B0D6-D59DCED1BC7D}"/>
+    <workbookView xWindow="3900" yWindow="2505" windowWidth="52710" windowHeight="29895" xr2:uid="{D9B1E835-4EA7-45B9-95AD-63C9A334A55D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="195">
   <si>
     <t>Building</t>
   </si>
@@ -191,7 +191,7 @@
     <t>Select Tenant:</t>
   </si>
   <si>
-    <t xml:space="preserve">114 Central_202_Tang Pacific LLC D/BA ARSA </t>
+    <t>36 South_101_HDR HOLDINGS LLC D/B/A WONDER</t>
   </si>
   <si>
     <t>EJS Westfield Toybox, LLC d/b/a Learning Express</t>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>Tenant</t>
+  </si>
+  <si>
+    <t>HDR HOLDINGS LLC D/B/A WONDER</t>
   </si>
   <si>
     <t>Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
@@ -296,6 +299,9 @@
     <t>Clauses</t>
   </si>
   <si>
+    <t>Two 5-Year 3% Annual Inc; 2nd Fl Non-Comp</t>
+  </si>
+  <si>
     <t>Westfield Education Association</t>
   </si>
   <si>
@@ -383,13 +389,7 @@
     <t>Easement</t>
   </si>
   <si>
-    <t>HDR HOLDINGS LLC D/B/A WONDER</t>
-  </si>
-  <si>
     <t>36 South1</t>
-  </si>
-  <si>
-    <t>Two 5-Year 3% Annual Inc</t>
   </si>
   <si>
     <t>Longo Architects &amp; Associates, LLC</t>
@@ -399,6 +399,9 @@
   </si>
   <si>
     <t>One 3-Year 31% Jump + 3% Annual Inc</t>
+  </si>
+  <si>
+    <t>Original</t>
   </si>
   <si>
     <t>Roof</t>
@@ -458,6 +461,9 @@
     <t>Two 2-Year</t>
   </si>
   <si>
+    <t>Option_1</t>
+  </si>
+  <si>
     <t>A-1</t>
   </si>
   <si>
@@ -471,6 +477,9 @@
   </si>
   <si>
     <t>Alan DiEsso</t>
+  </si>
+  <si>
+    <t>Option_2</t>
   </si>
   <si>
     <t>ID</t>
@@ -495,12 +504,6 @@
   </si>
   <si>
     <t>Cancel Date</t>
-  </si>
-  <si>
-    <t>36 South_101_HDR HOLDINGS LLC D/B/A WONDER</t>
-  </si>
-  <si>
-    <t>Original</t>
   </si>
   <si>
     <t>LEASE OPTIONS SUMMARY</t>
@@ -533,16 +536,10 @@
     <t>Option 1</t>
   </si>
   <si>
-    <t>Option_1</t>
-  </si>
-  <si>
     <t>Option 2</t>
   </si>
   <si>
     <t>Option 3</t>
-  </si>
-  <si>
-    <t>Option_2</t>
   </si>
   <si>
     <t>-</t>
@@ -1364,7 +1361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC2A20B-D228-4C4E-84F6-4F6471E25866}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B2C5D1-C167-4464-8B30-AB7D63A1BB8A}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1402,13 +1399,13 @@
     <col min="37" max="37" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="15.5703125" customWidth="1"/>
-    <col min="46" max="46" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="14" customWidth="1"/>
     <col min="47" max="47" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="18.140625" customWidth="1"/>
@@ -1852,8 +1849,8 @@
       <c r="AS12" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="AT12" s="22" t="e">
-        <v>#N/A</v>
+      <c r="AT12" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
@@ -1864,7 +1861,7 @@
         <v>106</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>45</v>
@@ -1931,7 +1928,7 @@
         <v>46810</v>
       </c>
       <c r="Z13" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA13" s="18">
         <v>46565</v>
@@ -1942,7 +1939,7 @@
       <c r="AC13" s="19"/>
       <c r="AD13" s="16"/>
       <c r="AE13" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AF13" s="13">
         <v>11.637681159420289</v>
@@ -1959,14 +1956,14 @@
       <c r="AK13" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="AL13" s="22" t="e">
-        <v>#N/A</v>
+      <c r="AL13" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="AS13" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT13" s="27" t="e">
-        <v>#N/A</v>
+        <v>58</v>
+      </c>
+      <c r="AT13" s="27">
+        <v>4064</v>
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
@@ -1977,7 +1974,7 @@
         <v>108</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>45</v>
@@ -2068,14 +2065,14 @@
       <c r="AK14" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="AL14" s="22" t="e">
-        <v>#N/A</v>
+      <c r="AL14" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="AS14" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="AT14" s="28" t="e">
-        <v>#N/A</v>
+        <v>60</v>
+      </c>
+      <c r="AT14" s="28">
+        <v>49034</v>
       </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
@@ -2086,16 +2083,16 @@
         <v>201</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="6">
         <v>2</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6">
@@ -2160,7 +2157,7 @@
       <c r="AC15" s="19"/>
       <c r="AD15" s="16"/>
       <c r="AE15" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AF15" s="13">
         <v>0</v>
@@ -2175,16 +2172,16 @@
         <v>1632.5</v>
       </c>
       <c r="AK15" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL15" s="22" t="e">
-        <v>#N/A</v>
+        <v>65</v>
+      </c>
+      <c r="AL15" s="22">
+        <v>101</v>
       </c>
       <c r="AS15" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="AT15" s="30" t="e">
-        <v>#N/A</v>
+        <v>66</v>
+      </c>
+      <c r="AT15" s="30">
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
@@ -2195,16 +2192,16 @@
         <v>202</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="6">
         <v>2</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6">
@@ -2262,7 +2259,7 @@
         <v>46507</v>
       </c>
       <c r="Z16" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA16" s="18">
         <v>46327</v>
@@ -2272,10 +2269,10 @@
       </c>
       <c r="AC16" s="19"/>
       <c r="AD16" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE16" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF16" s="13">
         <v>0</v>
@@ -2292,14 +2289,14 @@
       <c r="AK16" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AL16" s="22" t="e">
-        <v>#N/A</v>
+      <c r="AL16" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="AS16" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT16" s="31" t="e">
-        <v>#N/A</v>
+        <v>71</v>
+      </c>
+      <c r="AT16" s="31">
+        <v>45.618700000000004</v>
       </c>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
@@ -2310,16 +2307,16 @@
         <v>203</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="6">
         <v>2</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6">
@@ -2386,7 +2383,7 @@
       <c r="AC17" s="19"/>
       <c r="AD17" s="32"/>
       <c r="AE17" s="32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AF17" s="13">
         <v>0</v>
@@ -2401,22 +2398,22 @@
         <v>1555</v>
       </c>
       <c r="AK17" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL17" s="27" t="e">
-        <v>#N/A</v>
+        <v>58</v>
+      </c>
+      <c r="AL17" s="27">
+        <v>4064</v>
       </c>
       <c r="AM17" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN17" s="31" t="e">
-        <v>#N/A</v>
+        <v>74</v>
+      </c>
+      <c r="AN17" s="31">
+        <v>46348.599200000004</v>
       </c>
       <c r="AS17" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT17" s="33" t="e">
-        <v>#N/A</v>
+        <v>75</v>
+      </c>
+      <c r="AT17" s="33">
+        <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
@@ -2427,16 +2424,16 @@
         <v>204</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
@@ -2516,20 +2513,20 @@
       <c r="AK18" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="AL18" s="34" t="e">
-        <v>#N/A</v>
+      <c r="AL18" s="34">
+        <v>1</v>
       </c>
       <c r="AM18" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN18" s="34" t="s">
-        <v>68</v>
+        <v>77</v>
+      </c>
+      <c r="AN18" s="34">
+        <v>0.6</v>
       </c>
       <c r="AS18" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT18" s="35" t="e">
-        <v>#N/A</v>
+        <v>78</v>
+      </c>
+      <c r="AT18" s="35">
+        <v>48854</v>
       </c>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
@@ -2540,16 +2537,16 @@
         <v>205</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E19" s="6">
         <v>2</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6">
@@ -2629,22 +2626,22 @@
         <v>1225</v>
       </c>
       <c r="AK19" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL19" s="34" t="e">
-        <v>#N/A</v>
+        <v>75</v>
+      </c>
+      <c r="AL19" s="34">
+        <v>0.6</v>
       </c>
       <c r="AM19" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN19" s="34" t="s">
-        <v>68</v>
+        <v>80</v>
+      </c>
+      <c r="AN19" s="34">
+        <v>0.6</v>
       </c>
       <c r="AS19" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="AT19" s="36" t="s">
-        <v>68</v>
+      <c r="AT19" s="36">
+        <v>48854</v>
       </c>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
@@ -2655,16 +2652,16 @@
         <v>206</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6">
@@ -2722,7 +2719,7 @@
         <v>47968</v>
       </c>
       <c r="Z20" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA20" s="18">
         <v>46417</v>
@@ -2732,7 +2729,7 @@
       </c>
       <c r="AC20" s="19"/>
       <c r="AD20" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE20" s="16"/>
       <c r="AF20" s="13">
@@ -2748,22 +2745,22 @@
         <v>1465</v>
       </c>
       <c r="AK20" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL20" s="28" t="e">
-        <v>#N/A</v>
+        <v>83</v>
+      </c>
+      <c r="AL20" s="28">
+        <v>45383</v>
       </c>
       <c r="AM20" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN20" s="34" t="e">
-        <v>#VALUE!</v>
+        <v>84</v>
+      </c>
+      <c r="AN20" s="34">
+        <v>0</v>
       </c>
       <c r="AS20" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT20" s="27" t="e">
-        <v>#N/A</v>
+        <v>85</v>
+      </c>
+      <c r="AT20" s="27" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
@@ -2774,16 +2771,16 @@
         <v>207</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E21" s="6">
         <v>2</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6">
@@ -2850,7 +2847,7 @@
       <c r="AC21" s="19"/>
       <c r="AD21" s="16"/>
       <c r="AE21" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AF21" s="13">
         <v>0</v>
@@ -2865,19 +2862,19 @@
         <v>1982.5</v>
       </c>
       <c r="AK21" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL21" s="28" t="e">
-        <v>#N/A</v>
+        <v>89</v>
+      </c>
+      <c r="AL21" s="28">
+        <v>45566</v>
       </c>
       <c r="AM21" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN21" s="31" t="e">
-        <v>#N/A</v>
+        <v>90</v>
+      </c>
+      <c r="AN21" s="31">
+        <v>5080</v>
       </c>
       <c r="AS21" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AT21" s="36">
         <v>46301</v>
@@ -2891,16 +2888,16 @@
         <v>208</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6">
@@ -2980,19 +2977,19 @@
         <v>680</v>
       </c>
       <c r="AK22" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL22" s="38" t="e">
-        <v>#N/A</v>
+        <v>60</v>
+      </c>
+      <c r="AL22" s="38">
+        <v>49034</v>
       </c>
       <c r="AM22" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN22" s="30" t="e">
-        <v>#N/A</v>
+        <v>66</v>
+      </c>
+      <c r="AN22" s="30">
+        <v>96</v>
       </c>
       <c r="AS22" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AT22" s="39">
         <v>4.9000000000000004</v>
@@ -3006,16 +3003,16 @@
         <v>209</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" s="6">
         <v>2</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6">
@@ -3095,13 +3092,13 @@
         <v>687.5</v>
       </c>
       <c r="AK23" s="26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AL23" s="28" t="b">
         <v>1</v>
       </c>
       <c r="AS23" s="23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AT23" s="40"/>
     </row>
@@ -3112,7 +3109,7 @@
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
       <c r="F24" s="41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
@@ -3154,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>45</v>
@@ -3163,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6">
@@ -3221,10 +3218,10 @@
         <v>49064</v>
       </c>
       <c r="Z25" s="52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA25" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AB25" s="19"/>
       <c r="AC25" s="19"/>
@@ -3243,7 +3240,7 @@
         <v>16666.666666666668</v>
       </c>
       <c r="AK25" s="53" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AL25" s="54"/>
       <c r="AM25" s="54"/>
@@ -3263,19 +3260,19 @@
         <v>7</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E26" s="6">
         <v>1</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6">
@@ -3333,10 +3330,10 @@
         <v>47603</v>
       </c>
       <c r="Z26" s="52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA26" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AB26" s="19"/>
       <c r="AC26" s="19"/>
@@ -3355,43 +3352,43 @@
         <v>2300</v>
       </c>
       <c r="AK26" s="56" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AL26" s="56" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AM26" s="56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AN26" s="56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AO26" s="56" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AP26" s="56" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AQ26" s="56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AR26" s="56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AS26" s="56" t="s">
         <v>26</v>
       </c>
       <c r="AT26" s="56" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AU26" s="56" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AV26" s="57" t="s">
         <v>13</v>
       </c>
       <c r="AW26" s="56" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
@@ -3399,19 +3396,19 @@
         <v>7</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E27" s="6">
         <v>1</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6">
@@ -3487,43 +3484,43 @@
         <v>0</v>
       </c>
       <c r="AK27" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL27" s="58" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM27" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN27" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO27" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP27" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ27" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR27" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS27" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AT27" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU27" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV27" s="61" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AW27" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
@@ -3533,7 +3530,7 @@
       <c r="D28" s="41"/>
       <c r="E28" s="41"/>
       <c r="F28" s="41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G28" s="41"/>
       <c r="H28" s="41"/>
@@ -3569,43 +3566,43 @@
       </c>
       <c r="AI28" s="45"/>
       <c r="AK28" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL28" s="62" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM28" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN28" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO28" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP28" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ28" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR28" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS28" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AT28" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU28" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV28" s="67" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AW28" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
@@ -3616,7 +3613,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>45</v>
@@ -3625,7 +3622,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
@@ -3685,8 +3682,8 @@
       <c r="Z29" s="52">
         <v>0.03</v>
       </c>
-      <c r="AA29" s="32" t="s">
-        <v>116</v>
+      <c r="AA29" s="18">
+        <v>48854</v>
       </c>
       <c r="AB29" s="19">
         <v>3</v>
@@ -3695,7 +3692,9 @@
         <v>0</v>
       </c>
       <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
+      <c r="AE29" s="32" t="s">
+        <v>86</v>
+      </c>
       <c r="AF29" s="13">
         <v>15</v>
       </c>
@@ -3709,43 +3708,43 @@
         <v>16933.333333333332</v>
       </c>
       <c r="AK29" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL29" s="58" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM29" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN29" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO29" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP29" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ29" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR29" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS29" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AT29" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU29" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV29" s="61" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AW29" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
@@ -3759,7 +3758,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30" s="6">
         <v>2</v>
@@ -3847,43 +3846,43 @@
         <v>8747.9166666666661</v>
       </c>
       <c r="AK30" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL30" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM30" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN30" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO30" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP30" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ30" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR30" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS30" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT30" s="66" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL30" s="62">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="63">
+        <v>46113</v>
+      </c>
+      <c r="AN30" s="63">
+        <v>46477</v>
+      </c>
+      <c r="AO30" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP30" s="65">
+        <v>15449.533066666669</v>
+      </c>
+      <c r="AQ30" s="66">
+        <v>185394.39680000002</v>
+      </c>
+      <c r="AR30" s="65">
+        <v>45.618700000000004</v>
+      </c>
+      <c r="AS30" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT30" s="66">
+        <v>46348.599200000004</v>
       </c>
       <c r="AU30" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV30" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW30" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW30" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
@@ -3891,19 +3890,19 @@
         <v>8</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="E31" s="6">
         <v>3</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
@@ -3964,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AB31" s="19"/>
       <c r="AC31" s="19"/>
@@ -3983,43 +3982,43 @@
         <v>0</v>
       </c>
       <c r="AK31" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL31" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM31" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN31" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO31" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP31" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ31" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR31" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS31" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT31" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU31" s="60" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL31" s="58">
+        <v>4</v>
+      </c>
+      <c r="AM31" s="28">
+        <v>46478</v>
+      </c>
+      <c r="AN31" s="28">
+        <v>46843</v>
+      </c>
+      <c r="AO31" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP31" s="59">
+        <v>15913.019058666667</v>
+      </c>
+      <c r="AQ31" s="60">
+        <v>190956.22870400001</v>
+      </c>
+      <c r="AR31" s="59">
+        <v>46.987261000000004</v>
+      </c>
+      <c r="AS31" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT31" s="60">
+        <v>47739.057176000002</v>
+      </c>
+      <c r="AU31" s="60">
+        <v>1390.4579759999979</v>
       </c>
       <c r="AV31" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW31" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW31" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
@@ -4027,19 +4026,19 @@
         <v>8</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
@@ -4115,43 +4114,43 @@
         <v>0</v>
       </c>
       <c r="AK32" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL32" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM32" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN32" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO32" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP32" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ32" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR32" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS32" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT32" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU32" s="66" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL32" s="62">
+        <v>5</v>
+      </c>
+      <c r="AM32" s="63">
+        <v>46844</v>
+      </c>
+      <c r="AN32" s="63">
+        <v>47208</v>
+      </c>
+      <c r="AO32" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP32" s="65">
+        <v>16390.409630426668</v>
+      </c>
+      <c r="AQ32" s="66">
+        <v>196684.91556512003</v>
+      </c>
+      <c r="AR32" s="65">
+        <v>48.396878830000006</v>
+      </c>
+      <c r="AS32" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT32" s="66">
+        <v>49171.22889128</v>
+      </c>
+      <c r="AU32" s="66">
+        <v>1432.1717152799974</v>
       </c>
       <c r="AV32" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW32" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW32" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
@@ -4161,7 +4160,7 @@
       <c r="D33" s="41"/>
       <c r="E33" s="41"/>
       <c r="F33" s="41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G33" s="41"/>
       <c r="H33" s="41"/>
@@ -4197,43 +4196,43 @@
       </c>
       <c r="AI33" s="45"/>
       <c r="AK33" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL33" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM33" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN33" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO33" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP33" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ33" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR33" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS33" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT33" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU33" s="60" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL33" s="58">
+        <v>6</v>
+      </c>
+      <c r="AM33" s="28">
+        <v>47209</v>
+      </c>
+      <c r="AN33" s="28">
+        <v>47573</v>
+      </c>
+      <c r="AO33" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP33" s="59">
+        <v>16882.121919339468</v>
+      </c>
+      <c r="AQ33" s="60">
+        <v>202585.46303207363</v>
+      </c>
+      <c r="AR33" s="59">
+        <v>49.84878519490001</v>
+      </c>
+      <c r="AS33" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT33" s="60">
+        <v>50646.365758018408</v>
+      </c>
+      <c r="AU33" s="60">
+        <v>1475.1368667384086</v>
       </c>
       <c r="AV33" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW33" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW33" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
@@ -4244,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>45</v>
@@ -4253,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
@@ -4311,7 +4310,7 @@
         <v>46538</v>
       </c>
       <c r="Z34" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA34" s="32" t="s">
         <v>48</v>
@@ -4335,43 +4334,43 @@
         <v>3004.1666666666665</v>
       </c>
       <c r="AK34" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL34" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM34" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN34" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO34" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP34" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ34" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR34" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS34" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT34" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU34" s="66" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL34" s="62">
+        <v>7</v>
+      </c>
+      <c r="AM34" s="63">
+        <v>47574</v>
+      </c>
+      <c r="AN34" s="63">
+        <v>47938</v>
+      </c>
+      <c r="AO34" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP34" s="65">
+        <v>17388.585576919653</v>
+      </c>
+      <c r="AQ34" s="66">
+        <v>208663.02692303585</v>
+      </c>
+      <c r="AR34" s="65">
+        <v>51.344248750747013</v>
+      </c>
+      <c r="AS34" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT34" s="66">
+        <v>52165.756730758963</v>
+      </c>
+      <c r="AU34" s="66">
+        <v>1519.3909727405553</v>
       </c>
       <c r="AV34" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW34" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW34" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
@@ -4382,7 +4381,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>45</v>
@@ -4391,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6">
@@ -4449,7 +4448,7 @@
         <v>46706</v>
       </c>
       <c r="Z35" s="52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AA35" s="32" t="s">
         <v>48</v>
@@ -4473,43 +4472,43 @@
         <v>4150</v>
       </c>
       <c r="AK35" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL35" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM35" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN35" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO35" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP35" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ35" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR35" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS35" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT35" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU35" s="60" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL35" s="58">
+        <v>8</v>
+      </c>
+      <c r="AM35" s="28">
+        <v>47939</v>
+      </c>
+      <c r="AN35" s="28">
+        <v>48304</v>
+      </c>
+      <c r="AO35" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP35" s="59">
+        <v>17910.243144227246</v>
+      </c>
+      <c r="AQ35" s="60">
+        <v>214922.91773072694</v>
+      </c>
+      <c r="AR35" s="59">
+        <v>52.884576213269426</v>
+      </c>
+      <c r="AS35" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT35" s="60">
+        <v>53730.729432681735</v>
+      </c>
+      <c r="AU35" s="60">
+        <v>1564.9727019227721</v>
       </c>
       <c r="AV35" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW35" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW35" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
@@ -4520,7 +4519,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>45</v>
@@ -4529,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6">
@@ -4587,7 +4586,7 @@
         <v>47299</v>
       </c>
       <c r="Z36" s="52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AA36" s="32" t="s">
         <v>48</v>
@@ -4611,43 +4610,43 @@
         <v>6387.5</v>
       </c>
       <c r="AK36" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL36" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM36" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN36" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO36" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP36" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ36" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR36" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS36" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT36" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU36" s="66" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL36" s="62">
+        <v>9</v>
+      </c>
+      <c r="AM36" s="63">
+        <v>48305</v>
+      </c>
+      <c r="AN36" s="63">
+        <v>48669</v>
+      </c>
+      <c r="AO36" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP36" s="65">
+        <v>18447.550438554063</v>
+      </c>
+      <c r="AQ36" s="66">
+        <v>221370.60526264875</v>
+      </c>
+      <c r="AR36" s="65">
+        <v>54.47111349966751</v>
+      </c>
+      <c r="AS36" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT36" s="66">
+        <v>55342.651315662188</v>
+      </c>
+      <c r="AU36" s="66">
+        <v>1611.9218829804522</v>
       </c>
       <c r="AV36" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW36" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW36" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
@@ -4658,7 +4657,7 @@
         <v>1286</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>45</v>
@@ -4667,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6">
@@ -4725,10 +4724,10 @@
         <v>47573</v>
       </c>
       <c r="Z37" s="52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AA37" s="32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AB37" s="19">
         <v>3</v>
@@ -4749,43 +4748,43 @@
         <v>10450</v>
       </c>
       <c r="AK37" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL37" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM37" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN37" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO37" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP37" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ37" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR37" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS37" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT37" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU37" s="60" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="AL37" s="58">
+        <v>10</v>
+      </c>
+      <c r="AM37" s="28">
+        <v>48670</v>
+      </c>
+      <c r="AN37" s="28">
+        <v>49034</v>
+      </c>
+      <c r="AO37" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP37" s="59">
+        <v>19000.976951710687</v>
+      </c>
+      <c r="AQ37" s="60">
+        <v>228011.72342052823</v>
+      </c>
+      <c r="AR37" s="59">
+        <v>56.105246904657534</v>
+      </c>
+      <c r="AS37" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT37" s="60">
+        <v>57002.930855132057</v>
+      </c>
+      <c r="AU37" s="60">
+        <v>1660.2795394698696</v>
       </c>
       <c r="AV37" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW37" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW37" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
@@ -4793,19 +4792,19 @@
         <v>9</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E38" s="6">
         <v>2</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6">
@@ -4863,10 +4862,10 @@
         <v>46996</v>
       </c>
       <c r="Z38" s="52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AA38" s="32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AB38" s="19">
         <v>3</v>
@@ -4887,43 +4886,43 @@
         <v>2477.0833333333335</v>
       </c>
       <c r="AK38" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL38" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM38" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN38" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO38" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP38" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ38" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR38" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS38" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT38" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU38" s="66" t="s">
-        <v>94</v>
+        <v>140</v>
+      </c>
+      <c r="AL38" s="62">
+        <v>11</v>
+      </c>
+      <c r="AM38" s="63">
+        <v>49035</v>
+      </c>
+      <c r="AN38" s="63">
+        <v>49399</v>
+      </c>
+      <c r="AO38" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP38" s="65">
+        <v>19571.006260262006</v>
+      </c>
+      <c r="AQ38" s="66">
+        <v>234852.07512314408</v>
+      </c>
+      <c r="AR38" s="65">
+        <v>57.788404311797265</v>
+      </c>
+      <c r="AS38" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT38" s="66">
+        <v>58713.01878078602</v>
+      </c>
+      <c r="AU38" s="66">
+        <v>1710.0879256539629</v>
       </c>
       <c r="AV38" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW38" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW38" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
@@ -4931,19 +4930,19 @@
         <v>9</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E39" s="6">
         <v>2</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6">
@@ -5027,43 +5026,43 @@
         <v>2679.1666666666665</v>
       </c>
       <c r="AK39" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL39" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM39" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN39" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO39" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP39" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ39" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR39" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS39" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT39" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU39" s="60" t="s">
-        <v>94</v>
+        <v>140</v>
+      </c>
+      <c r="AL39" s="58">
+        <v>12</v>
+      </c>
+      <c r="AM39" s="28">
+        <v>49400</v>
+      </c>
+      <c r="AN39" s="28">
+        <v>49765</v>
+      </c>
+      <c r="AO39" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP39" s="59">
+        <v>20158.136448069868</v>
+      </c>
+      <c r="AQ39" s="60">
+        <v>241897.63737683842</v>
+      </c>
+      <c r="AR39" s="59">
+        <v>59.522056441151186</v>
+      </c>
+      <c r="AS39" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT39" s="60">
+        <v>60474.409344209605</v>
+      </c>
+      <c r="AU39" s="60">
+        <v>1761.3905634235853</v>
       </c>
       <c r="AV39" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW39" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW39" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
@@ -5071,19 +5070,19 @@
         <v>9</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6">
@@ -5167,43 +5166,43 @@
         <v>1614.5833333333333</v>
       </c>
       <c r="AK40" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL40" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM40" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN40" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO40" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP40" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ40" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR40" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS40" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT40" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU40" s="66" t="s">
-        <v>94</v>
+        <v>140</v>
+      </c>
+      <c r="AL40" s="62">
+        <v>13</v>
+      </c>
+      <c r="AM40" s="63">
+        <v>49766</v>
+      </c>
+      <c r="AN40" s="63">
+        <v>50130</v>
+      </c>
+      <c r="AO40" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP40" s="65">
+        <v>20762.880541511964</v>
+      </c>
+      <c r="AQ40" s="66">
+        <v>249154.56649814357</v>
+      </c>
+      <c r="AR40" s="65">
+        <v>61.307718134385723</v>
+      </c>
+      <c r="AS40" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT40" s="66">
+        <v>62288.641624535892</v>
+      </c>
+      <c r="AU40" s="66">
+        <v>1814.2322803262869</v>
       </c>
       <c r="AV40" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW40" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW40" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
@@ -5213,7 +5212,7 @@
       <c r="D41" s="41"/>
       <c r="E41" s="41"/>
       <c r="F41" s="41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G41" s="41"/>
       <c r="H41" s="41"/>
@@ -5249,211 +5248,211 @@
       </c>
       <c r="AI41" s="45"/>
       <c r="AK41" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL41" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM41" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN41" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO41" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP41" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ41" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR41" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS41" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT41" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU41" s="60" t="s">
-        <v>94</v>
+        <v>140</v>
+      </c>
+      <c r="AL41" s="58">
+        <v>14</v>
+      </c>
+      <c r="AM41" s="28">
+        <v>50131</v>
+      </c>
+      <c r="AN41" s="28">
+        <v>50495</v>
+      </c>
+      <c r="AO41" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP41" s="59">
+        <v>21385.766957757322</v>
+      </c>
+      <c r="AQ41" s="60">
+        <v>256629.20349308787</v>
+      </c>
+      <c r="AR41" s="59">
+        <v>63.146949678417293</v>
+      </c>
+      <c r="AS41" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT41" s="60">
+        <v>64157.300873271961</v>
+      </c>
+      <c r="AU41" s="60">
+        <v>1868.6592487360685</v>
       </c>
       <c r="AV41" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW41" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW41" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AI42" s="7"/>
       <c r="AK42" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL42" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM42" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN42" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO42" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP42" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ42" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR42" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS42" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT42" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU42" s="66" t="s">
-        <v>94</v>
+        <v>140</v>
+      </c>
+      <c r="AL42" s="62">
+        <v>15</v>
+      </c>
+      <c r="AM42" s="63">
+        <v>50496</v>
+      </c>
+      <c r="AN42" s="63">
+        <v>50860</v>
+      </c>
+      <c r="AO42" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP42" s="65">
+        <v>22027.339966490046</v>
+      </c>
+      <c r="AQ42" s="66">
+        <v>264328.07959788054</v>
+      </c>
+      <c r="AR42" s="65">
+        <v>65.041358168769818</v>
+      </c>
+      <c r="AS42" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT42" s="66">
+        <v>66082.019899470135</v>
+      </c>
+      <c r="AU42" s="66">
+        <v>1924.7190261981741</v>
       </c>
       <c r="AV42" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW42" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW42" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AK43" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL43" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM43" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN43" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO43" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP43" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ43" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR43" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS43" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT43" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU43" s="60" t="s">
-        <v>94</v>
+        <v>146</v>
+      </c>
+      <c r="AL43" s="58">
+        <v>16</v>
+      </c>
+      <c r="AM43" s="28">
+        <v>50861</v>
+      </c>
+      <c r="AN43" s="28">
+        <v>51226</v>
+      </c>
+      <c r="AO43" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP43" s="59">
+        <v>22688.160165484747</v>
+      </c>
+      <c r="AQ43" s="60">
+        <v>272257.92198581697</v>
+      </c>
+      <c r="AR43" s="59">
+        <v>66.992598913832921</v>
+      </c>
+      <c r="AS43" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT43" s="60">
+        <v>68064.480496454242</v>
+      </c>
+      <c r="AU43" s="60">
+        <v>1982.4605969841068</v>
       </c>
       <c r="AV43" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW43" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW43" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AK44" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL44" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM44" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN44" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO44" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP44" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ44" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR44" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS44" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT44" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU44" s="66" t="s">
-        <v>94</v>
+        <v>146</v>
+      </c>
+      <c r="AL44" s="62">
+        <v>17</v>
+      </c>
+      <c r="AM44" s="63">
+        <v>51227</v>
+      </c>
+      <c r="AN44" s="63">
+        <v>51591</v>
+      </c>
+      <c r="AO44" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP44" s="65">
+        <v>23368.804970449291</v>
+      </c>
+      <c r="AQ44" s="66">
+        <v>280425.65964539151</v>
+      </c>
+      <c r="AR44" s="65">
+        <v>69.002376881247912</v>
+      </c>
+      <c r="AS44" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT44" s="66">
+        <v>70106.414911347878</v>
+      </c>
+      <c r="AU44" s="66">
+        <v>2041.9344148936361</v>
       </c>
       <c r="AV44" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW44" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW44" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N45" s="69" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O45" s="69" t="s">
         <v>14</v>
@@ -5462,10 +5461,10 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>31</v>
@@ -5480,51 +5479,51 @@
         <v>37</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AK45" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL45" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM45" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN45" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO45" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP45" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ45" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR45" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS45" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT45" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU45" s="60" t="s">
-        <v>94</v>
+        <v>146</v>
+      </c>
+      <c r="AL45" s="58">
+        <v>18</v>
+      </c>
+      <c r="AM45" s="28">
+        <v>51592</v>
+      </c>
+      <c r="AN45" s="28">
+        <v>51956</v>
+      </c>
+      <c r="AO45" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP45" s="59">
+        <v>24069.869119562773</v>
+      </c>
+      <c r="AQ45" s="60">
+        <v>288838.42943475326</v>
+      </c>
+      <c r="AR45" s="59">
+        <v>71.072448187685353</v>
+      </c>
+      <c r="AS45" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT45" s="60">
+        <v>72209.607358688314</v>
+      </c>
+      <c r="AU45" s="60">
+        <v>2103.192447340436</v>
       </c>
       <c r="AV45" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW45" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW45" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -5533,10 +5532,10 @@
         <v>101</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F46" s="6">
         <v>0</v>
@@ -5591,48 +5590,48 @@
       </c>
       <c r="W46" s="13"/>
       <c r="AK46" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL46" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM46" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN46" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO46" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP46" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ46" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR46" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS46" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT46" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU46" s="66" t="s">
-        <v>94</v>
+        <v>146</v>
+      </c>
+      <c r="AL46" s="62">
+        <v>19</v>
+      </c>
+      <c r="AM46" s="63">
+        <v>51957</v>
+      </c>
+      <c r="AN46" s="63">
+        <v>52321</v>
+      </c>
+      <c r="AO46" s="64">
+        <v>0.03</v>
+      </c>
+      <c r="AP46" s="65">
+        <v>24791.965193149652</v>
+      </c>
+      <c r="AQ46" s="66">
+        <v>297503.58231779584</v>
+      </c>
+      <c r="AR46" s="65">
+        <v>73.204621633315909</v>
+      </c>
+      <c r="AS46" s="66">
+        <v>0.6</v>
+      </c>
+      <c r="AT46" s="66">
+        <v>74375.895579448959</v>
+      </c>
+      <c r="AU46" s="66">
+        <v>2166.2882207606453</v>
       </c>
       <c r="AV46" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW46" s="65" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW46" s="65">
+        <v>5080</v>
       </c>
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
@@ -5641,10 +5640,10 @@
         <v>101</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
@@ -5699,48 +5698,48 @@
       </c>
       <c r="W47" s="13"/>
       <c r="AK47" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL47" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM47" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN47" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO47" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP47" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ47" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR47" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS47" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT47" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU47" s="60" t="s">
-        <v>94</v>
+        <v>146</v>
+      </c>
+      <c r="AL47" s="58">
+        <v>20</v>
+      </c>
+      <c r="AM47" s="28">
+        <v>52322</v>
+      </c>
+      <c r="AN47" s="28">
+        <v>52687</v>
+      </c>
+      <c r="AO47" s="34">
+        <v>0.03</v>
+      </c>
+      <c r="AP47" s="59">
+        <v>25535.72414894414</v>
+      </c>
+      <c r="AQ47" s="60">
+        <v>306428.6897873297</v>
+      </c>
+      <c r="AR47" s="59">
+        <v>75.400760282315375</v>
+      </c>
+      <c r="AS47" s="60">
+        <v>0.6</v>
+      </c>
+      <c r="AT47" s="60">
+        <v>76607.172446832425</v>
+      </c>
+      <c r="AU47" s="60">
+        <v>2231.2768673834653</v>
       </c>
       <c r="AV47" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="AW47" s="59" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="AW47" s="59">
+        <v>5080</v>
       </c>
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
@@ -5749,10 +5748,10 @@
         <v>101</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F48" s="6">
         <v>2</v>
@@ -5807,48 +5806,48 @@
       </c>
       <c r="W48" s="13"/>
       <c r="AK48" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL48" s="62" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM48" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN48" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO48" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP48" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ48" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR48" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS48" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AT48" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU48" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV48" s="67" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AW48" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
@@ -5857,10 +5856,10 @@
         <v>101</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
@@ -5915,48 +5914,48 @@
       </c>
       <c r="W49" s="13"/>
       <c r="AK49" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL49" s="58" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM49" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN49" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO49" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP49" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ49" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR49" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS49" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AT49" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU49" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV49" s="61" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AW49" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
@@ -5965,10 +5964,10 @@
         <v>101</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F50" s="6">
         <v>4</v>
@@ -6023,48 +6022,48 @@
       </c>
       <c r="W50" s="13"/>
       <c r="AK50" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL50" s="62" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM50" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN50" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO50" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP50" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ50" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR50" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS50" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AT50" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU50" s="66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV50" s="67" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AW50" s="65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
@@ -6073,10 +6072,10 @@
         <v>101</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
@@ -6131,48 +6130,48 @@
       </c>
       <c r="W51" s="13"/>
       <c r="AK51" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL51" s="58" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM51" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN51" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO51" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP51" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ51" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR51" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS51" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AT51" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU51" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV51" s="61" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AW51" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
@@ -6181,10 +6180,10 @@
         <v>101</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
@@ -6241,7 +6240,7 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
@@ -6250,10 +6249,10 @@
         <v>101</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
@@ -6308,7 +6307,7 @@
       </c>
       <c r="W53" s="13"/>
       <c r="AK53" s="72" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AL53" s="22"/>
       <c r="AM53" s="22"/>
@@ -6320,7 +6319,7 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>8</v>
@@ -6329,10 +6328,10 @@
         <v>101</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F54" s="6">
         <v>8</v>
@@ -6387,33 +6386,33 @@
       </c>
       <c r="W54" s="13"/>
       <c r="AK54" s="56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL54" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM54" s="56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN54" s="56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO54" s="56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AP54" s="56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AQ54" s="56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AR54" s="56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>8</v>
@@ -6422,10 +6421,10 @@
         <v>101</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F55" s="6">
         <v>9</v>
@@ -6480,33 +6479,33 @@
       </c>
       <c r="W55" s="13"/>
       <c r="AK55" s="26" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="AL55" s="58">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AM55" s="28">
-        <v>0</v>
+        <v>45383</v>
       </c>
       <c r="AN55" s="28">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP55" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ55" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR55" s="60" t="s">
-        <v>94</v>
+        <v>49034</v>
+      </c>
+      <c r="AO55" s="59">
+        <v>0</v>
+      </c>
+      <c r="AP55" s="60">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="59">
+        <v>19000.976951710687</v>
+      </c>
+      <c r="AR55" s="60">
+        <v>228011.72342052823</v>
       </c>
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
@@ -6515,10 +6514,10 @@
         <v>101</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F56" s="6">
         <v>10</v>
@@ -6573,33 +6572,33 @@
       </c>
       <c r="W56" s="13"/>
       <c r="AK56" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL56" s="58">
-        <v>0</v>
-      </c>
-      <c r="AM56" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN56" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO56" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP56" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ56" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR56" s="60" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="AM56" s="28">
+        <v>49035</v>
+      </c>
+      <c r="AN56" s="28">
+        <v>50860</v>
+      </c>
+      <c r="AO56" s="59">
+        <v>19571.006260262006</v>
+      </c>
+      <c r="AP56" s="60">
+        <v>234852.07512314408</v>
+      </c>
+      <c r="AQ56" s="59">
+        <v>22027.339966490046</v>
+      </c>
+      <c r="AR56" s="60">
+        <v>264328.07959788054</v>
       </c>
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="73" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B57" s="73" t="s">
         <v>8</v>
@@ -6608,10 +6607,10 @@
         <v>101</v>
       </c>
       <c r="D57" s="73" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F57" s="73">
         <v>11</v>
@@ -6669,30 +6668,30 @@
         <v>165</v>
       </c>
       <c r="AL57" s="58">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AN57" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO57" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP57" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ57" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="AR57" s="60" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="AM57" s="28">
+        <v>50861</v>
+      </c>
+      <c r="AN57" s="28">
+        <v>52687</v>
+      </c>
+      <c r="AO57" s="59">
+        <v>22688.160165484747</v>
+      </c>
+      <c r="AP57" s="60">
+        <v>272257.92198581697</v>
+      </c>
+      <c r="AQ57" s="59">
+        <v>25535.72414894414</v>
+      </c>
+      <c r="AR57" s="60">
+        <v>306428.6897873297</v>
       </c>
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="73" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B58" s="73" t="s">
         <v>8</v>
@@ -6701,10 +6700,10 @@
         <v>101</v>
       </c>
       <c r="D58" s="73" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F58" s="73">
         <v>12</v>
@@ -6765,27 +6764,27 @@
         <v>0</v>
       </c>
       <c r="AM58" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN58" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO58" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AP58" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AQ58" s="59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AR58" s="60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="73" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B59" s="73" t="s">
         <v>8</v>
@@ -6794,10 +6793,10 @@
         <v>101</v>
       </c>
       <c r="D59" s="73" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F59" s="73">
         <v>13</v>
@@ -6854,7 +6853,7 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="73" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B60" s="73" t="s">
         <v>8</v>
@@ -6863,10 +6862,10 @@
         <v>101</v>
       </c>
       <c r="D60" s="73" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E60" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F60" s="73">
         <v>14</v>
@@ -6923,7 +6922,7 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="73" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B61" s="73" t="s">
         <v>8</v>
@@ -6932,10 +6931,10 @@
         <v>101</v>
       </c>
       <c r="D61" s="73" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F61" s="73">
         <v>15</v>
@@ -6992,7 +6991,7 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B62" s="78" t="s">
         <v>8</v>
@@ -7001,10 +7000,10 @@
         <v>101</v>
       </c>
       <c r="D62" s="78" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E62" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F62" s="78">
         <v>16</v>
@@ -7061,7 +7060,7 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="78" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B63" s="78" t="s">
         <v>8</v>
@@ -7070,10 +7069,10 @@
         <v>101</v>
       </c>
       <c r="D63" s="78" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E63" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F63" s="78">
         <v>17</v>
@@ -7130,7 +7129,7 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="78" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B64" s="78" t="s">
         <v>8</v>
@@ -7139,10 +7138,10 @@
         <v>101</v>
       </c>
       <c r="D64" s="78" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E64" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F64" s="78">
         <v>18</v>
@@ -7199,7 +7198,7 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="78" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B65" s="78" t="s">
         <v>8</v>
@@ -7208,10 +7207,10 @@
         <v>101</v>
       </c>
       <c r="D65" s="78" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E65" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F65" s="78">
         <v>19</v>
@@ -7268,7 +7267,7 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="78" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B66" s="78" t="s">
         <v>8</v>
@@ -7277,10 +7276,10 @@
         <v>101</v>
       </c>
       <c r="D66" s="78" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E66" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F66" s="78">
         <v>20</v>
@@ -7337,76 +7336,76 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V67" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W67" s="48"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>8</v>
@@ -7418,7 +7417,7 @@
         <v>117</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F68" s="6">
         <v>1</v>
@@ -7475,7 +7474,7 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
@@ -7487,7 +7486,7 @@
         <v>117</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F69" s="6">
         <v>2</v>
@@ -7544,7 +7543,7 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
@@ -7556,7 +7555,7 @@
         <v>117</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F70" s="6">
         <v>3</v>
@@ -7613,7 +7612,7 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
@@ -7625,7 +7624,7 @@
         <v>117</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F71" s="6">
         <v>4</v>
@@ -7682,88 +7681,88 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V72" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W72" s="48"/>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E73" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F73" s="6">
         <v>1</v>
@@ -7820,19 +7819,19 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E74" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F74" s="6">
         <v>2</v>
@@ -7889,19 +7888,19 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E75" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F75" s="6">
         <v>3</v>
@@ -7958,19 +7957,19 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F76" s="6">
         <v>4</v>
@@ -8027,19 +8026,19 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E77" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F77" s="6">
         <v>5</v>
@@ -8096,19 +8095,19 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F78" s="6">
         <v>6</v>
@@ -8165,19 +8164,19 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F79" s="6">
         <v>7</v>
@@ -8234,19 +8233,19 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E80" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F80" s="6">
         <v>8</v>
@@ -8303,19 +8302,19 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C81" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E81" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F81" s="6">
         <v>9</v>
@@ -8372,19 +8371,19 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E82" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F82" s="6">
         <v>10</v>
@@ -8441,19 +8440,19 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E83" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F83" s="6">
         <v>11</v>
@@ -8510,19 +8509,19 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F84" s="6">
         <v>12</v>
@@ -8579,19 +8578,19 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E85" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F85" s="6">
         <v>13</v>
@@ -8648,19 +8647,19 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E86" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="F86" s="6">
         <v>14</v>
@@ -8717,88 +8716,88 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V87" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W87" s="48"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F88" s="6">
         <v>1</v>
@@ -8855,19 +8854,19 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F89" s="6">
         <v>2</v>
@@ -8924,19 +8923,19 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F90" s="6">
         <v>3</v>
@@ -8993,19 +8992,19 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F91" s="6">
         <v>4</v>
@@ -9062,19 +9061,19 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F92" s="6">
         <v>5</v>
@@ -9131,19 +9130,19 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F93" s="6">
         <v>6</v>
@@ -9200,19 +9199,19 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F94" s="6">
         <v>7</v>
@@ -9269,19 +9268,19 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F95" s="6">
         <v>8</v>
@@ -9338,19 +9337,19 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F96" s="6">
         <v>9</v>
@@ -9407,19 +9406,19 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F97" s="6">
         <v>10</v>
@@ -9476,19 +9475,19 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F98" s="6">
         <v>11</v>
@@ -9545,76 +9544,76 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V99" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W99" s="48"/>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>7</v>
@@ -9623,10 +9622,10 @@
         <v>1</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F100" s="6">
         <v>1</v>
@@ -9683,7 +9682,7 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
@@ -9692,10 +9691,10 @@
         <v>1</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F101" s="6">
         <v>2</v>
@@ -9752,7 +9751,7 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
@@ -9761,10 +9760,10 @@
         <v>1</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F102" s="6">
         <v>3</v>
@@ -9821,7 +9820,7 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
@@ -9830,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F103" s="6">
         <v>4</v>
@@ -9890,7 +9889,7 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
@@ -9899,10 +9898,10 @@
         <v>1</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F104" s="6">
         <v>5</v>
@@ -9959,7 +9958,7 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -9968,10 +9967,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F105" s="6">
         <v>6</v>
@@ -10028,7 +10027,7 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>7</v>
@@ -10037,10 +10036,10 @@
         <v>1</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F106" s="6">
         <v>7</v>
@@ -10097,7 +10096,7 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>7</v>
@@ -10106,10 +10105,10 @@
         <v>1</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F107" s="6">
         <v>8</v>
@@ -10166,7 +10165,7 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>7</v>
@@ -10175,10 +10174,10 @@
         <v>1</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F108" s="6">
         <v>9</v>
@@ -10235,7 +10234,7 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
@@ -10244,10 +10243,10 @@
         <v>1</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F109" s="6">
         <v>10</v>
@@ -10304,7 +10303,7 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B110" s="73" t="s">
         <v>7</v>
@@ -10313,10 +10312,10 @@
         <v>1</v>
       </c>
       <c r="D110" s="73" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E110" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F110" s="73">
         <v>11</v>
@@ -10373,7 +10372,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B111" s="73" t="s">
         <v>7</v>
@@ -10382,10 +10381,10 @@
         <v>1</v>
       </c>
       <c r="D111" s="73" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E111" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F111" s="73">
         <v>12</v>
@@ -10442,7 +10441,7 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B112" s="73" t="s">
         <v>7</v>
@@ -10451,10 +10450,10 @@
         <v>1</v>
       </c>
       <c r="D112" s="73" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E112" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F112" s="73">
         <v>13</v>
@@ -10511,7 +10510,7 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B113" s="73" t="s">
         <v>7</v>
@@ -10520,10 +10519,10 @@
         <v>1</v>
       </c>
       <c r="D113" s="73" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E113" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F113" s="73">
         <v>14</v>
@@ -10580,7 +10579,7 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B114" s="73" t="s">
         <v>7</v>
@@ -10589,10 +10588,10 @@
         <v>1</v>
       </c>
       <c r="D114" s="73" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E114" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F114" s="73">
         <v>15</v>
@@ -10649,88 +10648,88 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V115" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W115" s="48"/>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F116" s="6">
         <v>1</v>
@@ -10787,19 +10786,19 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F117" s="6">
         <v>2</v>
@@ -10856,19 +10855,19 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F118" s="6">
         <v>3</v>
@@ -10925,19 +10924,19 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F119" s="6">
         <v>4</v>
@@ -10994,19 +10993,19 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F120" s="6">
         <v>5</v>
@@ -11063,19 +11062,19 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B121" s="73" t="s">
         <v>7</v>
       </c>
       <c r="C121" s="73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D121" s="73" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E121" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F121" s="73">
         <v>6</v>
@@ -11132,19 +11131,19 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B122" s="73" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D122" s="73" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E122" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F122" s="73">
         <v>7</v>
@@ -11201,19 +11200,19 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B123" s="73" t="s">
         <v>7</v>
       </c>
       <c r="C123" s="73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D123" s="73" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E123" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F123" s="73">
         <v>8</v>
@@ -11270,19 +11269,19 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B124" s="73" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D124" s="73" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E124" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F124" s="73">
         <v>9</v>
@@ -11339,19 +11338,19 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B125" s="73" t="s">
         <v>7</v>
       </c>
       <c r="C125" s="73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D125" s="73" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E125" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F125" s="73">
         <v>10</v>
@@ -11408,88 +11407,88 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V126" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W126" s="48"/>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F127" s="6">
         <v>1</v>
@@ -11546,19 +11545,19 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F128" s="6">
         <v>2</v>
@@ -11615,19 +11614,19 @@
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F129" s="6">
         <v>3</v>
@@ -11684,19 +11683,19 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F130" s="6">
         <v>4</v>
@@ -11753,19 +11752,19 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F131" s="6">
         <v>5</v>
@@ -11822,19 +11821,19 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F132" s="6">
         <v>6</v>
@@ -11891,19 +11890,19 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F133" s="6">
         <v>7</v>
@@ -11960,19 +11959,19 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F134" s="6">
         <v>8</v>
@@ -12029,19 +12028,19 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F135" s="6">
         <v>9</v>
@@ -12098,19 +12097,19 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F136" s="6">
         <v>10</v>
@@ -12167,19 +12166,19 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F137" s="6">
         <v>11</v>
@@ -12236,76 +12235,76 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V138" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W138" s="48"/>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>9</v>
@@ -12314,10 +12313,10 @@
         <v>1</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F139" s="6">
         <v>1</v>
@@ -12374,7 +12373,7 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>9</v>
@@ -12383,10 +12382,10 @@
         <v>1</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F140" s="6">
         <v>2</v>
@@ -12443,7 +12442,7 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>9</v>
@@ -12452,10 +12451,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F141" s="6">
         <v>3</v>
@@ -12512,7 +12511,7 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>9</v>
@@ -12521,10 +12520,10 @@
         <v>1</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F142" s="6">
         <v>4</v>
@@ -12581,7 +12580,7 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>9</v>
@@ -12590,10 +12589,10 @@
         <v>1</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F143" s="6">
         <v>5</v>
@@ -12650,76 +12649,76 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W144" s="48"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>9</v>
@@ -12728,10 +12727,10 @@
         <v>2</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F145" s="6">
         <v>1</v>
@@ -12788,7 +12787,7 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>9</v>
@@ -12797,10 +12796,10 @@
         <v>2</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F146" s="6">
         <v>2</v>
@@ -12857,7 +12856,7 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>9</v>
@@ -12866,10 +12865,10 @@
         <v>2</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F147" s="6">
         <v>3</v>
@@ -12926,7 +12925,7 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>9</v>
@@ -12935,10 +12934,10 @@
         <v>2</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F148" s="6">
         <v>4</v>
@@ -12995,7 +12994,7 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>9</v>
@@ -13004,10 +13003,10 @@
         <v>2</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F149" s="6">
         <v>5</v>
@@ -13062,76 +13061,76 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V150" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W150" s="48"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>9</v>
@@ -13140,10 +13139,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F151" s="6">
         <v>1</v>
@@ -13200,7 +13199,7 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>9</v>
@@ -13209,10 +13208,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F152" s="6">
         <v>2</v>
@@ -13269,7 +13268,7 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>9</v>
@@ -13278,10 +13277,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F153" s="6">
         <v>3</v>
@@ -13338,7 +13337,7 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>9</v>
@@ -13347,10 +13346,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F154" s="6">
         <v>4</v>
@@ -13407,7 +13406,7 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>9</v>
@@ -13416,10 +13415,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F155" s="6">
         <v>5</v>
@@ -13476,76 +13475,76 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V156" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W156" s="48"/>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>9</v>
@@ -13554,10 +13553,10 @@
         <v>1286</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F157" s="6">
         <v>1</v>
@@ -13614,7 +13613,7 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>9</v>
@@ -13623,10 +13622,10 @@
         <v>1286</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F158" s="6">
         <v>2</v>
@@ -13683,7 +13682,7 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>9</v>
@@ -13692,10 +13691,10 @@
         <v>1286</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F159" s="6">
         <v>3</v>
@@ -13752,7 +13751,7 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>9</v>
@@ -13761,10 +13760,10 @@
         <v>1286</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F160" s="6">
         <v>4</v>
@@ -13821,7 +13820,7 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>9</v>
@@ -13830,10 +13829,10 @@
         <v>1286</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F161" s="6">
         <v>5</v>
@@ -13890,7 +13889,7 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>9</v>
@@ -13899,10 +13898,10 @@
         <v>1286</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F162" s="6">
         <v>6</v>
@@ -13959,7 +13958,7 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>9</v>
@@ -13968,10 +13967,10 @@
         <v>1286</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F163" s="6">
         <v>7</v>
@@ -14028,7 +14027,7 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>9</v>
@@ -14037,10 +14036,10 @@
         <v>1286</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F164" s="6">
         <v>8</v>
@@ -14097,7 +14096,7 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>9</v>
@@ -14106,10 +14105,10 @@
         <v>1286</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F165" s="6">
         <v>9</v>
@@ -14166,7 +14165,7 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>9</v>
@@ -14175,10 +14174,10 @@
         <v>1286</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F166" s="6">
         <v>10</v>
@@ -14235,7 +14234,7 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B167" s="73" t="s">
         <v>9</v>
@@ -14244,10 +14243,10 @@
         <v>1286</v>
       </c>
       <c r="D167" s="73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E167" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F167" s="73">
         <v>11</v>
@@ -14304,7 +14303,7 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" s="73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B168" s="73" t="s">
         <v>9</v>
@@ -14313,10 +14312,10 @@
         <v>1286</v>
       </c>
       <c r="D168" s="73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E168" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F168" s="73">
         <v>12</v>
@@ -14373,7 +14372,7 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B169" s="73" t="s">
         <v>9</v>
@@ -14382,10 +14381,10 @@
         <v>1286</v>
       </c>
       <c r="D169" s="73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E169" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F169" s="73">
         <v>13</v>
@@ -14442,7 +14441,7 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" s="73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B170" s="73" t="s">
         <v>9</v>
@@ -14451,10 +14450,10 @@
         <v>1286</v>
       </c>
       <c r="D170" s="73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E170" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F170" s="73">
         <v>14</v>
@@ -14511,7 +14510,7 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" s="73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B171" s="73" t="s">
         <v>9</v>
@@ -14520,10 +14519,10 @@
         <v>1286</v>
       </c>
       <c r="D171" s="73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E171" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F171" s="73">
         <v>15</v>
@@ -14580,7 +14579,7 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B172" s="78" t="s">
         <v>9</v>
@@ -14589,10 +14588,10 @@
         <v>1286</v>
       </c>
       <c r="D172" s="78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E172" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F172" s="78">
         <v>16</v>
@@ -14649,7 +14648,7 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" s="78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B173" s="78" t="s">
         <v>9</v>
@@ -14658,10 +14657,10 @@
         <v>1286</v>
       </c>
       <c r="D173" s="78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E173" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F173" s="78">
         <v>17</v>
@@ -14718,7 +14717,7 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" s="78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B174" s="78" t="s">
         <v>9</v>
@@ -14727,10 +14726,10 @@
         <v>1286</v>
       </c>
       <c r="D174" s="78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E174" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F174" s="78">
         <v>18</v>
@@ -14787,7 +14786,7 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" s="78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B175" s="78" t="s">
         <v>9</v>
@@ -14796,10 +14795,10 @@
         <v>1286</v>
       </c>
       <c r="D175" s="78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E175" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F175" s="78">
         <v>19</v>
@@ -14856,7 +14855,7 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B176" s="78" t="s">
         <v>9</v>
@@ -14865,10 +14864,10 @@
         <v>1286</v>
       </c>
       <c r="D176" s="78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E176" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F176" s="78">
         <v>20</v>
@@ -14925,7 +14924,7 @@
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B177" s="86" t="s">
         <v>9</v>
@@ -14934,10 +14933,10 @@
         <v>1286</v>
       </c>
       <c r="D177" s="86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E177" s="86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F177" s="86">
         <v>21</v>
@@ -14994,7 +14993,7 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B178" s="86" t="s">
         <v>9</v>
@@ -15003,10 +15002,10 @@
         <v>1286</v>
       </c>
       <c r="D178" s="86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E178" s="86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F178" s="86">
         <v>22</v>
@@ -15063,7 +15062,7 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B179" s="86" t="s">
         <v>9</v>
@@ -15072,10 +15071,10 @@
         <v>1286</v>
       </c>
       <c r="D179" s="86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E179" s="86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F179" s="86">
         <v>23</v>
@@ -15132,7 +15131,7 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B180" s="86" t="s">
         <v>9</v>
@@ -15141,10 +15140,10 @@
         <v>1286</v>
       </c>
       <c r="D180" s="86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E180" s="86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F180" s="86">
         <v>24</v>
@@ -15201,7 +15200,7 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B181" s="86" t="s">
         <v>9</v>
@@ -15210,10 +15209,10 @@
         <v>1286</v>
       </c>
       <c r="D181" s="86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E181" s="86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F181" s="86">
         <v>25</v>
@@ -15270,88 +15269,88 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V182" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W182" s="48"/>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F183" s="6">
         <v>1</v>
@@ -15408,19 +15407,19 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F184" s="6">
         <v>2</v>
@@ -15477,19 +15476,19 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F185" s="6">
         <v>3</v>
@@ -15546,19 +15545,19 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F186" s="6">
         <v>4</v>
@@ -15615,19 +15614,19 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F187" s="6">
         <v>5</v>
@@ -15684,19 +15683,19 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F188" s="6">
         <v>6</v>
@@ -15753,19 +15752,19 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="78" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B189" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C189" s="78" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D189" s="78" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E189" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F189" s="78">
         <v>7</v>
@@ -15822,19 +15821,19 @@
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" s="78" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B190" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C190" s="78" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D190" s="78" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E190" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F190" s="78">
         <v>8</v>
@@ -15891,88 +15890,88 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V191" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W191" s="48"/>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F192" s="6">
         <v>1</v>
@@ -16029,88 +16028,88 @@
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V193" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W193" s="48"/>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F194" s="6">
         <v>1</v>
@@ -16167,76 +16166,76 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V195" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W195" s="48"/>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>6</v>
@@ -16248,7 +16247,7 @@
         <v>44</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F196" s="6">
         <v>1</v>
@@ -16305,76 +16304,76 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V197" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W197" s="48"/>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>6</v>
@@ -16386,7 +16385,7 @@
         <v>51</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F198" s="6">
         <v>1</v>
@@ -16443,7 +16442,7 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>6</v>
@@ -16455,7 +16454,7 @@
         <v>51</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F199" s="6">
         <v>1</v>
@@ -16512,76 +16511,76 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V200" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W200" s="48"/>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>6</v>
@@ -16590,10 +16589,10 @@
         <v>106</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F201" s="6">
         <v>1</v>
@@ -16650,7 +16649,7 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>6</v>
@@ -16659,10 +16658,10 @@
         <v>106</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F202" s="6">
         <v>2</v>
@@ -16719,7 +16718,7 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>6</v>
@@ -16728,10 +16727,10 @@
         <v>106</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F203" s="6">
         <v>3</v>
@@ -16788,7 +16787,7 @@
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>6</v>
@@ -16797,10 +16796,10 @@
         <v>106</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F204" s="6">
         <v>4</v>
@@ -16857,7 +16856,7 @@
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>6</v>
@@ -16866,10 +16865,10 @@
         <v>106</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F205" s="6">
         <v>5</v>
@@ -16926,7 +16925,7 @@
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>6</v>
@@ -16935,10 +16934,10 @@
         <v>106</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F206" s="6">
         <v>6</v>
@@ -16995,7 +16994,7 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B207" s="73" t="s">
         <v>6</v>
@@ -17004,10 +17003,10 @@
         <v>106</v>
       </c>
       <c r="D207" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E207" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F207" s="73">
         <v>7</v>
@@ -17064,7 +17063,7 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B208" s="73" t="s">
         <v>6</v>
@@ -17073,10 +17072,10 @@
         <v>106</v>
       </c>
       <c r="D208" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E208" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F208" s="73">
         <v>8</v>
@@ -17133,7 +17132,7 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B209" s="73" t="s">
         <v>6</v>
@@ -17142,10 +17141,10 @@
         <v>106</v>
       </c>
       <c r="D209" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E209" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F209" s="73">
         <v>9</v>
@@ -17202,7 +17201,7 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B210" s="73" t="s">
         <v>6</v>
@@ -17211,10 +17210,10 @@
         <v>106</v>
       </c>
       <c r="D210" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E210" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F210" s="73">
         <v>10</v>
@@ -17271,7 +17270,7 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B211" s="73" t="s">
         <v>6</v>
@@ -17280,10 +17279,10 @@
         <v>106</v>
       </c>
       <c r="D211" s="73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E211" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F211" s="73">
         <v>11</v>
@@ -17340,7 +17339,7 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" s="78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B212" s="78" t="s">
         <v>6</v>
@@ -17349,10 +17348,10 @@
         <v>106</v>
       </c>
       <c r="D212" s="78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E212" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F212" s="78">
         <v>12</v>
@@ -17409,7 +17408,7 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" s="78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B213" s="78" t="s">
         <v>6</v>
@@ -17418,10 +17417,10 @@
         <v>106</v>
       </c>
       <c r="D213" s="78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E213" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F213" s="78">
         <v>13</v>
@@ -17478,7 +17477,7 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" s="78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B214" s="78" t="s">
         <v>6</v>
@@ -17487,10 +17486,10 @@
         <v>106</v>
       </c>
       <c r="D214" s="78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E214" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F214" s="78">
         <v>14</v>
@@ -17547,7 +17546,7 @@
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" s="78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B215" s="78" t="s">
         <v>6</v>
@@ -17556,10 +17555,10 @@
         <v>106</v>
       </c>
       <c r="D215" s="78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E215" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F215" s="78">
         <v>15</v>
@@ -17616,7 +17615,7 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" s="78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B216" s="78" t="s">
         <v>6</v>
@@ -17625,10 +17624,10 @@
         <v>106</v>
       </c>
       <c r="D216" s="78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E216" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F216" s="78">
         <v>16</v>
@@ -17685,76 +17684,76 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V217" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W217" s="48"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>6</v>
@@ -17763,10 +17762,10 @@
         <v>108</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F218" s="6">
         <v>1</v>
@@ -17823,7 +17822,7 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>6</v>
@@ -17832,10 +17831,10 @@
         <v>108</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F219" s="6">
         <v>2</v>
@@ -17892,7 +17891,7 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>6</v>
@@ -17901,10 +17900,10 @@
         <v>108</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F220" s="6">
         <v>3</v>
@@ -17961,7 +17960,7 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>6</v>
@@ -17970,10 +17969,10 @@
         <v>108</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F221" s="6">
         <v>4</v>
@@ -18030,7 +18029,7 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>6</v>
@@ -18039,10 +18038,10 @@
         <v>108</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F222" s="6">
         <v>5</v>
@@ -18099,7 +18098,7 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>6</v>
@@ -18108,10 +18107,10 @@
         <v>108</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F223" s="6">
         <v>6</v>
@@ -18168,76 +18167,76 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V224" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W224" s="48"/>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>6</v>
@@ -18246,10 +18245,10 @@
         <v>201</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F225" s="6">
         <v>1</v>
@@ -18306,76 +18305,76 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V226" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W226" s="48"/>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>6</v>
@@ -18384,10 +18383,10 @@
         <v>202</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F227" s="6">
         <v>1</v>
@@ -18444,7 +18443,7 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>6</v>
@@ -18453,10 +18452,10 @@
         <v>202</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F228" s="6">
         <v>1</v>
@@ -18513,7 +18512,7 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="73" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B229" s="73" t="s">
         <v>6</v>
@@ -18522,10 +18521,10 @@
         <v>202</v>
       </c>
       <c r="D229" s="73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E229" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F229" s="73">
         <v>1</v>
@@ -18582,76 +18581,76 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V230" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W230" s="48"/>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>6</v>
@@ -18660,10 +18659,10 @@
         <v>203</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F231" s="6">
         <v>1</v>
@@ -18720,7 +18719,7 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>6</v>
@@ -18729,10 +18728,10 @@
         <v>203</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F232" s="6">
         <v>2</v>
@@ -18789,7 +18788,7 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B233" s="73" t="s">
         <v>6</v>
@@ -18798,10 +18797,10 @@
         <v>203</v>
       </c>
       <c r="D233" s="73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E233" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F233" s="73">
         <v>3</v>
@@ -18858,7 +18857,7 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="78" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B234" s="78" t="s">
         <v>6</v>
@@ -18867,10 +18866,10 @@
         <v>203</v>
       </c>
       <c r="D234" s="78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E234" s="78" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F234" s="78">
         <v>4</v>
@@ -18927,76 +18926,76 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V235" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W235" s="48"/>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>6</v>
@@ -19005,10 +19004,10 @@
         <v>204</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F236" s="6">
         <v>1</v>
@@ -19065,76 +19064,76 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V237" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W237" s="48"/>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>6</v>
@@ -19143,10 +19142,10 @@
         <v>205</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F238" s="6">
         <v>1</v>
@@ -19203,7 +19202,7 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>6</v>
@@ -19212,10 +19211,10 @@
         <v>205</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F239" s="6">
         <v>2</v>
@@ -19272,7 +19271,7 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>6</v>
@@ -19281,10 +19280,10 @@
         <v>205</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F240" s="6">
         <v>3</v>
@@ -19341,76 +19340,76 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V241" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W241" s="48"/>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>6</v>
@@ -19419,10 +19418,10 @@
         <v>209</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F242" s="6">
         <v>1</v>
@@ -19479,7 +19478,7 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>6</v>
@@ -19488,10 +19487,10 @@
         <v>209</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F243" s="6">
         <v>2</v>
@@ -19548,7 +19547,7 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>6</v>
@@ -19557,10 +19556,10 @@
         <v>209</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F244" s="6">
         <v>3</v>
@@ -19617,76 +19616,76 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V245" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W245" s="48"/>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>6</v>
@@ -19695,10 +19694,10 @@
         <v>206</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F246" s="6">
         <v>1</v>
@@ -19755,7 +19754,7 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>6</v>
@@ -19764,10 +19763,10 @@
         <v>206</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F247" s="6">
         <v>1</v>
@@ -19826,7 +19825,7 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>6</v>
@@ -19835,10 +19834,10 @@
         <v>206</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F248" s="6">
         <v>1</v>
@@ -19897,7 +19896,7 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>6</v>
@@ -19906,10 +19905,10 @@
         <v>206</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F249" s="6">
         <v>1</v>
@@ -19968,7 +19967,7 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>6</v>
@@ -19977,10 +19976,10 @@
         <v>206</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F250" s="6">
         <v>1</v>
@@ -20039,7 +20038,7 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>6</v>
@@ -20048,10 +20047,10 @@
         <v>206</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F251" s="6">
         <v>1</v>
@@ -20110,76 +20109,76 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V252" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W252" s="48"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>6</v>
@@ -20188,10 +20187,10 @@
         <v>207</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F253" s="6">
         <v>1</v>
@@ -20248,7 +20247,7 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>6</v>
@@ -20257,10 +20256,10 @@
         <v>207</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F254" s="6">
         <v>2</v>
@@ -20317,7 +20316,7 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>6</v>
@@ -20326,10 +20325,10 @@
         <v>207</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F255" s="6">
         <v>3</v>
@@ -20386,7 +20385,7 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>6</v>
@@ -20395,10 +20394,10 @@
         <v>207</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F256" s="6">
         <v>4</v>
@@ -20455,7 +20454,7 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="73" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B257" s="73" t="s">
         <v>6</v>
@@ -20464,10 +20463,10 @@
         <v>207</v>
       </c>
       <c r="D257" s="73" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E257" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F257" s="73">
         <v>5</v>
@@ -20524,7 +20523,7 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="73" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B258" s="73" t="s">
         <v>6</v>
@@ -20533,10 +20532,10 @@
         <v>207</v>
       </c>
       <c r="D258" s="73" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E258" s="73" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F258" s="73">
         <v>6</v>
@@ -20593,76 +20592,76 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V259" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W259" s="48"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>6</v>
@@ -20671,10 +20670,10 @@
         <v>208</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="F260" s="6">
         <v>1</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF15A9EE-BBF6-42E7-B10C-5A9FDC9E9109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B7B0ED2-E838-467F-9B77-D5FDDB1D1043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2505" windowWidth="52710" windowHeight="29895" xr2:uid="{D9B1E835-4EA7-45B9-95AD-63C9A334A55D}"/>
+    <workbookView xWindow="4890" yWindow="2505" windowWidth="52710" windowHeight="29895" xr2:uid="{3EBA7C37-EF48-42B6-AFC8-6B42723A749E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="194">
   <si>
     <t>Building</t>
   </si>
@@ -443,9 +443,6 @@
     <t>Three 5-Yr w 2% Ann Inc</t>
   </si>
   <si>
-    <t>O-1</t>
-  </si>
-  <si>
     <t>Sana Yoga Studio, LLC</t>
   </si>
   <si>
@@ -464,7 +461,7 @@
     <t>Option_1</t>
   </si>
   <si>
-    <t>A-1</t>
+    <t>202_Apt</t>
   </si>
   <si>
     <t>VACANT_6</t>
@@ -473,7 +470,7 @@
     <t>Apartment</t>
   </si>
   <si>
-    <t>A-2</t>
+    <t>203_Apt</t>
   </si>
   <si>
     <t>Alan DiEsso</t>
@@ -563,28 +560,28 @@
     <t>15 South_Easement_Easement</t>
   </si>
   <si>
-    <t>1280 Springfield_1_George's Appliance, LLC</t>
+    <t>1280 Springfield_101_George's Appliance, LLC</t>
   </si>
   <si>
-    <t>1280 Springfield_2_Juice House</t>
+    <t>1280 Springfield_102_Juice House</t>
   </si>
   <si>
-    <t>1280 Springfield_3_Uppleside Down Wellness, LLC D/B/A Air</t>
+    <t>1280 Springfield_103_Uppleside Down Wellness, LLC D/B/A Air</t>
   </si>
   <si>
-    <t>1280 Springfield_1286_SLK Enterprises, LLC D/B/A AFC Urgent Care</t>
+    <t>1280 Springfield_104_SLK Enterprises, LLC D/B/A AFC Urgent Care</t>
   </si>
   <si>
     <t>Option_3</t>
   </si>
   <si>
-    <t>1280 Springfield_O-1_Sana Yoga Studio, LLC</t>
+    <t>1280 Springfield_201_Sana Yoga Studio, LLC</t>
   </si>
   <si>
-    <t>1280 Springfield_A-1_VACANT_6</t>
+    <t>1280 Springfield_202_Apt_VACANT_6</t>
   </si>
   <si>
-    <t>1280 Springfield_A-2_Alan DiEsso</t>
+    <t>1280 Springfield_203_Apt_Alan DiEsso</t>
   </si>
   <si>
     <t>114 Central_102_Nabig Sakr</t>
@@ -1361,7 +1358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B2C5D1-C167-4464-8B30-AB7D63A1BB8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BF2352-2549-4FEC-ACAC-8E7C8FEE077F}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4240,7 +4237,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>125</v>
@@ -4378,7 +4375,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="6">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>128</v>
@@ -4516,7 +4513,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="6">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>130</v>
@@ -4654,7 +4651,7 @@
         <v>9</v>
       </c>
       <c r="B37" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>131</v>
@@ -4791,20 +4788,20 @@
       <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="6">
+        <v>201</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="E38" s="6">
         <v>2</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6">
@@ -4862,10 +4859,10 @@
         <v>46996</v>
       </c>
       <c r="Z38" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA38" s="32" t="s">
         <v>138</v>
-      </c>
-      <c r="AA38" s="32" t="s">
-        <v>139</v>
       </c>
       <c r="AB38" s="19">
         <v>3</v>
@@ -4886,7 +4883,7 @@
         <v>2477.0833333333335</v>
       </c>
       <c r="AK38" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AL38" s="62">
         <v>11</v>
@@ -4930,19 +4927,19 @@
         <v>9</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="E39" s="6">
         <v>2</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6">
@@ -5026,7 +5023,7 @@
         <v>2679.1666666666665</v>
       </c>
       <c r="AK39" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AL39" s="58">
         <v>12</v>
@@ -5070,19 +5067,19 @@
         <v>9</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6">
@@ -5166,7 +5163,7 @@
         <v>1614.5833333333333</v>
       </c>
       <c r="AK40" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AL40" s="62">
         <v>13</v>
@@ -5248,7 +5245,7 @@
       </c>
       <c r="AI41" s="45"/>
       <c r="AK41" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AL41" s="58">
         <v>14</v>
@@ -5290,7 +5287,7 @@
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AI42" s="7"/>
       <c r="AK42" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AL42" s="62">
         <v>15</v>
@@ -5331,7 +5328,7 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AK43" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AL43" s="58">
         <v>16</v>
@@ -5372,7 +5369,7 @@
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AK44" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AL44" s="62">
         <v>17</v>
@@ -5413,7 +5410,7 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
@@ -5428,7 +5425,7 @@
         <v>105</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>107</v>
@@ -5440,10 +5437,10 @@
         <v>109</v>
       </c>
       <c r="J45" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
@@ -5452,7 +5449,7 @@
         <v>58</v>
       </c>
       <c r="N45" s="69" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O45" s="69" t="s">
         <v>14</v>
@@ -5461,10 +5458,10 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R45" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>31</v>
@@ -5479,10 +5476,10 @@
         <v>37</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AK45" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AL45" s="58">
         <v>18</v>
@@ -5590,7 +5587,7 @@
       </c>
       <c r="W46" s="13"/>
       <c r="AK46" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AL46" s="62">
         <v>19</v>
@@ -5698,7 +5695,7 @@
       </c>
       <c r="W47" s="13"/>
       <c r="AK47" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AL47" s="58">
         <v>20</v>
@@ -6307,7 +6304,7 @@
       </c>
       <c r="W53" s="13"/>
       <c r="AK53" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AL53" s="22"/>
       <c r="AM53" s="22"/>
@@ -6386,28 +6383,28 @@
       </c>
       <c r="W54" s="13"/>
       <c r="AK54" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="AL54" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="AL54" s="56" t="s">
+      <c r="AM54" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="AM54" s="56" t="s">
+      <c r="AN54" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="AN54" s="56" t="s">
+      <c r="AO54" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="AO54" s="56" t="s">
+      <c r="AP54" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="AP54" s="56" t="s">
+      <c r="AQ54" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="AQ54" s="56" t="s">
+      <c r="AR54" s="56" t="s">
         <v>162</v>
-      </c>
-      <c r="AR54" s="56" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
@@ -6572,7 +6569,7 @@
       </c>
       <c r="W56" s="13"/>
       <c r="AK56" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL56" s="58">
         <v>5</v>
@@ -6610,7 +6607,7 @@
         <v>54</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F57" s="73">
         <v>11</v>
@@ -6665,7 +6662,7 @@
       </c>
       <c r="W57" s="76"/>
       <c r="AK57" s="26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL57" s="58">
         <v>5</v>
@@ -6703,7 +6700,7 @@
         <v>54</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F58" s="73">
         <v>12</v>
@@ -6758,7 +6755,7 @@
       </c>
       <c r="W58" s="76"/>
       <c r="AK58" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL58" s="58">
         <v>0</v>
@@ -6796,7 +6793,7 @@
         <v>54</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F59" s="73">
         <v>13</v>
@@ -6865,7 +6862,7 @@
         <v>54</v>
       </c>
       <c r="E60" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F60" s="73">
         <v>14</v>
@@ -6934,7 +6931,7 @@
         <v>54</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F61" s="73">
         <v>15</v>
@@ -7003,7 +7000,7 @@
         <v>54</v>
       </c>
       <c r="E62" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F62" s="78">
         <v>16</v>
@@ -7072,7 +7069,7 @@
         <v>54</v>
       </c>
       <c r="E63" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F63" s="78">
         <v>17</v>
@@ -7141,7 +7138,7 @@
         <v>54</v>
       </c>
       <c r="E64" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F64" s="78">
         <v>18</v>
@@ -7210,7 +7207,7 @@
         <v>54</v>
       </c>
       <c r="E65" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F65" s="78">
         <v>19</v>
@@ -7279,7 +7276,7 @@
         <v>54</v>
       </c>
       <c r="E66" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F66" s="78">
         <v>20</v>
@@ -7336,76 +7333,76 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V67" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W67" s="48"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>8</v>
@@ -7474,7 +7471,7 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
@@ -7543,7 +7540,7 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
@@ -7612,7 +7609,7 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
@@ -7681,76 +7678,76 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V72" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W72" s="48"/>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>8</v>
@@ -7819,7 +7816,7 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>8</v>
@@ -7888,7 +7885,7 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>8</v>
@@ -7957,7 +7954,7 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
@@ -8026,7 +8023,7 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>8</v>
@@ -8095,7 +8092,7 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>8</v>
@@ -8164,7 +8161,7 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>8</v>
@@ -8233,7 +8230,7 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>8</v>
@@ -8302,7 +8299,7 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>8</v>
@@ -8371,7 +8368,7 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>8</v>
@@ -8440,7 +8437,7 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>8</v>
@@ -8509,7 +8506,7 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>8</v>
@@ -8578,7 +8575,7 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>8</v>
@@ -8647,7 +8644,7 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>8</v>
@@ -8716,76 +8713,76 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V87" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W87" s="48"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>8</v>
@@ -8854,7 +8851,7 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>8</v>
@@ -8923,7 +8920,7 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>8</v>
@@ -8992,7 +8989,7 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>8</v>
@@ -9061,7 +9058,7 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>8</v>
@@ -9130,7 +9127,7 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>8</v>
@@ -9199,7 +9196,7 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>8</v>
@@ -9268,7 +9265,7 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>8</v>
@@ -9337,7 +9334,7 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>8</v>
@@ -9406,7 +9403,7 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>8</v>
@@ -9475,7 +9472,7 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>8</v>
@@ -9544,76 +9541,76 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V99" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W99" s="48"/>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>7</v>
@@ -9682,7 +9679,7 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
@@ -9751,7 +9748,7 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
@@ -9820,7 +9817,7 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
@@ -9889,7 +9886,7 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
@@ -9958,7 +9955,7 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -10027,7 +10024,7 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>7</v>
@@ -10096,7 +10093,7 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>7</v>
@@ -10165,7 +10162,7 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>7</v>
@@ -10234,7 +10231,7 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
@@ -10303,7 +10300,7 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B110" s="73" t="s">
         <v>7</v>
@@ -10315,7 +10312,7 @@
         <v>97</v>
       </c>
       <c r="E110" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F110" s="73">
         <v>11</v>
@@ -10372,7 +10369,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B111" s="73" t="s">
         <v>7</v>
@@ -10384,7 +10381,7 @@
         <v>97</v>
       </c>
       <c r="E111" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F111" s="73">
         <v>12</v>
@@ -10441,7 +10438,7 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B112" s="73" t="s">
         <v>7</v>
@@ -10453,7 +10450,7 @@
         <v>97</v>
       </c>
       <c r="E112" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F112" s="73">
         <v>13</v>
@@ -10510,7 +10507,7 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B113" s="73" t="s">
         <v>7</v>
@@ -10522,7 +10519,7 @@
         <v>97</v>
       </c>
       <c r="E113" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F113" s="73">
         <v>14</v>
@@ -10579,7 +10576,7 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B114" s="73" t="s">
         <v>7</v>
@@ -10591,7 +10588,7 @@
         <v>97</v>
       </c>
       <c r="E114" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F114" s="73">
         <v>15</v>
@@ -10648,76 +10645,76 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V115" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W115" s="48"/>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>7</v>
@@ -10786,7 +10783,7 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>7</v>
@@ -10855,7 +10852,7 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>7</v>
@@ -10924,7 +10921,7 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>7</v>
@@ -10993,7 +10990,7 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>7</v>
@@ -11062,7 +11059,7 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B121" s="73" t="s">
         <v>7</v>
@@ -11074,7 +11071,7 @@
         <v>103</v>
       </c>
       <c r="E121" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F121" s="73">
         <v>6</v>
@@ -11131,7 +11128,7 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B122" s="73" t="s">
         <v>7</v>
@@ -11143,7 +11140,7 @@
         <v>103</v>
       </c>
       <c r="E122" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F122" s="73">
         <v>7</v>
@@ -11200,7 +11197,7 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B123" s="73" t="s">
         <v>7</v>
@@ -11212,7 +11209,7 @@
         <v>103</v>
       </c>
       <c r="E123" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F123" s="73">
         <v>8</v>
@@ -11269,7 +11266,7 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B124" s="73" t="s">
         <v>7</v>
@@ -11281,7 +11278,7 @@
         <v>103</v>
       </c>
       <c r="E124" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F124" s="73">
         <v>9</v>
@@ -11338,7 +11335,7 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B125" s="73" t="s">
         <v>7</v>
@@ -11350,7 +11347,7 @@
         <v>103</v>
       </c>
       <c r="E125" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F125" s="73">
         <v>10</v>
@@ -11407,76 +11404,76 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V126" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W126" s="48"/>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>7</v>
@@ -11545,7 +11542,7 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
@@ -11614,7 +11611,7 @@
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
@@ -11683,7 +11680,7 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
@@ -11752,7 +11749,7 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
@@ -11821,7 +11818,7 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
@@ -11890,7 +11887,7 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
@@ -11959,7 +11956,7 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>7</v>
@@ -12028,7 +12025,7 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
@@ -12097,7 +12094,7 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>7</v>
@@ -12166,7 +12163,7 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
@@ -12235,82 +12232,82 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V138" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W138" s="48"/>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C139" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>125</v>
@@ -12373,13 +12370,13 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>125</v>
@@ -12442,13 +12439,13 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C141" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>125</v>
@@ -12511,13 +12508,13 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C142" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>125</v>
@@ -12580,13 +12577,13 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C143" s="6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>125</v>
@@ -12649,82 +12646,82 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W144" s="48"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C145" s="6">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>128</v>
@@ -12787,13 +12784,13 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C146" s="6">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>128</v>
@@ -12856,13 +12853,13 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C147" s="6">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>128</v>
@@ -12925,13 +12922,13 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C148" s="6">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>128</v>
@@ -12994,13 +12991,13 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C149" s="6">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>128</v>
@@ -13061,82 +13058,82 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V150" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W150" s="48"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C151" s="6">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>130</v>
@@ -13199,13 +13196,13 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C152" s="6">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>130</v>
@@ -13268,13 +13265,13 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C153" s="6">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>130</v>
@@ -13337,13 +13334,13 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C154" s="6">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>130</v>
@@ -13406,13 +13403,13 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C155" s="6">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>130</v>
@@ -13475,82 +13472,82 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V156" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W156" s="48"/>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C157" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>131</v>
@@ -13613,13 +13610,13 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C158" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>131</v>
@@ -13682,13 +13679,13 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>131</v>
@@ -13751,13 +13748,13 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C160" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>131</v>
@@ -13820,13 +13817,13 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C161" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>131</v>
@@ -13889,13 +13886,13 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C162" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>131</v>
@@ -13958,13 +13955,13 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C163" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>131</v>
@@ -14027,13 +14024,13 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C164" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>131</v>
@@ -14096,13 +14093,13 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>131</v>
@@ -14165,13 +14162,13 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="6">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>131</v>
@@ -14234,19 +14231,19 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B167" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C167" s="73">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D167" s="73" t="s">
         <v>131</v>
       </c>
       <c r="E167" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F167" s="73">
         <v>11</v>
@@ -14303,19 +14300,19 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B168" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C168" s="73">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D168" s="73" t="s">
         <v>131</v>
       </c>
       <c r="E168" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F168" s="73">
         <v>12</v>
@@ -14372,19 +14369,19 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B169" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C169" s="73">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D169" s="73" t="s">
         <v>131</v>
       </c>
       <c r="E169" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F169" s="73">
         <v>13</v>
@@ -14441,19 +14438,19 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B170" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C170" s="73">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D170" s="73" t="s">
         <v>131</v>
       </c>
       <c r="E170" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F170" s="73">
         <v>14</v>
@@ -14510,19 +14507,19 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B171" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C171" s="73">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D171" s="73" t="s">
         <v>131</v>
       </c>
       <c r="E171" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F171" s="73">
         <v>15</v>
@@ -14579,19 +14576,19 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B172" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="78">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D172" s="78" t="s">
         <v>131</v>
       </c>
       <c r="E172" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F172" s="78">
         <v>16</v>
@@ -14648,19 +14645,19 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" s="78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B173" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C173" s="78">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D173" s="78" t="s">
         <v>131</v>
       </c>
       <c r="E173" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F173" s="78">
         <v>17</v>
@@ -14717,19 +14714,19 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" s="78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B174" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C174" s="78">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D174" s="78" t="s">
         <v>131</v>
       </c>
       <c r="E174" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F174" s="78">
         <v>18</v>
@@ -14786,19 +14783,19 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" s="78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B175" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C175" s="78">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D175" s="78" t="s">
         <v>131</v>
       </c>
       <c r="E175" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F175" s="78">
         <v>19</v>
@@ -14855,19 +14852,19 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B176" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C176" s="78">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D176" s="78" t="s">
         <v>131</v>
       </c>
       <c r="E176" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F176" s="78">
         <v>20</v>
@@ -14924,19 +14921,19 @@
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" s="86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B177" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C177" s="86">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D177" s="86" t="s">
         <v>131</v>
       </c>
       <c r="E177" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F177" s="86">
         <v>21</v>
@@ -14993,19 +14990,19 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" s="86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B178" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C178" s="86">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D178" s="86" t="s">
         <v>131</v>
       </c>
       <c r="E178" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F178" s="86">
         <v>22</v>
@@ -15062,19 +15059,19 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" s="86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B179" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C179" s="86">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D179" s="86" t="s">
         <v>131</v>
       </c>
       <c r="E179" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F179" s="86">
         <v>23</v>
@@ -15131,19 +15128,19 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B180" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C180" s="86">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D180" s="86" t="s">
         <v>131</v>
       </c>
       <c r="E180" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F180" s="86">
         <v>24</v>
@@ -15200,19 +15197,19 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" s="86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B181" s="86" t="s">
         <v>9</v>
       </c>
       <c r="C181" s="86">
-        <v>1286</v>
+        <v>104</v>
       </c>
       <c r="D181" s="86" t="s">
         <v>131</v>
       </c>
       <c r="E181" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F181" s="86">
         <v>25</v>
@@ -15269,85 +15266,85 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V182" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W182" s="48"/>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C183" s="6" t="s">
+      <c r="C183" s="6">
+        <v>201</v>
+      </c>
+      <c r="D183" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="D183" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="E183" s="6" t="s">
         <v>120</v>
@@ -15407,16 +15404,16 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C184" s="6" t="s">
+      <c r="C184" s="6">
+        <v>201</v>
+      </c>
+      <c r="D184" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>120</v>
@@ -15476,16 +15473,16 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C185" s="6" t="s">
+      <c r="C185" s="6">
+        <v>201</v>
+      </c>
+      <c r="D185" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="D185" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>120</v>
@@ -15545,16 +15542,16 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C186" s="6" t="s">
+      <c r="C186" s="6">
+        <v>201</v>
+      </c>
+      <c r="D186" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="D186" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>120</v>
@@ -15614,16 +15611,16 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C187" s="6" t="s">
+      <c r="C187" s="6">
+        <v>201</v>
+      </c>
+      <c r="D187" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="E187" s="6" t="s">
         <v>120</v>
@@ -15683,16 +15680,16 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C188" s="6" t="s">
+      <c r="C188" s="6">
+        <v>201</v>
+      </c>
+      <c r="D188" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>120</v>
@@ -15752,19 +15749,19 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="78" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B189" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C189" s="78" t="s">
+      <c r="C189" s="78">
+        <v>201</v>
+      </c>
+      <c r="D189" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="D189" s="78" t="s">
-        <v>135</v>
-      </c>
       <c r="E189" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F189" s="78">
         <v>7</v>
@@ -15821,19 +15818,19 @@
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" s="78" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B190" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C190" s="78" t="s">
+      <c r="C190" s="78">
+        <v>201</v>
+      </c>
+      <c r="D190" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="D190" s="78" t="s">
-        <v>135</v>
-      </c>
       <c r="E190" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F190" s="78">
         <v>8</v>
@@ -15890,85 +15887,85 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V191" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W191" s="48"/>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C192" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D192" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="D192" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>120</v>
@@ -16028,85 +16025,85 @@
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V193" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W193" s="48"/>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C194" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D194" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="D194" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>120</v>
@@ -16166,76 +16163,76 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V195" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W195" s="48"/>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>6</v>
@@ -16304,76 +16301,76 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V197" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W197" s="48"/>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>6</v>
@@ -16442,7 +16439,7 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>6</v>
@@ -16511,76 +16508,76 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V200" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W200" s="48"/>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>6</v>
@@ -16649,7 +16646,7 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>6</v>
@@ -16718,7 +16715,7 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>6</v>
@@ -16787,7 +16784,7 @@
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>6</v>
@@ -16856,7 +16853,7 @@
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>6</v>
@@ -16925,7 +16922,7 @@
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>6</v>
@@ -16994,7 +16991,7 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" s="73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B207" s="73" t="s">
         <v>6</v>
@@ -17006,7 +17003,7 @@
         <v>55</v>
       </c>
       <c r="E207" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F207" s="73">
         <v>7</v>
@@ -17063,7 +17060,7 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" s="73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B208" s="73" t="s">
         <v>6</v>
@@ -17075,7 +17072,7 @@
         <v>55</v>
       </c>
       <c r="E208" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F208" s="73">
         <v>8</v>
@@ -17132,7 +17129,7 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" s="73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B209" s="73" t="s">
         <v>6</v>
@@ -17144,7 +17141,7 @@
         <v>55</v>
       </c>
       <c r="E209" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F209" s="73">
         <v>9</v>
@@ -17201,7 +17198,7 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" s="73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B210" s="73" t="s">
         <v>6</v>
@@ -17213,7 +17210,7 @@
         <v>55</v>
       </c>
       <c r="E210" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F210" s="73">
         <v>10</v>
@@ -17270,7 +17267,7 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" s="73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B211" s="73" t="s">
         <v>6</v>
@@ -17282,7 +17279,7 @@
         <v>55</v>
       </c>
       <c r="E211" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F211" s="73">
         <v>11</v>
@@ -17339,7 +17336,7 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" s="78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B212" s="78" t="s">
         <v>6</v>
@@ -17351,7 +17348,7 @@
         <v>55</v>
       </c>
       <c r="E212" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F212" s="78">
         <v>12</v>
@@ -17408,7 +17405,7 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" s="78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B213" s="78" t="s">
         <v>6</v>
@@ -17420,7 +17417,7 @@
         <v>55</v>
       </c>
       <c r="E213" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F213" s="78">
         <v>13</v>
@@ -17477,7 +17474,7 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" s="78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B214" s="78" t="s">
         <v>6</v>
@@ -17489,7 +17486,7 @@
         <v>55</v>
       </c>
       <c r="E214" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F214" s="78">
         <v>14</v>
@@ -17546,7 +17543,7 @@
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" s="78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B215" s="78" t="s">
         <v>6</v>
@@ -17558,7 +17555,7 @@
         <v>55</v>
       </c>
       <c r="E215" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F215" s="78">
         <v>15</v>
@@ -17615,7 +17612,7 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" s="78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B216" s="78" t="s">
         <v>6</v>
@@ -17627,7 +17624,7 @@
         <v>55</v>
       </c>
       <c r="E216" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F216" s="78">
         <v>16</v>
@@ -17684,76 +17681,76 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V217" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W217" s="48"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>6</v>
@@ -17822,7 +17819,7 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>6</v>
@@ -17891,7 +17888,7 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>6</v>
@@ -17960,7 +17957,7 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>6</v>
@@ -18029,7 +18026,7 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>6</v>
@@ -18098,7 +18095,7 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>6</v>
@@ -18167,76 +18164,76 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V224" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W224" s="48"/>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>6</v>
@@ -18305,76 +18302,76 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V226" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W226" s="48"/>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>6</v>
@@ -18443,7 +18440,7 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>6</v>
@@ -18512,7 +18509,7 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" s="73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B229" s="73" t="s">
         <v>6</v>
@@ -18524,7 +18521,7 @@
         <v>67</v>
       </c>
       <c r="E229" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F229" s="73">
         <v>1</v>
@@ -18581,76 +18578,76 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V230" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W230" s="48"/>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>6</v>
@@ -18719,7 +18716,7 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>6</v>
@@ -18788,7 +18785,7 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="73" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B233" s="73" t="s">
         <v>6</v>
@@ -18800,7 +18797,7 @@
         <v>72</v>
       </c>
       <c r="E233" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F233" s="73">
         <v>3</v>
@@ -18857,7 +18854,7 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="78" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B234" s="78" t="s">
         <v>6</v>
@@ -18869,7 +18866,7 @@
         <v>72</v>
       </c>
       <c r="E234" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F234" s="78">
         <v>4</v>
@@ -18926,76 +18923,76 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V235" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W235" s="48"/>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>6</v>
@@ -19064,76 +19061,76 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V237" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W237" s="48"/>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>6</v>
@@ -19202,7 +19199,7 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>6</v>
@@ -19271,7 +19268,7 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>6</v>
@@ -19340,76 +19337,76 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V241" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W241" s="48"/>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>6</v>
@@ -19478,7 +19475,7 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>6</v>
@@ -19547,7 +19544,7 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>6</v>
@@ -19616,76 +19613,76 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V245" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W245" s="48"/>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>6</v>
@@ -19754,7 +19751,7 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>6</v>
@@ -19825,7 +19822,7 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>6</v>
@@ -19896,7 +19893,7 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>6</v>
@@ -19967,7 +19964,7 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>6</v>
@@ -20038,7 +20035,7 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>6</v>
@@ -20109,76 +20106,76 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V252" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W252" s="48"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>6</v>
@@ -20247,7 +20244,7 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>6</v>
@@ -20316,7 +20313,7 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>6</v>
@@ -20385,7 +20382,7 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>6</v>
@@ -20454,7 +20451,7 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" s="73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B257" s="73" t="s">
         <v>6</v>
@@ -20466,7 +20463,7 @@
         <v>87</v>
       </c>
       <c r="E257" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F257" s="73">
         <v>5</v>
@@ -20523,7 +20520,7 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B258" s="73" t="s">
         <v>6</v>
@@ -20535,7 +20532,7 @@
         <v>87</v>
       </c>
       <c r="E258" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F258" s="73">
         <v>6</v>
@@ -20592,76 +20589,76 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V259" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W259" s="48"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>6</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B7B0ED2-E838-467F-9B77-D5FDDB1D1043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65D6DE4E-3BD6-425B-8FBE-57F760437E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4890" yWindow="2505" windowWidth="52710" windowHeight="29895" xr2:uid="{3EBA7C37-EF48-42B6-AFC8-6B42723A749E}"/>
+    <workbookView xWindow="3900" yWindow="2505" windowWidth="52710" windowHeight="29895" xr2:uid="{D1DE1A64-D3AF-4AC7-A8E4-251A3C5B9995}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1358,7 +1358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BF2352-2549-4FEC-ACAC-8E7C8FEE077F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A91FA5B-2706-42F8-B8A4-697676A78052}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2404,7 +2404,7 @@
         <v>74</v>
       </c>
       <c r="AN17" s="31">
-        <v>46348.599200000004</v>
+        <v>43688</v>
       </c>
       <c r="AS17" s="23" t="s">
         <v>75</v>
@@ -3870,7 +3870,7 @@
         <v>0.6</v>
       </c>
       <c r="AT30" s="66">
-        <v>46348.599200000004</v>
+        <v>43688</v>
       </c>
       <c r="AU30" s="66" t="s">
         <v>96</v>
@@ -4009,7 +4009,7 @@
         <v>47739.057176000002</v>
       </c>
       <c r="AU31" s="60">
-        <v>1390.4579759999979</v>
+        <v>4051.0571760000021</v>
       </c>
       <c r="AV31" s="61" t="s">
         <v>47</v>
@@ -5679,7 +5679,7 @@
         <v>21.500004921259844</v>
       </c>
       <c r="R47" s="13">
-        <v>43688.01</v>
+        <v>43688</v>
       </c>
       <c r="S47" s="70">
         <v>45383</v>
@@ -5787,7 +5787,7 @@
         <v>44.29</v>
       </c>
       <c r="R48" s="71">
-        <v>43688.01</v>
+        <v>43688</v>
       </c>
       <c r="S48" s="16">
         <v>45383</v>
@@ -5894,8 +5894,8 @@
       <c r="Q49" s="13">
         <v>45.618700000000004</v>
       </c>
-      <c r="R49" s="13">
-        <v>46348.599200000004</v>
+      <c r="R49" s="71">
+        <v>43688</v>
       </c>
       <c r="S49" s="16">
         <v>45383</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65D6DE4E-3BD6-425B-8FBE-57F760437E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5515C987-0E2F-4B8C-99D3-8869345756F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2505" windowWidth="52710" windowHeight="29895" xr2:uid="{D1DE1A64-D3AF-4AC7-A8E4-251A3C5B9995}"/>
+    <workbookView xWindow="0" yWindow="2505" windowWidth="76740" windowHeight="29895" xr2:uid="{9475DD9F-DCAC-4AA6-9475-B5C4FEF27D31}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="194">
   <si>
     <t>Building</t>
   </si>
@@ -191,7 +191,7 @@
     <t>Select Tenant:</t>
   </si>
   <si>
-    <t>36 South_101_HDR HOLDINGS LLC D/B/A WONDER</t>
+    <t>36 South_201_Longo Architects &amp; Associates, LLC</t>
   </si>
   <si>
     <t>EJS Westfield Toybox, LLC d/b/a Learning Express</t>
@@ -203,7 +203,7 @@
     <t>Tenant</t>
   </si>
   <si>
-    <t>HDR HOLDINGS LLC D/B/A WONDER</t>
+    <t>Longo Architects &amp; Associates, LLC</t>
   </si>
   <si>
     <t>Reves Smoothie Bar, LLC d/b/a Reves Cafe</t>
@@ -299,7 +299,7 @@
     <t>Clauses</t>
   </si>
   <si>
-    <t>Two 5-Year 3% Annual Inc; 2nd Fl Non-Comp</t>
+    <t>1x opt to Cancel</t>
   </si>
   <si>
     <t>Westfield Education Association</t>
@@ -332,7 +332,7 @@
     <t/>
   </si>
   <si>
-    <t>CITY PROPERTY USA NJ, LLC</t>
+    <t>City Property USA NJ, LLC</t>
   </si>
   <si>
     <t>15 South1</t>
@@ -389,19 +389,19 @@
     <t>Easement</t>
   </si>
   <si>
+    <t>Original</t>
+  </si>
+  <si>
+    <t>HDR Holdings LLC d/b/a Wonder</t>
+  </si>
+  <si>
     <t>36 South1</t>
   </si>
   <si>
-    <t>Longo Architects &amp; Associates, LLC</t>
+    <t>Two 5-Year 3% Annual Inc; 2nd Fl Non-Comp</t>
   </si>
   <si>
     <t>36 South2</t>
-  </si>
-  <si>
-    <t>One 3-Year 31% Jump + 3% Annual Inc</t>
-  </si>
-  <si>
-    <t>Original</t>
   </si>
   <si>
     <t>Roof</t>
@@ -458,9 +458,6 @@
     <t>Two 2-Year</t>
   </si>
   <si>
-    <t>Option_1</t>
-  </si>
-  <si>
     <t>202_Apt</t>
   </si>
   <si>
@@ -474,9 +471,6 @@
   </si>
   <si>
     <t>Alan DiEsso</t>
-  </si>
-  <si>
-    <t>Option_2</t>
   </si>
   <si>
     <t>ID</t>
@@ -501,6 +495,9 @@
   </si>
   <si>
     <t>Cancel Date</t>
+  </si>
+  <si>
+    <t>36 South_101_HDR Holdings LLC d/b/a Wonder</t>
   </si>
   <si>
     <t>LEASE OPTIONS SUMMARY</t>
@@ -533,16 +530,19 @@
     <t>Option 1</t>
   </si>
   <si>
+    <t>Option_1</t>
+  </si>
+  <si>
     <t>Option 2</t>
   </si>
   <si>
     <t>Option 3</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Option_2</t>
   </si>
   <si>
-    <t>36 South_201_Longo Architects &amp; Associates, LLC</t>
+    <t>-</t>
   </si>
   <si>
     <t>36 South_Roof_Verizon</t>
@@ -551,7 +551,7 @@
     <t>36 South_Easement_Easement</t>
   </si>
   <si>
-    <t>15 South_1_CITY PROPERTY USA NJ, LLC</t>
+    <t>15 South_1_City Property USA NJ, LLC</t>
   </si>
   <si>
     <t>15 South_Exterior_Wells Fargo</t>
@@ -1358,7 +1358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A91FA5B-2706-42F8-B8A4-697676A78052}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA00B1D-1280-4C7D-BE49-B32403B8407C}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1960,7 +1960,7 @@
         <v>58</v>
       </c>
       <c r="AT13" s="27">
-        <v>4064</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
@@ -2069,7 +2069,7 @@
         <v>60</v>
       </c>
       <c r="AT14" s="28">
-        <v>49034</v>
+        <v>47177</v>
       </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
@@ -2172,13 +2172,13 @@
         <v>65</v>
       </c>
       <c r="AL15" s="22">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AS15" s="23" t="s">
         <v>66</v>
       </c>
       <c r="AT15" s="30">
-        <v>96</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
@@ -2287,13 +2287,13 @@
         <v>17</v>
       </c>
       <c r="AL16" s="22" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="AS16" s="23" t="s">
         <v>71</v>
       </c>
       <c r="AT16" s="31">
-        <v>45.618700000000004</v>
+        <v>26.43486544415337</v>
       </c>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
@@ -2398,19 +2398,19 @@
         <v>58</v>
       </c>
       <c r="AL17" s="27">
-        <v>4064</v>
+        <v>4199</v>
       </c>
       <c r="AM17" s="26" t="s">
         <v>74</v>
       </c>
       <c r="AN17" s="31">
-        <v>43688</v>
+        <v>18500</v>
       </c>
       <c r="AS17" s="23" t="s">
         <v>75</v>
       </c>
       <c r="AT17" s="33">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
@@ -2517,13 +2517,13 @@
         <v>77</v>
       </c>
       <c r="AN18" s="34">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AS18" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="AT18" s="35">
-        <v>48854</v>
+      <c r="AT18" s="35" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
@@ -2626,19 +2626,19 @@
         <v>75</v>
       </c>
       <c r="AL19" s="34">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AM19" s="26" t="s">
         <v>80</v>
       </c>
       <c r="AN19" s="34">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AS19" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="AT19" s="36">
-        <v>48854</v>
+      <c r="AT19" s="36" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
@@ -2745,13 +2745,13 @@
         <v>83</v>
       </c>
       <c r="AL20" s="28">
-        <v>45383</v>
+        <v>38504</v>
       </c>
       <c r="AM20" s="26" t="s">
         <v>84</v>
       </c>
       <c r="AN20" s="34">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AS20" s="23" t="s">
         <v>85</v>
@@ -2862,13 +2862,13 @@
         <v>89</v>
       </c>
       <c r="AL21" s="28">
-        <v>45566</v>
+        <v>38504</v>
       </c>
       <c r="AM21" s="26" t="s">
         <v>90</v>
       </c>
       <c r="AN21" s="31">
-        <v>5080</v>
+        <v>5248.75</v>
       </c>
       <c r="AS21" s="23" t="s">
         <v>91</v>
@@ -2977,13 +2977,13 @@
         <v>60</v>
       </c>
       <c r="AL22" s="38">
-        <v>49034</v>
+        <v>47177</v>
       </c>
       <c r="AM22" s="26" t="s">
         <v>66</v>
       </c>
       <c r="AN22" s="30">
-        <v>96</v>
+        <v>34.1</v>
       </c>
       <c r="AS22" s="23" t="s">
         <v>66</v>
@@ -3563,43 +3563,43 @@
       </c>
       <c r="AI28" s="45"/>
       <c r="AK28" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="AL28" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM28" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="AN28" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO28" s="64" t="s">
-        <v>96</v>
-      </c>
-      <c r="AP28" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ28" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR28" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS28" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="AT28" s="66" t="s">
-        <v>96</v>
+        <v>116</v>
+      </c>
+      <c r="AL28" s="62">
+        <v>2</v>
+      </c>
+      <c r="AM28" s="63">
+        <v>46082</v>
+      </c>
+      <c r="AN28" s="63">
+        <v>46446</v>
+      </c>
+      <c r="AO28" s="64">
+        <v>0.05</v>
+      </c>
+      <c r="AP28" s="65">
+        <v>9250</v>
+      </c>
+      <c r="AQ28" s="66">
+        <v>111000</v>
+      </c>
+      <c r="AR28" s="65">
+        <v>26.43486544415337</v>
+      </c>
+      <c r="AS28" s="66">
+        <v>0.2</v>
+      </c>
+      <c r="AT28" s="66">
+        <v>18500</v>
       </c>
       <c r="AU28" s="66" t="s">
         <v>96</v>
       </c>
       <c r="AV28" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW28" s="65" t="s">
-        <v>96</v>
+        <v>27</v>
+      </c>
+      <c r="AW28" s="65">
+        <v>5248.75</v>
       </c>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
@@ -3610,7 +3610,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>45</v>
@@ -3619,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AD29" s="32"/>
       <c r="AE29" s="32" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="AF29" s="13">
         <v>15</v>
@@ -3705,43 +3705,43 @@
         <v>16933.333333333332</v>
       </c>
       <c r="AK29" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="AL29" s="58" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM29" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="AN29" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO29" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AP29" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ29" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR29" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS29" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="AT29" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="AU29" s="60" t="s">
-        <v>96</v>
+        <v>116</v>
+      </c>
+      <c r="AL29" s="58">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="28">
+        <v>46447</v>
+      </c>
+      <c r="AN29" s="28">
+        <v>46811</v>
+      </c>
+      <c r="AO29" s="34">
+        <v>0.05</v>
+      </c>
+      <c r="AP29" s="59">
+        <v>9712.5</v>
+      </c>
+      <c r="AQ29" s="60">
+        <v>116550</v>
+      </c>
+      <c r="AR29" s="59">
+        <v>27.75660871636104</v>
+      </c>
+      <c r="AS29" s="60">
+        <v>0.2</v>
+      </c>
+      <c r="AT29" s="60">
+        <v>19425</v>
+      </c>
+      <c r="AU29" s="60">
+        <v>925</v>
       </c>
       <c r="AV29" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW29" s="59" t="s">
-        <v>96</v>
+        <v>27</v>
+      </c>
+      <c r="AW29" s="59">
+        <v>5248.75</v>
       </c>
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
@@ -3752,7 +3752,7 @@
         <v>201</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>62</v>
@@ -3761,7 +3761,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
@@ -3822,14 +3822,16 @@
         <v>0.05</v>
       </c>
       <c r="AA30" s="32" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="AB30" s="19">
         <v>2</v>
       </c>
       <c r="AC30" s="19"/>
       <c r="AD30" s="32"/>
-      <c r="AE30" s="32"/>
+      <c r="AE30" s="32" t="s">
+        <v>86</v>
+      </c>
       <c r="AF30" s="13">
         <v>15</v>
       </c>
@@ -3843,43 +3845,43 @@
         <v>8747.9166666666661</v>
       </c>
       <c r="AK30" s="22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AL30" s="62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM30" s="63">
-        <v>46113</v>
+        <v>46812</v>
       </c>
       <c r="AN30" s="63">
-        <v>46477</v>
+        <v>47177</v>
       </c>
       <c r="AO30" s="64">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AP30" s="65">
-        <v>15449.533066666669</v>
+        <v>10198.125</v>
       </c>
       <c r="AQ30" s="66">
-        <v>185394.39680000002</v>
+        <v>122377.5</v>
       </c>
       <c r="AR30" s="65">
-        <v>45.618700000000004</v>
+        <v>29.144439152179089</v>
       </c>
       <c r="AS30" s="66">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AT30" s="66">
-        <v>43688</v>
-      </c>
-      <c r="AU30" s="66" t="s">
-        <v>96</v>
+        <v>20396.25</v>
+      </c>
+      <c r="AU30" s="66">
+        <v>971.25</v>
       </c>
       <c r="AV30" s="67" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="AW30" s="65">
-        <v>5080</v>
+        <v>5248.75</v>
       </c>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
@@ -3979,43 +3981,43 @@
         <v>0</v>
       </c>
       <c r="AK31" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL31" s="58">
-        <v>4</v>
-      </c>
-      <c r="AM31" s="28">
-        <v>46478</v>
-      </c>
-      <c r="AN31" s="28">
-        <v>46843</v>
-      </c>
-      <c r="AO31" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP31" s="59">
-        <v>15913.019058666667</v>
-      </c>
-      <c r="AQ31" s="60">
-        <v>190956.22870400001</v>
-      </c>
-      <c r="AR31" s="59">
-        <v>46.987261000000004</v>
-      </c>
-      <c r="AS31" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT31" s="60">
-        <v>47739.057176000002</v>
-      </c>
-      <c r="AU31" s="60">
-        <v>4051.0571760000021</v>
+        <v>96</v>
+      </c>
+      <c r="AL31" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM31" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN31" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO31" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP31" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ31" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR31" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS31" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT31" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU31" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV31" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW31" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW31" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
@@ -4111,43 +4113,43 @@
         <v>0</v>
       </c>
       <c r="AK32" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL32" s="62">
-        <v>5</v>
-      </c>
-      <c r="AM32" s="63">
-        <v>46844</v>
-      </c>
-      <c r="AN32" s="63">
-        <v>47208</v>
-      </c>
-      <c r="AO32" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP32" s="65">
-        <v>16390.409630426668</v>
-      </c>
-      <c r="AQ32" s="66">
-        <v>196684.91556512003</v>
-      </c>
-      <c r="AR32" s="65">
-        <v>48.396878830000006</v>
-      </c>
-      <c r="AS32" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT32" s="66">
-        <v>49171.22889128</v>
-      </c>
-      <c r="AU32" s="66">
-        <v>1432.1717152799974</v>
+        <v>96</v>
+      </c>
+      <c r="AL32" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM32" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN32" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO32" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP32" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ32" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR32" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS32" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT32" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU32" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV32" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW32" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW32" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
@@ -4193,43 +4195,43 @@
       </c>
       <c r="AI33" s="45"/>
       <c r="AK33" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL33" s="58">
-        <v>6</v>
-      </c>
-      <c r="AM33" s="28">
-        <v>47209</v>
-      </c>
-      <c r="AN33" s="28">
-        <v>47573</v>
-      </c>
-      <c r="AO33" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP33" s="59">
-        <v>16882.121919339468</v>
-      </c>
-      <c r="AQ33" s="60">
-        <v>202585.46303207363</v>
-      </c>
-      <c r="AR33" s="59">
-        <v>49.84878519490001</v>
-      </c>
-      <c r="AS33" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT33" s="60">
-        <v>50646.365758018408</v>
-      </c>
-      <c r="AU33" s="60">
-        <v>1475.1368667384086</v>
+        <v>96</v>
+      </c>
+      <c r="AL33" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM33" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN33" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO33" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP33" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ33" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR33" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS33" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT33" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU33" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV33" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW33" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW33" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
@@ -4331,43 +4333,43 @@
         <v>3004.1666666666665</v>
       </c>
       <c r="AK34" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL34" s="62">
-        <v>7</v>
-      </c>
-      <c r="AM34" s="63">
-        <v>47574</v>
-      </c>
-      <c r="AN34" s="63">
-        <v>47938</v>
-      </c>
-      <c r="AO34" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP34" s="65">
-        <v>17388.585576919653</v>
-      </c>
-      <c r="AQ34" s="66">
-        <v>208663.02692303585</v>
-      </c>
-      <c r="AR34" s="65">
-        <v>51.344248750747013</v>
-      </c>
-      <c r="AS34" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT34" s="66">
-        <v>52165.756730758963</v>
-      </c>
-      <c r="AU34" s="66">
-        <v>1519.3909727405553</v>
+        <v>96</v>
+      </c>
+      <c r="AL34" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM34" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN34" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO34" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP34" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ34" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR34" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS34" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT34" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU34" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV34" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW34" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW34" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
@@ -4469,43 +4471,43 @@
         <v>4150</v>
       </c>
       <c r="AK35" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL35" s="58">
-        <v>8</v>
-      </c>
-      <c r="AM35" s="28">
-        <v>47939</v>
-      </c>
-      <c r="AN35" s="28">
-        <v>48304</v>
-      </c>
-      <c r="AO35" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP35" s="59">
-        <v>17910.243144227246</v>
-      </c>
-      <c r="AQ35" s="60">
-        <v>214922.91773072694</v>
-      </c>
-      <c r="AR35" s="59">
-        <v>52.884576213269426</v>
-      </c>
-      <c r="AS35" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT35" s="60">
-        <v>53730.729432681735</v>
-      </c>
-      <c r="AU35" s="60">
-        <v>1564.9727019227721</v>
+        <v>96</v>
+      </c>
+      <c r="AL35" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM35" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN35" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO35" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP35" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ35" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR35" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS35" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT35" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU35" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV35" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW35" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW35" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
@@ -4607,43 +4609,43 @@
         <v>6387.5</v>
       </c>
       <c r="AK36" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL36" s="62">
-        <v>9</v>
-      </c>
-      <c r="AM36" s="63">
-        <v>48305</v>
-      </c>
-      <c r="AN36" s="63">
-        <v>48669</v>
-      </c>
-      <c r="AO36" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP36" s="65">
-        <v>18447.550438554063</v>
-      </c>
-      <c r="AQ36" s="66">
-        <v>221370.60526264875</v>
-      </c>
-      <c r="AR36" s="65">
-        <v>54.47111349966751</v>
-      </c>
-      <c r="AS36" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT36" s="66">
-        <v>55342.651315662188</v>
-      </c>
-      <c r="AU36" s="66">
-        <v>1611.9218829804522</v>
+        <v>96</v>
+      </c>
+      <c r="AL36" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM36" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN36" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO36" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP36" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ36" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR36" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS36" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT36" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU36" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV36" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW36" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW36" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
@@ -4745,43 +4747,43 @@
         <v>10450</v>
       </c>
       <c r="AK37" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL37" s="58">
-        <v>10</v>
-      </c>
-      <c r="AM37" s="28">
-        <v>48670</v>
-      </c>
-      <c r="AN37" s="28">
-        <v>49034</v>
-      </c>
-      <c r="AO37" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP37" s="59">
-        <v>19000.976951710687</v>
-      </c>
-      <c r="AQ37" s="60">
-        <v>228011.72342052823</v>
-      </c>
-      <c r="AR37" s="59">
-        <v>56.105246904657534</v>
-      </c>
-      <c r="AS37" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT37" s="60">
-        <v>57002.930855132057</v>
-      </c>
-      <c r="AU37" s="60">
-        <v>1660.2795394698696</v>
+        <v>96</v>
+      </c>
+      <c r="AL37" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM37" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN37" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO37" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP37" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ37" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR37" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS37" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT37" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU37" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV37" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW37" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW37" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
@@ -4883,43 +4885,43 @@
         <v>2477.0833333333335</v>
       </c>
       <c r="AK38" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL38" s="62">
-        <v>11</v>
-      </c>
-      <c r="AM38" s="63">
-        <v>49035</v>
-      </c>
-      <c r="AN38" s="63">
-        <v>49399</v>
-      </c>
-      <c r="AO38" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP38" s="65">
-        <v>19571.006260262006</v>
-      </c>
-      <c r="AQ38" s="66">
-        <v>234852.07512314408</v>
-      </c>
-      <c r="AR38" s="65">
-        <v>57.788404311797265</v>
-      </c>
-      <c r="AS38" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT38" s="66">
-        <v>58713.01878078602</v>
-      </c>
-      <c r="AU38" s="66">
-        <v>1710.0879256539629</v>
+        <v>96</v>
+      </c>
+      <c r="AL38" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM38" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN38" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO38" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP38" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ38" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR38" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS38" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT38" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU38" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV38" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW38" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW38" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
@@ -4927,13 +4929,13 @@
         <v>9</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="E39" s="6">
         <v>2</v>
@@ -5023,43 +5025,43 @@
         <v>2679.1666666666665</v>
       </c>
       <c r="AK39" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL39" s="58">
-        <v>12</v>
-      </c>
-      <c r="AM39" s="28">
-        <v>49400</v>
-      </c>
-      <c r="AN39" s="28">
-        <v>49765</v>
-      </c>
-      <c r="AO39" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP39" s="59">
-        <v>20158.136448069868</v>
-      </c>
-      <c r="AQ39" s="60">
-        <v>241897.63737683842</v>
-      </c>
-      <c r="AR39" s="59">
-        <v>59.522056441151186</v>
-      </c>
-      <c r="AS39" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT39" s="60">
-        <v>60474.409344209605</v>
-      </c>
-      <c r="AU39" s="60">
-        <v>1761.3905634235853</v>
+        <v>96</v>
+      </c>
+      <c r="AL39" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM39" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN39" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO39" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP39" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ39" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR39" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS39" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT39" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU39" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV39" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW39" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW39" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
@@ -5067,13 +5069,13 @@
         <v>9</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>144</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
@@ -5163,43 +5165,43 @@
         <v>1614.5833333333333</v>
       </c>
       <c r="AK40" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL40" s="62">
-        <v>13</v>
-      </c>
-      <c r="AM40" s="63">
-        <v>49766</v>
-      </c>
-      <c r="AN40" s="63">
-        <v>50130</v>
-      </c>
-      <c r="AO40" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP40" s="65">
-        <v>20762.880541511964</v>
-      </c>
-      <c r="AQ40" s="66">
-        <v>249154.56649814357</v>
-      </c>
-      <c r="AR40" s="65">
-        <v>61.307718134385723</v>
-      </c>
-      <c r="AS40" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT40" s="66">
-        <v>62288.641624535892</v>
-      </c>
-      <c r="AU40" s="66">
-        <v>1814.2322803262869</v>
+        <v>96</v>
+      </c>
+      <c r="AL40" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM40" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN40" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO40" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP40" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ40" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR40" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS40" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT40" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU40" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV40" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW40" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW40" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
@@ -5245,172 +5247,172 @@
       </c>
       <c r="AI41" s="45"/>
       <c r="AK41" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL41" s="58">
-        <v>14</v>
-      </c>
-      <c r="AM41" s="28">
-        <v>50131</v>
-      </c>
-      <c r="AN41" s="28">
-        <v>50495</v>
-      </c>
-      <c r="AO41" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP41" s="59">
-        <v>21385.766957757322</v>
-      </c>
-      <c r="AQ41" s="60">
-        <v>256629.20349308787</v>
-      </c>
-      <c r="AR41" s="59">
-        <v>63.146949678417293</v>
-      </c>
-      <c r="AS41" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT41" s="60">
-        <v>64157.300873271961</v>
-      </c>
-      <c r="AU41" s="60">
-        <v>1868.6592487360685</v>
+        <v>96</v>
+      </c>
+      <c r="AL41" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM41" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN41" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO41" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP41" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ41" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR41" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS41" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT41" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU41" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV41" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW41" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW41" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AI42" s="7"/>
       <c r="AK42" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL42" s="62">
-        <v>15</v>
-      </c>
-      <c r="AM42" s="63">
-        <v>50496</v>
-      </c>
-      <c r="AN42" s="63">
-        <v>50860</v>
-      </c>
-      <c r="AO42" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP42" s="65">
-        <v>22027.339966490046</v>
-      </c>
-      <c r="AQ42" s="66">
-        <v>264328.07959788054</v>
-      </c>
-      <c r="AR42" s="65">
-        <v>65.041358168769818</v>
-      </c>
-      <c r="AS42" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT42" s="66">
-        <v>66082.019899470135</v>
-      </c>
-      <c r="AU42" s="66">
-        <v>1924.7190261981741</v>
+        <v>96</v>
+      </c>
+      <c r="AL42" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM42" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN42" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO42" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP42" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ42" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR42" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS42" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT42" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU42" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV42" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW42" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW42" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AK43" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL43" s="58">
-        <v>16</v>
-      </c>
-      <c r="AM43" s="28">
-        <v>50861</v>
-      </c>
-      <c r="AN43" s="28">
-        <v>51226</v>
-      </c>
-      <c r="AO43" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP43" s="59">
-        <v>22688.160165484747</v>
-      </c>
-      <c r="AQ43" s="60">
-        <v>272257.92198581697</v>
-      </c>
-      <c r="AR43" s="59">
-        <v>66.992598913832921</v>
-      </c>
-      <c r="AS43" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT43" s="60">
-        <v>68064.480496454242</v>
-      </c>
-      <c r="AU43" s="60">
-        <v>1982.4605969841068</v>
+        <v>96</v>
+      </c>
+      <c r="AL43" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM43" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN43" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO43" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP43" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ43" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR43" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS43" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT43" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU43" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV43" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW43" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW43" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AK44" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL44" s="62">
-        <v>17</v>
-      </c>
-      <c r="AM44" s="63">
-        <v>51227</v>
-      </c>
-      <c r="AN44" s="63">
-        <v>51591</v>
-      </c>
-      <c r="AO44" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP44" s="65">
-        <v>23368.804970449291</v>
-      </c>
-      <c r="AQ44" s="66">
-        <v>280425.65964539151</v>
-      </c>
-      <c r="AR44" s="65">
-        <v>69.002376881247912</v>
-      </c>
-      <c r="AS44" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT44" s="66">
-        <v>70106.414911347878</v>
-      </c>
-      <c r="AU44" s="66">
-        <v>2041.9344148936361</v>
+        <v>96</v>
+      </c>
+      <c r="AL44" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM44" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN44" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO44" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP44" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ44" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR44" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS44" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT44" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU44" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV44" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW44" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW44" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
@@ -5425,7 +5427,7 @@
         <v>105</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>107</v>
@@ -5437,10 +5439,10 @@
         <v>109</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
@@ -5449,7 +5451,7 @@
         <v>58</v>
       </c>
       <c r="N45" s="69" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O45" s="69" t="s">
         <v>14</v>
@@ -5458,10 +5460,10 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>31</v>
@@ -5476,51 +5478,51 @@
         <v>37</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AK45" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL45" s="58">
-        <v>18</v>
-      </c>
-      <c r="AM45" s="28">
-        <v>51592</v>
-      </c>
-      <c r="AN45" s="28">
-        <v>51956</v>
-      </c>
-      <c r="AO45" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP45" s="59">
-        <v>24069.869119562773</v>
-      </c>
-      <c r="AQ45" s="60">
-        <v>288838.42943475326</v>
-      </c>
-      <c r="AR45" s="59">
-        <v>71.072448187685353</v>
-      </c>
-      <c r="AS45" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT45" s="60">
-        <v>72209.607358688314</v>
-      </c>
-      <c r="AU45" s="60">
-        <v>2103.192447340436</v>
+        <v>96</v>
+      </c>
+      <c r="AL45" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM45" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN45" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO45" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP45" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ45" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR45" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS45" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT45" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU45" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV45" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW45" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW45" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -5529,10 +5531,10 @@
         <v>101</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F46" s="6">
         <v>0</v>
@@ -5587,48 +5589,48 @@
       </c>
       <c r="W46" s="13"/>
       <c r="AK46" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL46" s="62">
-        <v>19</v>
-      </c>
-      <c r="AM46" s="63">
-        <v>51957</v>
-      </c>
-      <c r="AN46" s="63">
-        <v>52321</v>
-      </c>
-      <c r="AO46" s="64">
-        <v>0.03</v>
-      </c>
-      <c r="AP46" s="65">
-        <v>24791.965193149652</v>
-      </c>
-      <c r="AQ46" s="66">
-        <v>297503.58231779584</v>
-      </c>
-      <c r="AR46" s="65">
-        <v>73.204621633315909</v>
-      </c>
-      <c r="AS46" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="AT46" s="66">
-        <v>74375.895579448959</v>
-      </c>
-      <c r="AU46" s="66">
-        <v>2166.2882207606453</v>
+        <v>96</v>
+      </c>
+      <c r="AL46" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM46" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN46" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO46" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP46" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ46" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR46" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS46" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT46" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU46" s="66" t="s">
+        <v>96</v>
       </c>
       <c r="AV46" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW46" s="65">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW46" s="65" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
@@ -5637,10 +5639,10 @@
         <v>101</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
@@ -5695,48 +5697,48 @@
       </c>
       <c r="W47" s="13"/>
       <c r="AK47" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL47" s="58">
-        <v>20</v>
-      </c>
-      <c r="AM47" s="28">
-        <v>52322</v>
-      </c>
-      <c r="AN47" s="28">
-        <v>52687</v>
-      </c>
-      <c r="AO47" s="34">
-        <v>0.03</v>
-      </c>
-      <c r="AP47" s="59">
-        <v>25535.72414894414</v>
-      </c>
-      <c r="AQ47" s="60">
-        <v>306428.6897873297</v>
-      </c>
-      <c r="AR47" s="59">
-        <v>75.400760282315375</v>
-      </c>
-      <c r="AS47" s="60">
-        <v>0.6</v>
-      </c>
-      <c r="AT47" s="60">
-        <v>76607.172446832425</v>
-      </c>
-      <c r="AU47" s="60">
-        <v>2231.2768673834653</v>
+        <v>96</v>
+      </c>
+      <c r="AL47" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM47" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN47" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO47" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP47" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ47" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR47" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS47" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT47" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU47" s="60" t="s">
+        <v>96</v>
       </c>
       <c r="AV47" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW47" s="59">
-        <v>5080</v>
+        <v>96</v>
+      </c>
+      <c r="AW47" s="59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
@@ -5745,10 +5747,10 @@
         <v>101</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F48" s="6">
         <v>2</v>
@@ -5844,7 +5846,7 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
@@ -5853,10 +5855,10 @@
         <v>101</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
@@ -5952,7 +5954,7 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
@@ -5961,10 +5963,10 @@
         <v>101</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F50" s="6">
         <v>4</v>
@@ -6003,7 +6005,7 @@
         <v>46.987261000000004</v>
       </c>
       <c r="R50" s="13">
-        <v>47739.057176000002</v>
+        <v>29125.33</v>
       </c>
       <c r="S50" s="16">
         <v>45383</v>
@@ -6060,7 +6062,7 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
@@ -6069,10 +6071,10 @@
         <v>101</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
@@ -6111,7 +6113,7 @@
         <v>48.396878830000006</v>
       </c>
       <c r="R51" s="13">
-        <v>49171.22889128</v>
+        <v>29125.33</v>
       </c>
       <c r="S51" s="16">
         <v>45383</v>
@@ -6168,7 +6170,7 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
@@ -6177,10 +6179,10 @@
         <v>101</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
@@ -6219,7 +6221,7 @@
         <v>49.84878519490001</v>
       </c>
       <c r="R52" s="13">
-        <v>50646.365758018408</v>
+        <v>29125.33</v>
       </c>
       <c r="S52" s="16">
         <v>45383</v>
@@ -6237,7 +6239,7 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
@@ -6246,10 +6248,10 @@
         <v>101</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
@@ -6288,7 +6290,7 @@
         <v>51.344248750747013</v>
       </c>
       <c r="R53" s="13">
-        <v>52165.756730758963</v>
+        <v>29125.33</v>
       </c>
       <c r="S53" s="16">
         <v>45383</v>
@@ -6304,7 +6306,7 @@
       </c>
       <c r="W53" s="13"/>
       <c r="AK53" s="72" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AL53" s="22"/>
       <c r="AM53" s="22"/>
@@ -6316,7 +6318,7 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>8</v>
@@ -6325,10 +6327,10 @@
         <v>101</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F54" s="6">
         <v>8</v>
@@ -6367,7 +6369,7 @@
         <v>52.884576213269426</v>
       </c>
       <c r="R54" s="13">
-        <v>53730.729432681735</v>
+        <v>29125.33</v>
       </c>
       <c r="S54" s="16">
         <v>45383</v>
@@ -6383,33 +6385,33 @@
       </c>
       <c r="W54" s="13"/>
       <c r="AK54" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL54" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="AL54" s="56" t="s">
+      <c r="AM54" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="AM54" s="56" t="s">
+      <c r="AN54" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="AN54" s="56" t="s">
+      <c r="AO54" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="AO54" s="56" t="s">
+      <c r="AP54" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="AP54" s="56" t="s">
+      <c r="AQ54" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="AQ54" s="56" t="s">
+      <c r="AR54" s="56" t="s">
         <v>161</v>
-      </c>
-      <c r="AR54" s="56" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>8</v>
@@ -6418,10 +6420,10 @@
         <v>101</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F55" s="6">
         <v>9</v>
@@ -6460,7 +6462,7 @@
         <v>54.47111349966751</v>
       </c>
       <c r="R55" s="13">
-        <v>55342.651315662188</v>
+        <v>29125.33</v>
       </c>
       <c r="S55" s="16">
         <v>45383</v>
@@ -6476,33 +6478,33 @@
       </c>
       <c r="W55" s="13"/>
       <c r="AK55" s="26" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AL55" s="58">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AM55" s="28">
-        <v>45383</v>
+        <v>45717</v>
       </c>
       <c r="AN55" s="28">
-        <v>49034</v>
+        <v>47177</v>
       </c>
       <c r="AO55" s="59">
-        <v>0</v>
+        <v>8775</v>
       </c>
       <c r="AP55" s="60">
-        <v>0</v>
+        <v>105300</v>
       </c>
       <c r="AQ55" s="59">
-        <v>19000.976951710687</v>
+        <v>10198.125</v>
       </c>
       <c r="AR55" s="60">
-        <v>228011.72342052823</v>
+        <v>122377.5</v>
       </c>
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
@@ -6511,10 +6513,10 @@
         <v>101</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F56" s="6">
         <v>10</v>
@@ -6553,7 +6555,7 @@
         <v>56.105246904657534</v>
       </c>
       <c r="R56" s="13">
-        <v>57002.930855132057</v>
+        <v>29125.33</v>
       </c>
       <c r="S56" s="16">
         <v>45383</v>
@@ -6569,33 +6571,33 @@
       </c>
       <c r="W56" s="13"/>
       <c r="AK56" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AL56" s="58">
-        <v>5</v>
-      </c>
-      <c r="AM56" s="28">
-        <v>49035</v>
-      </c>
-      <c r="AN56" s="28">
-        <v>50860</v>
-      </c>
-      <c r="AO56" s="59">
-        <v>19571.006260262006</v>
-      </c>
-      <c r="AP56" s="60">
-        <v>234852.07512314408</v>
-      </c>
-      <c r="AQ56" s="59">
-        <v>22027.339966490046</v>
-      </c>
-      <c r="AR56" s="60">
-        <v>264328.07959788054</v>
+        <v>0</v>
+      </c>
+      <c r="AM56" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN56" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO56" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP56" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ56" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR56" s="60" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="73" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B57" s="73" t="s">
         <v>8</v>
@@ -6604,10 +6606,10 @@
         <v>101</v>
       </c>
       <c r="D57" s="73" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F57" s="73">
         <v>11</v>
@@ -6646,7 +6648,7 @@
         <v>57.788404311797265</v>
       </c>
       <c r="R57" s="76">
-        <v>58713.01878078602</v>
+        <v>29125.33</v>
       </c>
       <c r="S57" s="74">
         <v>45383</v>
@@ -6665,30 +6667,30 @@
         <v>164</v>
       </c>
       <c r="AL57" s="58">
-        <v>5</v>
-      </c>
-      <c r="AM57" s="28">
-        <v>50861</v>
-      </c>
-      <c r="AN57" s="28">
-        <v>52687</v>
-      </c>
-      <c r="AO57" s="59">
-        <v>22688.160165484747</v>
-      </c>
-      <c r="AP57" s="60">
-        <v>272257.92198581697</v>
-      </c>
-      <c r="AQ57" s="59">
-        <v>25535.72414894414</v>
-      </c>
-      <c r="AR57" s="60">
-        <v>306428.6897873297</v>
+        <v>0</v>
+      </c>
+      <c r="AM57" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN57" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO57" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP57" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ57" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR57" s="60" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="73" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B58" s="73" t="s">
         <v>8</v>
@@ -6697,10 +6699,10 @@
         <v>101</v>
       </c>
       <c r="D58" s="73" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F58" s="73">
         <v>12</v>
@@ -6739,7 +6741,7 @@
         <v>59.522056441151186</v>
       </c>
       <c r="R58" s="76">
-        <v>60474.409344209605</v>
+        <v>29125.33</v>
       </c>
       <c r="S58" s="74">
         <v>45383</v>
@@ -6781,7 +6783,7 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="73" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B59" s="73" t="s">
         <v>8</v>
@@ -6790,10 +6792,10 @@
         <v>101</v>
       </c>
       <c r="D59" s="73" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F59" s="73">
         <v>13</v>
@@ -6832,7 +6834,7 @@
         <v>61.307718134385723</v>
       </c>
       <c r="R59" s="76">
-        <v>62288.641624535892</v>
+        <v>29125.33</v>
       </c>
       <c r="S59" s="74">
         <v>45383</v>
@@ -6850,7 +6852,7 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="73" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B60" s="73" t="s">
         <v>8</v>
@@ -6859,10 +6861,10 @@
         <v>101</v>
       </c>
       <c r="D60" s="73" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E60" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F60" s="73">
         <v>14</v>
@@ -6901,7 +6903,7 @@
         <v>63.146949678417293</v>
       </c>
       <c r="R60" s="76">
-        <v>64157.300873271961</v>
+        <v>29125.33</v>
       </c>
       <c r="S60" s="74">
         <v>45383</v>
@@ -6919,7 +6921,7 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="73" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B61" s="73" t="s">
         <v>8</v>
@@ -6928,10 +6930,10 @@
         <v>101</v>
       </c>
       <c r="D61" s="73" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F61" s="73">
         <v>15</v>
@@ -6970,7 +6972,7 @@
         <v>65.041358168769818</v>
       </c>
       <c r="R61" s="76">
-        <v>66082.019899470135</v>
+        <v>29125.33</v>
       </c>
       <c r="S61" s="74">
         <v>45383</v>
@@ -6988,7 +6990,7 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B62" s="78" t="s">
         <v>8</v>
@@ -6997,10 +6999,10 @@
         <v>101</v>
       </c>
       <c r="D62" s="78" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E62" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F62" s="78">
         <v>16</v>
@@ -7039,7 +7041,7 @@
         <v>66.992598913832921</v>
       </c>
       <c r="R62" s="81">
-        <v>68064.480496454242</v>
+        <v>29125.33</v>
       </c>
       <c r="S62" s="79">
         <v>45383</v>
@@ -7057,7 +7059,7 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="78" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B63" s="78" t="s">
         <v>8</v>
@@ -7066,10 +7068,10 @@
         <v>101</v>
       </c>
       <c r="D63" s="78" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E63" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F63" s="78">
         <v>17</v>
@@ -7108,7 +7110,7 @@
         <v>69.002376881247912</v>
       </c>
       <c r="R63" s="81">
-        <v>70106.414911347878</v>
+        <v>29125.33</v>
       </c>
       <c r="S63" s="79">
         <v>45383</v>
@@ -7126,7 +7128,7 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="78" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B64" s="78" t="s">
         <v>8</v>
@@ -7135,10 +7137,10 @@
         <v>101</v>
       </c>
       <c r="D64" s="78" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E64" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F64" s="78">
         <v>18</v>
@@ -7177,7 +7179,7 @@
         <v>71.072448187685353</v>
       </c>
       <c r="R64" s="81">
-        <v>72209.607358688314</v>
+        <v>29125.33</v>
       </c>
       <c r="S64" s="79">
         <v>45383</v>
@@ -7195,7 +7197,7 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="78" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B65" s="78" t="s">
         <v>8</v>
@@ -7204,10 +7206,10 @@
         <v>101</v>
       </c>
       <c r="D65" s="78" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E65" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F65" s="78">
         <v>19</v>
@@ -7246,7 +7248,7 @@
         <v>73.204621633315909</v>
       </c>
       <c r="R65" s="81">
-        <v>74375.895579448959</v>
+        <v>29125.33</v>
       </c>
       <c r="S65" s="79">
         <v>45383</v>
@@ -7264,7 +7266,7 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="78" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B66" s="78" t="s">
         <v>8</v>
@@ -7273,10 +7275,10 @@
         <v>101</v>
       </c>
       <c r="D66" s="78" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E66" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F66" s="78">
         <v>20</v>
@@ -7315,7 +7317,7 @@
         <v>75.400760282315375</v>
       </c>
       <c r="R66" s="81">
-        <v>76607.172446832425</v>
+        <v>29125.33</v>
       </c>
       <c r="S66" s="79">
         <v>45383</v>
@@ -7333,76 +7335,76 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V67" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W67" s="48"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>8</v>
@@ -7411,10 +7413,10 @@
         <v>201</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F68" s="6">
         <v>1</v>
@@ -7471,7 +7473,7 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
@@ -7480,10 +7482,10 @@
         <v>201</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F69" s="6">
         <v>2</v>
@@ -7540,7 +7542,7 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
@@ -7549,10 +7551,10 @@
         <v>201</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F70" s="6">
         <v>3</v>
@@ -7609,7 +7611,7 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
@@ -7618,10 +7620,10 @@
         <v>201</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F71" s="6">
         <v>4</v>
@@ -7678,70 +7680,70 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V72" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W72" s="48"/>
     </row>
@@ -7759,7 +7761,7 @@
         <v>122</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F73" s="6">
         <v>1</v>
@@ -7828,7 +7830,7 @@
         <v>122</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F74" s="6">
         <v>2</v>
@@ -7897,7 +7899,7 @@
         <v>122</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F75" s="6">
         <v>3</v>
@@ -7966,7 +7968,7 @@
         <v>122</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F76" s="6">
         <v>4</v>
@@ -8035,7 +8037,7 @@
         <v>122</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F77" s="6">
         <v>5</v>
@@ -8104,7 +8106,7 @@
         <v>122</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F78" s="6">
         <v>6</v>
@@ -8173,7 +8175,7 @@
         <v>122</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F79" s="6">
         <v>7</v>
@@ -8242,7 +8244,7 @@
         <v>122</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F80" s="6">
         <v>8</v>
@@ -8311,7 +8313,7 @@
         <v>122</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F81" s="6">
         <v>9</v>
@@ -8380,7 +8382,7 @@
         <v>122</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F82" s="6">
         <v>10</v>
@@ -8449,7 +8451,7 @@
         <v>122</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F83" s="6">
         <v>11</v>
@@ -8518,7 +8520,7 @@
         <v>122</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F84" s="6">
         <v>12</v>
@@ -8587,7 +8589,7 @@
         <v>122</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F85" s="6">
         <v>13</v>
@@ -8656,7 +8658,7 @@
         <v>122</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F86" s="6">
         <v>14</v>
@@ -8713,70 +8715,70 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V87" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W87" s="48"/>
     </row>
@@ -8794,7 +8796,7 @@
         <v>115</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F88" s="6">
         <v>1</v>
@@ -8863,7 +8865,7 @@
         <v>115</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F89" s="6">
         <v>2</v>
@@ -8932,7 +8934,7 @@
         <v>115</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F90" s="6">
         <v>3</v>
@@ -9001,7 +9003,7 @@
         <v>115</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F91" s="6">
         <v>4</v>
@@ -9070,7 +9072,7 @@
         <v>115</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F92" s="6">
         <v>5</v>
@@ -9139,7 +9141,7 @@
         <v>115</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F93" s="6">
         <v>6</v>
@@ -9208,7 +9210,7 @@
         <v>115</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F94" s="6">
         <v>7</v>
@@ -9277,7 +9279,7 @@
         <v>115</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F95" s="6">
         <v>8</v>
@@ -9346,7 +9348,7 @@
         <v>115</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F96" s="6">
         <v>9</v>
@@ -9415,7 +9417,7 @@
         <v>115</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F97" s="6">
         <v>10</v>
@@ -9484,7 +9486,7 @@
         <v>115</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F98" s="6">
         <v>11</v>
@@ -9541,70 +9543,70 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V99" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W99" s="48"/>
     </row>
@@ -9622,7 +9624,7 @@
         <v>97</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F100" s="6">
         <v>1</v>
@@ -9691,7 +9693,7 @@
         <v>97</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F101" s="6">
         <v>2</v>
@@ -9760,7 +9762,7 @@
         <v>97</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F102" s="6">
         <v>3</v>
@@ -9829,7 +9831,7 @@
         <v>97</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F103" s="6">
         <v>4</v>
@@ -9898,7 +9900,7 @@
         <v>97</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F104" s="6">
         <v>5</v>
@@ -9967,7 +9969,7 @@
         <v>97</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F105" s="6">
         <v>6</v>
@@ -10036,7 +10038,7 @@
         <v>97</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F106" s="6">
         <v>7</v>
@@ -10105,7 +10107,7 @@
         <v>97</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F107" s="6">
         <v>8</v>
@@ -10174,7 +10176,7 @@
         <v>97</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F108" s="6">
         <v>9</v>
@@ -10243,7 +10245,7 @@
         <v>97</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F109" s="6">
         <v>10</v>
@@ -10312,7 +10314,7 @@
         <v>97</v>
       </c>
       <c r="E110" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F110" s="73">
         <v>11</v>
@@ -10381,7 +10383,7 @@
         <v>97</v>
       </c>
       <c r="E111" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F111" s="73">
         <v>12</v>
@@ -10450,7 +10452,7 @@
         <v>97</v>
       </c>
       <c r="E112" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F112" s="73">
         <v>13</v>
@@ -10519,7 +10521,7 @@
         <v>97</v>
       </c>
       <c r="E113" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F113" s="73">
         <v>14</v>
@@ -10588,7 +10590,7 @@
         <v>97</v>
       </c>
       <c r="E114" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F114" s="73">
         <v>15</v>
@@ -10645,70 +10647,70 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V115" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W115" s="48"/>
     </row>
@@ -10726,7 +10728,7 @@
         <v>103</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F116" s="6">
         <v>1</v>
@@ -10795,7 +10797,7 @@
         <v>103</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F117" s="6">
         <v>2</v>
@@ -10864,7 +10866,7 @@
         <v>103</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F118" s="6">
         <v>3</v>
@@ -10933,7 +10935,7 @@
         <v>103</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F119" s="6">
         <v>4</v>
@@ -11002,7 +11004,7 @@
         <v>103</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F120" s="6">
         <v>5</v>
@@ -11071,7 +11073,7 @@
         <v>103</v>
       </c>
       <c r="E121" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F121" s="73">
         <v>6</v>
@@ -11140,7 +11142,7 @@
         <v>103</v>
       </c>
       <c r="E122" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F122" s="73">
         <v>7</v>
@@ -11209,7 +11211,7 @@
         <v>103</v>
       </c>
       <c r="E123" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F123" s="73">
         <v>8</v>
@@ -11278,7 +11280,7 @@
         <v>103</v>
       </c>
       <c r="E124" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F124" s="73">
         <v>9</v>
@@ -11347,7 +11349,7 @@
         <v>103</v>
       </c>
       <c r="E125" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F125" s="73">
         <v>10</v>
@@ -11404,70 +11406,70 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V126" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W126" s="48"/>
     </row>
@@ -11485,7 +11487,7 @@
         <v>115</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F127" s="6">
         <v>1</v>
@@ -11554,7 +11556,7 @@
         <v>115</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F128" s="6">
         <v>2</v>
@@ -11623,7 +11625,7 @@
         <v>115</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F129" s="6">
         <v>3</v>
@@ -11692,7 +11694,7 @@
         <v>115</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F130" s="6">
         <v>4</v>
@@ -11761,7 +11763,7 @@
         <v>115</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F131" s="6">
         <v>5</v>
@@ -11830,7 +11832,7 @@
         <v>115</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F132" s="6">
         <v>6</v>
@@ -11899,7 +11901,7 @@
         <v>115</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F133" s="6">
         <v>7</v>
@@ -11968,7 +11970,7 @@
         <v>115</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F134" s="6">
         <v>8</v>
@@ -12037,7 +12039,7 @@
         <v>115</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F135" s="6">
         <v>9</v>
@@ -12106,7 +12108,7 @@
         <v>115</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F136" s="6">
         <v>10</v>
@@ -12175,7 +12177,7 @@
         <v>115</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F137" s="6">
         <v>11</v>
@@ -12232,70 +12234,70 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V138" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W138" s="48"/>
     </row>
@@ -12313,7 +12315,7 @@
         <v>125</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F139" s="6">
         <v>1</v>
@@ -12382,7 +12384,7 @@
         <v>125</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F140" s="6">
         <v>2</v>
@@ -12451,7 +12453,7 @@
         <v>125</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F141" s="6">
         <v>3</v>
@@ -12520,7 +12522,7 @@
         <v>125</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F142" s="6">
         <v>4</v>
@@ -12589,7 +12591,7 @@
         <v>125</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F143" s="6">
         <v>5</v>
@@ -12646,70 +12648,70 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W144" s="48"/>
     </row>
@@ -12727,7 +12729,7 @@
         <v>128</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F145" s="6">
         <v>1</v>
@@ -12796,7 +12798,7 @@
         <v>128</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F146" s="6">
         <v>2</v>
@@ -12865,7 +12867,7 @@
         <v>128</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F147" s="6">
         <v>3</v>
@@ -12934,7 +12936,7 @@
         <v>128</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F148" s="6">
         <v>4</v>
@@ -13003,7 +13005,7 @@
         <v>128</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F149" s="6">
         <v>5</v>
@@ -13058,70 +13060,70 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V150" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W150" s="48"/>
     </row>
@@ -13139,7 +13141,7 @@
         <v>130</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F151" s="6">
         <v>1</v>
@@ -13208,7 +13210,7 @@
         <v>130</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F152" s="6">
         <v>2</v>
@@ -13277,7 +13279,7 @@
         <v>130</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F153" s="6">
         <v>3</v>
@@ -13346,7 +13348,7 @@
         <v>130</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F154" s="6">
         <v>4</v>
@@ -13415,7 +13417,7 @@
         <v>130</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F155" s="6">
         <v>5</v>
@@ -13472,70 +13474,70 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V156" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W156" s="48"/>
     </row>
@@ -13553,7 +13555,7 @@
         <v>131</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F157" s="6">
         <v>1</v>
@@ -13622,7 +13624,7 @@
         <v>131</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F158" s="6">
         <v>2</v>
@@ -13691,7 +13693,7 @@
         <v>131</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F159" s="6">
         <v>3</v>
@@ -13760,7 +13762,7 @@
         <v>131</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F160" s="6">
         <v>4</v>
@@ -13829,7 +13831,7 @@
         <v>131</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F161" s="6">
         <v>5</v>
@@ -13898,7 +13900,7 @@
         <v>131</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F162" s="6">
         <v>6</v>
@@ -13967,7 +13969,7 @@
         <v>131</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F163" s="6">
         <v>7</v>
@@ -14036,7 +14038,7 @@
         <v>131</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F164" s="6">
         <v>8</v>
@@ -14105,7 +14107,7 @@
         <v>131</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F165" s="6">
         <v>9</v>
@@ -14174,7 +14176,7 @@
         <v>131</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F166" s="6">
         <v>10</v>
@@ -14243,7 +14245,7 @@
         <v>131</v>
       </c>
       <c r="E167" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F167" s="73">
         <v>11</v>
@@ -14312,7 +14314,7 @@
         <v>131</v>
       </c>
       <c r="E168" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F168" s="73">
         <v>12</v>
@@ -14381,7 +14383,7 @@
         <v>131</v>
       </c>
       <c r="E169" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F169" s="73">
         <v>13</v>
@@ -14450,7 +14452,7 @@
         <v>131</v>
       </c>
       <c r="E170" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F170" s="73">
         <v>14</v>
@@ -14519,7 +14521,7 @@
         <v>131</v>
       </c>
       <c r="E171" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F171" s="73">
         <v>15</v>
@@ -14588,7 +14590,7 @@
         <v>131</v>
       </c>
       <c r="E172" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F172" s="78">
         <v>16</v>
@@ -14657,7 +14659,7 @@
         <v>131</v>
       </c>
       <c r="E173" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F173" s="78">
         <v>17</v>
@@ -14726,7 +14728,7 @@
         <v>131</v>
       </c>
       <c r="E174" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F174" s="78">
         <v>18</v>
@@ -14795,7 +14797,7 @@
         <v>131</v>
       </c>
       <c r="E175" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F175" s="78">
         <v>19</v>
@@ -14864,7 +14866,7 @@
         <v>131</v>
       </c>
       <c r="E176" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F176" s="78">
         <v>20</v>
@@ -15266,70 +15268,70 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V182" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W182" s="48"/>
     </row>
@@ -15347,7 +15349,7 @@
         <v>134</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F183" s="6">
         <v>1</v>
@@ -15416,7 +15418,7 @@
         <v>134</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F184" s="6">
         <v>2</v>
@@ -15485,7 +15487,7 @@
         <v>134</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F185" s="6">
         <v>3</v>
@@ -15554,7 +15556,7 @@
         <v>134</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F186" s="6">
         <v>4</v>
@@ -15623,7 +15625,7 @@
         <v>134</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F187" s="6">
         <v>5</v>
@@ -15692,7 +15694,7 @@
         <v>134</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F188" s="6">
         <v>6</v>
@@ -15761,7 +15763,7 @@
         <v>134</v>
       </c>
       <c r="E189" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F189" s="78">
         <v>7</v>
@@ -15830,7 +15832,7 @@
         <v>134</v>
       </c>
       <c r="E190" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F190" s="78">
         <v>8</v>
@@ -15887,70 +15889,70 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V191" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W191" s="48"/>
     </row>
@@ -15962,13 +15964,13 @@
         <v>9</v>
       </c>
       <c r="C192" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D192" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D192" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="E192" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F192" s="6">
         <v>1</v>
@@ -16025,70 +16027,70 @@
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V193" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W193" s="48"/>
     </row>
@@ -16100,13 +16102,13 @@
         <v>9</v>
       </c>
       <c r="C194" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D194" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D194" s="6" t="s">
-        <v>144</v>
-      </c>
       <c r="E194" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F194" s="6">
         <v>1</v>
@@ -16163,70 +16165,70 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V195" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W195" s="48"/>
     </row>
@@ -16244,7 +16246,7 @@
         <v>44</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F196" s="6">
         <v>1</v>
@@ -16301,70 +16303,70 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V197" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W197" s="48"/>
     </row>
@@ -16382,7 +16384,7 @@
         <v>51</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F198" s="6">
         <v>1</v>
@@ -16451,7 +16453,7 @@
         <v>51</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F199" s="6">
         <v>1</v>
@@ -16508,70 +16510,70 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V200" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W200" s="48"/>
     </row>
@@ -16589,7 +16591,7 @@
         <v>55</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F201" s="6">
         <v>1</v>
@@ -16658,7 +16660,7 @@
         <v>55</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F202" s="6">
         <v>2</v>
@@ -16727,7 +16729,7 @@
         <v>55</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F203" s="6">
         <v>3</v>
@@ -16796,7 +16798,7 @@
         <v>55</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F204" s="6">
         <v>4</v>
@@ -16865,7 +16867,7 @@
         <v>55</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F205" s="6">
         <v>5</v>
@@ -16934,7 +16936,7 @@
         <v>55</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F206" s="6">
         <v>6</v>
@@ -17003,7 +17005,7 @@
         <v>55</v>
       </c>
       <c r="E207" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F207" s="73">
         <v>7</v>
@@ -17072,7 +17074,7 @@
         <v>55</v>
       </c>
       <c r="E208" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F208" s="73">
         <v>8</v>
@@ -17141,7 +17143,7 @@
         <v>55</v>
       </c>
       <c r="E209" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F209" s="73">
         <v>9</v>
@@ -17210,7 +17212,7 @@
         <v>55</v>
       </c>
       <c r="E210" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F210" s="73">
         <v>10</v>
@@ -17279,7 +17281,7 @@
         <v>55</v>
       </c>
       <c r="E211" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F211" s="73">
         <v>11</v>
@@ -17348,7 +17350,7 @@
         <v>55</v>
       </c>
       <c r="E212" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F212" s="78">
         <v>12</v>
@@ -17417,7 +17419,7 @@
         <v>55</v>
       </c>
       <c r="E213" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F213" s="78">
         <v>13</v>
@@ -17486,7 +17488,7 @@
         <v>55</v>
       </c>
       <c r="E214" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F214" s="78">
         <v>14</v>
@@ -17555,7 +17557,7 @@
         <v>55</v>
       </c>
       <c r="E215" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F215" s="78">
         <v>15</v>
@@ -17624,7 +17626,7 @@
         <v>55</v>
       </c>
       <c r="E216" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F216" s="78">
         <v>16</v>
@@ -17681,70 +17683,70 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V217" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W217" s="48"/>
     </row>
@@ -17762,7 +17764,7 @@
         <v>59</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F218" s="6">
         <v>1</v>
@@ -17831,7 +17833,7 @@
         <v>59</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F219" s="6">
         <v>2</v>
@@ -17900,7 +17902,7 @@
         <v>59</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F220" s="6">
         <v>3</v>
@@ -17969,7 +17971,7 @@
         <v>59</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F221" s="6">
         <v>4</v>
@@ -18038,7 +18040,7 @@
         <v>59</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F222" s="6">
         <v>5</v>
@@ -18107,7 +18109,7 @@
         <v>59</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F223" s="6">
         <v>6</v>
@@ -18164,70 +18166,70 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V224" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W224" s="48"/>
     </row>
@@ -18245,7 +18247,7 @@
         <v>61</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F225" s="6">
         <v>1</v>
@@ -18302,70 +18304,70 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V226" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W226" s="48"/>
     </row>
@@ -18383,7 +18385,7 @@
         <v>67</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F227" s="6">
         <v>1</v>
@@ -18452,7 +18454,7 @@
         <v>67</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F228" s="6">
         <v>1</v>
@@ -18521,7 +18523,7 @@
         <v>67</v>
       </c>
       <c r="E229" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F229" s="73">
         <v>1</v>
@@ -18578,70 +18580,70 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V230" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W230" s="48"/>
     </row>
@@ -18659,7 +18661,7 @@
         <v>72</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F231" s="6">
         <v>1</v>
@@ -18728,7 +18730,7 @@
         <v>72</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F232" s="6">
         <v>2</v>
@@ -18797,7 +18799,7 @@
         <v>72</v>
       </c>
       <c r="E233" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F233" s="73">
         <v>3</v>
@@ -18866,7 +18868,7 @@
         <v>72</v>
       </c>
       <c r="E234" s="78" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F234" s="78">
         <v>4</v>
@@ -18923,70 +18925,70 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V235" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W235" s="48"/>
     </row>
@@ -19004,7 +19006,7 @@
         <v>76</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F236" s="6">
         <v>1</v>
@@ -19061,70 +19063,70 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V237" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W237" s="48"/>
     </row>
@@ -19142,7 +19144,7 @@
         <v>79</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F238" s="6">
         <v>1</v>
@@ -19211,7 +19213,7 @@
         <v>79</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F239" s="6">
         <v>2</v>
@@ -19280,7 +19282,7 @@
         <v>79</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F240" s="6">
         <v>3</v>
@@ -19337,70 +19339,70 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V241" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W241" s="48"/>
     </row>
@@ -19418,7 +19420,7 @@
         <v>93</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F242" s="6">
         <v>1</v>
@@ -19487,7 +19489,7 @@
         <v>93</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F243" s="6">
         <v>2</v>
@@ -19556,7 +19558,7 @@
         <v>93</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F244" s="6">
         <v>3</v>
@@ -19613,70 +19615,70 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V245" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W245" s="48"/>
     </row>
@@ -19694,7 +19696,7 @@
         <v>81</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F246" s="6">
         <v>1</v>
@@ -19763,7 +19765,7 @@
         <v>81</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F247" s="6">
         <v>1</v>
@@ -19834,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F248" s="6">
         <v>1</v>
@@ -19905,7 +19907,7 @@
         <v>81</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F249" s="6">
         <v>1</v>
@@ -19976,7 +19978,7 @@
         <v>81</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F250" s="6">
         <v>1</v>
@@ -20047,7 +20049,7 @@
         <v>81</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F251" s="6">
         <v>1</v>
@@ -20106,70 +20108,70 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V252" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W252" s="48"/>
     </row>
@@ -20187,7 +20189,7 @@
         <v>87</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F253" s="6">
         <v>1</v>
@@ -20256,7 +20258,7 @@
         <v>87</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F254" s="6">
         <v>2</v>
@@ -20325,7 +20327,7 @@
         <v>87</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F255" s="6">
         <v>3</v>
@@ -20394,7 +20396,7 @@
         <v>87</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F256" s="6">
         <v>4</v>
@@ -20463,7 +20465,7 @@
         <v>87</v>
       </c>
       <c r="E257" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F257" s="73">
         <v>5</v>
@@ -20532,7 +20534,7 @@
         <v>87</v>
       </c>
       <c r="E258" s="73" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F258" s="73">
         <v>6</v>
@@ -20589,70 +20591,70 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V259" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W259" s="48"/>
     </row>
@@ -20670,7 +20672,7 @@
         <v>92</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F260" s="6">
         <v>1</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AD47716-537A-4A22-BB21-1E2F6F378D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{458BC4D3-B259-4146-BE7D-C6565AD9B8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="76740" windowHeight="29895" xr2:uid="{75AC79F8-51D6-451A-BA5E-F59182317FA2}"/>
+    <workbookView xWindow="0" yWindow="1170" windowWidth="76740" windowHeight="29895" xr2:uid="{ABD13070-944B-4C96-89F5-E5D4D5548C69}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1364,7 +1364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB15EA63-138B-483C-BECA-67C4905E8192}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E38054-2EAC-4B8A-97D1-C6E85A881457}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13258,7 +13258,7 @@
         <v>32.250489236790607</v>
       </c>
       <c r="R152" s="75">
-        <v>8300</v>
+        <v>8299.9500000000007</v>
       </c>
       <c r="S152" s="17">
         <v>43631</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{458BC4D3-B259-4146-BE7D-C6565AD9B8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60B5315B-A78F-4A95-9323-D9515CD2AC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1170" windowWidth="76740" windowHeight="29895" xr2:uid="{ABD13070-944B-4C96-89F5-E5D4D5548C69}"/>
+    <workbookView xWindow="0" yWindow="2505" windowWidth="76740" windowHeight="29895" xr2:uid="{7836C6DC-3EDD-4328-AF62-4D3841D4D0AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -473,7 +473,7 @@
     <t>203_Apt</t>
   </si>
   <si>
-    <t>Alan DiEsso</t>
+    <t>Gary DiEsso</t>
   </si>
   <si>
     <t>ID</t>
@@ -581,7 +581,7 @@
     <t>1280 Springfield_202_Apt_VACANT_6</t>
   </si>
   <si>
-    <t>1280 Springfield_203_Apt_Alan DiEsso</t>
+    <t>1280 Springfield_203_Apt_Gary DiEsso</t>
   </si>
   <si>
     <t>114 Central_102_Nabig Sakr</t>
@@ -1364,7 +1364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E38054-2EAC-4B8A-97D1-C6E85A881457}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184512F1-06E0-462E-BFCD-6356E62C4150}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2184,7 +2184,7 @@
         <v>66</v>
       </c>
       <c r="AT15" s="32">
-        <v>28.066666666666666</v>
+        <v>28.033333333333335</v>
       </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
@@ -2485,13 +2485,13 @@
         <v>-10.571254319983737</v>
       </c>
       <c r="W18" s="17">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="X18" s="17">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Y18" s="17">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="Z18" s="18"/>
       <c r="AA18" s="19" t="s">
@@ -2989,13 +2989,13 @@
         <v>66</v>
       </c>
       <c r="AN22" s="32">
-        <v>28.066666666666666</v>
+        <v>28.033333333333335</v>
       </c>
       <c r="AS22" s="25" t="s">
         <v>66</v>
       </c>
       <c r="AT22" s="41">
-        <v>4.9000000000000004</v>
+        <v>4.8666666666666663</v>
       </c>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
@@ -13258,7 +13258,7 @@
         <v>32.250489236790607</v>
       </c>
       <c r="R152" s="75">
-        <v>8299.9500000000007</v>
+        <v>8300</v>
       </c>
       <c r="S152" s="17">
         <v>43631</v>
@@ -19021,10 +19021,10 @@
         <v>1</v>
       </c>
       <c r="G236" s="97">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H236" s="97">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="I236" s="11">
         <v>0</v>
@@ -19057,13 +19057,13 @@
         <v>0</v>
       </c>
       <c r="S236" s="74">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="T236" s="74">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="U236" s="74">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="V236" s="14">
         <v>0</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60B5315B-A78F-4A95-9323-D9515CD2AC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54109B08-E85C-4C40-AC19-E2ABA2965B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2505" windowWidth="76740" windowHeight="29895" xr2:uid="{7836C6DC-3EDD-4328-AF62-4D3841D4D0AC}"/>
+    <workbookView xWindow="0" yWindow="2505" windowWidth="76740" windowHeight="29895" xr2:uid="{AA865F56-9907-4CCB-98DA-821957C2BF23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1364,7 +1364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184512F1-06E0-462E-BFCD-6356E62C4150}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD7EC12-EF6E-4A06-AA24-D161A1B68BBA}">
   <dimension ref="A1:AW260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13258,7 +13258,7 @@
         <v>32.250489236790607</v>
       </c>
       <c r="R152" s="75">
-        <v>8300</v>
+        <v>8299.9500000000007</v>
       </c>
       <c r="S152" s="17">
         <v>43631</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26711B88-8415-4F79-8D24-5286C2BB357F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C35D5FE7-5C03-4483-A71C-F4A8F6442E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="2505" windowWidth="56400" windowHeight="29895" xr2:uid="{7A321B7E-018A-4423-AAE2-A9BCD4FB6406}"/>
+    <workbookView xWindow="1200" yWindow="2505" windowWidth="56400" windowHeight="29895" xr2:uid="{315CDE70-047F-4E1E-9E2C-A2F9F7222378}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -628,7 +628,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -696,7 +696,6 @@
     <xf numFmtId="44" fontId="2" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -1034,7 +1033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A85AC4B-68A9-41CE-9691-6468B00C91F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B787EC-957D-4A2C-9B3C-BF22C0723396}">
   <dimension ref="A1:AI261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4324,7 +4323,7 @@
       <c r="F47" s="6">
         <v>1</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="36">
         <v>45566</v>
       </c>
       <c r="H47" s="36">
@@ -5846,7 +5845,7 @@
         <v>0.05</v>
       </c>
       <c r="J68" s="12">
-        <v>8775</v>
+        <v>8755</v>
       </c>
       <c r="K68" s="12">
         <v>105300</v>
@@ -5870,7 +5869,7 @@
         <v>25.077399380804952</v>
       </c>
       <c r="R68" s="12">
-        <v>17550</v>
+        <v>17510</v>
       </c>
       <c r="S68" s="36">
         <v>38504</v>
@@ -5879,7 +5878,7 @@
         <v>38504</v>
       </c>
       <c r="U68" s="36">
-        <v>47543</v>
+        <v>47542</v>
       </c>
       <c r="V68" s="12">
         <v>0</v>
@@ -5915,7 +5914,7 @@
         <v>46446</v>
       </c>
       <c r="I69" s="9">
-        <v>5.4131054131054235E-2</v>
+        <v>5.6539120502570039E-2</v>
       </c>
       <c r="J69" s="12">
         <v>9250</v>
@@ -5951,7 +5950,7 @@
         <v>38504</v>
       </c>
       <c r="U69" s="15">
-        <v>47543</v>
+        <v>47542</v>
       </c>
       <c r="V69" s="12">
         <v>0</v>
@@ -6023,7 +6022,7 @@
         <v>38504</v>
       </c>
       <c r="U70" s="15">
-        <v>47543</v>
+        <v>47542</v>
       </c>
       <c r="V70" s="12">
         <v>0</v>
@@ -6056,7 +6055,7 @@
         <v>46813</v>
       </c>
       <c r="H71" s="15">
-        <v>47178</v>
+        <v>47177</v>
       </c>
       <c r="I71" s="9">
         <v>5.0000514800514706E-2</v>
@@ -6095,7 +6094,7 @@
         <v>38504</v>
       </c>
       <c r="U71" s="15">
-        <v>47543</v>
+        <v>47542</v>
       </c>
       <c r="V71" s="12">
         <v>0</v>
@@ -6125,10 +6124,10 @@
         <v>5</v>
       </c>
       <c r="G72" s="15">
-        <v>47179</v>
+        <v>47178</v>
       </c>
       <c r="H72" s="15">
-        <v>47543</v>
+        <v>47542</v>
       </c>
       <c r="I72" s="9">
         <v>4.9999362628246669E-2</v>
@@ -6167,7 +6166,7 @@
         <v>38504</v>
       </c>
       <c r="U72" s="15">
-        <v>47543</v>
+        <v>47542</v>
       </c>
       <c r="V72" s="12">
         <v>0</v>
@@ -11092,10 +11091,10 @@
       <c r="F141" s="6">
         <v>2</v>
       </c>
-      <c r="G141" s="15">
+      <c r="G141" s="36">
         <v>45078</v>
       </c>
-      <c r="H141" s="15">
+      <c r="H141" s="36">
         <v>45443</v>
       </c>
       <c r="I141" s="9">
@@ -11164,10 +11163,10 @@
       <c r="F142" s="6">
         <v>3</v>
       </c>
-      <c r="G142" s="15">
+      <c r="G142" s="36">
         <v>45444</v>
       </c>
-      <c r="H142" s="15">
+      <c r="H142" s="36">
         <v>45808</v>
       </c>
       <c r="I142" s="9">
@@ -11236,10 +11235,10 @@
       <c r="F143" s="6">
         <v>4</v>
       </c>
-      <c r="G143" s="15">
+      <c r="G143" s="36">
         <v>45809</v>
       </c>
-      <c r="H143" s="15">
+      <c r="H143" s="36">
         <v>46173</v>
       </c>
       <c r="I143" s="9">
@@ -11308,10 +11307,10 @@
       <c r="F144" s="6">
         <v>5</v>
       </c>
-      <c r="G144" s="15">
+      <c r="G144" s="36">
         <v>46174</v>
       </c>
-      <c r="H144" s="15">
+      <c r="H144" s="36">
         <v>46538</v>
       </c>
       <c r="I144" s="9">
@@ -11741,10 +11740,10 @@
       <c r="F150" s="6">
         <v>5</v>
       </c>
-      <c r="G150" s="36">
+      <c r="G150" s="15">
         <v>46692</v>
       </c>
-      <c r="H150" s="36">
+      <c r="H150" s="15">
         <v>46706</v>
       </c>
       <c r="I150" s="9">
@@ -15846,7 +15845,7 @@
       <c r="G207" s="15">
         <v>46661</v>
       </c>
-      <c r="H207" s="36">
+      <c r="H207" s="15">
         <v>46810</v>
       </c>
       <c r="I207" s="9">
@@ -15919,7 +15918,7 @@
         <v>46811</v>
       </c>
       <c r="H208" s="39">
-        <v>47176</v>
+        <v>47177</v>
       </c>
       <c r="I208" s="40">
         <v>3.0174399212185676E-2</v>
@@ -15988,10 +15987,10 @@
         <v>8</v>
       </c>
       <c r="G209" s="39">
-        <v>47177</v>
+        <v>47178</v>
       </c>
       <c r="H209" s="39">
-        <v>47541</v>
+        <v>47542</v>
       </c>
       <c r="I209" s="40">
         <v>2.9829290206648595E-2</v>
@@ -16060,10 +16059,10 @@
         <v>9</v>
       </c>
       <c r="G210" s="39">
-        <v>47542</v>
+        <v>47543</v>
       </c>
       <c r="H210" s="39">
-        <v>47906</v>
+        <v>47907</v>
       </c>
       <c r="I210" s="40">
         <v>3.0012214273250848E-2</v>
@@ -16132,10 +16131,10 @@
         <v>10</v>
       </c>
       <c r="G211" s="39">
-        <v>47907</v>
+        <v>47908</v>
       </c>
       <c r="H211" s="39">
-        <v>48271</v>
+        <v>48273</v>
       </c>
       <c r="I211" s="40">
         <v>2.9984753515161611E-2</v>
@@ -16204,10 +16203,10 @@
         <v>11</v>
       </c>
       <c r="G212" s="39">
-        <v>48272</v>
+        <v>48274</v>
       </c>
       <c r="H212" s="39">
-        <v>48637</v>
+        <v>48638</v>
       </c>
       <c r="I212" s="40">
         <v>3.0098684210526416E-2</v>
@@ -16276,10 +16275,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="44">
-        <v>48638</v>
+        <v>48639</v>
       </c>
       <c r="H213" s="44">
-        <v>49002</v>
+        <v>49003</v>
       </c>
       <c r="I213" s="45">
         <v>2.0000000000000018E-2</v>
@@ -16348,10 +16347,10 @@
         <v>13</v>
       </c>
       <c r="G214" s="44">
-        <v>49003</v>
+        <v>49004</v>
       </c>
       <c r="H214" s="44">
-        <v>49367</v>
+        <v>49368</v>
       </c>
       <c r="I214" s="45">
         <v>2.0000000000000018E-2</v>
@@ -16420,10 +16419,10 @@
         <v>14</v>
       </c>
       <c r="G215" s="44">
-        <v>49368</v>
+        <v>49369</v>
       </c>
       <c r="H215" s="44">
-        <v>49732</v>
+        <v>49734</v>
       </c>
       <c r="I215" s="45">
         <v>2.0000000000000018E-2</v>
@@ -16492,10 +16491,10 @@
         <v>15</v>
       </c>
       <c r="G216" s="44">
-        <v>49733</v>
+        <v>49735</v>
       </c>
       <c r="H216" s="44">
-        <v>50098</v>
+        <v>50099</v>
       </c>
       <c r="I216" s="45">
         <v>2.0000000000000018E-2</v>
@@ -16564,10 +16563,10 @@
         <v>16</v>
       </c>
       <c r="G217" s="44">
-        <v>50099</v>
+        <v>50100</v>
       </c>
       <c r="H217" s="44">
-        <v>50463</v>
+        <v>50464</v>
       </c>
       <c r="I217" s="45">
         <v>2.0000000000000018E-2</v>
@@ -18003,10 +18002,10 @@
       <c r="F237" s="6">
         <v>1</v>
       </c>
-      <c r="G237" s="59">
+      <c r="G237" s="36">
         <v>46158</v>
       </c>
-      <c r="H237" s="59">
+      <c r="H237" s="36">
         <v>46158</v>
       </c>
       <c r="I237" s="9">
@@ -18795,10 +18794,10 @@
       <c r="F248" s="6">
         <v>1</v>
       </c>
-      <c r="G248" s="15">
+      <c r="G248" s="36">
         <v>46143</v>
       </c>
-      <c r="H248" s="15">
+      <c r="H248" s="36">
         <v>46507</v>
       </c>
       <c r="I248" s="9">
@@ -18843,7 +18842,7 @@
       <c r="V248" s="12">
         <v>0</v>
       </c>
-      <c r="W248" s="60">
+      <c r="W248" s="59">
         <v>46417</v>
       </c>
       <c r="Z248" s="4"/>
@@ -18869,10 +18868,10 @@
       <c r="F249" s="6">
         <v>1</v>
       </c>
-      <c r="G249" s="15">
+      <c r="G249" s="36">
         <v>46508</v>
       </c>
-      <c r="H249" s="15">
+      <c r="H249" s="36">
         <v>46873</v>
       </c>
       <c r="I249" s="9">
@@ -18917,7 +18916,7 @@
       <c r="V249" s="12">
         <v>0</v>
       </c>
-      <c r="W249" s="60">
+      <c r="W249" s="59">
         <v>46783</v>
       </c>
       <c r="Z249" s="4"/>
@@ -18943,10 +18942,10 @@
       <c r="F250" s="6">
         <v>1</v>
       </c>
-      <c r="G250" s="15">
+      <c r="G250" s="36">
         <v>46874</v>
       </c>
-      <c r="H250" s="15">
+      <c r="H250" s="36">
         <v>47238</v>
       </c>
       <c r="I250" s="9">
@@ -18991,7 +18990,7 @@
       <c r="V250" s="12">
         <v>0</v>
       </c>
-      <c r="W250" s="60">
+      <c r="W250" s="59">
         <v>47148</v>
       </c>
       <c r="Z250" s="4"/>
@@ -19017,10 +19016,10 @@
       <c r="F251" s="6">
         <v>1</v>
       </c>
-      <c r="G251" s="15">
+      <c r="G251" s="36">
         <v>47239</v>
       </c>
-      <c r="H251" s="15">
+      <c r="H251" s="36">
         <v>47603</v>
       </c>
       <c r="I251" s="9">
@@ -19065,7 +19064,7 @@
       <c r="V251" s="12">
         <v>0</v>
       </c>
-      <c r="W251" s="60">
+      <c r="W251" s="59">
         <v>47513</v>
       </c>
       <c r="Z251" s="4"/>
@@ -19091,10 +19090,10 @@
       <c r="F252" s="6">
         <v>1</v>
       </c>
-      <c r="G252" s="15">
+      <c r="G252" s="36">
         <v>47604</v>
       </c>
-      <c r="H252" s="15">
+      <c r="H252" s="36">
         <v>47968</v>
       </c>
       <c r="I252" s="9">
@@ -19139,7 +19138,7 @@
       <c r="V252" s="12">
         <v>0</v>
       </c>
-      <c r="W252" s="60">
+      <c r="W252" s="59">
         <v>47878</v>
       </c>
       <c r="Z252" s="4"/>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{432208CB-A5AB-48D5-B6BE-8CE5A58873AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBCA2DA9-5B07-408A-9BDD-E50F8AB69296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2505" windowWidth="102195" windowHeight="29895" xr2:uid="{376DE17B-4BB9-463B-8B69-86970228FA31}"/>
+    <workbookView xWindow="0" yWindow="1560" windowWidth="102195" windowHeight="29895" xr2:uid="{FDF07004-B17F-4383-9650-38929DE4C458}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="271">
   <si>
     <t>Building</t>
   </si>
@@ -425,126 +425,90 @@
     <t>YES - STRONG EXCLUSIVE</t>
   </si>
   <si>
+    <t>200% of last months rent</t>
+  </si>
+  <si>
+    <t>Easement</t>
+  </si>
+  <si>
+    <t>HDR Holdings LLC d/b/a Wonder</t>
+  </si>
+  <si>
+    <t>36 South1</t>
+  </si>
+  <si>
+    <t>Two 5-Year 3% Annual Inc; 2nd Fl Non-Comp</t>
+  </si>
+  <si>
+    <t>Two (2) x 60 months</t>
+  </si>
+  <si>
+    <t>YES - Does not apply to existing 2nd floor</t>
+  </si>
+  <si>
+    <t>60.00% of building CAM (NNN)</t>
+  </si>
+  <si>
+    <t>5% after 5th</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alcohol sales permitted</t>
+  </si>
+  <si>
+    <t>Longo Architects &amp; Associates, LLC</t>
+  </si>
+  <si>
+    <t>36 South2</t>
+  </si>
+  <si>
+    <t>YES - Vincent Wolk</t>
+  </si>
+  <si>
+    <t>250% of highest rent</t>
+  </si>
+  <si>
+    <t>Landlord may install exterior elevator/stairwel</t>
+  </si>
+  <si>
+    <t>Roof</t>
+  </si>
+  <si>
+    <t>Verizon</t>
+  </si>
+  <si>
+    <t>36 South3</t>
+  </si>
+  <si>
+    <t>Four (4) x 5-year AUTO-RENEWALS (no notice needed)</t>
+  </si>
+  <si>
+    <t>Annual termination on any anniversary w/ 90 days</t>
+  </si>
+  <si>
+    <t>Electric Meter</t>
+  </si>
+  <si>
+    <t>ROFR</t>
+  </si>
+  <si>
+    <t>Equipment removal within 30 days. 24/7 access</t>
+  </si>
+  <si>
+    <t>George's Appliance, LLC</t>
+  </si>
+  <si>
+    <t>1280 Springfield1</t>
+  </si>
+  <si>
+    <t>3.0% Annual</t>
+  </si>
+  <si>
+    <t>One (1) x 60-month option (exercised per 2021 modification). 12 months notice. Rent: $2,485-$2,797/mo with 3% annual. Landlord may deny to assignee/sublessee.</t>
+  </si>
+  <si>
     <t>None</t>
   </si>
   <si>
-    <t>200% of last months rent</t>
-  </si>
-  <si>
-    <t>Easement</t>
-  </si>
-  <si>
-    <t>HDR Holdings LLC d/b/a Wonder</t>
-  </si>
-  <si>
-    <t>36 South1</t>
-  </si>
-  <si>
-    <t>Two 5-Year 3% Annual Inc; 2nd Fl Non-Comp</t>
-  </si>
-  <si>
-    <t>Two (2) x 60 months. Opt 1: $19,571/mo + 3%/yr. Opt 2: $22,688/mo + 3%/yr.</t>
-  </si>
-  <si>
-    <t>May terminate if: (1) premises not delivered within 90 days; (2) permits not obtained within 180 days; (3) Certificate of Approval not obtained within 90 days.</t>
-  </si>
-  <si>
-    <t>YES - EXCLUSIVE USE: Landlord cannot permit any other tenant whose primary use is multi-cuisine restaurant (3+ cuisines). Does not apply to existing 2nd floor tenants.</t>
-  </si>
-  <si>
-    <t>60% pro rata share of building/property expenses. Excludes capital expenses, 2nd floor costs, depreciation, mortgage, income taxes, Landlord salaries.</t>
-  </si>
-  <si>
-    <t>Consent required (not unreasonably withheld). Permitted transfers: mergers (3+ locations), affiliates, concurrent 2+ lease assignments. $2,000 + $3,000 attorney.</t>
-  </si>
-  <si>
-    <t>YES - Separate Guarantee of Lease executed 3/4/24. Guarantor identity in separate document.</t>
-  </si>
-  <si>
-    <t>150% of highest rent + additional rent</t>
-  </si>
-  <si>
-    <t>5% after 5th</t>
-  </si>
-  <si>
-    <t>6-month free rent. 25% daily rent abatement if Phase 2 power not done within 270 days. 2-day credit per day Landlord delayed beyond 90 days. Alcohol sales permitted. 10-business-day estoppel (max 2x/year). Emergency self-help for tenant.</t>
-  </si>
-  <si>
-    <t>Longo Architects &amp; Associates, LLC</t>
-  </si>
-  <si>
-    <t>36 South2</t>
-  </si>
-  <si>
-    <t>Original 36-month option superseded by direct extension. No further options.</t>
-  </si>
-  <si>
-    <t>YES - Mutual one-time cancellation: 270 days notice by June 1, 2026. Tenant responsible for rent through Feb 28, 2027. Tenant previously exercised cancellation but renegotiated.</t>
-  </si>
-  <si>
-    <t>None - Gross. Tenant pays own utilities ($350/mo if no independent meter).</t>
-  </si>
-  <si>
-    <t>Consent required (not unreasonably withheld). $2,000 + $3,000 attorney. Excess sublease per SF formula.</t>
-  </si>
-  <si>
-    <t>YES - Vincent Wolk personal guaranty. Full term + option. Terminates on approved assignment.</t>
-  </si>
-  <si>
-    <t>250% of highest rent (punitive)</t>
-  </si>
-  <si>
-    <t>10% after 5th (no grace)</t>
-  </si>
-  <si>
-    <t>Landlord may install exterior elevator/stairwell. Up to 24 parking spots for specific tenant. Access easement for 44 South St. Free rent July 2025 (clawback if early termination). Tenant responsible for roof. 3-day estoppel.</t>
-  </si>
-  <si>
-    <t>Roof</t>
-  </si>
-  <si>
-    <t>Verizon</t>
-  </si>
-  <si>
-    <t>36 South3</t>
-  </si>
-  <si>
-    <t>Four (4) x 5-year AUTO-RENEWALS (no notice needed). Only terminates if Lessee gives 3 months notice.</t>
-  </si>
-  <si>
-    <t>Two 5-Year 7.5% Jump then Flat</t>
-  </si>
-  <si>
-    <t>YES - Annual termination on any anniversary with 3 months notice. Also: if govt approvals rejected/canceled.</t>
-  </si>
-  <si>
-    <t>None explicit</t>
-  </si>
-  <si>
-    <t>None - flat annual rent.</t>
-  </si>
-  <si>
-    <t>YES - ROFR: If Landlord grants 3rd party easement/interest for communications in Lessees area, Lessee has 30-day ROFR to match.</t>
-  </si>
-  <si>
-    <t>May assign without consent to affiliates/subsidiaries or acquirer of all assets in market. Others need consent (not unreasonably withheld).</t>
-  </si>
-  <si>
-    <t>ROFR for competing communications facilities. Sale of property must be subject to agreement. Equipment removal within 30 days. 24/7 access. Memorandum of Lease recorded.</t>
-  </si>
-  <si>
-    <t>George's Appliance, LLC</t>
-  </si>
-  <si>
-    <t>1280 Springfield1</t>
-  </si>
-  <si>
-    <t>3.0% Annual</t>
-  </si>
-  <si>
-    <t>One (1) x 60-month option (exercised per 2021 modification). 12 months notice. Rent: $2,485-$2,797/mo with 3% annual. Landlord may deny to assignee/sublessee.</t>
-  </si>
-  <si>
     <t>None for tenant. Landlord may terminate on default (5 days notice).</t>
   </si>
   <si>
@@ -681,9 +645,6 @@
   </si>
   <si>
     <t>YES - Viviana Gago AND David Gago. Full term. Terminates on approved assignment.</t>
-  </si>
-  <si>
-    <t>250% of highest rent</t>
   </si>
   <si>
     <t>Pays 39% of 2nd floor gas. HVAC service contract required. Force majeure includes pandemic. Waiver of jury trial.</t>
@@ -1452,7 +1413,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D17375-3888-402F-A980-AB662670E6BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ABAA3C7-CD82-41F9-B815-45CFFD03204D}">
   <dimension ref="A1:AT261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3553,15 +3514,13 @@
       <c r="AN26" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="AO26" s="20" t="s">
-        <v>128</v>
-      </c>
+      <c r="AO26" s="20"/>
       <c r="AP26" s="20" t="s">
         <v>64</v>
       </c>
       <c r="AQ26" s="20"/>
       <c r="AR26" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AS26" s="20"/>
       <c r="AT26" s="20"/>
@@ -3571,13 +3530,13 @@
         <v>7</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E27" s="6">
         <v>1</v>
@@ -3732,7 +3691,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>54</v>
@@ -3741,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
@@ -3809,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AE29" s="13">
         <v>15</v>
@@ -3824,38 +3783,34 @@
         <v>16933.333333333332</v>
       </c>
       <c r="AI29" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AJ29" s="18">
         <v>48854</v>
       </c>
-      <c r="AK29" s="20" t="s">
-        <v>135</v>
-      </c>
+      <c r="AK29" s="20"/>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN29" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="AO29" s="20"/>
+      <c r="AP29" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ29" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR29" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="AS29" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="AN29" s="20" t="s">
+      <c r="AT29" s="20" t="s">
         <v>137</v>
-      </c>
-      <c r="AO29" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP29" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="AQ29" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="AR29" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="AS29" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="AT29" s="20" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:46" x14ac:dyDescent="0.25">
@@ -3866,7 +3821,7 @@
         <v>201</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>80</v>
@@ -3875,7 +3830,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
@@ -3953,39 +3908,29 @@
       <c r="AH30" s="7">
         <v>8747.9166666666661</v>
       </c>
-      <c r="AI30" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="AJ30" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK30" s="20" t="s">
-        <v>146</v>
-      </c>
+      <c r="AI30" s="20"/>
+      <c r="AJ30" s="23"/>
+      <c r="AK30" s="20"/>
       <c r="AL30" s="20"/>
-      <c r="AM30" s="20" t="s">
-        <v>128</v>
-      </c>
+      <c r="AM30" s="20"/>
       <c r="AN30" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO30" s="20" t="s">
-        <v>128</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="AO30" s="20"/>
       <c r="AP30" s="20" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="AQ30" s="20" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="AR30" s="20" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="AS30" s="20" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="AT30" s="20" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:46" x14ac:dyDescent="0.25">
@@ -3993,19 +3938,19 @@
         <v>8</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E31" s="6">
         <v>3</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
@@ -4082,38 +4027,30 @@
         <v>0</v>
       </c>
       <c r="AI31" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="AJ31" s="23" t="s">
-        <v>157</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="AJ31" s="23"/>
       <c r="AK31" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="AL31" s="20"/>
-      <c r="AM31" s="20" t="s">
-        <v>159</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="AL31" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM31" s="20"/>
       <c r="AN31" s="20" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AO31" s="20" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="AP31" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="AQ31" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR31" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS31" s="20" t="s">
-        <v>77</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="AQ31" s="20"/>
+      <c r="AR31" s="20"/>
+      <c r="AS31" s="20"/>
       <c r="AT31" s="20" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:46" x14ac:dyDescent="0.25">
@@ -4121,19 +4058,19 @@
         <v>8</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
@@ -4207,38 +4144,18 @@
       <c r="AH32" s="7">
         <v>0</v>
       </c>
-      <c r="AI32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="AI32" s="20"/>
       <c r="AJ32" s="23"/>
-      <c r="AK32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="AK32" s="20"/>
       <c r="AL32" s="20"/>
-      <c r="AM32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT32" s="20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="AM32" s="20"/>
+      <c r="AN32" s="20"/>
+      <c r="AO32" s="20"/>
+      <c r="AP32" s="20"/>
+      <c r="AQ32" s="20"/>
+      <c r="AR32" s="20"/>
+      <c r="AS32" s="20"/>
+      <c r="AT32" s="20"/>
     </row>
     <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
@@ -4302,7 +4219,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>54</v>
@@ -4311,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
@@ -4369,7 +4286,7 @@
         <v>46538</v>
       </c>
       <c r="Z34" s="36" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="AA34" s="23"/>
       <c r="AB34" s="19">
@@ -4390,38 +4307,38 @@
         <v>3004.1666666666665</v>
       </c>
       <c r="AI34" s="20" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="AJ34" s="23" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AK34" s="20" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AN34" s="20" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="AO34" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AP34" s="20" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="AQ34" s="20" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="AR34" s="20" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="AS34" s="20" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="AT34" s="20" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:46" x14ac:dyDescent="0.25">
@@ -4432,7 +4349,7 @@
         <v>102</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>54</v>
@@ -4441,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6">
@@ -4499,7 +4416,7 @@
         <v>46706</v>
       </c>
       <c r="Z35" s="36" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="AA35" s="23"/>
       <c r="AB35" s="19">
@@ -4520,38 +4437,38 @@
         <v>4150</v>
       </c>
       <c r="AI35" s="20" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="AJ35" s="23" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AK35" s="20" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="AN35" s="20" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="AO35" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AP35" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="AQ35" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AR35" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="AS35" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="AQ35" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="AR35" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="AS35" s="20" t="s">
-        <v>183</v>
-      </c>
       <c r="AT35" s="20" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:46" x14ac:dyDescent="0.25">
@@ -4562,7 +4479,7 @@
         <v>103</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>54</v>
@@ -4571,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6">
@@ -4629,7 +4546,7 @@
         <v>47299</v>
       </c>
       <c r="Z36" s="36" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="AA36" s="23"/>
       <c r="AB36" s="19">
@@ -4650,38 +4567,38 @@
         <v>6387.5</v>
       </c>
       <c r="AI36" s="20" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="AJ36" s="23" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AK36" s="20" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AN36" s="20" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="AO36" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AP36" s="20" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AQ36" s="20" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="AR36" s="20" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="AS36" s="20" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="AT36" s="20" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:46" x14ac:dyDescent="0.25">
@@ -4692,7 +4609,7 @@
         <v>104</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>54</v>
@@ -4701,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6">
@@ -4759,7 +4676,7 @@
         <v>47573</v>
       </c>
       <c r="Z37" s="36" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="AA37" s="23"/>
       <c r="AB37" s="19">
@@ -4780,38 +4697,38 @@
         <v>10450</v>
       </c>
       <c r="AI37" s="20" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="AJ37" s="23" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="AK37" s="20" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="AN37" s="20" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="AO37" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AP37" s="20" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="AQ37" s="20" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="AR37" s="20" t="s">
         <v>109</v>
       </c>
       <c r="AS37" s="20" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="AT37" s="20" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
@@ -4822,16 +4739,16 @@
         <v>201</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E38" s="6">
         <v>2</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6">
@@ -4889,7 +4806,7 @@
         <v>46996</v>
       </c>
       <c r="Z38" s="36" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="AA38" s="18"/>
       <c r="AB38" s="19">
@@ -4897,7 +4814,7 @@
       </c>
       <c r="AC38" s="19"/>
       <c r="AD38" s="23" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="AE38" s="13">
         <v>0</v>
@@ -4912,38 +4829,38 @@
         <v>2477.0833333333335</v>
       </c>
       <c r="AI38" s="20" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="AJ38" s="18">
         <v>46816</v>
       </c>
       <c r="AK38" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AN38" s="20" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="AO38" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AP38" s="20" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="AQ38" s="20" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="AR38" s="20" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="AS38" s="20" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="AT38" s="20" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:46" x14ac:dyDescent="0.25">
@@ -4951,19 +4868,19 @@
         <v>9</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E39" s="6">
         <v>2</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6">
@@ -5021,7 +4938,7 @@
         <v>45626</v>
       </c>
       <c r="Z39" s="36" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AA39" s="23"/>
       <c r="AB39" s="19">
@@ -5044,38 +4961,38 @@
         <v>2679.1666666666665</v>
       </c>
       <c r="AI39" s="20" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="AJ39" s="23" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AK39" s="20" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="AL39" s="20"/>
       <c r="AM39" s="20" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AN39" s="20" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="AO39" s="20" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AP39" s="20" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="AQ39" s="20" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="AR39" s="20" t="s">
         <v>77</v>
       </c>
       <c r="AS39" s="20" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="AT39" s="20" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:46" x14ac:dyDescent="0.25">
@@ -5083,19 +5000,19 @@
         <v>9</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6">
@@ -5153,7 +5070,7 @@
         <v>45626</v>
       </c>
       <c r="Z40" s="36" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AA40" s="23"/>
       <c r="AB40" s="19">
@@ -5176,38 +5093,38 @@
         <v>1614.5833333333333</v>
       </c>
       <c r="AI40" s="20" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="AJ40" s="23" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AK40" s="20" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="AN40" s="20" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="AO40" s="20" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="AP40" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="AQ40" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="AR40" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="AS40" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="AT40" s="20" t="s">
         <v>223</v>
-      </c>
-      <c r="AQ40" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="AR40" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS40" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="AT40" s="20" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="41" spans="1:46" x14ac:dyDescent="0.25">
@@ -5293,46 +5210,46 @@
     </row>
     <row r="45" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="N45" s="38" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="O45" s="38" t="s">
         <v>14</v>
@@ -5341,10 +5258,10 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>31</v>
@@ -5359,7 +5276,7 @@
         <v>36</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="Z45" s="4"/>
       <c r="AG45" s="5"/>
@@ -5367,7 +5284,7 @@
     </row>
     <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -5376,10 +5293,10 @@
         <v>101</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F46" s="6">
         <v>0</v>
@@ -5439,7 +5356,7 @@
     </row>
     <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
@@ -5448,10 +5365,10 @@
         <v>101</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
@@ -5511,7 +5428,7 @@
     </row>
     <row r="48" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
@@ -5520,10 +5437,10 @@
         <v>101</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F48" s="6">
         <v>2</v>
@@ -5583,7 +5500,7 @@
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
@@ -5592,10 +5509,10 @@
         <v>101</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
@@ -5655,7 +5572,7 @@
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
@@ -5664,10 +5581,10 @@
         <v>101</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F50" s="6">
         <v>4</v>
@@ -5727,7 +5644,7 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
@@ -5736,10 +5653,10 @@
         <v>101</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
@@ -5799,7 +5716,7 @@
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
@@ -5808,10 +5725,10 @@
         <v>101</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
@@ -5871,7 +5788,7 @@
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
@@ -5880,10 +5797,10 @@
         <v>101</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
@@ -5943,7 +5860,7 @@
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>8</v>
@@ -5952,10 +5869,10 @@
         <v>101</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F54" s="6">
         <v>8</v>
@@ -6015,7 +5932,7 @@
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>8</v>
@@ -6024,10 +5941,10 @@
         <v>101</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F55" s="6">
         <v>9</v>
@@ -6087,7 +6004,7 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
@@ -6096,10 +6013,10 @@
         <v>101</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F56" s="6">
         <v>10</v>
@@ -6159,7 +6076,7 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B57" s="41" t="s">
         <v>8</v>
@@ -6168,10 +6085,10 @@
         <v>101</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E57" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F57" s="41">
         <v>11</v>
@@ -6231,7 +6148,7 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="41" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B58" s="41" t="s">
         <v>8</v>
@@ -6240,10 +6157,10 @@
         <v>101</v>
       </c>
       <c r="D58" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E58" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F58" s="41">
         <v>12</v>
@@ -6303,7 +6220,7 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" s="41" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B59" s="41" t="s">
         <v>8</v>
@@ -6312,10 +6229,10 @@
         <v>101</v>
       </c>
       <c r="D59" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E59" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F59" s="41">
         <v>13</v>
@@ -6375,7 +6292,7 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B60" s="41" t="s">
         <v>8</v>
@@ -6384,10 +6301,10 @@
         <v>101</v>
       </c>
       <c r="D60" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E60" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F60" s="41">
         <v>14</v>
@@ -6447,7 +6364,7 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="41" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B61" s="41" t="s">
         <v>8</v>
@@ -6456,10 +6373,10 @@
         <v>101</v>
       </c>
       <c r="D61" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E61" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F61" s="41">
         <v>15</v>
@@ -6519,7 +6436,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="46" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B62" s="46" t="s">
         <v>8</v>
@@ -6528,10 +6445,10 @@
         <v>101</v>
       </c>
       <c r="D62" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F62" s="46">
         <v>16</v>
@@ -6591,7 +6508,7 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="46" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B63" s="46" t="s">
         <v>8</v>
@@ -6600,10 +6517,10 @@
         <v>101</v>
       </c>
       <c r="D63" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E63" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F63" s="46">
         <v>17</v>
@@ -6663,7 +6580,7 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" s="46" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B64" s="46" t="s">
         <v>8</v>
@@ -6672,10 +6589,10 @@
         <v>101</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E64" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F64" s="46">
         <v>18</v>
@@ -6735,7 +6652,7 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65" s="46" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B65" s="46" t="s">
         <v>8</v>
@@ -6744,10 +6661,10 @@
         <v>101</v>
       </c>
       <c r="D65" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E65" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F65" s="46">
         <v>19</v>
@@ -6807,7 +6724,7 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" s="46" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B66" s="46" t="s">
         <v>8</v>
@@ -6816,10 +6733,10 @@
         <v>101</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E66" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F66" s="46">
         <v>20</v>
@@ -6879,70 +6796,70 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V67" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W67" s="31"/>
       <c r="Z67" s="4"/>
@@ -6951,7 +6868,7 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>8</v>
@@ -6960,10 +6877,10 @@
         <v>201</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F68" s="6">
         <v>1</v>
@@ -7023,7 +6940,7 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
@@ -7032,10 +6949,10 @@
         <v>201</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F69" s="6">
         <v>2</v>
@@ -7095,7 +7012,7 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
@@ -7104,10 +7021,10 @@
         <v>201</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F70" s="6">
         <v>3</v>
@@ -7167,7 +7084,7 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
@@ -7176,10 +7093,10 @@
         <v>201</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F71" s="6">
         <v>4</v>
@@ -7239,7 +7156,7 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>8</v>
@@ -7248,10 +7165,10 @@
         <v>201</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6">
         <v>5</v>
@@ -7311,70 +7228,70 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V73" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W73" s="31"/>
       <c r="Z73" s="4"/>
@@ -7383,19 +7300,19 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F74" s="6">
         <v>1</v>
@@ -7455,19 +7372,19 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F75" s="6">
         <v>2</v>
@@ -7527,19 +7444,19 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F76" s="6">
         <v>3</v>
@@ -7599,19 +7516,19 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F77" s="6">
         <v>4</v>
@@ -7671,19 +7588,19 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F78" s="6">
         <v>5</v>
@@ -7743,19 +7660,19 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F79" s="6">
         <v>6</v>
@@ -7815,19 +7732,19 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F80" s="6">
         <v>7</v>
@@ -7887,19 +7804,19 @@
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F81" s="6">
         <v>8</v>
@@ -7959,19 +7876,19 @@
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F82" s="6">
         <v>9</v>
@@ -8031,19 +7948,19 @@
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F83" s="6">
         <v>10</v>
@@ -8103,19 +8020,19 @@
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F84" s="6">
         <v>11</v>
@@ -8175,19 +8092,19 @@
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F85" s="6">
         <v>12</v>
@@ -8247,19 +8164,19 @@
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F86" s="6">
         <v>13</v>
@@ -8319,19 +8236,19 @@
     </row>
     <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F87" s="6">
         <v>14</v>
@@ -8391,70 +8308,70 @@
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V88" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W88" s="31"/>
       <c r="Z88" s="4"/>
@@ -8463,19 +8380,19 @@
     </row>
     <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F89" s="6">
         <v>1</v>
@@ -8535,19 +8452,19 @@
     </row>
     <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F90" s="6">
         <v>2</v>
@@ -8607,19 +8524,19 @@
     </row>
     <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F91" s="6">
         <v>3</v>
@@ -8679,19 +8596,19 @@
     </row>
     <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F92" s="6">
         <v>4</v>
@@ -8751,19 +8668,19 @@
     </row>
     <row r="93" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F93" s="6">
         <v>5</v>
@@ -8823,19 +8740,19 @@
     </row>
     <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F94" s="6">
         <v>6</v>
@@ -8895,19 +8812,19 @@
     </row>
     <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F95" s="6">
         <v>7</v>
@@ -8967,19 +8884,19 @@
     </row>
     <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F96" s="6">
         <v>8</v>
@@ -9039,19 +8956,19 @@
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F97" s="6">
         <v>9</v>
@@ -9111,19 +9028,19 @@
     </row>
     <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F98" s="6">
         <v>10</v>
@@ -9183,19 +9100,19 @@
     </row>
     <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F99" s="6">
         <v>11</v>
@@ -9255,70 +9172,70 @@
     </row>
     <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V100" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W100" s="31"/>
       <c r="Z100" s="4"/>
@@ -9327,7 +9244,7 @@
     </row>
     <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
@@ -9339,7 +9256,7 @@
         <v>114</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F101" s="6">
         <v>1</v>
@@ -9399,7 +9316,7 @@
     </row>
     <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
@@ -9411,7 +9328,7 @@
         <v>114</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F102" s="6">
         <v>2</v>
@@ -9471,7 +9388,7 @@
     </row>
     <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
@@ -9483,7 +9400,7 @@
         <v>114</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F103" s="6">
         <v>3</v>
@@ -9543,7 +9460,7 @@
     </row>
     <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
@@ -9555,7 +9472,7 @@
         <v>114</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F104" s="6">
         <v>4</v>
@@ -9615,7 +9532,7 @@
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -9627,7 +9544,7 @@
         <v>114</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F105" s="6">
         <v>5</v>
@@ -9687,7 +9604,7 @@
     </row>
     <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>7</v>
@@ -9699,7 +9616,7 @@
         <v>114</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F106" s="6">
         <v>6</v>
@@ -9759,7 +9676,7 @@
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>7</v>
@@ -9771,7 +9688,7 @@
         <v>114</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F107" s="6">
         <v>7</v>
@@ -9831,7 +9748,7 @@
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>7</v>
@@ -9843,7 +9760,7 @@
         <v>114</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F108" s="6">
         <v>8</v>
@@ -9903,7 +9820,7 @@
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
@@ -9915,7 +9832,7 @@
         <v>114</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F109" s="6">
         <v>9</v>
@@ -9975,7 +9892,7 @@
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>7</v>
@@ -9987,7 +9904,7 @@
         <v>114</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F110" s="6">
         <v>10</v>
@@ -10047,7 +9964,7 @@
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111" s="41" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B111" s="41" t="s">
         <v>7</v>
@@ -10059,7 +9976,7 @@
         <v>114</v>
       </c>
       <c r="E111" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F111" s="41">
         <v>11</v>
@@ -10119,7 +10036,7 @@
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112" s="41" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B112" s="41" t="s">
         <v>7</v>
@@ -10131,7 +10048,7 @@
         <v>114</v>
       </c>
       <c r="E112" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F112" s="41">
         <v>12</v>
@@ -10191,7 +10108,7 @@
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113" s="41" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B113" s="41" t="s">
         <v>7</v>
@@ -10203,7 +10120,7 @@
         <v>114</v>
       </c>
       <c r="E113" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F113" s="41">
         <v>13</v>
@@ -10263,7 +10180,7 @@
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114" s="41" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B114" s="41" t="s">
         <v>7</v>
@@ -10275,7 +10192,7 @@
         <v>114</v>
       </c>
       <c r="E114" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F114" s="41">
         <v>14</v>
@@ -10335,7 +10252,7 @@
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115" s="41" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B115" s="41" t="s">
         <v>7</v>
@@ -10347,7 +10264,7 @@
         <v>114</v>
       </c>
       <c r="E115" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F115" s="41">
         <v>15</v>
@@ -10407,70 +10324,70 @@
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V116" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W116" s="31"/>
       <c r="Z116" s="4"/>
@@ -10479,7 +10396,7 @@
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>7</v>
@@ -10491,7 +10408,7 @@
         <v>123</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F117" s="6">
         <v>1</v>
@@ -10551,7 +10468,7 @@
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>7</v>
@@ -10563,7 +10480,7 @@
         <v>123</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F118" s="6">
         <v>2</v>
@@ -10623,7 +10540,7 @@
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>7</v>
@@ -10635,7 +10552,7 @@
         <v>123</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F119" s="6">
         <v>3</v>
@@ -10695,7 +10612,7 @@
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>7</v>
@@ -10707,7 +10624,7 @@
         <v>123</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F120" s="6">
         <v>4</v>
@@ -10767,7 +10684,7 @@
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>7</v>
@@ -10779,7 +10696,7 @@
         <v>123</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F121" s="6">
         <v>5</v>
@@ -10839,7 +10756,7 @@
     </row>
     <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122" s="41" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B122" s="41" t="s">
         <v>7</v>
@@ -10851,7 +10768,7 @@
         <v>123</v>
       </c>
       <c r="E122" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F122" s="41">
         <v>6</v>
@@ -10911,7 +10828,7 @@
     </row>
     <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123" s="41" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B123" s="41" t="s">
         <v>7</v>
@@ -10923,7 +10840,7 @@
         <v>123</v>
       </c>
       <c r="E123" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F123" s="41">
         <v>7</v>
@@ -10983,7 +10900,7 @@
     </row>
     <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124" s="41" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B124" s="41" t="s">
         <v>7</v>
@@ -10995,7 +10912,7 @@
         <v>123</v>
       </c>
       <c r="E124" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F124" s="41">
         <v>8</v>
@@ -11055,7 +10972,7 @@
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125" s="41" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B125" s="41" t="s">
         <v>7</v>
@@ -11067,7 +10984,7 @@
         <v>123</v>
       </c>
       <c r="E125" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F125" s="41">
         <v>9</v>
@@ -11127,7 +11044,7 @@
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126" s="41" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B126" s="41" t="s">
         <v>7</v>
@@ -11139,7 +11056,7 @@
         <v>123</v>
       </c>
       <c r="E126" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F126" s="41">
         <v>10</v>
@@ -11199,70 +11116,70 @@
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V127" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W127" s="31"/>
       <c r="Z127" s="4"/>
@@ -11271,19 +11188,19 @@
     </row>
     <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F128" s="6">
         <v>1</v>
@@ -11343,19 +11260,19 @@
     </row>
     <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F129" s="6">
         <v>2</v>
@@ -11415,19 +11332,19 @@
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F130" s="6">
         <v>3</v>
@@ -11487,19 +11404,19 @@
     </row>
     <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F131" s="6">
         <v>4</v>
@@ -11559,19 +11476,19 @@
     </row>
     <row r="132" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F132" s="6">
         <v>5</v>
@@ -11631,19 +11548,19 @@
     </row>
     <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F133" s="6">
         <v>6</v>
@@ -11703,19 +11620,19 @@
     </row>
     <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F134" s="6">
         <v>7</v>
@@ -11775,19 +11692,19 @@
     </row>
     <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F135" s="6">
         <v>8</v>
@@ -11847,19 +11764,19 @@
     </row>
     <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F136" s="6">
         <v>9</v>
@@ -11919,19 +11836,19 @@
     </row>
     <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F137" s="6">
         <v>10</v>
@@ -11991,19 +11908,19 @@
     </row>
     <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F138" s="6">
         <v>11</v>
@@ -12063,70 +11980,70 @@
     </row>
     <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V139" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W139" s="31"/>
       <c r="Z139" s="4"/>
@@ -12135,7 +12052,7 @@
     </row>
     <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>9</v>
@@ -12144,10 +12061,10 @@
         <v>101</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F140" s="6">
         <v>1</v>
@@ -12207,7 +12124,7 @@
     </row>
     <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>9</v>
@@ -12216,10 +12133,10 @@
         <v>101</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F141" s="6">
         <v>2</v>
@@ -12279,7 +12196,7 @@
     </row>
     <row r="142" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>9</v>
@@ -12288,10 +12205,10 @@
         <v>101</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F142" s="6">
         <v>3</v>
@@ -12351,7 +12268,7 @@
     </row>
     <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>9</v>
@@ -12360,10 +12277,10 @@
         <v>101</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F143" s="6">
         <v>4</v>
@@ -12423,7 +12340,7 @@
     </row>
     <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>9</v>
@@ -12432,10 +12349,10 @@
         <v>101</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F144" s="6">
         <v>5</v>
@@ -12496,70 +12413,70 @@
     </row>
     <row r="145" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V145" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W145" s="31"/>
       <c r="Z145" s="4"/>
@@ -12568,7 +12485,7 @@
     </row>
     <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>9</v>
@@ -12577,10 +12494,10 @@
         <v>102</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F146" s="6">
         <v>1</v>
@@ -12640,7 +12557,7 @@
     </row>
     <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>9</v>
@@ -12649,10 +12566,10 @@
         <v>102</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F147" s="6">
         <v>2</v>
@@ -12712,7 +12629,7 @@
     </row>
     <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>9</v>
@@ -12721,10 +12638,10 @@
         <v>102</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F148" s="6">
         <v>3</v>
@@ -12784,7 +12701,7 @@
     </row>
     <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>9</v>
@@ -12793,10 +12710,10 @@
         <v>102</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F149" s="6">
         <v>4</v>
@@ -12856,7 +12773,7 @@
     </row>
     <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>9</v>
@@ -12865,10 +12782,10 @@
         <v>102</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F150" s="6">
         <v>5</v>
@@ -12926,70 +12843,70 @@
     </row>
     <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V151" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W151" s="31"/>
       <c r="Z151" s="4"/>
@@ -12998,7 +12915,7 @@
     </row>
     <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>9</v>
@@ -13007,10 +12924,10 @@
         <v>103</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F152" s="6">
         <v>1</v>
@@ -13070,7 +12987,7 @@
     </row>
     <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>9</v>
@@ -13079,10 +12996,10 @@
         <v>103</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F153" s="6">
         <v>2</v>
@@ -13142,7 +13059,7 @@
     </row>
     <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>9</v>
@@ -13151,10 +13068,10 @@
         <v>103</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F154" s="6">
         <v>3</v>
@@ -13214,7 +13131,7 @@
     </row>
     <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>9</v>
@@ -13223,10 +13140,10 @@
         <v>103</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F155" s="6">
         <v>4</v>
@@ -13286,7 +13203,7 @@
     </row>
     <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>9</v>
@@ -13295,10 +13212,10 @@
         <v>103</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F156" s="6">
         <v>5</v>
@@ -13358,70 +13275,70 @@
     </row>
     <row r="157" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V157" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W157" s="31"/>
       <c r="Z157" s="4"/>
@@ -13430,7 +13347,7 @@
     </row>
     <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>9</v>
@@ -13439,10 +13356,10 @@
         <v>104</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F158" s="6">
         <v>1</v>
@@ -13502,7 +13419,7 @@
     </row>
     <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>9</v>
@@ -13511,10 +13428,10 @@
         <v>104</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F159" s="6">
         <v>2</v>
@@ -13574,7 +13491,7 @@
     </row>
     <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>9</v>
@@ -13583,10 +13500,10 @@
         <v>104</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F160" s="6">
         <v>3</v>
@@ -13646,7 +13563,7 @@
     </row>
     <row r="161" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>9</v>
@@ -13655,10 +13572,10 @@
         <v>104</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F161" s="6">
         <v>4</v>
@@ -13718,7 +13635,7 @@
     </row>
     <row r="162" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>9</v>
@@ -13727,10 +13644,10 @@
         <v>104</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F162" s="6">
         <v>5</v>
@@ -13790,7 +13707,7 @@
     </row>
     <row r="163" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>9</v>
@@ -13799,10 +13716,10 @@
         <v>104</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F163" s="6">
         <v>6</v>
@@ -13862,7 +13779,7 @@
     </row>
     <row r="164" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>9</v>
@@ -13871,10 +13788,10 @@
         <v>104</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F164" s="6">
         <v>7</v>
@@ -13934,7 +13851,7 @@
     </row>
     <row r="165" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>9</v>
@@ -13943,10 +13860,10 @@
         <v>104</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F165" s="6">
         <v>8</v>
@@ -14006,7 +13923,7 @@
     </row>
     <row r="166" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>9</v>
@@ -14015,10 +13932,10 @@
         <v>104</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F166" s="6">
         <v>9</v>
@@ -14078,7 +13995,7 @@
     </row>
     <row r="167" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>9</v>
@@ -14087,10 +14004,10 @@
         <v>104</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F167" s="6">
         <v>10</v>
@@ -14150,7 +14067,7 @@
     </row>
     <row r="168" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A168" s="41" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B168" s="41" t="s">
         <v>9</v>
@@ -14159,10 +14076,10 @@
         <v>104</v>
       </c>
       <c r="D168" s="41" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E168" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F168" s="41">
         <v>11</v>
@@ -14222,7 +14139,7 @@
     </row>
     <row r="169" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A169" s="41" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B169" s="41" t="s">
         <v>9</v>
@@ -14231,10 +14148,10 @@
         <v>104</v>
       </c>
       <c r="D169" s="41" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E169" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F169" s="41">
         <v>12</v>
@@ -14294,7 +14211,7 @@
     </row>
     <row r="170" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A170" s="41" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B170" s="41" t="s">
         <v>9</v>
@@ -14303,10 +14220,10 @@
         <v>104</v>
       </c>
       <c r="D170" s="41" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E170" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F170" s="41">
         <v>13</v>
@@ -14366,7 +14283,7 @@
     </row>
     <row r="171" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A171" s="41" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B171" s="41" t="s">
         <v>9</v>
@@ -14375,10 +14292,10 @@
         <v>104</v>
       </c>
       <c r="D171" s="41" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E171" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F171" s="41">
         <v>14</v>
@@ -14438,7 +14355,7 @@
     </row>
     <row r="172" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A172" s="41" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B172" s="41" t="s">
         <v>9</v>
@@ -14447,10 +14364,10 @@
         <v>104</v>
       </c>
       <c r="D172" s="41" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E172" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F172" s="41">
         <v>15</v>
@@ -14510,7 +14427,7 @@
     </row>
     <row r="173" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A173" s="46" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B173" s="46" t="s">
         <v>9</v>
@@ -14519,10 +14436,10 @@
         <v>104</v>
       </c>
       <c r="D173" s="46" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E173" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F173" s="46">
         <v>16</v>
@@ -14582,7 +14499,7 @@
     </row>
     <row r="174" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A174" s="46" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B174" s="46" t="s">
         <v>9</v>
@@ -14591,10 +14508,10 @@
         <v>104</v>
       </c>
       <c r="D174" s="46" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E174" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F174" s="46">
         <v>17</v>
@@ -14654,7 +14571,7 @@
     </row>
     <row r="175" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A175" s="46" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B175" s="46" t="s">
         <v>9</v>
@@ -14663,10 +14580,10 @@
         <v>104</v>
       </c>
       <c r="D175" s="46" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E175" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F175" s="46">
         <v>18</v>
@@ -14726,7 +14643,7 @@
     </row>
     <row r="176" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A176" s="46" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B176" s="46" t="s">
         <v>9</v>
@@ -14735,10 +14652,10 @@
         <v>104</v>
       </c>
       <c r="D176" s="46" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E176" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F176" s="46">
         <v>19</v>
@@ -14798,7 +14715,7 @@
     </row>
     <row r="177" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A177" s="46" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B177" s="46" t="s">
         <v>9</v>
@@ -14807,10 +14724,10 @@
         <v>104</v>
       </c>
       <c r="D177" s="46" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E177" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F177" s="46">
         <v>20</v>
@@ -14870,7 +14787,7 @@
     </row>
     <row r="178" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A178" s="55" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B178" s="55" t="s">
         <v>9</v>
@@ -14879,10 +14796,10 @@
         <v>104</v>
       </c>
       <c r="D178" s="55" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E178" s="55" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F178" s="55">
         <v>21</v>
@@ -14942,7 +14859,7 @@
     </row>
     <row r="179" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A179" s="55" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B179" s="55" t="s">
         <v>9</v>
@@ -14951,10 +14868,10 @@
         <v>104</v>
       </c>
       <c r="D179" s="55" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E179" s="55" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F179" s="55">
         <v>22</v>
@@ -15014,7 +14931,7 @@
     </row>
     <row r="180" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A180" s="55" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B180" s="55" t="s">
         <v>9</v>
@@ -15023,10 +14940,10 @@
         <v>104</v>
       </c>
       <c r="D180" s="55" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E180" s="55" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F180" s="55">
         <v>23</v>
@@ -15086,7 +15003,7 @@
     </row>
     <row r="181" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A181" s="55" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B181" s="55" t="s">
         <v>9</v>
@@ -15095,10 +15012,10 @@
         <v>104</v>
       </c>
       <c r="D181" s="55" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E181" s="55" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F181" s="55">
         <v>24</v>
@@ -15158,7 +15075,7 @@
     </row>
     <row r="182" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A182" s="55" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B182" s="55" t="s">
         <v>9</v>
@@ -15167,10 +15084,10 @@
         <v>104</v>
       </c>
       <c r="D182" s="55" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E182" s="55" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F182" s="55">
         <v>25</v>
@@ -15230,70 +15147,70 @@
     </row>
     <row r="183" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V183" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W183" s="31"/>
       <c r="Z183" s="4"/>
@@ -15302,7 +15219,7 @@
     </row>
     <row r="184" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>9</v>
@@ -15311,10 +15228,10 @@
         <v>201</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F184" s="6">
         <v>1</v>
@@ -15374,7 +15291,7 @@
     </row>
     <row r="185" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>9</v>
@@ -15383,10 +15300,10 @@
         <v>201</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F185" s="6">
         <v>2</v>
@@ -15446,7 +15363,7 @@
     </row>
     <row r="186" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>9</v>
@@ -15455,10 +15372,10 @@
         <v>201</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F186" s="6">
         <v>3</v>
@@ -15518,7 +15435,7 @@
     </row>
     <row r="187" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>9</v>
@@ -15527,10 +15444,10 @@
         <v>201</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F187" s="6">
         <v>4</v>
@@ -15590,7 +15507,7 @@
     </row>
     <row r="188" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>9</v>
@@ -15599,10 +15516,10 @@
         <v>201</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F188" s="6">
         <v>5</v>
@@ -15662,7 +15579,7 @@
     </row>
     <row r="189" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>9</v>
@@ -15671,10 +15588,10 @@
         <v>201</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F189" s="6">
         <v>6</v>
@@ -15734,7 +15651,7 @@
     </row>
     <row r="190" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A190" s="46" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B190" s="46" t="s">
         <v>9</v>
@@ -15743,10 +15660,10 @@
         <v>201</v>
       </c>
       <c r="D190" s="46" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E190" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F190" s="46">
         <v>7</v>
@@ -15806,7 +15723,7 @@
     </row>
     <row r="191" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A191" s="46" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B191" s="46" t="s">
         <v>9</v>
@@ -15815,10 +15732,10 @@
         <v>201</v>
       </c>
       <c r="D191" s="46" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E191" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F191" s="46">
         <v>8</v>
@@ -15878,70 +15795,70 @@
     </row>
     <row r="192" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V192" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W192" s="31"/>
       <c r="Z192" s="4"/>
@@ -15950,19 +15867,19 @@
     </row>
     <row r="193" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F193" s="6">
         <v>1</v>
@@ -16022,70 +15939,70 @@
     </row>
     <row r="194" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V194" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W194" s="31"/>
       <c r="Z194" s="4"/>
@@ -16094,19 +16011,19 @@
     </row>
     <row r="195" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F195" s="6">
         <v>1</v>
@@ -16166,70 +16083,70 @@
     </row>
     <row r="196" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V196" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W196" s="31"/>
       <c r="Z196" s="4"/>
@@ -16238,7 +16155,7 @@
     </row>
     <row r="197" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>6</v>
@@ -16250,7 +16167,7 @@
         <v>53</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F197" s="6">
         <v>1</v>
@@ -16310,70 +16227,70 @@
     </row>
     <row r="198" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V198" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W198" s="31"/>
       <c r="Z198" s="4"/>
@@ -16382,7 +16299,7 @@
     </row>
     <row r="199" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>6</v>
@@ -16394,7 +16311,7 @@
         <v>61</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F199" s="6">
         <v>1</v>
@@ -16454,7 +16371,7 @@
     </row>
     <row r="200" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>6</v>
@@ -16466,7 +16383,7 @@
         <v>61</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F200" s="6">
         <v>1</v>
@@ -16526,70 +16443,70 @@
     </row>
     <row r="201" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V201" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W201" s="31"/>
       <c r="Z201" s="4"/>
@@ -16598,7 +16515,7 @@
     </row>
     <row r="202" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>6</v>
@@ -16610,7 +16527,7 @@
         <v>67</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F202" s="6">
         <v>1</v>
@@ -16670,7 +16587,7 @@
     </row>
     <row r="203" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>6</v>
@@ -16682,7 +16599,7 @@
         <v>67</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F203" s="6">
         <v>2</v>
@@ -16742,7 +16659,7 @@
     </row>
     <row r="204" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>6</v>
@@ -16754,7 +16671,7 @@
         <v>67</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F204" s="6">
         <v>3</v>
@@ -16814,7 +16731,7 @@
     </row>
     <row r="205" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>6</v>
@@ -16826,7 +16743,7 @@
         <v>67</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F205" s="6">
         <v>4</v>
@@ -16886,7 +16803,7 @@
     </row>
     <row r="206" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>6</v>
@@ -16898,7 +16815,7 @@
         <v>67</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F206" s="6">
         <v>5</v>
@@ -16958,7 +16875,7 @@
     </row>
     <row r="207" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>6</v>
@@ -16970,7 +16887,7 @@
         <v>67</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F207" s="6">
         <v>6</v>
@@ -17030,7 +16947,7 @@
     </row>
     <row r="208" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A208" s="41" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B208" s="41" t="s">
         <v>6</v>
@@ -17042,7 +16959,7 @@
         <v>67</v>
       </c>
       <c r="E208" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F208" s="41">
         <v>7</v>
@@ -17102,7 +17019,7 @@
     </row>
     <row r="209" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A209" s="41" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B209" s="41" t="s">
         <v>6</v>
@@ -17114,7 +17031,7 @@
         <v>67</v>
       </c>
       <c r="E209" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F209" s="41">
         <v>8</v>
@@ -17174,7 +17091,7 @@
     </row>
     <row r="210" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A210" s="41" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B210" s="41" t="s">
         <v>6</v>
@@ -17186,7 +17103,7 @@
         <v>67</v>
       </c>
       <c r="E210" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F210" s="41">
         <v>9</v>
@@ -17246,7 +17163,7 @@
     </row>
     <row r="211" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A211" s="41" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B211" s="41" t="s">
         <v>6</v>
@@ -17258,7 +17175,7 @@
         <v>67</v>
       </c>
       <c r="E211" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F211" s="41">
         <v>10</v>
@@ -17318,7 +17235,7 @@
     </row>
     <row r="212" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A212" s="41" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B212" s="41" t="s">
         <v>6</v>
@@ -17330,7 +17247,7 @@
         <v>67</v>
       </c>
       <c r="E212" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F212" s="41">
         <v>11</v>
@@ -17390,7 +17307,7 @@
     </row>
     <row r="213" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A213" s="46" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B213" s="46" t="s">
         <v>6</v>
@@ -17402,7 +17319,7 @@
         <v>67</v>
       </c>
       <c r="E213" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F213" s="46">
         <v>12</v>
@@ -17462,7 +17379,7 @@
     </row>
     <row r="214" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A214" s="46" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B214" s="46" t="s">
         <v>6</v>
@@ -17474,7 +17391,7 @@
         <v>67</v>
       </c>
       <c r="E214" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F214" s="46">
         <v>13</v>
@@ -17534,7 +17451,7 @@
     </row>
     <row r="215" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A215" s="46" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B215" s="46" t="s">
         <v>6</v>
@@ -17546,7 +17463,7 @@
         <v>67</v>
       </c>
       <c r="E215" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F215" s="46">
         <v>14</v>
@@ -17606,7 +17523,7 @@
     </row>
     <row r="216" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A216" s="46" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B216" s="46" t="s">
         <v>6</v>
@@ -17618,7 +17535,7 @@
         <v>67</v>
       </c>
       <c r="E216" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F216" s="46">
         <v>15</v>
@@ -17678,7 +17595,7 @@
     </row>
     <row r="217" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A217" s="46" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B217" s="46" t="s">
         <v>6</v>
@@ -17690,7 +17607,7 @@
         <v>67</v>
       </c>
       <c r="E217" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F217" s="46">
         <v>16</v>
@@ -17750,70 +17667,70 @@
     </row>
     <row r="218" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V218" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W218" s="31"/>
       <c r="Z218" s="4"/>
@@ -17822,7 +17739,7 @@
     </row>
     <row r="219" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>6</v>
@@ -17834,7 +17751,7 @@
         <v>75</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F219" s="6">
         <v>1</v>
@@ -17894,7 +17811,7 @@
     </row>
     <row r="220" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>6</v>
@@ -17906,7 +17823,7 @@
         <v>75</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F220" s="6">
         <v>2</v>
@@ -17966,7 +17883,7 @@
     </row>
     <row r="221" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>6</v>
@@ -17978,7 +17895,7 @@
         <v>75</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F221" s="6">
         <v>3</v>
@@ -18038,7 +17955,7 @@
     </row>
     <row r="222" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>6</v>
@@ -18050,7 +17967,7 @@
         <v>75</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F222" s="6">
         <v>4</v>
@@ -18110,7 +18027,7 @@
     </row>
     <row r="223" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>6</v>
@@ -18122,7 +18039,7 @@
         <v>75</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F223" s="6">
         <v>5</v>
@@ -18182,7 +18099,7 @@
     </row>
     <row r="224" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>6</v>
@@ -18194,7 +18111,7 @@
         <v>75</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F224" s="6">
         <v>6</v>
@@ -18254,70 +18171,70 @@
     </row>
     <row r="225" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V225" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W225" s="31"/>
       <c r="Z225" s="4"/>
@@ -18326,7 +18243,7 @@
     </row>
     <row r="226" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>6</v>
@@ -18338,7 +18255,7 @@
         <v>79</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F226" s="6">
         <v>1</v>
@@ -18398,70 +18315,70 @@
     </row>
     <row r="227" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V227" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W227" s="31"/>
       <c r="Z227" s="4"/>
@@ -18470,7 +18387,7 @@
     </row>
     <row r="228" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>6</v>
@@ -18482,7 +18399,7 @@
         <v>87</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F228" s="6">
         <v>1</v>
@@ -18542,7 +18459,7 @@
     </row>
     <row r="229" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>6</v>
@@ -18554,7 +18471,7 @@
         <v>87</v>
       </c>
       <c r="E229" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F229" s="6">
         <v>1</v>
@@ -18614,7 +18531,7 @@
     </row>
     <row r="230" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A230" s="41" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B230" s="41" t="s">
         <v>6</v>
@@ -18626,7 +18543,7 @@
         <v>87</v>
       </c>
       <c r="E230" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F230" s="41">
         <v>1</v>
@@ -18686,70 +18603,70 @@
     </row>
     <row r="231" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V231" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W231" s="31"/>
       <c r="Z231" s="4"/>
@@ -18758,7 +18675,7 @@
     </row>
     <row r="232" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>6</v>
@@ -18770,7 +18687,7 @@
         <v>93</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F232" s="6">
         <v>1</v>
@@ -18830,7 +18747,7 @@
     </row>
     <row r="233" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>6</v>
@@ -18842,7 +18759,7 @@
         <v>93</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F233" s="6">
         <v>2</v>
@@ -18902,7 +18819,7 @@
     </row>
     <row r="234" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A234" s="41" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B234" s="41" t="s">
         <v>6</v>
@@ -18914,7 +18831,7 @@
         <v>93</v>
       </c>
       <c r="E234" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F234" s="41">
         <v>3</v>
@@ -18974,7 +18891,7 @@
     </row>
     <row r="235" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A235" s="46" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B235" s="46" t="s">
         <v>6</v>
@@ -18986,7 +18903,7 @@
         <v>93</v>
       </c>
       <c r="E235" s="46" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F235" s="46">
         <v>4</v>
@@ -19046,70 +18963,70 @@
     </row>
     <row r="236" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V236" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W236" s="31"/>
       <c r="Z236" s="4"/>
@@ -19118,7 +19035,7 @@
     </row>
     <row r="237" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>6</v>
@@ -19130,7 +19047,7 @@
         <v>97</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F237" s="6">
         <v>1</v>
@@ -19190,70 +19107,70 @@
     </row>
     <row r="238" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V238" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W238" s="31"/>
       <c r="Z238" s="4"/>
@@ -19262,7 +19179,7 @@
     </row>
     <row r="239" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>6</v>
@@ -19274,7 +19191,7 @@
         <v>98</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F239" s="6">
         <v>1</v>
@@ -19334,7 +19251,7 @@
     </row>
     <row r="240" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>6</v>
@@ -19346,7 +19263,7 @@
         <v>98</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F240" s="6">
         <v>2</v>
@@ -19406,7 +19323,7 @@
     </row>
     <row r="241" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>6</v>
@@ -19418,7 +19335,7 @@
         <v>98</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F241" s="6">
         <v>3</v>
@@ -19478,70 +19395,70 @@
     </row>
     <row r="242" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V242" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W242" s="31"/>
       <c r="Z242" s="4"/>
@@ -19550,7 +19467,7 @@
     </row>
     <row r="243" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>6</v>
@@ -19562,7 +19479,7 @@
         <v>112</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F243" s="6">
         <v>1</v>
@@ -19622,7 +19539,7 @@
     </row>
     <row r="244" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>6</v>
@@ -19634,7 +19551,7 @@
         <v>112</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F244" s="6">
         <v>2</v>
@@ -19694,7 +19611,7 @@
     </row>
     <row r="245" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>6</v>
@@ -19706,7 +19623,7 @@
         <v>112</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F245" s="6">
         <v>3</v>
@@ -19766,70 +19683,70 @@
     </row>
     <row r="246" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V246" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W246" s="31"/>
       <c r="Z246" s="4"/>
@@ -19838,7 +19755,7 @@
     </row>
     <row r="247" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>6</v>
@@ -19850,7 +19767,7 @@
         <v>101</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F247" s="6">
         <v>1</v>
@@ -19910,7 +19827,7 @@
     </row>
     <row r="248" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>6</v>
@@ -19922,7 +19839,7 @@
         <v>101</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F248" s="6">
         <v>1</v>
@@ -19984,7 +19901,7 @@
     </row>
     <row r="249" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>6</v>
@@ -19996,7 +19913,7 @@
         <v>101</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F249" s="6">
         <v>1</v>
@@ -20058,7 +19975,7 @@
     </row>
     <row r="250" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>6</v>
@@ -20070,7 +19987,7 @@
         <v>101</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F250" s="6">
         <v>1</v>
@@ -20132,7 +20049,7 @@
     </row>
     <row r="251" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>6</v>
@@ -20144,7 +20061,7 @@
         <v>101</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F251" s="6">
         <v>1</v>
@@ -20206,7 +20123,7 @@
     </row>
     <row r="252" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>6</v>
@@ -20218,7 +20135,7 @@
         <v>101</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F252" s="6">
         <v>1</v>
@@ -20280,70 +20197,70 @@
     </row>
     <row r="253" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V253" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W253" s="31"/>
       <c r="Z253" s="4"/>
@@ -20352,7 +20269,7 @@
     </row>
     <row r="254" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>6</v>
@@ -20364,7 +20281,7 @@
         <v>105</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F254" s="6">
         <v>1</v>
@@ -20424,7 +20341,7 @@
     </row>
     <row r="255" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>6</v>
@@ -20436,7 +20353,7 @@
         <v>105</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F255" s="6">
         <v>2</v>
@@ -20496,7 +20413,7 @@
     </row>
     <row r="256" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>6</v>
@@ -20508,7 +20425,7 @@
         <v>105</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F256" s="6">
         <v>3</v>
@@ -20568,7 +20485,7 @@
     </row>
     <row r="257" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>6</v>
@@ -20580,7 +20497,7 @@
         <v>105</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F257" s="6">
         <v>4</v>
@@ -20640,7 +20557,7 @@
     </row>
     <row r="258" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A258" s="41" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B258" s="41" t="s">
         <v>6</v>
@@ -20652,7 +20569,7 @@
         <v>105</v>
       </c>
       <c r="E258" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F258" s="41">
         <v>5</v>
@@ -20712,7 +20629,7 @@
     </row>
     <row r="259" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A259" s="41" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B259" s="41" t="s">
         <v>6</v>
@@ -20724,7 +20641,7 @@
         <v>105</v>
       </c>
       <c r="E259" s="41" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F259" s="41">
         <v>6</v>
@@ -20784,70 +20701,70 @@
     </row>
     <row r="260" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="H260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="O260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="Q260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="R260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="S260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="T260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="U260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="V260" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="W260" s="31"/>
       <c r="Z260" s="4"/>
@@ -20856,7 +20773,7 @@
     </row>
     <row r="261" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>6</v>
@@ -20868,7 +20785,7 @@
         <v>110</v>
       </c>
       <c r="E261" s="6" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F261" s="6">
         <v>1</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE19DE4C-BFD4-40E9-9119-3C35D6CA3FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8745BF2F-DDBA-49AD-BFD6-931CA14D35B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2505" windowWidth="102195" windowHeight="29895" xr2:uid="{B32626A3-35DB-4FED-BFD5-02FEE635C51E}"/>
+    <workbookView xWindow="0" yWindow="2505" windowWidth="102195" windowHeight="29895" xr2:uid="{91136297-5822-44C6-A3F2-6CC3985E9C67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="227">
   <si>
     <t>Building</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Gross Mod</t>
   </si>
   <si>
-    <t>Covenents</t>
-  </si>
-  <si>
     <t>CAMEst/Ft</t>
   </si>
   <si>
@@ -248,9 +245,6 @@
     <t>3% Annually</t>
   </si>
   <si>
-    <t>Two- 5 Yr Opt;  Non-Compete</t>
-  </si>
-  <si>
     <t>Two (2) x 5-year options</t>
   </si>
   <si>
@@ -287,9 +281,6 @@
     <t>114 Central2</t>
   </si>
   <si>
-    <t>Mutual Extension/Cancel</t>
-  </si>
-  <si>
     <t>Auto-renewal annually unless Cancel</t>
   </si>
   <si>
@@ -308,9 +299,6 @@
     <t>Annual Variable</t>
   </si>
   <si>
-    <t>One 1-Year</t>
-  </si>
-  <si>
     <t>One (1) x 12 months w/ 180 days notice</t>
   </si>
   <si>
@@ -323,9 +311,6 @@
     <t>Rentokil North America dba Terminix</t>
   </si>
   <si>
-    <t>Two 1-Year Opt</t>
-  </si>
-  <si>
     <t>Two (2) x 1 year w/ 6 months notice.</t>
   </si>
   <si>
@@ -359,9 +344,6 @@
     <t>Westfield Education Association</t>
   </si>
   <si>
-    <t>One-Two Year</t>
-  </si>
-  <si>
     <t>One (1) x 24 months w/180 days notice</t>
   </si>
   <si>
@@ -437,9 +419,6 @@
     <t>36 South1</t>
   </si>
   <si>
-    <t>Two 5-Year 3% Annual Inc; 2nd Fl Non-Comp</t>
-  </si>
-  <si>
     <t>Two (2) x 60 months</t>
   </si>
   <si>
@@ -567,9 +546,6 @@
   </si>
   <si>
     <t>$1200 / Yr</t>
-  </si>
-  <si>
-    <t>One 2Yr Opt</t>
   </si>
   <si>
     <t>None</t>
@@ -1306,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DA311A-A1CC-4A9F-8D4E-4A01C43371C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C57F37A-D4FD-4926-86E8-D42A75076906}">
   <dimension ref="A1:AT261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1560,54 +1536,52 @@
       <c r="AC10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AD10" s="1" t="s">
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AE10" s="1" t="s">
+      <c r="AF10" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="AF10" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AI10" s="9" t="s">
+      <c r="AJ10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AJ10" s="1" t="s">
+      <c r="AK10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AK10" s="9" t="s">
+      <c r="AL10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AL10" s="9" t="s">
+      <c r="AM10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AM10" s="9" t="s">
+      <c r="AN10" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AN10" s="9" t="s">
+      <c r="AO10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AO10" s="9" t="s">
+      <c r="AP10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AP10" s="9" t="s">
+      <c r="AQ10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="AQ10" s="9" t="s">
+      <c r="AR10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AR10" s="9" t="s">
+      <c r="AS10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="AS10" s="9" t="s">
+      <c r="AT10" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="AT10" s="9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.25">
@@ -1618,23 +1592,23 @@
         <v>102</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="E11" s="6">
         <v>1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6">
         <v>1063</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J11" s="10">
         <v>0.21720474049856967</v>
@@ -1706,21 +1680,21 @@
       <c r="AI11" s="20"/>
       <c r="AJ11" s="18"/>
       <c r="AK11" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
       <c r="AN11" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AO11" s="20"/>
       <c r="AP11" s="20"/>
       <c r="AQ11" s="20"/>
       <c r="AR11" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS11" s="20" t="s">
         <v>59</v>
-      </c>
-      <c r="AS11" s="20" t="s">
-        <v>60</v>
       </c>
       <c r="AT11" s="20"/>
     </row>
@@ -1732,23 +1706,23 @@
         <v>104</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6">
         <v>1360</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J12" s="10">
         <v>0.27789129546383329</v>
@@ -1820,27 +1794,27 @@
       <c r="AI12" s="20"/>
       <c r="AJ12" s="18"/>
       <c r="AK12" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AL12" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AM12" s="20"/>
       <c r="AN12" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO12" s="20"/>
       <c r="AP12" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ12" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="AR12" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="AQ12" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR12" s="20" t="s">
+      <c r="AS12" s="20" t="s">
         <v>65</v>
-      </c>
-      <c r="AS12" s="20" t="s">
-        <v>66</v>
       </c>
       <c r="AT12" s="20"/>
     </row>
@@ -1852,23 +1826,23 @@
         <v>106</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="6">
         <v>1</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6">
         <v>1035</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J13" s="10">
         <v>0.21148344912137312</v>
@@ -1919,16 +1893,14 @@
         <v>46810</v>
       </c>
       <c r="Z13" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA13" s="18"/>
       <c r="AB13" s="19">
         <v>2</v>
       </c>
       <c r="AC13" s="19"/>
-      <c r="AD13" s="16" t="s">
-        <v>69</v>
-      </c>
+      <c r="AD13" s="16"/>
       <c r="AE13" s="13">
         <v>11.637681159420289</v>
       </c>
@@ -1942,7 +1914,7 @@
         <v>4743.75</v>
       </c>
       <c r="AI13" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AJ13" s="18">
         <v>46565</v>
@@ -1950,23 +1922,23 @@
       <c r="AK13" s="20"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AN13" s="20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AO13" s="20"/>
       <c r="AP13" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ13" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AR13" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AS13" s="20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AT13" s="20"/>
     </row>
@@ -1978,23 +1950,23 @@
         <v>108</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="6">
         <v>1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6">
         <v>1436</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J14" s="10">
         <v>0.29342051491622395</v>
@@ -2069,19 +2041,19 @@
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
       <c r="AN14" s="20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AO14" s="20"/>
       <c r="AP14" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ14" s="20"/>
       <c r="AR14" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AS14" s="20"/>
       <c r="AT14" s="20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.25">
@@ -2092,16 +2064,16 @@
         <v>201</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E15" s="6">
         <v>2</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6">
@@ -2162,9 +2134,7 @@
       <c r="AA15" s="18"/>
       <c r="AB15" s="19"/>
       <c r="AC15" s="19"/>
-      <c r="AD15" s="16" t="s">
-        <v>82</v>
-      </c>
+      <c r="AD15" s="16"/>
       <c r="AE15" s="13">
         <v>0</v>
       </c>
@@ -2178,16 +2148,16 @@
         <v>1632.5</v>
       </c>
       <c r="AI15" s="20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AJ15" s="18">
         <v>46295</v>
       </c>
       <c r="AK15" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AL15" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AM15" s="20"/>
       <c r="AN15" s="20" t="s">
@@ -2195,15 +2165,15 @@
       </c>
       <c r="AO15" s="20"/>
       <c r="AP15" s="20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AQ15" s="20"/>
       <c r="AR15" s="20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AS15" s="20"/>
       <c r="AT15" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.25">
@@ -2214,16 +2184,16 @@
         <v>202</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E16" s="6">
         <v>2</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6">
@@ -2281,16 +2251,14 @@
         <v>46507</v>
       </c>
       <c r="Z16" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AA16" s="18"/>
       <c r="AB16" s="19">
         <v>1</v>
       </c>
       <c r="AC16" s="19"/>
-      <c r="AD16" s="16" t="s">
-        <v>89</v>
-      </c>
+      <c r="AD16" s="16"/>
       <c r="AE16" s="13">
         <v>0</v>
       </c>
@@ -2304,7 +2272,7 @@
         <v>1517.5</v>
       </c>
       <c r="AI16" s="20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AJ16" s="18">
         <v>46327</v>
@@ -2317,14 +2285,14 @@
       </c>
       <c r="AO16" s="20"/>
       <c r="AP16" s="20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AQ16" s="20"/>
       <c r="AR16" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AS16" s="20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AT16" s="20"/>
     </row>
@@ -2336,16 +2304,16 @@
         <v>203</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" s="6">
         <v>2</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6">
@@ -2408,9 +2376,7 @@
         <v>2</v>
       </c>
       <c r="AC17" s="19"/>
-      <c r="AD17" s="23" t="s">
-        <v>94</v>
-      </c>
+      <c r="AD17" s="23"/>
       <c r="AE17" s="13">
         <v>0</v>
       </c>
@@ -2424,7 +2390,7 @@
         <v>1555</v>
       </c>
       <c r="AI17" s="20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ17" s="18">
         <v>46356</v>
@@ -2437,12 +2403,12 @@
       </c>
       <c r="AO17" s="20"/>
       <c r="AP17" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ17" s="20"/>
       <c r="AR17" s="20"/>
       <c r="AS17" s="20" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AT17" s="20"/>
     </row>
@@ -2454,16 +2420,16 @@
         <v>204</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
@@ -2558,16 +2524,16 @@
         <v>205</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E19" s="6">
         <v>2</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6">
@@ -2649,16 +2615,16 @@
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
       <c r="AN19" s="20" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="AO19" s="20"/>
       <c r="AP19" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ19" s="20"/>
       <c r="AR19" s="20"/>
       <c r="AS19" s="20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AT19" s="20"/>
     </row>
@@ -2670,16 +2636,16 @@
         <v>206</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6">
@@ -2737,7 +2703,7 @@
         <v>47968</v>
       </c>
       <c r="Z20" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AA20" s="18"/>
       <c r="AB20" s="19">
@@ -2760,7 +2726,7 @@
       <c r="AI20" s="20"/>
       <c r="AJ20" s="18"/>
       <c r="AK20" s="20" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
@@ -2769,17 +2735,17 @@
       </c>
       <c r="AO20" s="20"/>
       <c r="AP20" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ20" s="20"/>
       <c r="AR20" s="20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="AS20" s="20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AT20" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:46" x14ac:dyDescent="0.25">
@@ -2790,16 +2756,16 @@
         <v>207</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E21" s="6">
         <v>2</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6">
@@ -2862,9 +2828,7 @@
         <v>1</v>
       </c>
       <c r="AC21" s="19"/>
-      <c r="AD21" s="16" t="s">
-        <v>106</v>
-      </c>
+      <c r="AD21" s="16"/>
       <c r="AE21" s="13">
         <v>0</v>
       </c>
@@ -2878,7 +2842,7 @@
         <v>1982.5</v>
       </c>
       <c r="AI21" s="20" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="AJ21" s="18">
         <v>47303</v>
@@ -2887,18 +2851,18 @@
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
       <c r="AN21" s="20" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AO21" s="20"/>
       <c r="AP21" s="20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AQ21" s="20"/>
       <c r="AR21" s="20" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AS21" s="20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AT21" s="20"/>
     </row>
@@ -2910,16 +2874,16 @@
         <v>208</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6">
@@ -3000,15 +2964,17 @@
       <c r="AK22" s="20"/>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="20"/>
+      <c r="AN22" s="20" t="s">
+        <v>27</v>
+      </c>
       <c r="AO22" s="20"/>
       <c r="AP22" s="20"/>
       <c r="AQ22" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AR22" s="20"/>
       <c r="AS22" s="20" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="AT22" s="20"/>
     </row>
@@ -3020,16 +2986,16 @@
         <v>209</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E23" s="6">
         <v>2</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6">
@@ -3111,16 +3077,16 @@
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
       <c r="AN23" s="20" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="AO23" s="20"/>
       <c r="AP23" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ23" s="20"/>
       <c r="AR23" s="20"/>
       <c r="AS23" s="20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AT23" s="20"/>
     </row>
@@ -3131,7 +3097,7 @@
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
@@ -3184,23 +3150,23 @@
         <v>1</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" s="6">
         <v>1</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6">
         <v>4000</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J25" s="10">
         <v>0.99950024987506247</v>
@@ -3251,7 +3217,7 @@
         <v>49064</v>
       </c>
       <c r="Z25" s="36" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="AA25" s="23"/>
       <c r="AB25" s="19"/>
@@ -3270,7 +3236,7 @@
         <v>16666.666666666668</v>
       </c>
       <c r="AI25" s="20" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="AJ25" s="18">
         <v>48794</v>
@@ -3279,23 +3245,23 @@
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
       <c r="AN25" s="20" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="AO25" s="20"/>
       <c r="AP25" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ25" s="20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AR25" s="20" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AS25" s="20" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AT25" s="20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:46" x14ac:dyDescent="0.25">
@@ -3303,19 +3269,19 @@
         <v>7</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E26" s="6">
         <v>1</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6">
@@ -3373,7 +3339,7 @@
         <v>47603</v>
       </c>
       <c r="Z26" s="36" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="AA26" s="23"/>
       <c r="AB26" s="19"/>
@@ -3392,28 +3358,28 @@
         <v>2300</v>
       </c>
       <c r="AI26" s="20" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AJ26" s="18">
         <v>47423</v>
       </c>
       <c r="AK26" s="20" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AN26" s="20" t="s">
         <v>27</v>
       </c>
       <c r="AO26" s="20"/>
       <c r="AP26" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ26" s="20"/>
       <c r="AR26" s="20" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="AS26" s="20"/>
       <c r="AT26" s="20"/>
@@ -3423,19 +3389,19 @@
         <v>7</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E27" s="6">
         <v>1</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6">
@@ -3529,7 +3495,7 @@
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
       <c r="F28" s="24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
@@ -3584,23 +3550,23 @@
         <v>101</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" s="6">
         <v>1</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
         <v>4064</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J29" s="10">
         <v>1</v>
@@ -3660,9 +3626,7 @@
       <c r="AC29" s="19">
         <v>0</v>
       </c>
-      <c r="AD29" s="23" t="s">
-        <v>132</v>
-      </c>
+      <c r="AD29" s="23"/>
       <c r="AE29" s="13">
         <v>15</v>
       </c>
@@ -3676,7 +3640,7 @@
         <v>16933.333333333332</v>
       </c>
       <c r="AI29" s="20" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="AJ29" s="18">
         <v>48854</v>
@@ -3684,26 +3648,26 @@
       <c r="AK29" s="20"/>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="AN29" s="20" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AO29" s="20"/>
       <c r="AP29" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ29" s="20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AR29" s="20" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AS29" s="20" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AT29" s="20" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:46" x14ac:dyDescent="0.25">
@@ -3714,16 +3678,16 @@
         <v>201</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E30" s="6">
         <v>2</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
@@ -3811,19 +3775,19 @@
       </c>
       <c r="AO30" s="20"/>
       <c r="AP30" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ30" s="20" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AR30" s="20" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AS30" s="20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AT30" s="20" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:46" x14ac:dyDescent="0.25">
@@ -3831,19 +3795,19 @@
         <v>8</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E31" s="6">
         <v>3</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
@@ -3920,30 +3884,30 @@
         <v>0</v>
       </c>
       <c r="AI31" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="AJ31" s="23"/>
       <c r="AK31" s="20" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="AL31" s="20" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="AM31" s="20"/>
       <c r="AN31" s="20" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AO31" s="20" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="AP31" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ31" s="20"/>
       <c r="AR31" s="20"/>
       <c r="AS31" s="20"/>
       <c r="AT31" s="20" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:46" x14ac:dyDescent="0.25">
@@ -3951,19 +3915,19 @@
         <v>8</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
@@ -4057,7 +4021,7 @@
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
@@ -4112,23 +4076,23 @@
         <v>101</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E34" s="6">
         <v>1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
         <v>721</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J34" s="10">
         <v>0.12521708926710665</v>
@@ -4179,7 +4143,7 @@
         <v>46538</v>
       </c>
       <c r="Z34" s="36" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AA34" s="23"/>
       <c r="AB34" s="19">
@@ -4205,20 +4169,20 @@
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
       <c r="AN34" s="38" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="AO34" s="20"/>
       <c r="AP34" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ34" s="20" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AR34" s="20" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AS34" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AT34" s="20"/>
     </row>
@@ -4230,23 +4194,23 @@
         <v>102</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" s="6">
         <v>1</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6">
         <v>996</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J35" s="10">
         <v>0.17297672803056616</v>
@@ -4297,7 +4261,7 @@
         <v>46706</v>
       </c>
       <c r="Z35" s="36" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AA35" s="23"/>
       <c r="AB35" s="19">
@@ -4323,20 +4287,20 @@
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
       <c r="AN35" s="38" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AO35" s="20"/>
       <c r="AP35" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ35" s="20" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="AR35" s="20" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AS35" s="20" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AT35" s="20"/>
     </row>
@@ -4348,23 +4312,23 @@
         <v>103</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" s="6">
         <v>1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6">
         <v>1533</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J36" s="10">
         <v>0.26623827717957627</v>
@@ -4415,7 +4379,7 @@
         <v>47299</v>
       </c>
       <c r="Z36" s="36" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AA36" s="23"/>
       <c r="AB36" s="19">
@@ -4441,20 +4405,20 @@
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
       <c r="AN36" s="38" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AO36" s="20"/>
       <c r="AP36" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ36" s="20" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="AR36" s="20" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AS36" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AT36" s="20"/>
     </row>
@@ -4466,23 +4430,23 @@
         <v>104</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" s="6">
         <v>1</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6">
         <v>2508</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J37" s="10">
         <v>0.43556790552275093</v>
@@ -4533,7 +4497,7 @@
         <v>47573</v>
       </c>
       <c r="Z37" s="36" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="AA37" s="23"/>
       <c r="AB37" s="19">
@@ -4554,7 +4518,7 @@
         <v>10450</v>
       </c>
       <c r="AI37" s="20" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="AJ37" s="18">
         <v>47303</v>
@@ -4563,23 +4527,23 @@
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
       <c r="AN37" s="38" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AO37" s="20"/>
       <c r="AP37" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ37" s="20" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AR37" s="20" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AS37" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AT37" s="20" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
@@ -4590,16 +4554,16 @@
         <v>201</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E38" s="6">
         <v>2</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6">
@@ -4657,16 +4621,14 @@
         <v>46996</v>
       </c>
       <c r="Z38" s="36" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AA38" s="18"/>
       <c r="AB38" s="19">
         <v>3</v>
       </c>
       <c r="AC38" s="19"/>
-      <c r="AD38" s="23" t="s">
-        <v>176</v>
-      </c>
+      <c r="AD38" s="23"/>
       <c r="AE38" s="13">
         <v>0</v>
       </c>
@@ -4680,31 +4642,31 @@
         <v>2477.0833333333335</v>
       </c>
       <c r="AI38" s="20" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="AJ38" s="18">
         <v>46816</v>
       </c>
       <c r="AK38" s="20" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
       <c r="AN38" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="AO38" s="20"/>
       <c r="AP38" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ38" s="20" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="AR38" s="20" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AS38" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AT38" s="20"/>
     </row>
@@ -4761,19 +4723,19 @@
         <v>9</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6">
@@ -4831,7 +4793,7 @@
         <v>45626</v>
       </c>
       <c r="Z40" s="36" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AA40" s="23"/>
       <c r="AB40" s="19">
@@ -4854,28 +4816,28 @@
         <v>1614.5833333333333</v>
       </c>
       <c r="AI40" s="20" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AJ40" s="23" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AK40" s="20" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
       <c r="AN40" s="38" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AO40" s="20"/>
       <c r="AP40" s="20"/>
       <c r="AQ40" s="20"/>
       <c r="AR40" s="20"/>
       <c r="AS40" s="20" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AT40" s="20" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:46" x14ac:dyDescent="0.25">
@@ -4885,7 +4847,7 @@
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G41" s="24"/>
       <c r="H41" s="24"/>
@@ -4961,46 +4923,46 @@
     </row>
     <row r="45" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="N45" s="39" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="O45" s="39" t="s">
         <v>14</v>
@@ -5009,10 +4971,10 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>31</v>
@@ -5027,7 +4989,7 @@
         <v>36</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Z45" s="4"/>
       <c r="AG45" s="5"/>
@@ -5035,7 +4997,7 @@
     </row>
     <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -5044,10 +5006,10 @@
         <v>101</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F46" s="6">
         <v>0</v>
@@ -5068,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M46" s="8">
         <v>4064</v>
@@ -5107,7 +5069,7 @@
     </row>
     <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
@@ -5116,10 +5078,10 @@
         <v>101</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
@@ -5140,7 +5102,7 @@
         <v>87376.02</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M47" s="8">
         <v>4064</v>
@@ -5179,7 +5141,7 @@
     </row>
     <row r="48" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
@@ -5188,10 +5150,10 @@
         <v>101</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F48" s="6">
         <v>2</v>
@@ -5212,7 +5174,7 @@
         <v>179994.56</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M48" s="8">
         <v>4064</v>
@@ -5251,7 +5213,7 @@
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
@@ -5260,10 +5222,10 @@
         <v>101</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
@@ -5284,7 +5246,7 @@
         <v>185394.39680000002</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M49" s="8">
         <v>4064</v>
@@ -5323,7 +5285,7 @@
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
@@ -5332,10 +5294,10 @@
         <v>101</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F50" s="6">
         <v>4</v>
@@ -5356,7 +5318,7 @@
         <v>190956.22870400001</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M50" s="8">
         <v>4064</v>
@@ -5395,7 +5357,7 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
@@ -5404,10 +5366,10 @@
         <v>101</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
@@ -5428,7 +5390,7 @@
         <v>196684.91556512003</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M51" s="8">
         <v>4064</v>
@@ -5467,7 +5429,7 @@
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
@@ -5476,10 +5438,10 @@
         <v>101</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
@@ -5500,7 +5462,7 @@
         <v>202585.46303207363</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M52" s="8">
         <v>4064</v>
@@ -5539,7 +5501,7 @@
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
@@ -5548,10 +5510,10 @@
         <v>101</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
@@ -5572,7 +5534,7 @@
         <v>208663.02692303585</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M53" s="8">
         <v>4064</v>
@@ -5611,7 +5573,7 @@
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>8</v>
@@ -5620,10 +5582,10 @@
         <v>101</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F54" s="6">
         <v>8</v>
@@ -5644,7 +5606,7 @@
         <v>214922.91773072694</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M54" s="8">
         <v>4064</v>
@@ -5683,7 +5645,7 @@
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>8</v>
@@ -5692,10 +5654,10 @@
         <v>101</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F55" s="6">
         <v>9</v>
@@ -5716,7 +5678,7 @@
         <v>221370.60526264875</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M55" s="8">
         <v>4064</v>
@@ -5755,7 +5717,7 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
@@ -5764,10 +5726,10 @@
         <v>101</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6">
         <v>10</v>
@@ -5788,7 +5750,7 @@
         <v>228011.72342052823</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M56" s="8">
         <v>4064</v>
@@ -5827,7 +5789,7 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="42" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B57" s="42" t="s">
         <v>8</v>
@@ -5836,10 +5798,10 @@
         <v>101</v>
       </c>
       <c r="D57" s="42" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E57" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F57" s="42">
         <v>11</v>
@@ -5860,7 +5822,7 @@
         <v>234852.07512314408</v>
       </c>
       <c r="L57" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M57" s="46">
         <v>4064</v>
@@ -5899,7 +5861,7 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="42" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B58" s="42" t="s">
         <v>8</v>
@@ -5908,10 +5870,10 @@
         <v>101</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E58" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F58" s="42">
         <v>12</v>
@@ -5932,7 +5894,7 @@
         <v>241897.63737683842</v>
       </c>
       <c r="L58" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M58" s="46">
         <v>4064</v>
@@ -5971,7 +5933,7 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" s="42" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B59" s="42" t="s">
         <v>8</v>
@@ -5980,10 +5942,10 @@
         <v>101</v>
       </c>
       <c r="D59" s="42" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E59" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F59" s="42">
         <v>13</v>
@@ -6004,7 +5966,7 @@
         <v>249154.56649814357</v>
       </c>
       <c r="L59" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M59" s="46">
         <v>4064</v>
@@ -6043,7 +6005,7 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="42" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B60" s="42" t="s">
         <v>8</v>
@@ -6052,10 +6014,10 @@
         <v>101</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E60" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F60" s="42">
         <v>14</v>
@@ -6076,7 +6038,7 @@
         <v>256629.20349308787</v>
       </c>
       <c r="L60" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M60" s="46">
         <v>4064</v>
@@ -6115,7 +6077,7 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="42" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>8</v>
@@ -6124,10 +6086,10 @@
         <v>101</v>
       </c>
       <c r="D61" s="42" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E61" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F61" s="42">
         <v>15</v>
@@ -6148,7 +6110,7 @@
         <v>264328.07959788054</v>
       </c>
       <c r="L61" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M61" s="46">
         <v>4064</v>
@@ -6187,7 +6149,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="47" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B62" s="47" t="s">
         <v>8</v>
@@ -6196,10 +6158,10 @@
         <v>101</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F62" s="47">
         <v>16</v>
@@ -6220,7 +6182,7 @@
         <v>272257.92198581697</v>
       </c>
       <c r="L62" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M62" s="51">
         <v>4064</v>
@@ -6259,7 +6221,7 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="47" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B63" s="47" t="s">
         <v>8</v>
@@ -6268,10 +6230,10 @@
         <v>101</v>
       </c>
       <c r="D63" s="47" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F63" s="47">
         <v>17</v>
@@ -6292,7 +6254,7 @@
         <v>280425.65964539151</v>
       </c>
       <c r="L63" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M63" s="51">
         <v>4064</v>
@@ -6331,7 +6293,7 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" s="47" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B64" s="47" t="s">
         <v>8</v>
@@ -6340,10 +6302,10 @@
         <v>101</v>
       </c>
       <c r="D64" s="47" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F64" s="47">
         <v>18</v>
@@ -6364,7 +6326,7 @@
         <v>288838.42943475326</v>
       </c>
       <c r="L64" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M64" s="51">
         <v>4064</v>
@@ -6403,7 +6365,7 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65" s="47" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B65" s="47" t="s">
         <v>8</v>
@@ -6412,10 +6374,10 @@
         <v>101</v>
       </c>
       <c r="D65" s="47" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E65" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F65" s="47">
         <v>19</v>
@@ -6436,7 +6398,7 @@
         <v>297503.58231779584</v>
       </c>
       <c r="L65" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M65" s="51">
         <v>4064</v>
@@ -6475,7 +6437,7 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" s="47" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B66" s="47" t="s">
         <v>8</v>
@@ -6484,10 +6446,10 @@
         <v>101</v>
       </c>
       <c r="D66" s="47" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F66" s="47">
         <v>20</v>
@@ -6508,7 +6470,7 @@
         <v>306428.6897873297</v>
       </c>
       <c r="L66" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M66" s="51">
         <v>4064</v>
@@ -6547,70 +6509,70 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V67" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W67" s="31"/>
       <c r="Z67" s="4"/>
@@ -6619,7 +6581,7 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>8</v>
@@ -6628,10 +6590,10 @@
         <v>201</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F68" s="6">
         <v>1</v>
@@ -6691,7 +6653,7 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
@@ -6700,10 +6662,10 @@
         <v>201</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F69" s="6">
         <v>2</v>
@@ -6763,7 +6725,7 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
@@ -6772,10 +6734,10 @@
         <v>201</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F70" s="6">
         <v>3</v>
@@ -6835,7 +6797,7 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
@@ -6844,10 +6806,10 @@
         <v>201</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F71" s="6">
         <v>4</v>
@@ -6907,7 +6869,7 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>8</v>
@@ -6916,10 +6878,10 @@
         <v>201</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F72" s="6">
         <v>5</v>
@@ -6979,70 +6941,70 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V73" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W73" s="31"/>
       <c r="Z73" s="4"/>
@@ -7051,19 +7013,19 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F74" s="6">
         <v>1</v>
@@ -7123,19 +7085,19 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F75" s="6">
         <v>2</v>
@@ -7195,19 +7157,19 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F76" s="6">
         <v>3</v>
@@ -7267,19 +7229,19 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F77" s="6">
         <v>4</v>
@@ -7339,19 +7301,19 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6">
         <v>5</v>
@@ -7411,19 +7373,19 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F79" s="6">
         <v>6</v>
@@ -7483,19 +7445,19 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F80" s="6">
         <v>7</v>
@@ -7555,19 +7517,19 @@
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F81" s="6">
         <v>8</v>
@@ -7627,19 +7589,19 @@
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F82" s="6">
         <v>9</v>
@@ -7699,19 +7661,19 @@
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F83" s="6">
         <v>10</v>
@@ -7771,19 +7733,19 @@
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F84" s="6">
         <v>11</v>
@@ -7843,19 +7805,19 @@
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F85" s="6">
         <v>12</v>
@@ -7915,19 +7877,19 @@
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F86" s="6">
         <v>13</v>
@@ -7987,19 +7949,19 @@
     </row>
     <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F87" s="6">
         <v>14</v>
@@ -8059,70 +8021,70 @@
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V88" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W88" s="31"/>
       <c r="Z88" s="4"/>
@@ -8131,19 +8093,19 @@
     </row>
     <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F89" s="6">
         <v>1</v>
@@ -8203,19 +8165,19 @@
     </row>
     <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F90" s="6">
         <v>2</v>
@@ -8275,19 +8237,19 @@
     </row>
     <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F91" s="6">
         <v>3</v>
@@ -8347,19 +8309,19 @@
     </row>
     <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F92" s="6">
         <v>4</v>
@@ -8419,19 +8381,19 @@
     </row>
     <row r="93" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F93" s="6">
         <v>5</v>
@@ -8491,19 +8453,19 @@
     </row>
     <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F94" s="6">
         <v>6</v>
@@ -8563,19 +8525,19 @@
     </row>
     <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F95" s="6">
         <v>7</v>
@@ -8635,19 +8597,19 @@
     </row>
     <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F96" s="6">
         <v>8</v>
@@ -8707,19 +8669,19 @@
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F97" s="6">
         <v>9</v>
@@ -8779,19 +8741,19 @@
     </row>
     <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F98" s="6">
         <v>10</v>
@@ -8851,19 +8813,19 @@
     </row>
     <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F99" s="6">
         <v>11</v>
@@ -8923,70 +8885,70 @@
     </row>
     <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V100" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W100" s="31"/>
       <c r="Z100" s="4"/>
@@ -8995,7 +8957,7 @@
     </row>
     <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
@@ -9004,10 +8966,10 @@
         <v>1</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F101" s="6">
         <v>1</v>
@@ -9028,7 +8990,7 @@
         <v>190000.08</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M101" s="8">
         <v>4000</v>
@@ -9067,7 +9029,7 @@
     </row>
     <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
@@ -9076,10 +9038,10 @@
         <v>1</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F102" s="6">
         <v>2</v>
@@ -9100,7 +9062,7 @@
         <v>190000.08</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M102" s="8">
         <v>4000</v>
@@ -9139,7 +9101,7 @@
     </row>
     <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
@@ -9148,10 +9110,10 @@
         <v>1</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F103" s="6">
         <v>3</v>
@@ -9172,7 +9134,7 @@
         <v>190000.08</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M103" s="8">
         <v>4000</v>
@@ -9211,7 +9173,7 @@
     </row>
     <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
@@ -9220,10 +9182,10 @@
         <v>1</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F104" s="6">
         <v>4</v>
@@ -9244,7 +9206,7 @@
         <v>190000.08</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M104" s="8">
         <v>4000</v>
@@ -9283,7 +9245,7 @@
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -9292,10 +9254,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F105" s="6">
         <v>5</v>
@@ -9316,7 +9278,7 @@
         <v>190000.08</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M105" s="8">
         <v>4000</v>
@@ -9355,7 +9317,7 @@
     </row>
     <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>7</v>
@@ -9364,10 +9326,10 @@
         <v>1</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F106" s="6">
         <v>6</v>
@@ -9388,7 +9350,7 @@
         <v>209000.03999999998</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M106" s="8">
         <v>4000</v>
@@ -9427,7 +9389,7 @@
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>7</v>
@@ -9436,10 +9398,10 @@
         <v>1</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F107" s="6">
         <v>7</v>
@@ -9460,7 +9422,7 @@
         <v>209000.03999999998</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M107" s="8">
         <v>4000</v>
@@ -9499,7 +9461,7 @@
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>7</v>
@@ -9508,10 +9470,10 @@
         <v>1</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F108" s="6">
         <v>8</v>
@@ -9532,7 +9494,7 @@
         <v>209000.03999999998</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M108" s="8">
         <v>4000</v>
@@ -9571,7 +9533,7 @@
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
@@ -9580,10 +9542,10 @@
         <v>1</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F109" s="6">
         <v>9</v>
@@ -9604,7 +9566,7 @@
         <v>209000.03999999998</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M109" s="8">
         <v>4000</v>
@@ -9643,7 +9605,7 @@
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>7</v>
@@ -9652,10 +9614,10 @@
         <v>1</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F110" s="6">
         <v>10</v>
@@ -9676,7 +9638,7 @@
         <v>209000.03999999998</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M110" s="8">
         <v>4000</v>
@@ -9715,7 +9677,7 @@
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111" s="42" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B111" s="42" t="s">
         <v>7</v>
@@ -9724,10 +9686,10 @@
         <v>1</v>
       </c>
       <c r="D111" s="42" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E111" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F111" s="42">
         <v>11</v>
@@ -9748,7 +9710,7 @@
         <v>229900.04399999999</v>
       </c>
       <c r="L111" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M111" s="46">
         <v>4000</v>
@@ -9787,7 +9749,7 @@
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112" s="42" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B112" s="42" t="s">
         <v>7</v>
@@ -9796,10 +9758,10 @@
         <v>1</v>
       </c>
       <c r="D112" s="42" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E112" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F112" s="42">
         <v>12</v>
@@ -9820,7 +9782,7 @@
         <v>229900.04399999999</v>
       </c>
       <c r="L112" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M112" s="46">
         <v>4000</v>
@@ -9859,7 +9821,7 @@
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113" s="42" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B113" s="42" t="s">
         <v>7</v>
@@ -9868,10 +9830,10 @@
         <v>1</v>
       </c>
       <c r="D113" s="42" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E113" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F113" s="42">
         <v>13</v>
@@ -9892,7 +9854,7 @@
         <v>229900.04399999999</v>
       </c>
       <c r="L113" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M113" s="46">
         <v>4000</v>
@@ -9931,7 +9893,7 @@
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114" s="42" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B114" s="42" t="s">
         <v>7</v>
@@ -9940,10 +9902,10 @@
         <v>1</v>
       </c>
       <c r="D114" s="42" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E114" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F114" s="42">
         <v>14</v>
@@ -9964,7 +9926,7 @@
         <v>229900.04399999999</v>
       </c>
       <c r="L114" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M114" s="46">
         <v>4000</v>
@@ -10003,7 +9965,7 @@
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115" s="42" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B115" s="42" t="s">
         <v>7</v>
@@ -10012,10 +9974,10 @@
         <v>1</v>
       </c>
       <c r="D115" s="42" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E115" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F115" s="42">
         <v>15</v>
@@ -10036,7 +9998,7 @@
         <v>229900.04399999999</v>
       </c>
       <c r="L115" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M115" s="46">
         <v>4000</v>
@@ -10075,70 +10037,70 @@
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V116" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W116" s="31"/>
       <c r="Z116" s="4"/>
@@ -10147,19 +10109,19 @@
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F117" s="6">
         <v>1</v>
@@ -10219,19 +10181,19 @@
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F118" s="6">
         <v>2</v>
@@ -10291,19 +10253,19 @@
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F119" s="6">
         <v>3</v>
@@ -10363,19 +10325,19 @@
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F120" s="6">
         <v>4</v>
@@ -10435,19 +10397,19 @@
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F121" s="6">
         <v>5</v>
@@ -10507,19 +10469,19 @@
     </row>
     <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122" s="42" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B122" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="42" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E122" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F122" s="42">
         <v>6</v>
@@ -10579,19 +10541,19 @@
     </row>
     <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123" s="42" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B123" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C123" s="42" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D123" s="42" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E123" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F123" s="42">
         <v>7</v>
@@ -10651,19 +10613,19 @@
     </row>
     <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124" s="42" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B124" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="42" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D124" s="42" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E124" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F124" s="42">
         <v>8</v>
@@ -10723,19 +10685,19 @@
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125" s="42" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B125" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C125" s="42" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E125" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F125" s="42">
         <v>9</v>
@@ -10795,19 +10757,19 @@
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126" s="42" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B126" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C126" s="42" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D126" s="42" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E126" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F126" s="42">
         <v>10</v>
@@ -10867,70 +10829,70 @@
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V127" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W127" s="31"/>
       <c r="Z127" s="4"/>
@@ -10939,19 +10901,19 @@
     </row>
     <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F128" s="6">
         <v>1</v>
@@ -11011,19 +10973,19 @@
     </row>
     <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F129" s="6">
         <v>2</v>
@@ -11083,19 +11045,19 @@
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F130" s="6">
         <v>3</v>
@@ -11155,19 +11117,19 @@
     </row>
     <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F131" s="6">
         <v>4</v>
@@ -11227,19 +11189,19 @@
     </row>
     <row r="132" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F132" s="6">
         <v>5</v>
@@ -11299,19 +11261,19 @@
     </row>
     <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F133" s="6">
         <v>6</v>
@@ -11371,19 +11333,19 @@
     </row>
     <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F134" s="6">
         <v>7</v>
@@ -11443,19 +11405,19 @@
     </row>
     <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F135" s="6">
         <v>8</v>
@@ -11515,19 +11477,19 @@
     </row>
     <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F136" s="6">
         <v>9</v>
@@ -11587,19 +11549,19 @@
     </row>
     <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F137" s="6">
         <v>10</v>
@@ -11659,19 +11621,19 @@
     </row>
     <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F138" s="6">
         <v>11</v>
@@ -11731,70 +11693,70 @@
     </row>
     <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V139" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W139" s="31"/>
       <c r="Z139" s="4"/>
@@ -11803,7 +11765,7 @@
     </row>
     <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>9</v>
@@ -11812,10 +11774,10 @@
         <v>101</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F140" s="6">
         <v>1</v>
@@ -11836,7 +11798,7 @@
         <v>29822.28</v>
       </c>
       <c r="L140" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M140" s="8">
         <v>721</v>
@@ -11875,7 +11837,7 @@
     </row>
     <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>9</v>
@@ -11884,10 +11846,10 @@
         <v>101</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F141" s="6">
         <v>2</v>
@@ -11908,7 +11870,7 @@
         <v>30717</v>
       </c>
       <c r="L141" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M141" s="8">
         <v>721</v>
@@ -11947,7 +11909,7 @@
     </row>
     <row r="142" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>9</v>
@@ -11956,10 +11918,10 @@
         <v>101</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F142" s="6">
         <v>3</v>
@@ -11980,7 +11942,7 @@
         <v>31638.48</v>
       </c>
       <c r="L142" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M142" s="8">
         <v>721</v>
@@ -12019,7 +11981,7 @@
     </row>
     <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>9</v>
@@ -12028,10 +11990,10 @@
         <v>101</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F143" s="6">
         <v>4</v>
@@ -12052,7 +12014,7 @@
         <v>32587.68</v>
       </c>
       <c r="L143" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M143" s="8">
         <v>721</v>
@@ -12091,7 +12053,7 @@
     </row>
     <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>9</v>
@@ -12100,10 +12062,10 @@
         <v>101</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F144" s="6">
         <v>5</v>
@@ -12124,7 +12086,7 @@
         <v>33565.32</v>
       </c>
       <c r="L144" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M144" s="8">
         <v>721</v>
@@ -12164,70 +12126,70 @@
     </row>
     <row r="145" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V145" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W145" s="31"/>
       <c r="Z145" s="4"/>
@@ -12236,7 +12198,7 @@
     </row>
     <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>9</v>
@@ -12245,10 +12207,10 @@
         <v>102</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F146" s="6">
         <v>1</v>
@@ -12269,7 +12231,7 @@
         <v>45749.64</v>
       </c>
       <c r="L146" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M146" s="8">
         <v>996</v>
@@ -12308,7 +12270,7 @@
     </row>
     <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>9</v>
@@ -12317,10 +12279,10 @@
         <v>102</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F147" s="6">
         <v>2</v>
@@ -12341,7 +12303,7 @@
         <v>47350.92</v>
       </c>
       <c r="L147" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M147" s="8">
         <v>996</v>
@@ -12380,7 +12342,7 @@
     </row>
     <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>9</v>
@@ -12389,10 +12351,10 @@
         <v>102</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F148" s="6">
         <v>3</v>
@@ -12413,7 +12375,7 @@
         <v>49008.24</v>
       </c>
       <c r="L148" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M148" s="8">
         <v>996</v>
@@ -12452,7 +12414,7 @@
     </row>
     <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>9</v>
@@ -12461,10 +12423,10 @@
         <v>102</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F149" s="6">
         <v>4</v>
@@ -12485,7 +12447,7 @@
         <v>50723.519999999997</v>
       </c>
       <c r="L149" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M149" s="8">
         <v>996</v>
@@ -12524,7 +12486,7 @@
     </row>
     <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>9</v>
@@ -12533,10 +12495,10 @@
         <v>102</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F150" s="6">
         <v>5</v>
@@ -12555,7 +12517,7 @@
       </c>
       <c r="K150" s="52"/>
       <c r="L150" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M150" s="8">
         <v>996</v>
@@ -12594,70 +12556,70 @@
     </row>
     <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V151" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W151" s="31"/>
       <c r="Z151" s="4"/>
@@ -12666,7 +12628,7 @@
     </row>
     <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>9</v>
@@ -12675,10 +12637,10 @@
         <v>103</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F152" s="6">
         <v>1</v>
@@ -12699,7 +12661,7 @@
         <v>48000</v>
       </c>
       <c r="L152" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M152" s="8">
         <v>1533</v>
@@ -12738,7 +12700,7 @@
     </row>
     <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>9</v>
@@ -12747,10 +12709,10 @@
         <v>103</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F153" s="6">
         <v>2</v>
@@ -12771,7 +12733,7 @@
         <v>49440</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M153" s="8">
         <v>1533</v>
@@ -12810,7 +12772,7 @@
     </row>
     <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>9</v>
@@ -12819,10 +12781,10 @@
         <v>103</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F154" s="6">
         <v>3</v>
@@ -12843,7 +12805,7 @@
         <v>50923.199999999997</v>
       </c>
       <c r="L154" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M154" s="8">
         <v>1533</v>
@@ -12882,7 +12844,7 @@
     </row>
     <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>9</v>
@@ -12891,10 +12853,10 @@
         <v>103</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F155" s="6">
         <v>4</v>
@@ -12915,7 +12877,7 @@
         <v>52450.9</v>
       </c>
       <c r="L155" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M155" s="8">
         <v>1533</v>
@@ -12954,7 +12916,7 @@
     </row>
     <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>9</v>
@@ -12963,10 +12925,10 @@
         <v>103</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F156" s="6">
         <v>5</v>
@@ -12987,7 +12949,7 @@
         <v>54024.42</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M156" s="8">
         <v>1533</v>
@@ -13026,70 +12988,70 @@
     </row>
     <row r="157" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V157" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W157" s="31"/>
       <c r="Z157" s="4"/>
@@ -13098,7 +13060,7 @@
     </row>
     <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>9</v>
@@ -13107,10 +13069,10 @@
         <v>104</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F158" s="6">
         <v>1</v>
@@ -13131,7 +13093,7 @@
         <v>95304</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M158" s="8">
         <v>2508</v>
@@ -13170,7 +13132,7 @@
     </row>
     <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>9</v>
@@ -13179,10 +13141,10 @@
         <v>104</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F159" s="6">
         <v>2</v>
@@ -13203,7 +13165,7 @@
         <v>97210.08</v>
       </c>
       <c r="L159" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M159" s="8">
         <v>2508</v>
@@ -13242,7 +13204,7 @@
     </row>
     <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>9</v>
@@ -13251,10 +13213,10 @@
         <v>104</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F160" s="6">
         <v>3</v>
@@ -13275,7 +13237,7 @@
         <v>99154.28</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M160" s="8">
         <v>2508</v>
@@ -13314,7 +13276,7 @@
     </row>
     <row r="161" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>9</v>
@@ -13323,10 +13285,10 @@
         <v>104</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F161" s="6">
         <v>4</v>
@@ -13347,7 +13309,7 @@
         <v>101137.37</v>
       </c>
       <c r="L161" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M161" s="8">
         <v>2508</v>
@@ -13386,7 +13348,7 @@
     </row>
     <row r="162" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>9</v>
@@ -13395,10 +13357,10 @@
         <v>104</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F162" s="6">
         <v>5</v>
@@ -13419,7 +13381,7 @@
         <v>103160.12</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M162" s="8">
         <v>2508</v>
@@ -13458,7 +13420,7 @@
     </row>
     <row r="163" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>9</v>
@@ -13467,10 +13429,10 @@
         <v>104</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F163" s="6">
         <v>6</v>
@@ -13491,7 +13453,7 @@
         <v>105223.32</v>
       </c>
       <c r="L163" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M163" s="8">
         <v>2508</v>
@@ -13530,7 +13492,7 @@
     </row>
     <row r="164" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>9</v>
@@ -13539,10 +13501,10 @@
         <v>104</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F164" s="6">
         <v>7</v>
@@ -13563,7 +13525,7 @@
         <v>107327.79</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M164" s="8">
         <v>2508</v>
@@ -13602,7 +13564,7 @@
     </row>
     <row r="165" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>9</v>
@@ -13611,10 +13573,10 @@
         <v>104</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F165" s="6">
         <v>8</v>
@@ -13635,7 +13597,7 @@
         <v>109474.35</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M165" s="8">
         <v>2508</v>
@@ -13674,7 +13636,7 @@
     </row>
     <row r="166" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>9</v>
@@ -13683,10 +13645,10 @@
         <v>104</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F166" s="6">
         <v>9</v>
@@ -13707,7 +13669,7 @@
         <v>111663.83</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M166" s="8">
         <v>2508</v>
@@ -13746,7 +13708,7 @@
     </row>
     <row r="167" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>9</v>
@@ -13755,10 +13717,10 @@
         <v>104</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F167" s="6">
         <v>10</v>
@@ -13779,7 +13741,7 @@
         <v>113897.11</v>
       </c>
       <c r="L167" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M167" s="8">
         <v>2508</v>
@@ -13818,7 +13780,7 @@
     </row>
     <row r="168" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A168" s="42" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B168" s="42" t="s">
         <v>9</v>
@@ -13827,10 +13789,10 @@
         <v>104</v>
       </c>
       <c r="D168" s="42" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E168" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F168" s="42">
         <v>11</v>
@@ -13851,7 +13813,7 @@
         <v>116175</v>
       </c>
       <c r="L168" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M168" s="46">
         <v>2508</v>
@@ -13890,7 +13852,7 @@
     </row>
     <row r="169" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A169" s="42" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B169" s="42" t="s">
         <v>9</v>
@@ -13899,10 +13861,10 @@
         <v>104</v>
       </c>
       <c r="D169" s="42" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E169" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F169" s="42">
         <v>12</v>
@@ -13923,7 +13885,7 @@
         <v>118498.44</v>
       </c>
       <c r="L169" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M169" s="46">
         <v>2508</v>
@@ -13962,7 +13924,7 @@
     </row>
     <row r="170" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A170" s="42" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B170" s="42" t="s">
         <v>9</v>
@@ -13971,10 +13933,10 @@
         <v>104</v>
       </c>
       <c r="D170" s="42" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E170" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F170" s="42">
         <v>13</v>
@@ -13995,7 +13957,7 @@
         <v>120868.44</v>
       </c>
       <c r="L170" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M170" s="46">
         <v>2508</v>
@@ -14034,7 +13996,7 @@
     </row>
     <row r="171" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A171" s="42" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B171" s="42" t="s">
         <v>9</v>
@@ -14043,10 +14005,10 @@
         <v>104</v>
       </c>
       <c r="D171" s="42" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E171" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F171" s="42">
         <v>14</v>
@@ -14067,7 +14029,7 @@
         <v>123285.84</v>
       </c>
       <c r="L171" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M171" s="46">
         <v>2508</v>
@@ -14106,7 +14068,7 @@
     </row>
     <row r="172" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A172" s="42" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B172" s="42" t="s">
         <v>9</v>
@@ -14115,10 +14077,10 @@
         <v>104</v>
       </c>
       <c r="D172" s="42" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E172" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F172" s="42">
         <v>15</v>
@@ -14139,7 +14101,7 @@
         <v>125751.48</v>
       </c>
       <c r="L172" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M172" s="46">
         <v>2508</v>
@@ -14178,7 +14140,7 @@
     </row>
     <row r="173" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A173" s="47" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B173" s="47" t="s">
         <v>9</v>
@@ -14187,10 +14149,10 @@
         <v>104</v>
       </c>
       <c r="D173" s="47" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E173" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F173" s="47">
         <v>16</v>
@@ -14211,7 +14173,7 @@
         <v>128266.56</v>
       </c>
       <c r="L173" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M173" s="51">
         <v>2508</v>
@@ -14250,7 +14212,7 @@
     </row>
     <row r="174" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A174" s="47" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B174" s="47" t="s">
         <v>9</v>
@@ -14259,10 +14221,10 @@
         <v>104</v>
       </c>
       <c r="D174" s="47" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E174" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F174" s="47">
         <v>17</v>
@@ -14283,7 +14245,7 @@
         <v>130831.92</v>
       </c>
       <c r="L174" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M174" s="51">
         <v>2508</v>
@@ -14322,7 +14284,7 @@
     </row>
     <row r="175" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A175" s="47" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B175" s="47" t="s">
         <v>9</v>
@@ -14331,10 +14293,10 @@
         <v>104</v>
       </c>
       <c r="D175" s="47" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E175" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F175" s="47">
         <v>18</v>
@@ -14355,7 +14317,7 @@
         <v>133448.51999999999</v>
       </c>
       <c r="L175" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M175" s="51">
         <v>2508</v>
@@ -14394,7 +14356,7 @@
     </row>
     <row r="176" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A176" s="47" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B176" s="47" t="s">
         <v>9</v>
@@ -14403,10 +14365,10 @@
         <v>104</v>
       </c>
       <c r="D176" s="47" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E176" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F176" s="47">
         <v>19</v>
@@ -14427,7 +14389,7 @@
         <v>136117.56</v>
       </c>
       <c r="L176" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M176" s="51">
         <v>2508</v>
@@ -14466,7 +14428,7 @@
     </row>
     <row r="177" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A177" s="47" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B177" s="47" t="s">
         <v>9</v>
@@ -14475,10 +14437,10 @@
         <v>104</v>
       </c>
       <c r="D177" s="47" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E177" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F177" s="47">
         <v>20</v>
@@ -14499,7 +14461,7 @@
         <v>138839.88</v>
       </c>
       <c r="L177" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M177" s="51">
         <v>2508</v>
@@ -14538,7 +14500,7 @@
     </row>
     <row r="178" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A178" s="56" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B178" s="56" t="s">
         <v>9</v>
@@ -14547,10 +14509,10 @@
         <v>104</v>
       </c>
       <c r="D178" s="56" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E178" s="56" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F178" s="56">
         <v>21</v>
@@ -14571,7 +14533,7 @@
         <v>141616.68</v>
       </c>
       <c r="L178" s="56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M178" s="61">
         <v>2508</v>
@@ -14610,7 +14572,7 @@
     </row>
     <row r="179" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A179" s="56" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B179" s="56" t="s">
         <v>9</v>
@@ -14619,10 +14581,10 @@
         <v>104</v>
       </c>
       <c r="D179" s="56" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E179" s="56" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F179" s="56">
         <v>22</v>
@@ -14643,7 +14605,7 @@
         <v>144449.04</v>
       </c>
       <c r="L179" s="56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M179" s="61">
         <v>2508</v>
@@ -14682,7 +14644,7 @@
     </row>
     <row r="180" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A180" s="56" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B180" s="56" t="s">
         <v>9</v>
@@ -14691,10 +14653,10 @@
         <v>104</v>
       </c>
       <c r="D180" s="56" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E180" s="56" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F180" s="56">
         <v>23</v>
@@ -14715,7 +14677,7 @@
         <v>147337.92000000001</v>
       </c>
       <c r="L180" s="56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M180" s="61">
         <v>2508</v>
@@ -14754,7 +14716,7 @@
     </row>
     <row r="181" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A181" s="56" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B181" s="56" t="s">
         <v>9</v>
@@ -14763,10 +14725,10 @@
         <v>104</v>
       </c>
       <c r="D181" s="56" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E181" s="56" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F181" s="56">
         <v>24</v>
@@ -14787,7 +14749,7 @@
         <v>150284.64000000001</v>
       </c>
       <c r="L181" s="56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M181" s="61">
         <v>2508</v>
@@ -14826,7 +14788,7 @@
     </row>
     <row r="182" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A182" s="56" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B182" s="56" t="s">
         <v>9</v>
@@ -14835,10 +14797,10 @@
         <v>104</v>
       </c>
       <c r="D182" s="56" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E182" s="56" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F182" s="56">
         <v>25</v>
@@ -14859,7 +14821,7 @@
         <v>153290.4</v>
       </c>
       <c r="L182" s="56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M182" s="61">
         <v>2508</v>
@@ -14898,70 +14860,70 @@
     </row>
     <row r="183" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V183" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W183" s="31"/>
       <c r="Z183" s="4"/>
@@ -14970,7 +14932,7 @@
     </row>
     <row r="184" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>9</v>
@@ -14979,10 +14941,10 @@
         <v>201</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F184" s="6">
         <v>1</v>
@@ -15042,7 +15004,7 @@
     </row>
     <row r="185" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>9</v>
@@ -15051,10 +15013,10 @@
         <v>201</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F185" s="6">
         <v>2</v>
@@ -15114,7 +15076,7 @@
     </row>
     <row r="186" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>9</v>
@@ -15123,10 +15085,10 @@
         <v>201</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F186" s="6">
         <v>3</v>
@@ -15186,7 +15148,7 @@
     </row>
     <row r="187" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>9</v>
@@ -15195,10 +15157,10 @@
         <v>201</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F187" s="6">
         <v>4</v>
@@ -15258,7 +15220,7 @@
     </row>
     <row r="188" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>9</v>
@@ -15267,10 +15229,10 @@
         <v>201</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F188" s="6">
         <v>5</v>
@@ -15330,7 +15292,7 @@
     </row>
     <row r="189" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>9</v>
@@ -15339,10 +15301,10 @@
         <v>201</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F189" s="6">
         <v>6</v>
@@ -15402,7 +15364,7 @@
     </row>
     <row r="190" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A190" s="47" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B190" s="47" t="s">
         <v>9</v>
@@ -15411,10 +15373,10 @@
         <v>201</v>
       </c>
       <c r="D190" s="47" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E190" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F190" s="47">
         <v>7</v>
@@ -15474,7 +15436,7 @@
     </row>
     <row r="191" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A191" s="47" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B191" s="47" t="s">
         <v>9</v>
@@ -15483,10 +15445,10 @@
         <v>201</v>
       </c>
       <c r="D191" s="47" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E191" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F191" s="47">
         <v>8</v>
@@ -15546,70 +15508,70 @@
     </row>
     <row r="192" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V192" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W192" s="31"/>
       <c r="Z192" s="4"/>
@@ -15627,10 +15589,10 @@
         <v>#N/A</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F193" s="6">
         <v>1</v>
@@ -15690,70 +15652,70 @@
     </row>
     <row r="194" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V194" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W194" s="31"/>
       <c r="Z194" s="4"/>
@@ -15762,19 +15724,19 @@
     </row>
     <row r="195" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F195" s="6">
         <v>1</v>
@@ -15834,70 +15796,70 @@
     </row>
     <row r="196" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V196" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W196" s="31"/>
       <c r="Z196" s="4"/>
@@ -15906,7 +15868,7 @@
     </row>
     <row r="197" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>6</v>
@@ -15915,10 +15877,10 @@
         <v>102</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F197" s="6">
         <v>1</v>
@@ -15939,7 +15901,7 @@
         <v>38400</v>
       </c>
       <c r="L197" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M197" s="8">
         <v>1063</v>
@@ -15978,70 +15940,70 @@
     </row>
     <row r="198" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V198" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W198" s="31"/>
       <c r="Z198" s="4"/>
@@ -16050,7 +16012,7 @@
     </row>
     <row r="199" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>6</v>
@@ -16059,10 +16021,10 @@
         <v>104</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F199" s="6">
         <v>1</v>
@@ -16083,7 +16045,7 @@
         <v>43300.2</v>
       </c>
       <c r="L199" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M199" s="8">
         <v>1360</v>
@@ -16122,7 +16084,7 @@
     </row>
     <row r="200" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>6</v>
@@ -16131,10 +16093,10 @@
         <v>104</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F200" s="6">
         <v>1</v>
@@ -16155,7 +16117,7 @@
         <v>43300.2</v>
       </c>
       <c r="L200" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M200" s="8">
         <v>1360</v>
@@ -16194,70 +16156,70 @@
     </row>
     <row r="201" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V201" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W201" s="31"/>
       <c r="Z201" s="4"/>
@@ -16266,7 +16228,7 @@
     </row>
     <row r="202" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>6</v>
@@ -16275,10 +16237,10 @@
         <v>106</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F202" s="6">
         <v>1</v>
@@ -16299,7 +16261,7 @@
         <v>46992</v>
       </c>
       <c r="L202" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M202" s="8">
         <v>1035</v>
@@ -16338,7 +16300,7 @@
     </row>
     <row r="203" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>6</v>
@@ -16347,10 +16309,10 @@
         <v>106</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F203" s="6">
         <v>2</v>
@@ -16371,7 +16333,7 @@
         <v>48401.760000000002</v>
       </c>
       <c r="L203" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M203" s="8">
         <v>1035</v>
@@ -16410,7 +16372,7 @@
     </row>
     <row r="204" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>6</v>
@@ -16419,10 +16381,10 @@
         <v>106</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F204" s="6">
         <v>3</v>
@@ -16443,7 +16405,7 @@
         <v>49850.68</v>
       </c>
       <c r="L204" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M204" s="8">
         <v>1035</v>
@@ -16482,7 +16444,7 @@
     </row>
     <row r="205" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>6</v>
@@ -16491,10 +16453,10 @@
         <v>106</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F205" s="6">
         <v>4</v>
@@ -16515,7 +16477,7 @@
         <v>51348.55</v>
       </c>
       <c r="L205" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M205" s="8">
         <v>1035</v>
@@ -16554,7 +16516,7 @@
     </row>
     <row r="206" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>6</v>
@@ -16563,10 +16525,10 @@
         <v>106</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F206" s="6">
         <v>5</v>
@@ -16587,7 +16549,7 @@
         <v>52885.56</v>
       </c>
       <c r="L206" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M206" s="8">
         <v>1035</v>
@@ -16626,7 +16588,7 @@
     </row>
     <row r="207" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>6</v>
@@ -16635,10 +16597,10 @@
         <v>106</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F207" s="6">
         <v>6</v>
@@ -16659,7 +16621,7 @@
         <v>52885.56</v>
       </c>
       <c r="L207" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M207" s="8">
         <v>1035</v>
@@ -16698,7 +16660,7 @@
     </row>
     <row r="208" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A208" s="42" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B208" s="42" t="s">
         <v>6</v>
@@ -16707,10 +16669,10 @@
         <v>106</v>
       </c>
       <c r="D208" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E208" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F208" s="42">
         <v>7</v>
@@ -16731,7 +16693,7 @@
         <v>54481.35</v>
       </c>
       <c r="L208" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M208" s="46">
         <v>1035</v>
@@ -16770,7 +16732,7 @@
     </row>
     <row r="209" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A209" s="42" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B209" s="42" t="s">
         <v>6</v>
@@ -16779,10 +16741,10 @@
         <v>106</v>
       </c>
       <c r="D209" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E209" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F209" s="42">
         <v>8</v>
@@ -16803,7 +16765,7 @@
         <v>56106.49</v>
       </c>
       <c r="L209" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M209" s="46">
         <v>1035</v>
@@ -16842,7 +16804,7 @@
     </row>
     <row r="210" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A210" s="42" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B210" s="42" t="s">
         <v>6</v>
@@ -16851,10 +16813,10 @@
         <v>106</v>
       </c>
       <c r="D210" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E210" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F210" s="42">
         <v>9</v>
@@ -16875,7 +16837,7 @@
         <v>57790.37</v>
       </c>
       <c r="L210" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M210" s="46">
         <v>1035</v>
@@ -16914,7 +16876,7 @@
     </row>
     <row r="211" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A211" s="42" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B211" s="42" t="s">
         <v>6</v>
@@ -16923,10 +16885,10 @@
         <v>106</v>
       </c>
       <c r="D211" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E211" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F211" s="42">
         <v>10</v>
@@ -16947,7 +16909,7 @@
         <v>59523.199999999997</v>
       </c>
       <c r="L211" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M211" s="46">
         <v>1035</v>
@@ -16986,7 +16948,7 @@
     </row>
     <row r="212" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A212" s="42" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B212" s="42" t="s">
         <v>6</v>
@@ -16995,10 +16957,10 @@
         <v>106</v>
       </c>
       <c r="D212" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E212" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F212" s="42">
         <v>11</v>
@@ -17019,7 +16981,7 @@
         <v>61314.77</v>
       </c>
       <c r="L212" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M212" s="46">
         <v>1035</v>
@@ -17058,7 +17020,7 @@
     </row>
     <row r="213" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A213" s="47" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B213" s="47" t="s">
         <v>6</v>
@@ -17067,10 +17029,10 @@
         <v>106</v>
       </c>
       <c r="D213" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E213" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F213" s="47">
         <v>12</v>
@@ -17091,7 +17053,7 @@
         <v>62541.065399999999</v>
       </c>
       <c r="L213" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M213" s="51">
         <v>1035</v>
@@ -17130,7 +17092,7 @@
     </row>
     <row r="214" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A214" s="47" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B214" s="47" t="s">
         <v>6</v>
@@ -17139,10 +17101,10 @@
         <v>106</v>
       </c>
       <c r="D214" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E214" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F214" s="47">
         <v>13</v>
@@ -17163,7 +17125,7 @@
         <v>63791.886707999998</v>
       </c>
       <c r="L214" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M214" s="51">
         <v>1035</v>
@@ -17202,7 +17164,7 @@
     </row>
     <row r="215" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A215" s="47" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B215" s="47" t="s">
         <v>6</v>
@@ -17211,10 +17173,10 @@
         <v>106</v>
       </c>
       <c r="D215" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E215" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F215" s="47">
         <v>14</v>
@@ -17235,7 +17197,7 @@
         <v>65067.724442159997</v>
       </c>
       <c r="L215" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M215" s="51">
         <v>1035</v>
@@ -17274,7 +17236,7 @@
     </row>
     <row r="216" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A216" s="47" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B216" s="47" t="s">
         <v>6</v>
@@ -17283,10 +17245,10 @@
         <v>106</v>
       </c>
       <c r="D216" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E216" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F216" s="47">
         <v>15</v>
@@ -17307,7 +17269,7 @@
         <v>66369.078931003198</v>
       </c>
       <c r="L216" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M216" s="51">
         <v>1035</v>
@@ -17346,7 +17308,7 @@
     </row>
     <row r="217" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A217" s="47" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B217" s="47" t="s">
         <v>6</v>
@@ -17355,10 +17317,10 @@
         <v>106</v>
       </c>
       <c r="D217" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E217" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F217" s="47">
         <v>16</v>
@@ -17379,7 +17341,7 @@
         <v>67696.46050962327</v>
       </c>
       <c r="L217" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M217" s="51">
         <v>1035</v>
@@ -17418,70 +17380,70 @@
     </row>
     <row r="218" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V218" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W218" s="31"/>
       <c r="Z218" s="4"/>
@@ -17490,7 +17452,7 @@
     </row>
     <row r="219" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>6</v>
@@ -17499,10 +17461,10 @@
         <v>108</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F219" s="6">
         <v>1</v>
@@ -17523,7 +17485,7 @@
         <v>52920</v>
       </c>
       <c r="L219" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M219" s="8">
         <v>1436</v>
@@ -17562,7 +17524,7 @@
     </row>
     <row r="220" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>6</v>
@@ -17571,10 +17533,10 @@
         <v>108</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F220" s="6">
         <v>2</v>
@@ -17595,7 +17557,7 @@
         <v>52920</v>
       </c>
       <c r="L220" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M220" s="8">
         <v>1436</v>
@@ -17634,7 +17596,7 @@
     </row>
     <row r="221" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>6</v>
@@ -17643,10 +17605,10 @@
         <v>108</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F221" s="6">
         <v>3</v>
@@ -17667,7 +17629,7 @@
         <v>52920</v>
       </c>
       <c r="L221" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M221" s="8">
         <v>1436</v>
@@ -17706,7 +17668,7 @@
     </row>
     <row r="222" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>6</v>
@@ -17715,10 +17677,10 @@
         <v>108</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F222" s="6">
         <v>4</v>
@@ -17739,7 +17701,7 @@
         <v>55566</v>
       </c>
       <c r="L222" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M222" s="8">
         <v>1436</v>
@@ -17778,7 +17740,7 @@
     </row>
     <row r="223" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>6</v>
@@ -17787,10 +17749,10 @@
         <v>108</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F223" s="6">
         <v>5</v>
@@ -17811,7 +17773,7 @@
         <v>55566</v>
       </c>
       <c r="L223" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M223" s="8">
         <v>1436</v>
@@ -17850,7 +17812,7 @@
     </row>
     <row r="224" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>6</v>
@@ -17859,10 +17821,10 @@
         <v>108</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F224" s="6">
         <v>6</v>
@@ -17883,7 +17845,7 @@
         <v>55566</v>
       </c>
       <c r="L224" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M224" s="8">
         <v>1436</v>
@@ -17922,70 +17884,70 @@
     </row>
     <row r="225" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V225" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W225" s="31"/>
       <c r="Z225" s="4"/>
@@ -17994,7 +17956,7 @@
     </row>
     <row r="226" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>6</v>
@@ -18003,10 +17965,10 @@
         <v>201</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F226" s="6">
         <v>1</v>
@@ -18066,70 +18028,70 @@
     </row>
     <row r="227" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V227" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W227" s="31"/>
       <c r="Z227" s="4"/>
@@ -18138,7 +18100,7 @@
     </row>
     <row r="228" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>6</v>
@@ -18147,10 +18109,10 @@
         <v>202</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F228" s="6">
         <v>1</v>
@@ -18210,7 +18172,7 @@
     </row>
     <row r="229" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>6</v>
@@ -18219,10 +18181,10 @@
         <v>202</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E229" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F229" s="6">
         <v>1</v>
@@ -18282,7 +18244,7 @@
     </row>
     <row r="230" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A230" s="42" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B230" s="42" t="s">
         <v>6</v>
@@ -18291,10 +18253,10 @@
         <v>202</v>
       </c>
       <c r="D230" s="42" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E230" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F230" s="42">
         <v>1</v>
@@ -18354,70 +18316,70 @@
     </row>
     <row r="231" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V231" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W231" s="31"/>
       <c r="Z231" s="4"/>
@@ -18426,7 +18388,7 @@
     </row>
     <row r="232" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>6</v>
@@ -18435,10 +18397,10 @@
         <v>203</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F232" s="6">
         <v>1</v>
@@ -18498,7 +18460,7 @@
     </row>
     <row r="233" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>6</v>
@@ -18507,10 +18469,10 @@
         <v>203</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F233" s="6">
         <v>2</v>
@@ -18570,7 +18532,7 @@
     </row>
     <row r="234" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A234" s="42" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B234" s="42" t="s">
         <v>6</v>
@@ -18579,10 +18541,10 @@
         <v>203</v>
       </c>
       <c r="D234" s="42" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E234" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F234" s="42">
         <v>3</v>
@@ -18642,7 +18604,7 @@
     </row>
     <row r="235" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A235" s="47" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B235" s="47" t="s">
         <v>6</v>
@@ -18651,10 +18613,10 @@
         <v>203</v>
       </c>
       <c r="D235" s="47" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E235" s="47" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F235" s="47">
         <v>4</v>
@@ -18714,70 +18676,70 @@
     </row>
     <row r="236" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V236" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W236" s="31"/>
       <c r="Z236" s="4"/>
@@ -18786,7 +18748,7 @@
     </row>
     <row r="237" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>6</v>
@@ -18795,10 +18757,10 @@
         <v>204</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F237" s="6">
         <v>1</v>
@@ -18858,70 +18820,70 @@
     </row>
     <row r="238" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V238" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W238" s="31"/>
       <c r="Z238" s="4"/>
@@ -18930,7 +18892,7 @@
     </row>
     <row r="239" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>6</v>
@@ -18939,10 +18901,10 @@
         <v>205</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F239" s="6">
         <v>1</v>
@@ -19002,7 +18964,7 @@
     </row>
     <row r="240" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>6</v>
@@ -19011,10 +18973,10 @@
         <v>205</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F240" s="6">
         <v>2</v>
@@ -19074,7 +19036,7 @@
     </row>
     <row r="241" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>6</v>
@@ -19083,10 +19045,10 @@
         <v>205</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F241" s="6">
         <v>3</v>
@@ -19146,70 +19108,70 @@
     </row>
     <row r="242" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V242" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W242" s="31"/>
       <c r="Z242" s="4"/>
@@ -19218,7 +19180,7 @@
     </row>
     <row r="243" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>6</v>
@@ -19227,10 +19189,10 @@
         <v>209</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F243" s="6">
         <v>1</v>
@@ -19290,7 +19252,7 @@
     </row>
     <row r="244" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>6</v>
@@ -19299,10 +19261,10 @@
         <v>209</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F244" s="6">
         <v>2</v>
@@ -19362,7 +19324,7 @@
     </row>
     <row r="245" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>6</v>
@@ -19371,10 +19333,10 @@
         <v>209</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F245" s="6">
         <v>3</v>
@@ -19434,70 +19396,70 @@
     </row>
     <row r="246" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V246" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W246" s="31"/>
       <c r="Z246" s="4"/>
@@ -19506,7 +19468,7 @@
     </row>
     <row r="247" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>6</v>
@@ -19515,10 +19477,10 @@
         <v>206</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F247" s="6">
         <v>1</v>
@@ -19578,7 +19540,7 @@
     </row>
     <row r="248" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>6</v>
@@ -19587,10 +19549,10 @@
         <v>206</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F248" s="6">
         <v>1</v>
@@ -19652,7 +19614,7 @@
     </row>
     <row r="249" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>6</v>
@@ -19661,10 +19623,10 @@
         <v>206</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F249" s="6">
         <v>1</v>
@@ -19726,7 +19688,7 @@
     </row>
     <row r="250" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>6</v>
@@ -19735,10 +19697,10 @@
         <v>206</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F250" s="6">
         <v>1</v>
@@ -19800,7 +19762,7 @@
     </row>
     <row r="251" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>6</v>
@@ -19809,10 +19771,10 @@
         <v>206</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F251" s="6">
         <v>1</v>
@@ -19874,7 +19836,7 @@
     </row>
     <row r="252" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>6</v>
@@ -19883,10 +19845,10 @@
         <v>206</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F252" s="6">
         <v>1</v>
@@ -19948,70 +19910,70 @@
     </row>
     <row r="253" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V253" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W253" s="31"/>
       <c r="Z253" s="4"/>
@@ -20020,7 +19982,7 @@
     </row>
     <row r="254" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>6</v>
@@ -20029,10 +19991,10 @@
         <v>207</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F254" s="6">
         <v>1</v>
@@ -20092,7 +20054,7 @@
     </row>
     <row r="255" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>6</v>
@@ -20101,10 +20063,10 @@
         <v>207</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F255" s="6">
         <v>2</v>
@@ -20164,7 +20126,7 @@
     </row>
     <row r="256" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>6</v>
@@ -20173,10 +20135,10 @@
         <v>207</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F256" s="6">
         <v>3</v>
@@ -20236,7 +20198,7 @@
     </row>
     <row r="257" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>6</v>
@@ -20245,10 +20207,10 @@
         <v>207</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F257" s="6">
         <v>4</v>
@@ -20308,7 +20270,7 @@
     </row>
     <row r="258" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A258" s="42" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B258" s="42" t="s">
         <v>6</v>
@@ -20317,10 +20279,10 @@
         <v>207</v>
       </c>
       <c r="D258" s="42" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E258" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F258" s="42">
         <v>5</v>
@@ -20380,7 +20342,7 @@
     </row>
     <row r="259" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A259" s="42" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B259" s="42" t="s">
         <v>6</v>
@@ -20389,10 +20351,10 @@
         <v>207</v>
       </c>
       <c r="D259" s="42" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E259" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F259" s="42">
         <v>6</v>
@@ -20452,70 +20414,70 @@
     </row>
     <row r="260" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="J260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="O260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="P260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="Q260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="T260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="U260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V260" s="31" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="W260" s="31"/>
       <c r="Z260" s="4"/>
@@ -20524,7 +20486,7 @@
     </row>
     <row r="261" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>6</v>
@@ -20533,10 +20495,10 @@
         <v>208</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E261" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F261" s="6">
         <v>1</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8745BF2F-DDBA-49AD-BFD6-931CA14D35B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57E11860-C566-4DF6-B426-9CF179C4981F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2505" windowWidth="102195" windowHeight="29895" xr2:uid="{91136297-5822-44C6-A3F2-6CC3985E9C67}"/>
+    <workbookView xWindow="0" yWindow="2505" windowWidth="102195" windowHeight="29895" xr2:uid="{22111DD6-099B-4E7E-9EFF-4B98D6E63F34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="227">
   <si>
     <t>Building</t>
   </si>
@@ -461,7 +461,7 @@
     <t>Four (4) x 5-year AUTO-RENEWALS (no notice needed)</t>
   </si>
   <si>
-    <t>Annual termination on any anniversary w/ 90 days</t>
+    <t>Ann Anniversary w/ 90 days</t>
   </si>
   <si>
     <t>Electric Meter</t>
@@ -1282,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C57F37A-D4FD-4926-86E8-D42A75076906}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FE9E19-F5EE-4DE3-BBD6-0D8558D90B59}">
   <dimension ref="A1:AT261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3887,9 +3887,7 @@
         <v>139</v>
       </c>
       <c r="AJ31" s="23"/>
-      <c r="AK31" s="20" t="s">
-        <v>140</v>
-      </c>
+      <c r="AK31" s="20"/>
       <c r="AL31" s="20" t="s">
         <v>140</v>
       </c>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57E11860-C566-4DF6-B426-9CF179C4981F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7921047B-9B90-4DB1-9D65-C4898713F0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2505" windowWidth="102195" windowHeight="29895" xr2:uid="{22111DD6-099B-4E7E-9EFF-4B98D6E63F34}"/>
+    <workbookView xWindow="1380" yWindow="1290" windowWidth="50955" windowHeight="29895" xr2:uid="{4C8F54F5-FFF3-4038-96C5-A3C180D4E153}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1282,7 +1282,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FE9E19-F5EE-4DE3-BBD6-0D8558D90B59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4E9431-E7F0-4412-A681-A0B0B0CD3550}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AT261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2478,13 +2479,13 @@
         <v>-10.571254319983737</v>
       </c>
       <c r="W18" s="16">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="X18" s="16">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="Y18" s="16">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="Z18" s="17"/>
       <c r="AA18" s="18"/>
@@ -18764,10 +18765,10 @@
         <v>1</v>
       </c>
       <c r="G237" s="40">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="H237" s="40">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="I237" s="10">
         <v>0</v>
@@ -18800,13 +18801,13 @@
         <v>0</v>
       </c>
       <c r="S237" s="40">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="T237" s="40">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="U237" s="40">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="V237" s="13">
         <v>0</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7921047B-9B90-4DB1-9D65-C4898713F0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13E2EB8D-AD26-4432-9A11-07F6835F740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1290" windowWidth="50955" windowHeight="29895" xr2:uid="{4C8F54F5-FFF3-4038-96C5-A3C180D4E153}"/>
+    <workbookView xWindow="2730" yWindow="1470" windowWidth="50955" windowHeight="29895" xr2:uid="{0E71905A-5A3E-47C2-A5C0-D077A0F4413D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1282,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4E9431-E7F0-4412-A681-A0B0B0CD3550}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1380F1F3-91D5-4501-B71E-49695EF212CD}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AT261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2479,13 +2479,13 @@
         <v>-10.571254319983737</v>
       </c>
       <c r="W18" s="16">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="X18" s="16">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="Y18" s="16">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="Z18" s="17"/>
       <c r="AA18" s="18"/>
@@ -18765,10 +18765,10 @@
         <v>1</v>
       </c>
       <c r="G237" s="40">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="H237" s="40">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="I237" s="10">
         <v>0</v>
@@ -18801,13 +18801,13 @@
         <v>0</v>
       </c>
       <c r="S237" s="40">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="T237" s="40">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="U237" s="40">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="V237" s="13">
         <v>0</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EA2EF8C-B10F-440D-B3B5-0FE2AB8AB47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1F7E56E-72B5-429C-A408-4449914A8988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="1170" windowWidth="52665" windowHeight="29925" xr2:uid="{92DBAD3C-EEC5-4140-B380-777927B5ED34}"/>
+    <workbookView xWindow="1770" yWindow="825" windowWidth="55830" windowHeight="31575" xr2:uid="{2343475C-3A1E-46A0-A498-F63CD467A17F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1361,7 +1361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637CCEBB-4FD6-486F-9E2D-6DA576487E5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B22CD9-737D-43B8-B147-104813946A5C}">
   <dimension ref="A1:AT299"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -22349,10 +22349,10 @@
         <v>0</v>
       </c>
       <c r="J274" s="13">
-        <v>875</v>
+        <v>1500</v>
       </c>
       <c r="K274" s="56">
-        <v>10500</v>
+        <v>18000</v>
       </c>
       <c r="L274" s="6" t="s">
         <v>27</v>
@@ -22370,7 +22370,7 @@
         <v>3.9845497052246395E-2</v>
       </c>
       <c r="Q274" s="13">
-        <v>21.428571428571427</v>
+        <v>36.734693877551024</v>
       </c>
       <c r="R274" s="45">
         <v>2800</v>
@@ -22421,13 +22421,13 @@
         <v>46203</v>
       </c>
       <c r="I275" s="10">
-        <v>2.857142857142847E-2</v>
+        <v>3.3333333333333437E-2</v>
       </c>
       <c r="J275" s="13">
-        <v>900</v>
+        <v>1550</v>
       </c>
       <c r="K275" s="56">
-        <v>10800</v>
+        <v>18600</v>
       </c>
       <c r="L275" s="6" t="s">
         <v>27</v>
@@ -22445,7 +22445,7 @@
         <v>3.9845497052246395E-2</v>
       </c>
       <c r="Q275" s="13">
-        <v>22.040816326530614</v>
+        <v>37.95918367346939</v>
       </c>
       <c r="R275" s="45">
         <v>2800</v>
@@ -22496,13 +22496,13 @@
         <v>46568</v>
       </c>
       <c r="I276" s="10">
-        <v>2.7777777777777679E-2</v>
+        <v>3.2258064516129004E-2</v>
       </c>
       <c r="J276" s="13">
-        <v>925</v>
+        <v>1600</v>
       </c>
       <c r="K276" s="56">
-        <v>11100</v>
+        <v>19200</v>
       </c>
       <c r="L276" s="6" t="s">
         <v>27</v>
@@ -22520,7 +22520,7 @@
         <v>3.9845497052246395E-2</v>
       </c>
       <c r="Q276" s="13">
-        <v>22.653061224489797</v>
+        <v>39.183673469387756</v>
       </c>
       <c r="R276" s="45">
         <v>2800</v>
@@ -22647,10 +22647,10 @@
         <v>0</v>
       </c>
       <c r="J278" s="13">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="K278" s="56">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="L278" s="6" t="s">
         <v>27</v>
@@ -22668,7 +22668,7 @@
         <v>2.2362268753811754E-2</v>
       </c>
       <c r="Q278" s="13">
-        <v>27.272727272727273</v>
+        <v>0</v>
       </c>
       <c r="R278" s="13">
         <v>0</v>
@@ -22718,14 +22718,14 @@
       <c r="H279" s="16">
         <v>46203</v>
       </c>
-      <c r="I279" s="10">
-        <v>4.0000000000000036E-2</v>
+      <c r="I279" s="10" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J279" s="13">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="K279" s="56">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="L279" s="6" t="s">
         <v>27</v>
@@ -22743,7 +22743,7 @@
         <v>2.2362268753811754E-2</v>
       </c>
       <c r="Q279" s="13">
-        <v>28.363636363636363</v>
+        <v>0</v>
       </c>
       <c r="R279" s="13">
         <v>0</v>
@@ -22793,14 +22793,14 @@
       <c r="H280" s="16">
         <v>46568</v>
       </c>
-      <c r="I280" s="10">
-        <v>3.8461538461538547E-2</v>
+      <c r="I280" s="10" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J280" s="13">
-        <v>675</v>
+        <v>0</v>
       </c>
       <c r="K280" s="56">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="L280" s="6" t="s">
         <v>27</v>
@@ -22818,7 +22818,7 @@
         <v>2.2362268753811754E-2</v>
       </c>
       <c r="Q280" s="13">
-        <v>29.454545454545453</v>
+        <v>0</v>
       </c>
       <c r="R280" s="13">
         <v>0</v>

--- a/data/MSP Tenancy.xlsx
+++ b/data/MSP Tenancy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\OpenClaw\Share Jason\General Procedures\msp-dashboard-src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1F7E56E-72B5-429C-A408-4449914A8988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A01070D5-8645-4D4B-B525-6E0C5E48D612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="825" windowWidth="55830" windowHeight="31575" xr2:uid="{2343475C-3A1E-46A0-A498-F63CD467A17F}"/>
+    <workbookView xWindow="1770" yWindow="825" windowWidth="55830" windowHeight="31575" xr2:uid="{ACF3E97C-5406-46E4-9E78-276C232D0021}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1361,7 +1361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B22CD9-737D-43B8-B147-104813946A5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50AC4753-2301-471E-B36E-F3CC99F16AFA}">
   <dimension ref="A1:AT299"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16325,10 +16325,10 @@
         <v>0</v>
       </c>
       <c r="J194" s="13">
-        <v>1</v>
+        <v>2600</v>
       </c>
       <c r="K194" s="56">
-        <v>12</v>
+        <v>31200</v>
       </c>
       <c r="L194" s="6" t="s">
         <v>36</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="Q194" s="13">
-        <v>9.3312597200622092E-3</v>
+        <v>24.261275272161743</v>
       </c>
       <c r="R194" s="13">
-        <v>1.5</v>
+        <v>3900</v>
       </c>
       <c r="S194" s="43">
         <v>46249</v>
@@ -20331,13 +20331,13 @@
         <v>46599</v>
       </c>
       <c r="I247" s="10">
-        <v>5.0000000000000044E-2</v>
+        <v>4.9886621315192725E-2</v>
       </c>
       <c r="J247" s="13">
-        <v>4630.5</v>
+        <v>4630</v>
       </c>
       <c r="K247" s="56">
-        <v>55566</v>
+        <v>55560</v>
       </c>
       <c r="L247" s="6" t="s">
         <v>56</v>
@@ -20355,7 +20355,7 @@
         <v>0.1741</v>
       </c>
       <c r="Q247" s="13">
-        <v>38.694986072423397</v>
+        <v>38.690807799442894</v>
       </c>
       <c r="R247" s="45">
         <v>3000</v>
@@ -20409,10 +20409,10 @@
         <v>0</v>
       </c>
       <c r="J248" s="13">
-        <v>4630.5</v>
+        <v>4630</v>
       </c>
       <c r="K248" s="56">
-        <v>55566</v>
+        <v>55560</v>
       </c>
       <c r="L248" s="6" t="s">
         <v>56</v>
@@ -20430,7 +20430,7 @@
         <v>0.1741</v>
       </c>
       <c r="Q248" s="13">
-        <v>38.694986072423397</v>
+        <v>38.690807799442894</v>
       </c>
       <c r="R248" s="45">
         <v>3000</v>
@@ -20484,10 +20484,10 @@
         <v>0</v>
       </c>
       <c r="J249" s="13">
-        <v>4630.5</v>
+        <v>4630</v>
       </c>
       <c r="K249" s="56">
-        <v>55566</v>
+        <v>55560</v>
       </c>
       <c r="L249" s="6" t="s">
         <v>56</v>
@@ -20505,7 +20505,7 @@
         <v>0.1741</v>
       </c>
       <c r="Q249" s="13">
-        <v>38.694986072423397</v>
+        <v>38.690807799442894</v>
       </c>
       <c r="R249" s="45">
         <v>3000</v>
@@ -21474,8 +21474,8 @@
       <c r="Q262" s="13">
         <v>0</v>
       </c>
-      <c r="R262" s="13">
-        <v>0</v>
+      <c r="R262" s="56">
+        <v>4800</v>
       </c>
       <c r="S262" s="43">
         <v>46235</v>
@@ -23501,8 +23501,8 @@
       <c r="Q289" s="13">
         <v>17.402269861286253</v>
       </c>
-      <c r="R289" s="13">
-        <v>0</v>
+      <c r="R289" s="56">
+        <v>1700</v>
       </c>
       <c r="S289" s="43">
         <v>39520</v>
